--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="319">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="339">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -986,6 +986,66 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1320-600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL S. BURBURAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FB-0878-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1354-796</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUCERO R. ALBARACIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/a N/A, Balintawak, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1307-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1352-743</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REMEGIO T. BURBURAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0884-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1364-213</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REMEGIO T. BURBURAN JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS-4878-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1362-288</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHARLO F  SALUMAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/a, Poblacion, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25-SROPIX-16154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1363-573</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -13360,57 +13420,262 @@
       </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B8" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="H8" s="16">
+        <x:v>46076.1792361111</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="n">
+        <x:v>1216147</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46090.2042708333</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="H9" s="16">
+        <x:v>46076.1139583333</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="n">
+        <x:v>1216146</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46090.1919444444</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>46077.2598726852</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="n">
+        <x:v>1216158</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46090.2758680556</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>46077.2024189815</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45948</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="n">
+        <x:v>1216154</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46090.2495949074</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>46077.2103587963</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="n">
+        <x:v>1216155</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46090.2536226852</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="20" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="22" t="s"/>
-      <x:c r="F10" s="22" t="s"/>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+      <x:c r="C15" s="21" t="s"/>
+      <x:c r="D15" s="21" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="22" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="23" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="s">
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="25" t="s">
         <x:v>43</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="26" t="s">
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B13" s="29" t="s">
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="26" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="26" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B20" s="29" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C13" s="30" t="s"/>
-      <x:c r="D13" s="30" t="s"/>
-      <x:c r="E13" s="30" t="s"/>
-      <x:c r="F13" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C20" s="30" t="s"/>
+      <x:c r="D20" s="30" t="s"/>
+      <x:c r="E20" s="30" t="s"/>
+      <x:c r="F20" s="31" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
@@ -14385,13 +14650,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
+  <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B10:F10"/>
-    <x:mergeCell ref="B11:E11"/>
-    <x:mergeCell ref="B12:E12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B15:F15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="339">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="343">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1046,6 +1046,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1363-573</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PONCIANO O. SINDAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, Samboang, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ponciano O. Sinday</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1365-581</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -13610,73 +13622,110 @@
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>46077.2683564815</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="n">
+        <x:v>1216159</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46090.2806018519</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="20" t="s">
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="20" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C15" s="21" t="s"/>
-      <x:c r="D15" s="21" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="22" t="s"/>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="23" t="s">
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="22" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="23" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="s">
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="s">
         <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
       <x:c r="B18" s="26" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C18" s="27" t="s"/>
       <x:c r="D18" s="27" t="s"/>
       <x:c r="E18" s="27" t="s"/>
       <x:c r="F18" s="28" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
       <x:c r="B19" s="26" t="s">
-        <x:v>100</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C19" s="27" t="s"/>
       <x:c r="D19" s="27" t="s"/>
       <x:c r="E19" s="27" t="s"/>
       <x:c r="F19" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B20" s="29" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B21" s="29" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C20" s="30" t="s"/>
-      <x:c r="D20" s="30" t="s"/>
-      <x:c r="E20" s="30" t="s"/>
-      <x:c r="F20" s="31" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C21" s="30" t="s"/>
+      <x:c r="D21" s="30" t="s"/>
+      <x:c r="E21" s="30" t="s"/>
+      <x:c r="F21" s="31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
@@ -14653,12 +14702,12 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B15:F15"/>
-    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B16:F16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="343">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="349">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1025,6 +1025,24 @@
   </x:si>
   <x:si>
     <x:t>REMEGIO T. BURBURAN JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A PUROK DAISY 2, POBLACION, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0882-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1369-049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, POBLACION, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1077-20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1367-348</x:t>
   </x:si>
   <x:si>
     <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
@@ -13566,19 +13584,19 @@
         <x:v>334</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46077.2024189815</x:v>
+        <x:v>46077.5191782407</x:v>
       </x:c>
       <x:c r="I11" s="17">
-        <x:v>45948</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J11" s="15" t="n">
-        <x:v>1216154</x:v>
+        <x:v>1216163</x:v>
       </x:c>
       <x:c r="K11" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L11" s="19">
-        <x:v>46090.2495949074</x:v>
+        <x:v>46090.3154976852</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>19</x:v>
@@ -13586,37 +13604,37 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>100</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>335</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>337</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>338</x:v>
-      </x:c>
       <x:c r="H12" s="16">
-        <x:v>46077.2103587963</x:v>
+        <x:v>46077.4722337963</x:v>
       </x:c>
       <x:c r="I12" s="17">
-        <x:v>46042</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J12" s="15" t="n">
-        <x:v>1216155</x:v>
+        <x:v>1216161</x:v>
       </x:c>
       <x:c r="K12" s="18" t="n">
-        <x:v>240</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L12" s="19">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46090.2963078704</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>19</x:v>
@@ -13624,89 +13642,143 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>100</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>339</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>341</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>342</x:v>
-      </x:c>
       <x:c r="H13" s="16">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46077.2024189815</x:v>
       </x:c>
       <x:c r="I13" s="17">
-        <x:v>45748</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216154</x:v>
       </x:c>
       <x:c r="K13" s="18" t="n">
-        <x:v>270</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L13" s="19">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46090.2495949074</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="20" t="s">
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>46077.2103587963</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="n">
+        <x:v>1216155</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>46090.2536226852</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>46077.2683564815</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="n">
+        <x:v>1216159</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>46090.2806018519</x:v>
+      </x:c>
+      <x:c r="M15" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="20" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="22" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="23" t="s">
+      <x:c r="C18" s="21" t="s"/>
+      <x:c r="D18" s="21" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="22" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="23" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="s">
+      <x:c r="C19" s="24" t="s"/>
+      <x:c r="D19" s="24" t="s"/>
+      <x:c r="E19" s="24" t="s"/>
+      <x:c r="F19" s="25" t="s">
         <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
       <x:c r="B20" s="26" t="s">
-        <x:v>100</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C20" s="27" t="s"/>
       <x:c r="D20" s="27" t="s"/>
@@ -13715,19 +13787,39 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="29" t="s">
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="26" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="26" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B23" s="29" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C21" s="30" t="s"/>
-      <x:c r="D21" s="30" t="s"/>
-      <x:c r="E21" s="30" t="s"/>
-      <x:c r="F21" s="31" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C23" s="30" t="s"/>
+      <x:c r="D23" s="30" t="s"/>
+      <x:c r="E23" s="30" t="s"/>
+      <x:c r="F23" s="31" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
@@ -14702,12 +14794,12 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B16:F16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="349">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="353">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1076,6 +1076,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1365-581</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROBERTO Q CORPIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A N/A, Limamawan, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25-SROPIX-16158</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1361-291</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -13754,73 +13766,110 @@
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46077.1834259259</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="n">
+        <x:v>1216166</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>46091.2388773148</x:v>
+      </x:c>
+      <x:c r="M16" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="20" t="s">
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="20" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C18" s="21" t="s"/>
-      <x:c r="D18" s="21" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="22" t="s"/>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="23" t="s">
+      <x:c r="C19" s="21" t="s"/>
+      <x:c r="D19" s="21" t="s"/>
+      <x:c r="E19" s="22" t="s"/>
+      <x:c r="F19" s="22" t="s"/>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B20" s="23" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="s">
+      <x:c r="C20" s="24" t="s"/>
+      <x:c r="D20" s="24" t="s"/>
+      <x:c r="E20" s="24" t="s"/>
+      <x:c r="F20" s="25" t="s">
         <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
       <x:c r="B21" s="26" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C21" s="27" t="s"/>
       <x:c r="D21" s="27" t="s"/>
       <x:c r="E21" s="27" t="s"/>
       <x:c r="F21" s="28" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="26" t="s">
-        <x:v>100</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C22" s="27" t="s"/>
       <x:c r="D22" s="27" t="s"/>
       <x:c r="E22" s="27" t="s"/>
       <x:c r="F22" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="29" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="26" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B24" s="29" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C23" s="30" t="s"/>
-      <x:c r="D23" s="30" t="s"/>
-      <x:c r="E23" s="30" t="s"/>
-      <x:c r="F23" s="31" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C24" s="30" t="s"/>
+      <x:c r="D24" s="30" t="s"/>
+      <x:c r="E24" s="30" t="s"/>
+      <x:c r="F24" s="31" t="n">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
@@ -14794,12 +14843,12 @@
   <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B18:F18"/>
-    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B19:F19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="353">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="357">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -986,6 +986,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1320-600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYTECH CELLPHONE AND ACC. SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>none Prk.San francisco, San jose, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110622F-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1359-531</x:t>
   </x:si>
   <x:si>
     <x:t>AL S. BURBURAN</x:t>
@@ -13464,7 +13476,7 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B8" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
         <x:v>319</x:v>
@@ -13482,19 +13494,19 @@
         <x:v>322</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46076.1792361111</x:v>
+        <x:v>46076.318900463</x:v>
       </x:c>
       <x:c r="I8" s="17">
-        <x:v>46058</x:v>
+        <x:v>46074</x:v>
       </x:c>
       <x:c r="J8" s="15" t="n">
-        <x:v>1216147</x:v>
+        <x:v>1216168</x:v>
       </x:c>
       <x:c r="K8" s="18" t="n">
-        <x:v>1830</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L8" s="19">
-        <x:v>46090.2042708333</x:v>
+        <x:v>46092.1400231481</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>19</x:v>
@@ -13520,19 +13532,19 @@
         <x:v>326</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46076.1139583333</x:v>
+        <x:v>46076.1792361111</x:v>
       </x:c>
       <x:c r="I9" s="17">
-        <x:v>46084</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
-        <x:v>1216146</x:v>
+        <x:v>1216147</x:v>
       </x:c>
       <x:c r="K9" s="18" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L9" s="19">
-        <x:v>46090.1919444444</x:v>
+        <x:v>46090.2042708333</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>19</x:v>
@@ -13558,19 +13570,19 @@
         <x:v>330</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46077.2598726852</x:v>
+        <x:v>46076.1139583333</x:v>
       </x:c>
       <x:c r="I10" s="17">
-        <x:v>46058</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J10" s="15" t="n">
-        <x:v>1216158</x:v>
+        <x:v>1216146</x:v>
       </x:c>
       <x:c r="K10" s="18" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L10" s="19">
-        <x:v>46090.2758680556</x:v>
+        <x:v>46090.1919444444</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>19</x:v>
@@ -13596,19 +13608,19 @@
         <x:v>334</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46077.5191782407</x:v>
+        <x:v>46077.2598726852</x:v>
       </x:c>
       <x:c r="I11" s="17">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J11" s="15" t="n">
-        <x:v>1216163</x:v>
+        <x:v>1216158</x:v>
       </x:c>
       <x:c r="K11" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L11" s="19">
-        <x:v>46090.3154976852</x:v>
+        <x:v>46090.2758680556</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>19</x:v>
@@ -13619,34 +13631,34 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>331</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>335</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>336</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>337</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46077.4722337963</x:v>
+        <x:v>46077.5191782407</x:v>
       </x:c>
       <x:c r="I12" s="17">
-        <x:v>46030</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J12" s="15" t="n">
-        <x:v>1216161</x:v>
+        <x:v>1216163</x:v>
       </x:c>
       <x:c r="K12" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L12" s="19">
-        <x:v>46090.2963078704</x:v>
+        <x:v>46090.3154976852</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>19</x:v>
@@ -13657,34 +13669,34 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>331</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>338</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>339</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>340</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46077.2024189815</x:v>
+        <x:v>46077.4722337963</x:v>
       </x:c>
       <x:c r="I13" s="17">
-        <x:v>45948</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
-        <x:v>1216154</x:v>
+        <x:v>1216161</x:v>
       </x:c>
       <x:c r="K13" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L13" s="19">
-        <x:v>46090.2495949074</x:v>
+        <x:v>46090.2963078704</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>19</x:v>
@@ -13692,10 +13704,10 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>100</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>341</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>26</x:v>
@@ -13710,19 +13722,19 @@
         <x:v>344</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46077.2103587963</x:v>
+        <x:v>46077.2024189815</x:v>
       </x:c>
       <x:c r="I14" s="17">
-        <x:v>46042</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J14" s="15" t="n">
-        <x:v>1216155</x:v>
+        <x:v>1216154</x:v>
       </x:c>
       <x:c r="K14" s="18" t="n">
-        <x:v>240</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L14" s="19">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46090.2495949074</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>19</x:v>
@@ -13748,19 +13760,19 @@
         <x:v>348</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46077.2103587963</x:v>
       </x:c>
       <x:c r="I15" s="17">
-        <x:v>45748</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J15" s="15" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216155</x:v>
       </x:c>
       <x:c r="K15" s="18" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L15" s="19">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46090.2536226852</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>19</x:v>
@@ -13786,92 +13798,139 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46077.1834259259</x:v>
+        <x:v>46077.2683564815</x:v>
       </x:c>
       <x:c r="I16" s="17">
-        <x:v>46115</x:v>
+        <x:v>45748</x:v>
       </x:c>
       <x:c r="J16" s="15" t="n">
-        <x:v>1216166</x:v>
+        <x:v>1216159</x:v>
       </x:c>
       <x:c r="K16" s="18" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L16" s="19">
-        <x:v>46091.2388773148</x:v>
+        <x:v>46090.2806018519</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46077.1834259259</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="n">
+        <x:v>1216166</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>46091.2388773148</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="20" t="s">
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="20" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C19" s="21" t="s"/>
-      <x:c r="D19" s="21" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="22" t="s"/>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="23" t="s">
+      <x:c r="C20" s="21" t="s"/>
+      <x:c r="D20" s="21" t="s"/>
+      <x:c r="E20" s="22" t="s"/>
+      <x:c r="F20" s="22" t="s"/>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B21" s="23" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C20" s="24" t="s"/>
-      <x:c r="D20" s="24" t="s"/>
-      <x:c r="E20" s="24" t="s"/>
-      <x:c r="F20" s="25" t="s">
+      <x:c r="C21" s="24" t="s"/>
+      <x:c r="D21" s="24" t="s"/>
+      <x:c r="E21" s="24" t="s"/>
+      <x:c r="F21" s="25" t="s">
         <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="26" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C22" s="27" t="s"/>
       <x:c r="D22" s="27" t="s"/>
       <x:c r="E22" s="27" t="s"/>
       <x:c r="F22" s="28" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="26" t="s">
-        <x:v>100</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C23" s="27" t="s"/>
       <x:c r="D23" s="27" t="s"/>
       <x:c r="E23" s="27" t="s"/>
       <x:c r="F23" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="26" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C24" s="27" t="s"/>
+      <x:c r="D24" s="27" t="s"/>
+      <x:c r="E24" s="27" t="s"/>
+      <x:c r="F24" s="28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="26" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C25" s="27" t="s"/>
+      <x:c r="D25" s="27" t="s"/>
+      <x:c r="E25" s="27" t="s"/>
+      <x:c r="F25" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="29" t="s">
+    <x:row r="26" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B26" s="29" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C24" s="30" t="s"/>
-      <x:c r="D24" s="30" t="s"/>
-      <x:c r="E24" s="30" t="s"/>
-      <x:c r="F24" s="31" t="n">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C26" s="30" t="s"/>
+      <x:c r="D26" s="30" t="s"/>
+      <x:c r="E26" s="30" t="s"/>
+      <x:c r="F26" s="31" t="n">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
@@ -14840,15 +14899,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B19:F19"/>
-    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B20:F20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="357">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="395">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -976,6 +976,18 @@
     <x:t>61-2-2026-1322-666</x:t>
   </x:si>
   <x:si>
+    <x:t>LILIA R. FLORIDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A PUROK 1, BINTANA, Tangub City, Misamis Occidental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>97-1PX-18986</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1378-820</x:t>
+  </x:si>
+  <x:si>
     <x:t>MERIAM MANON-OG LICAYAN</x:t>
   </x:si>
   <x:si>
@@ -988,6 +1000,102 @@
     <x:t>61-2-2026-1320-600</x:t>
   </x:si>
   <x:si>
+    <x:t>MYRNA M MANUGAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A P-6, Lorenzo, Tangub City, Misamis Occidental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-3PX-3945</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1381-306</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WILMA E BERMUDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Saging-saging, Micanaway, Tangub City, Misamis Occidental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-1PX-23569</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1379-115</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dealer Permit (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MINZ CELLPHONE AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>km. 5 lantawan drive, pasonanca, Zamboanga City, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIX-06868-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1384-689</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A &amp; B - GADGETZ CELLPHONE AND ACCESSORIES STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POBLACION, Diplahan, Zamboanga Sibugay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110624G-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1294-762</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AB GADGETZ ELECTRONIC GADGETS TRADING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAN PEDRO, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-110613A-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1293-860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POBLACION, Aurora, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110615E-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1292-941</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AB- GADGETZ MOBILE PHONES AND ACCESSORIES STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POBLACION, Guipos, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110618E-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1289-791</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AB-GADGETZ CELLPHONE STORE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POBLACION, Dumalinao, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110616G-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1295-381</x:t>
+  </x:si>
+  <x:si>
     <x:t>SKYTECH CELLPHONE AND ACC. SHOP</x:t>
   </x:si>
   <x:si>
@@ -1064,6 +1172,12 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1362-288</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1283-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-11-2025-1252-294</x:t>
   </x:si>
   <x:si>
     <x:t>CHARLO F  SALUMAG</x:t>
@@ -13455,19 +13569,19 @@
         <x:v>318</x:v>
       </x:c>
       <x:c r="H7" s="12">
-        <x:v>46065.2288541667</x:v>
+        <x:v>46085.2764814815</x:v>
       </x:c>
       <x:c r="I7" s="32">
-        <x:v>46070</x:v>
+        <x:v>44879</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>1216140</x:v>
+        <x:v>1216175</x:v>
       </x:c>
       <x:c r="K7" s="13" t="n">
-        <x:v>390</x:v>
+        <x:v>1290</x:v>
       </x:c>
       <x:c r="L7" s="12">
-        <x:v>46084.1582175926</x:v>
+        <x:v>46093.2000115741</x:v>
       </x:c>
       <x:c r="M7" s="11" t="s">
         <x:v>19</x:v>
@@ -13476,7 +13590,7 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B8" s="14" t="s">
-        <x:v>61</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C8" s="14" t="s">
         <x:v>319</x:v>
@@ -13494,19 +13608,19 @@
         <x:v>322</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46076.318900463</x:v>
+        <x:v>46065.2288541667</x:v>
       </x:c>
       <x:c r="I8" s="17">
-        <x:v>46074</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="J8" s="15" t="n">
-        <x:v>1216168</x:v>
+        <x:v>1216140</x:v>
       </x:c>
       <x:c r="K8" s="18" t="n">
-        <x:v>3780</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="L8" s="19">
-        <x:v>46092.1400231481</x:v>
+        <x:v>46084.1582175926</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>19</x:v>
@@ -13514,7 +13628,7 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
         <x:v>323</x:v>
@@ -13532,19 +13646,19 @@
         <x:v>326</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46076.1792361111</x:v>
+        <x:v>46085.3007986111</x:v>
       </x:c>
       <x:c r="I9" s="17">
-        <x:v>46058</x:v>
+        <x:v>46386</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
-        <x:v>1216147</x:v>
+        <x:v>1216177</x:v>
       </x:c>
       <x:c r="K9" s="18" t="n">
-        <x:v>1830</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="L9" s="19">
-        <x:v>46090.2042708333</x:v>
+        <x:v>46093.215162037</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>19</x:v>
@@ -13552,7 +13666,7 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
         <x:v>327</x:v>
@@ -13570,19 +13684,19 @@
         <x:v>330</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46076.1139583333</x:v>
+        <x:v>46085.2858333333</x:v>
       </x:c>
       <x:c r="I10" s="17">
-        <x:v>46084</x:v>
+        <x:v>46096</x:v>
       </x:c>
       <x:c r="J10" s="15" t="n">
-        <x:v>1216146</x:v>
+        <x:v>1216176</x:v>
       </x:c>
       <x:c r="K10" s="18" t="n">
-        <x:v>1470</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="L10" s="19">
-        <x:v>46090.1919444444</x:v>
+        <x:v>46093.2057060185</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>19</x:v>
@@ -13590,37 +13704,37 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>333</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="G11" s="14" t="s">
-        <x:v>334</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46077.2598726852</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>46058</x:v>
+        <x:v>46088.1798263889</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46088.179837963</x:v>
       </x:c>
       <x:c r="J11" s="15" t="n">
-        <x:v>1216158</x:v>
+        <x:v>1216179</x:v>
       </x:c>
       <x:c r="K11" s="18" t="n">
-        <x:v>1830</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="L11" s="19">
-        <x:v>46090.2758680556</x:v>
+        <x:v>46093.2393865741</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>19</x:v>
@@ -13628,37 +13742,37 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>335</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>336</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>337</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>338</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46077.5191782407</x:v>
+        <x:v>46046.1343634259</x:v>
       </x:c>
       <x:c r="I12" s="17">
-        <x:v>46058</x:v>
+        <x:v>45917</x:v>
       </x:c>
       <x:c r="J12" s="15" t="n">
-        <x:v>1216163</x:v>
+        <x:v>1216183</x:v>
       </x:c>
       <x:c r="K12" s="18" t="n">
-        <x:v>1830</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L12" s="19">
-        <x:v>46090.3154976852</x:v>
+        <x:v>46093.2878703704</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>19</x:v>
@@ -13666,37 +13780,37 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>335</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>339</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>340</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>341</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46077.4722337963</x:v>
+        <x:v>46046.1309027778</x:v>
       </x:c>
       <x:c r="I13" s="17">
-        <x:v>46030</x:v>
+        <x:v>46021</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
-        <x:v>1216161</x:v>
+        <x:v>1216181</x:v>
       </x:c>
       <x:c r="K13" s="18" t="n">
-        <x:v>1830</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="L13" s="19">
-        <x:v>46090.2963078704</x:v>
+        <x:v>46093.273287037</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>19</x:v>
@@ -13704,37 +13818,37 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>335</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>342</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>343</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>344</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46077.2024189815</x:v>
+        <x:v>46046.1237615741</x:v>
       </x:c>
       <x:c r="I14" s="17">
-        <x:v>45948</x:v>
+        <x:v>45991</x:v>
       </x:c>
       <x:c r="J14" s="15" t="n">
-        <x:v>1216154</x:v>
+        <x:v>1216180</x:v>
       </x:c>
       <x:c r="K14" s="18" t="n">
-        <x:v>1830</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L14" s="19">
-        <x:v>46090.2495949074</x:v>
+        <x:v>46093.2636342593</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>19</x:v>
@@ -13742,37 +13856,37 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>100</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>345</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>346</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>347</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>348</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46077.2103587963</x:v>
+        <x:v>46046.1140856482</x:v>
       </x:c>
       <x:c r="I15" s="17">
-        <x:v>46042</x:v>
+        <x:v>46024</x:v>
       </x:c>
       <x:c r="J15" s="15" t="n">
-        <x:v>1216155</x:v>
+        <x:v>1216182</x:v>
       </x:c>
       <x:c r="K15" s="18" t="n">
-        <x:v>240</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L15" s="19">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46093.2825231481</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>19</x:v>
@@ -13780,37 +13894,37 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>100</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>349</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
-        <x:v>350</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="F16" s="14" t="s">
-        <x:v>351</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="G16" s="14" t="s">
-        <x:v>352</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46048.0974768518</x:v>
       </x:c>
       <x:c r="I16" s="17">
-        <x:v>45748</x:v>
+        <x:v>45883</x:v>
       </x:c>
       <x:c r="J16" s="15" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216184</x:v>
       </x:c>
       <x:c r="K16" s="18" t="n">
-        <x:v>270</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L16" s="19">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46093.2926041667</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>19</x:v>
@@ -13818,130 +13932,510 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>100</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>353</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
-        <x:v>354</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="F17" s="14" t="s">
-        <x:v>355</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="G17" s="14" t="s">
-        <x:v>356</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46077.1834259259</x:v>
+        <x:v>46076.318900463</x:v>
       </x:c>
       <x:c r="I17" s="17">
-        <x:v>46115</x:v>
+        <x:v>46074</x:v>
       </x:c>
       <x:c r="J17" s="15" t="n">
-        <x:v>1216166</x:v>
+        <x:v>1216168</x:v>
       </x:c>
       <x:c r="K17" s="18" t="n">
-        <x:v>210</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L17" s="19">
-        <x:v>46091.2388773148</x:v>
+        <x:v>46092.1400231481</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="20" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C20" s="21" t="s"/>
-      <x:c r="D20" s="21" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="22" t="s"/>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B21" s="23" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C21" s="24" t="s"/>
-      <x:c r="D21" s="24" t="s"/>
-      <x:c r="E21" s="24" t="s"/>
-      <x:c r="F21" s="25" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="26" t="s">
+      <x:c r="C18" s="14" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46076.1792361111</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="n">
+        <x:v>1216147</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L18" s="19">
+        <x:v>46090.2042708333</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46076.1139583333</x:v>
+      </x:c>
+      <x:c r="I19" s="17">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="n">
+        <x:v>1216146</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L19" s="19">
+        <x:v>46090.1919444444</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46077.2598726852</x:v>
+      </x:c>
+      <x:c r="I20" s="17">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="n">
+        <x:v>1216158</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L20" s="19">
+        <x:v>46090.2758680556</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46077.5191782407</x:v>
+      </x:c>
+      <x:c r="I21" s="17">
+        <x:v>46058</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="n">
+        <x:v>1216163</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L21" s="19">
+        <x:v>46090.3154976852</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46077.4722337963</x:v>
+      </x:c>
+      <x:c r="I22" s="17">
+        <x:v>46030</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="n">
+        <x:v>1216161</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L22" s="19">
+        <x:v>46090.2963078704</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46077.2024189815</x:v>
+      </x:c>
+      <x:c r="I23" s="17">
+        <x:v>45948</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="n">
+        <x:v>1216154</x:v>
+      </x:c>
+      <x:c r="K23" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L23" s="19">
+        <x:v>46090.2495949074</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>45988.1893402778</x:v>
+      </x:c>
+      <x:c r="I24" s="17">
+        <x:v>45973</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="n">
+        <x:v>1216173</x:v>
+      </x:c>
+      <x:c r="K24" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L24" s="19">
+        <x:v>46093.1383912037</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="14" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B26" s="29" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C26" s="30" t="s"/>
-      <x:c r="D26" s="30" t="s"/>
-      <x:c r="E26" s="30" t="s"/>
-      <x:c r="F26" s="31" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C25" s="14" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46077.2103587963</x:v>
+      </x:c>
+      <x:c r="I25" s="17">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="n">
+        <x:v>1216155</x:v>
+      </x:c>
+      <x:c r="K25" s="18" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L25" s="19">
+        <x:v>46090.2536226852</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
+        <x:v>46077.2683564815</x:v>
+      </x:c>
+      <x:c r="I26" s="17">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="n">
+        <x:v>1216159</x:v>
+      </x:c>
+      <x:c r="K26" s="18" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L26" s="19">
+        <x:v>46090.2806018519</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="H27" s="16">
+        <x:v>46077.1834259259</x:v>
+      </x:c>
+      <x:c r="I27" s="17">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J27" s="15" t="n">
+        <x:v>1216166</x:v>
+      </x:c>
+      <x:c r="K27" s="18" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L27" s="19">
+        <x:v>46091.2388773148</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B30" s="20" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C30" s="21" t="s"/>
+      <x:c r="D30" s="21" t="s"/>
+      <x:c r="E30" s="22" t="s"/>
+      <x:c r="F30" s="22" t="s"/>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B31" s="23" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C31" s="24" t="s"/>
+      <x:c r="D31" s="24" t="s"/>
+      <x:c r="E31" s="24" t="s"/>
+      <x:c r="F31" s="25" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="26" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="26" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="C33" s="27" t="s"/>
+      <x:c r="D33" s="27" t="s"/>
+      <x:c r="E33" s="27" t="s"/>
+      <x:c r="F33" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="26" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C34" s="27" t="s"/>
+      <x:c r="D34" s="27" t="s"/>
+      <x:c r="E34" s="27" t="s"/>
+      <x:c r="F34" s="28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="26" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C35" s="27" t="s"/>
+      <x:c r="D35" s="27" t="s"/>
+      <x:c r="E35" s="27" t="s"/>
+      <x:c r="F35" s="28" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="26" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C36" s="27" t="s"/>
+      <x:c r="D36" s="27" t="s"/>
+      <x:c r="E36" s="27" t="s"/>
+      <x:c r="F36" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B37" s="29" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C37" s="30" t="s"/>
+      <x:c r="D37" s="30" t="s"/>
+      <x:c r="E37" s="30" t="s"/>
+      <x:c r="F37" s="31" t="n">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
     <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
@@ -14899,16 +15393,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
+  <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B20:F20"/>
-    <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
-    <x:mergeCell ref="B23:E23"/>
-    <x:mergeCell ref="B24:E24"/>
-    <x:mergeCell ref="B25:E25"/>
-    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B30:F30"/>
+    <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B32:E32"/>
+    <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B34:E34"/>
+    <x:mergeCell ref="B35:E35"/>
+    <x:mergeCell ref="B36:E36"/>
+    <x:mergeCell ref="B37:E37"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="395">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="406">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1178,6 +1178,39 @@
   </x:si>
   <x:si>
     <x:t>61-11-2025-1252-294</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AILYN G. PANIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PURON NANGKA, TENIAPAN, San Pablo, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIX-06923-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1389-850</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERLINDA G. PANES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUROK NANGKA, TENIAPAN, San Pablo, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIX-06918-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1388-689</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JORELYN P. SOLES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEMP-ROIX-06912-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1387-457</x:t>
   </x:si>
   <x:si>
     <x:t>CHARLO F  SALUMAG</x:t>
@@ -14236,14 +14269,12 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B25" s="14" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
         <x:v>383</x:v>
       </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
+      <x:c r="D25" s="15" t="s"/>
       <x:c r="E25" s="14" t="s">
         <x:v>384</x:v>
       </x:c>
@@ -14254,19 +14285,19 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="H25" s="16">
-        <x:v>46077.2103587963</x:v>
-      </x:c>
-      <x:c r="I25" s="17">
-        <x:v>46042</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="n">
-        <x:v>1216155</x:v>
+        <x:v>46090.2854050926</x:v>
+      </x:c>
+      <x:c r="I25" s="16">
+        <x:v>46090.2854282407</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="s">
+        <x:v>386</x:v>
       </x:c>
       <x:c r="K25" s="18" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L25" s="19">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46094.0865740741</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
         <x:v>19</x:v>
@@ -14274,14 +14305,12 @@
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B26" s="14" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C26" s="14" t="s">
         <x:v>387</x:v>
       </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
+      <x:c r="D26" s="15" t="s"/>
       <x:c r="E26" s="14" t="s">
         <x:v>388</x:v>
       </x:c>
@@ -14292,19 +14321,19 @@
         <x:v>390</x:v>
       </x:c>
       <x:c r="H26" s="16">
-        <x:v>46077.2683564815</x:v>
-      </x:c>
-      <x:c r="I26" s="17">
-        <x:v>45748</x:v>
+        <x:v>46090.2540972222</x:v>
+      </x:c>
+      <x:c r="I26" s="16">
+        <x:v>46090.2541203704</x:v>
       </x:c>
       <x:c r="J26" s="15" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216185</x:v>
       </x:c>
       <x:c r="K26" s="18" t="n">
-        <x:v>270</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L26" s="19">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46094.0818981481</x:v>
       </x:c>
       <x:c r="M26" s="14" t="s">
         <x:v>19</x:v>
@@ -14312,134 +14341,253 @@
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B27" s="14" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C27" s="14" t="s">
         <x:v>391</x:v>
       </x:c>
-      <x:c r="D27" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
+      <x:c r="D27" s="15" t="s"/>
       <x:c r="E27" s="14" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="F27" s="14" t="s">
+      <x:c r="G27" s="14" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="G27" s="14" t="s">
-        <x:v>394</x:v>
-      </x:c>
       <x:c r="H27" s="16">
-        <x:v>46077.1834259259</x:v>
-      </x:c>
-      <x:c r="I27" s="17">
-        <x:v>46115</x:v>
+        <x:v>46090.2349189815</x:v>
+      </x:c>
+      <x:c r="I27" s="16">
+        <x:v>46090.2349305556</x:v>
       </x:c>
       <x:c r="J27" s="15" t="n">
-        <x:v>1216166</x:v>
+        <x:v>1216187</x:v>
       </x:c>
       <x:c r="K27" s="18" t="n">
-        <x:v>210</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L27" s="19">
-        <x:v>46091.2388773148</x:v>
+        <x:v>46094.0939351852</x:v>
       </x:c>
       <x:c r="M27" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="20" t="s">
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="H28" s="16">
+        <x:v>46077.2103587963</x:v>
+      </x:c>
+      <x:c r="I28" s="17">
+        <x:v>46042</x:v>
+      </x:c>
+      <x:c r="J28" s="15" t="n">
+        <x:v>1216155</x:v>
+      </x:c>
+      <x:c r="K28" s="18" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L28" s="19">
+        <x:v>46090.2536226852</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="H29" s="16">
+        <x:v>46077.2683564815</x:v>
+      </x:c>
+      <x:c r="I29" s="17">
+        <x:v>45748</x:v>
+      </x:c>
+      <x:c r="J29" s="15" t="n">
+        <x:v>1216159</x:v>
+      </x:c>
+      <x:c r="K29" s="18" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L29" s="19">
+        <x:v>46090.2806018519</x:v>
+      </x:c>
+      <x:c r="M29" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="H30" s="16">
+        <x:v>46077.1834259259</x:v>
+      </x:c>
+      <x:c r="I30" s="17">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J30" s="15" t="n">
+        <x:v>1216166</x:v>
+      </x:c>
+      <x:c r="K30" s="18" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L30" s="19">
+        <x:v>46091.2388773148</x:v>
+      </x:c>
+      <x:c r="M30" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B33" s="20" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C30" s="21" t="s"/>
-      <x:c r="D30" s="21" t="s"/>
-      <x:c r="E30" s="22" t="s"/>
-      <x:c r="F30" s="22" t="s"/>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B31" s="23" t="s">
+      <x:c r="C33" s="21" t="s"/>
+      <x:c r="D33" s="21" t="s"/>
+      <x:c r="E33" s="22" t="s"/>
+      <x:c r="F33" s="22" t="s"/>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B34" s="23" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C31" s="24" t="s"/>
-      <x:c r="D31" s="24" t="s"/>
-      <x:c r="E31" s="24" t="s"/>
-      <x:c r="F31" s="25" t="s">
+      <x:c r="C34" s="24" t="s"/>
+      <x:c r="D34" s="24" t="s"/>
+      <x:c r="E34" s="24" t="s"/>
+      <x:c r="F34" s="25" t="s">
         <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
-        <x:v>331</x:v>
-      </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="26" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C34" s="27" t="s"/>
-      <x:c r="D34" s="27" t="s"/>
-      <x:c r="E34" s="27" t="s"/>
-      <x:c r="F34" s="28" t="n">
-        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
       <x:c r="B35" s="26" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C35" s="27" t="s"/>
       <x:c r="D35" s="27" t="s"/>
       <x:c r="E35" s="27" t="s"/>
       <x:c r="F35" s="28" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
       <x:c r="B36" s="26" t="s">
-        <x:v>100</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C36" s="27" t="s"/>
       <x:c r="D36" s="27" t="s"/>
       <x:c r="E36" s="27" t="s"/>
       <x:c r="F36" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B37" s="26" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C37" s="27" t="s"/>
+      <x:c r="D37" s="27" t="s"/>
+      <x:c r="E37" s="27" t="s"/>
+      <x:c r="F37" s="28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B38" s="26" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C38" s="27" t="s"/>
+      <x:c r="D38" s="27" t="s"/>
+      <x:c r="E38" s="27" t="s"/>
+      <x:c r="F38" s="28" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B39" s="26" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C39" s="27" t="s"/>
+      <x:c r="D39" s="27" t="s"/>
+      <x:c r="E39" s="27" t="s"/>
+      <x:c r="F39" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B37" s="29" t="s">
+    <x:row r="40" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B40" s="26" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C40" s="27" t="s"/>
+      <x:c r="D40" s="27" t="s"/>
+      <x:c r="E40" s="27" t="s"/>
+      <x:c r="F40" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B41" s="29" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C37" s="30" t="s"/>
-      <x:c r="D37" s="30" t="s"/>
-      <x:c r="E37" s="30" t="s"/>
-      <x:c r="F37" s="31" t="n">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C41" s="30" t="s"/>
+      <x:c r="D41" s="30" t="s"/>
+      <x:c r="E41" s="30" t="s"/>
+      <x:c r="F41" s="31" t="n">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
@@ -15393,17 +15541,18 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="10">
+  <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B30:F30"/>
-    <x:mergeCell ref="B31:E31"/>
-    <x:mergeCell ref="B32:E32"/>
-    <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B33:F33"/>
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
     <x:mergeCell ref="B36:E36"/>
     <x:mergeCell ref="B37:E37"/>
+    <x:mergeCell ref="B38:E38"/>
+    <x:mergeCell ref="B39:E39"/>
+    <x:mergeCell ref="B40:E40"/>
+    <x:mergeCell ref="B41:E41"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="406">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="410">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -661,7 +661,7 @@
     <x:t>61-11-2025-1227</x:t>
   </x:si>
   <x:si>
-    <x:t>RUEL  BUGAS BALILI</x:t>
+    <x:t>RUEL BUGAS BALILI</x:t>
   </x:si>
   <x:si>
     <x:t>24-SROPPIX-16142</x:t>
@@ -1039,6 +1039,18 @@
     <x:t>61-3-2026-1384-689</x:t>
   </x:si>
   <x:si>
+    <x:t>PEARL'S ONLINE SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ariosa Street, San Francisco, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIX-06359-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1357-656</x:t>
+  </x:si>
+  <x:si>
     <x:t>A &amp; B - GADGETZ CELLPHONE AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -1213,7 +1225,7 @@
     <x:t>61-3-2026-1387-457</x:t>
   </x:si>
   <x:si>
-    <x:t>CHARLO F  SALUMAG</x:t>
+    <x:t>CHARLO F SALUMAG</x:t>
   </x:si>
   <x:si>
     <x:t>N/A N/a, Poblacion, Tukuran, Zamboanga Del Sur</x:t>
@@ -13775,13 +13787,13 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>61</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
         <x:v>336</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
         <x:v>337</x:v>
@@ -13793,19 +13805,19 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46046.1343634259</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>45917</x:v>
+        <x:v>46076.2633564815</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46076.2633680556</x:v>
       </x:c>
       <x:c r="J12" s="15" t="n">
-        <x:v>1216183</x:v>
+        <x:v>1216188</x:v>
       </x:c>
       <x:c r="K12" s="18" t="n">
-        <x:v>3780</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="L12" s="19">
-        <x:v>46093.2878703704</x:v>
+        <x:v>46094.1562731481</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>19</x:v>
@@ -13831,19 +13843,19 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46046.1309027778</x:v>
+        <x:v>46046.1343634259</x:v>
       </x:c>
       <x:c r="I13" s="17">
-        <x:v>46021</x:v>
+        <x:v>45917</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
-        <x:v>1216181</x:v>
+        <x:v>1216183</x:v>
       </x:c>
       <x:c r="K13" s="18" t="n">
-        <x:v>5280</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L13" s="19">
-        <x:v>46093.273287037</x:v>
+        <x:v>46093.2878703704</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>19</x:v>
@@ -13854,34 +13866,34 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>340</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>344</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>345</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>346</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46046.1237615741</x:v>
+        <x:v>46046.1309027778</x:v>
       </x:c>
       <x:c r="I14" s="17">
-        <x:v>45991</x:v>
+        <x:v>46021</x:v>
       </x:c>
       <x:c r="J14" s="15" t="n">
-        <x:v>1216180</x:v>
+        <x:v>1216181</x:v>
       </x:c>
       <x:c r="K14" s="18" t="n">
-        <x:v>3780</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="L14" s="19">
-        <x:v>46093.2636342593</x:v>
+        <x:v>46093.273287037</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>19</x:v>
@@ -13892,7 +13904,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>347</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>26</x:v>
@@ -13907,19 +13919,19 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46046.1140856482</x:v>
+        <x:v>46046.1237615741</x:v>
       </x:c>
       <x:c r="I15" s="17">
-        <x:v>46024</x:v>
+        <x:v>45991</x:v>
       </x:c>
       <x:c r="J15" s="15" t="n">
-        <x:v>1216182</x:v>
+        <x:v>1216180</x:v>
       </x:c>
       <x:c r="K15" s="18" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L15" s="19">
-        <x:v>46093.2825231481</x:v>
+        <x:v>46093.2636342593</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>19</x:v>
@@ -13945,19 +13957,19 @@
         <x:v>354</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46048.0974768518</x:v>
+        <x:v>46046.1140856482</x:v>
       </x:c>
       <x:c r="I16" s="17">
-        <x:v>45883</x:v>
+        <x:v>46024</x:v>
       </x:c>
       <x:c r="J16" s="15" t="n">
-        <x:v>1216184</x:v>
+        <x:v>1216182</x:v>
       </x:c>
       <x:c r="K16" s="18" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L16" s="19">
-        <x:v>46093.2926041667</x:v>
+        <x:v>46093.2825231481</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>19</x:v>
@@ -13983,19 +13995,19 @@
         <x:v>358</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46076.318900463</x:v>
+        <x:v>46048.0974768518</x:v>
       </x:c>
       <x:c r="I17" s="17">
-        <x:v>46074</x:v>
+        <x:v>45883</x:v>
       </x:c>
       <x:c r="J17" s="15" t="n">
-        <x:v>1216168</x:v>
+        <x:v>1216184</x:v>
       </x:c>
       <x:c r="K17" s="18" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L17" s="19">
-        <x:v>46092.1400231481</x:v>
+        <x:v>46093.2926041667</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>19</x:v>
@@ -14003,7 +14015,7 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
         <x:v>359</x:v>
@@ -14021,19 +14033,19 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46076.1792361111</x:v>
+        <x:v>46076.318900463</x:v>
       </x:c>
       <x:c r="I18" s="17">
-        <x:v>46058</x:v>
+        <x:v>46074</x:v>
       </x:c>
       <x:c r="J18" s="15" t="n">
-        <x:v>1216147</x:v>
+        <x:v>1216168</x:v>
       </x:c>
       <x:c r="K18" s="18" t="n">
-        <x:v>1830</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L18" s="19">
-        <x:v>46090.2042708333</x:v>
+        <x:v>46092.1400231481</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>19</x:v>
@@ -14059,19 +14071,19 @@
         <x:v>366</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46076.1139583333</x:v>
+        <x:v>46076.1792361111</x:v>
       </x:c>
       <x:c r="I19" s="17">
-        <x:v>46084</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J19" s="15" t="n">
-        <x:v>1216146</x:v>
+        <x:v>1216147</x:v>
       </x:c>
       <x:c r="K19" s="18" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L19" s="19">
-        <x:v>46090.1919444444</x:v>
+        <x:v>46090.2042708333</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>19</x:v>
@@ -14097,19 +14109,19 @@
         <x:v>370</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46077.2598726852</x:v>
+        <x:v>46076.1139583333</x:v>
       </x:c>
       <x:c r="I20" s="17">
-        <x:v>46058</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J20" s="15" t="n">
-        <x:v>1216158</x:v>
+        <x:v>1216146</x:v>
       </x:c>
       <x:c r="K20" s="18" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L20" s="19">
-        <x:v>46090.2758680556</x:v>
+        <x:v>46090.1919444444</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
         <x:v>19</x:v>
@@ -14135,19 +14147,19 @@
         <x:v>374</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46077.5191782407</x:v>
+        <x:v>46077.2598726852</x:v>
       </x:c>
       <x:c r="I21" s="17">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J21" s="15" t="n">
-        <x:v>1216163</x:v>
+        <x:v>1216158</x:v>
       </x:c>
       <x:c r="K21" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L21" s="19">
-        <x:v>46090.3154976852</x:v>
+        <x:v>46090.2758680556</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>19</x:v>
@@ -14158,34 +14170,34 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>371</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E22" s="14" t="s">
-        <x:v>375</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="F22" s="14" t="s">
-        <x:v>376</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="G22" s="14" t="s">
-        <x:v>377</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46077.4722337963</x:v>
+        <x:v>46077.5191782407</x:v>
       </x:c>
       <x:c r="I22" s="17">
-        <x:v>46030</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J22" s="15" t="n">
-        <x:v>1216161</x:v>
+        <x:v>1216163</x:v>
       </x:c>
       <x:c r="K22" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L22" s="19">
-        <x:v>46090.2963078704</x:v>
+        <x:v>46090.3154976852</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
         <x:v>19</x:v>
@@ -14196,34 +14208,34 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>371</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E23" s="14" t="s">
-        <x:v>378</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="F23" s="14" t="s">
-        <x:v>379</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G23" s="14" t="s">
-        <x:v>380</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46077.2024189815</x:v>
+        <x:v>46077.4722337963</x:v>
       </x:c>
       <x:c r="I23" s="17">
-        <x:v>45948</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J23" s="15" t="n">
-        <x:v>1216154</x:v>
+        <x:v>1216161</x:v>
       </x:c>
       <x:c r="K23" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L23" s="19">
-        <x:v>46090.2495949074</x:v>
+        <x:v>46090.2963078704</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>19</x:v>
@@ -14234,34 +14246,34 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>124</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D24" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E24" s="14" t="s">
-        <x:v>125</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F24" s="14" t="s">
-        <x:v>381</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="G24" s="14" t="s">
-        <x:v>382</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="H24" s="16">
-        <x:v>45988.1893402778</x:v>
+        <x:v>46077.2024189815</x:v>
       </x:c>
       <x:c r="I24" s="17">
-        <x:v>45973</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J24" s="15" t="n">
-        <x:v>1216173</x:v>
+        <x:v>1216154</x:v>
       </x:c>
       <x:c r="K24" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L24" s="19">
-        <x:v>46093.1383912037</x:v>
+        <x:v>46090.2495949074</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
         <x:v>19</x:v>
@@ -14269,14 +14281,16 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B25" s="14" t="s">
-        <x:v>90</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>383</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s"/>
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
       <x:c r="E25" s="14" t="s">
-        <x:v>384</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F25" s="14" t="s">
         <x:v>385</x:v>
@@ -14285,19 +14299,19 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="H25" s="16">
-        <x:v>46090.2854050926</x:v>
-      </x:c>
-      <x:c r="I25" s="16">
-        <x:v>46090.2854282407</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="s">
-        <x:v>386</x:v>
+        <x:v>45988.1893402778</x:v>
+      </x:c>
+      <x:c r="I25" s="17">
+        <x:v>45973</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="n">
+        <x:v>1216173</x:v>
       </x:c>
       <x:c r="K25" s="18" t="n">
-        <x:v>426</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L25" s="19">
-        <x:v>46094.0865740741</x:v>
+        <x:v>46093.1383912037</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
         <x:v>19</x:v>
@@ -14321,19 +14335,19 @@
         <x:v>390</x:v>
       </x:c>
       <x:c r="H26" s="16">
-        <x:v>46090.2540972222</x:v>
+        <x:v>46090.2854050926</x:v>
       </x:c>
       <x:c r="I26" s="16">
-        <x:v>46090.2541203704</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="n">
-        <x:v>1216185</x:v>
+        <x:v>46090.2854282407</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="s">
+        <x:v>390</x:v>
       </x:c>
       <x:c r="K26" s="18" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L26" s="19">
-        <x:v>46094.0818981481</x:v>
+        <x:v>46094.0865740741</x:v>
       </x:c>
       <x:c r="M26" s="14" t="s">
         <x:v>19</x:v>
@@ -14348,28 +14362,28 @@
       </x:c>
       <x:c r="D27" s="15" t="s"/>
       <x:c r="E27" s="14" t="s">
-        <x:v>388</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="F27" s="14" t="s">
-        <x:v>392</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="G27" s="14" t="s">
-        <x:v>393</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="H27" s="16">
-        <x:v>46090.2349189815</x:v>
+        <x:v>46090.2540972222</x:v>
       </x:c>
       <x:c r="I27" s="16">
-        <x:v>46090.2349305556</x:v>
+        <x:v>46090.2541203704</x:v>
       </x:c>
       <x:c r="J27" s="15" t="n">
-        <x:v>1216187</x:v>
+        <x:v>1216185</x:v>
       </x:c>
       <x:c r="K27" s="18" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L27" s="19">
-        <x:v>46094.0939351852</x:v>
+        <x:v>46094.0818981481</x:v>
       </x:c>
       <x:c r="M27" s="14" t="s">
         <x:v>19</x:v>
@@ -14377,16 +14391,14 @@
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B28" s="14" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C28" s="14" t="s">
-        <x:v>394</x:v>
-      </x:c>
-      <x:c r="D28" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="s"/>
       <x:c r="E28" s="14" t="s">
-        <x:v>395</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="F28" s="14" t="s">
         <x:v>396</x:v>
@@ -14395,19 +14407,19 @@
         <x:v>397</x:v>
       </x:c>
       <x:c r="H28" s="16">
-        <x:v>46077.2103587963</x:v>
-      </x:c>
-      <x:c r="I28" s="17">
-        <x:v>46042</x:v>
+        <x:v>46090.2349189815</x:v>
+      </x:c>
+      <x:c r="I28" s="16">
+        <x:v>46090.2349305556</x:v>
       </x:c>
       <x:c r="J28" s="15" t="n">
-        <x:v>1216155</x:v>
+        <x:v>1216187</x:v>
       </x:c>
       <x:c r="K28" s="18" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L28" s="19">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46094.0939351852</x:v>
       </x:c>
       <x:c r="M28" s="14" t="s">
         <x:v>19</x:v>
@@ -14433,19 +14445,19 @@
         <x:v>401</x:v>
       </x:c>
       <x:c r="H29" s="16">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46077.2103587963</x:v>
       </x:c>
       <x:c r="I29" s="17">
-        <x:v>45748</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J29" s="15" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216155</x:v>
       </x:c>
       <x:c r="K29" s="18" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L29" s="19">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46090.2536226852</x:v>
       </x:c>
       <x:c r="M29" s="14" t="s">
         <x:v>19</x:v>
@@ -14471,125 +14483,172 @@
         <x:v>405</x:v>
       </x:c>
       <x:c r="H30" s="16">
-        <x:v>46077.1834259259</x:v>
+        <x:v>46077.2683564815</x:v>
       </x:c>
       <x:c r="I30" s="17">
-        <x:v>46115</x:v>
+        <x:v>45748</x:v>
       </x:c>
       <x:c r="J30" s="15" t="n">
-        <x:v>1216166</x:v>
+        <x:v>1216159</x:v>
       </x:c>
       <x:c r="K30" s="18" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L30" s="19">
-        <x:v>46091.2388773148</x:v>
+        <x:v>46090.2806018519</x:v>
       </x:c>
       <x:c r="M30" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="H31" s="16">
+        <x:v>46077.1834259259</x:v>
+      </x:c>
+      <x:c r="I31" s="17">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J31" s="15" t="n">
+        <x:v>1216166</x:v>
+      </x:c>
+      <x:c r="K31" s="18" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L31" s="19">
+        <x:v>46091.2388773148</x:v>
+      </x:c>
+      <x:c r="M31" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="20" t="s">
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B34" s="20" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C33" s="21" t="s"/>
-      <x:c r="D33" s="21" t="s"/>
-      <x:c r="E33" s="22" t="s"/>
-      <x:c r="F33" s="22" t="s"/>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B34" s="23" t="s">
+      <x:c r="C34" s="21" t="s"/>
+      <x:c r="D34" s="21" t="s"/>
+      <x:c r="E34" s="22" t="s"/>
+      <x:c r="F34" s="22" t="s"/>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B35" s="23" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C34" s="24" t="s"/>
-      <x:c r="D34" s="24" t="s"/>
-      <x:c r="E34" s="24" t="s"/>
-      <x:c r="F34" s="25" t="s">
+      <x:c r="C35" s="24" t="s"/>
+      <x:c r="D35" s="24" t="s"/>
+      <x:c r="E35" s="24" t="s"/>
+      <x:c r="F35" s="25" t="s">
         <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="26" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C35" s="27" t="s"/>
-      <x:c r="D35" s="27" t="s"/>
-      <x:c r="E35" s="27" t="s"/>
-      <x:c r="F35" s="28" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
       <x:c r="B36" s="26" t="s">
-        <x:v>331</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C36" s="27" t="s"/>
       <x:c r="D36" s="27" t="s"/>
       <x:c r="E36" s="27" t="s"/>
       <x:c r="F36" s="28" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="18" customHeight="1">
       <x:c r="B37" s="26" t="s">
-        <x:v>61</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C37" s="27" t="s"/>
       <x:c r="D37" s="27" t="s"/>
       <x:c r="E37" s="27" t="s"/>
       <x:c r="F37" s="28" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="18" customHeight="1">
       <x:c r="B38" s="26" t="s">
-        <x:v>29</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C38" s="27" t="s"/>
       <x:c r="D38" s="27" t="s"/>
       <x:c r="E38" s="27" t="s"/>
       <x:c r="F38" s="28" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="18" customHeight="1">
       <x:c r="B39" s="26" t="s">
-        <x:v>90</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C39" s="27" t="s"/>
       <x:c r="D39" s="27" t="s"/>
       <x:c r="E39" s="27" t="s"/>
       <x:c r="F39" s="28" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="18" customHeight="1">
       <x:c r="B40" s="26" t="s">
-        <x:v>100</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C40" s="27" t="s"/>
       <x:c r="D40" s="27" t="s"/>
       <x:c r="E40" s="27" t="s"/>
       <x:c r="F40" s="28" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B41" s="26" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C41" s="27" t="s"/>
+      <x:c r="D41" s="27" t="s"/>
+      <x:c r="E41" s="27" t="s"/>
+      <x:c r="F41" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B41" s="29" t="s">
+    <x:row r="42" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B42" s="26" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C42" s="27" t="s"/>
+      <x:c r="D42" s="27" t="s"/>
+      <x:c r="E42" s="27" t="s"/>
+      <x:c r="F42" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B43" s="29" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C41" s="30" t="s"/>
-      <x:c r="D41" s="30" t="s"/>
-      <x:c r="E41" s="30" t="s"/>
-      <x:c r="F41" s="31" t="n">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C43" s="30" t="s"/>
+      <x:c r="D43" s="30" t="s"/>
+      <x:c r="E43" s="30" t="s"/>
+      <x:c r="F43" s="31" t="n">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
@@ -15541,11 +15600,10 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="11">
+  <x:mergeCells count="12">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B33:F33"/>
-    <x:mergeCell ref="B34:E34"/>
+    <x:mergeCell ref="B34:F34"/>
     <x:mergeCell ref="B35:E35"/>
     <x:mergeCell ref="B36:E36"/>
     <x:mergeCell ref="B37:E37"/>
@@ -15553,6 +15611,8 @@
     <x:mergeCell ref="B39:E39"/>
     <x:mergeCell ref="B40:E40"/>
     <x:mergeCell ref="B41:E41"/>
+    <x:mergeCell ref="B42:E42"/>
+    <x:mergeCell ref="B43:E43"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="410">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="418">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -1051,6 +1051,18 @@
     <x:t>61-2-2026-1357-656</x:t>
   </x:si>
   <x:si>
+    <x:t>SLIM BX ELECTRONICS AND TELECOMMUNICATION PARTS AND EQUIPMENT RETAILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vicencio Sagun Street, Brgy San Francisco, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIX-06389-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1360-023</x:t>
+  </x:si>
+  <x:si>
     <x:t>A &amp; B - GADGETZ CELLPHONE AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -1259,6 +1271,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1361-291</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROMEO CAPANGPANGAN DUMAOG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NA GUMAMELA, SAN CARLOS, Tukuran, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22-SROPIX-13860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1390-540</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -13825,13 +13849,13 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>61</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
         <x:v>340</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
         <x:v>341</x:v>
@@ -13843,19 +13867,19 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46046.1343634259</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>45917</x:v>
+        <x:v>46076.3755324074</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46076.3755439815</x:v>
       </x:c>
       <x:c r="J13" s="15" t="n">
-        <x:v>1216183</x:v>
+        <x:v>1216189</x:v>
       </x:c>
       <x:c r="K13" s="18" t="n">
-        <x:v>3780</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L13" s="19">
-        <x:v>46093.2878703704</x:v>
+        <x:v>46094.1653935185</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>19</x:v>
@@ -13881,19 +13905,19 @@
         <x:v>347</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46046.1309027778</x:v>
+        <x:v>46046.1343634259</x:v>
       </x:c>
       <x:c r="I14" s="17">
-        <x:v>46021</x:v>
+        <x:v>45917</x:v>
       </x:c>
       <x:c r="J14" s="15" t="n">
-        <x:v>1216181</x:v>
+        <x:v>1216183</x:v>
       </x:c>
       <x:c r="K14" s="18" t="n">
-        <x:v>5280</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L14" s="19">
-        <x:v>46093.273287037</x:v>
+        <x:v>46093.2878703704</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>19</x:v>
@@ -13904,34 +13928,34 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>344</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>348</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>349</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>350</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46046.1237615741</x:v>
+        <x:v>46046.1309027778</x:v>
       </x:c>
       <x:c r="I15" s="17">
-        <x:v>45991</x:v>
+        <x:v>46021</x:v>
       </x:c>
       <x:c r="J15" s="15" t="n">
-        <x:v>1216180</x:v>
+        <x:v>1216181</x:v>
       </x:c>
       <x:c r="K15" s="18" t="n">
-        <x:v>3780</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="L15" s="19">
-        <x:v>46093.2636342593</x:v>
+        <x:v>46093.273287037</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>19</x:v>
@@ -13942,7 +13966,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>351</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>26</x:v>
@@ -13957,19 +13981,19 @@
         <x:v>354</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46046.1140856482</x:v>
+        <x:v>46046.1237615741</x:v>
       </x:c>
       <x:c r="I16" s="17">
-        <x:v>46024</x:v>
+        <x:v>45991</x:v>
       </x:c>
       <x:c r="J16" s="15" t="n">
-        <x:v>1216182</x:v>
+        <x:v>1216180</x:v>
       </x:c>
       <x:c r="K16" s="18" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L16" s="19">
-        <x:v>46093.2825231481</x:v>
+        <x:v>46093.2636342593</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>19</x:v>
@@ -13995,19 +14019,19 @@
         <x:v>358</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46048.0974768518</x:v>
+        <x:v>46046.1140856482</x:v>
       </x:c>
       <x:c r="I17" s="17">
-        <x:v>45883</x:v>
+        <x:v>46024</x:v>
       </x:c>
       <x:c r="J17" s="15" t="n">
-        <x:v>1216184</x:v>
+        <x:v>1216182</x:v>
       </x:c>
       <x:c r="K17" s="18" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L17" s="19">
-        <x:v>46093.2926041667</x:v>
+        <x:v>46093.2825231481</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>19</x:v>
@@ -14033,19 +14057,19 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46076.318900463</x:v>
+        <x:v>46048.0974768518</x:v>
       </x:c>
       <x:c r="I18" s="17">
-        <x:v>46074</x:v>
+        <x:v>45883</x:v>
       </x:c>
       <x:c r="J18" s="15" t="n">
-        <x:v>1216168</x:v>
+        <x:v>1216184</x:v>
       </x:c>
       <x:c r="K18" s="18" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L18" s="19">
-        <x:v>46092.1400231481</x:v>
+        <x:v>46093.2926041667</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>19</x:v>
@@ -14053,7 +14077,7 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
         <x:v>363</x:v>
@@ -14071,19 +14095,19 @@
         <x:v>366</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46076.1792361111</x:v>
+        <x:v>46076.318900463</x:v>
       </x:c>
       <x:c r="I19" s="17">
-        <x:v>46058</x:v>
+        <x:v>46074</x:v>
       </x:c>
       <x:c r="J19" s="15" t="n">
-        <x:v>1216147</x:v>
+        <x:v>1216168</x:v>
       </x:c>
       <x:c r="K19" s="18" t="n">
-        <x:v>1830</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L19" s="19">
-        <x:v>46090.2042708333</x:v>
+        <x:v>46092.1400231481</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>19</x:v>
@@ -14109,19 +14133,19 @@
         <x:v>370</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46076.1139583333</x:v>
+        <x:v>46076.1792361111</x:v>
       </x:c>
       <x:c r="I20" s="17">
-        <x:v>46084</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J20" s="15" t="n">
-        <x:v>1216146</x:v>
+        <x:v>1216147</x:v>
       </x:c>
       <x:c r="K20" s="18" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L20" s="19">
-        <x:v>46090.1919444444</x:v>
+        <x:v>46090.2042708333</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
         <x:v>19</x:v>
@@ -14147,19 +14171,19 @@
         <x:v>374</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46077.2598726852</x:v>
+        <x:v>46076.1139583333</x:v>
       </x:c>
       <x:c r="I21" s="17">
-        <x:v>46058</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J21" s="15" t="n">
-        <x:v>1216158</x:v>
+        <x:v>1216146</x:v>
       </x:c>
       <x:c r="K21" s="18" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L21" s="19">
-        <x:v>46090.2758680556</x:v>
+        <x:v>46090.1919444444</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>19</x:v>
@@ -14185,19 +14209,19 @@
         <x:v>378</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46077.5191782407</x:v>
+        <x:v>46077.2598726852</x:v>
       </x:c>
       <x:c r="I22" s="17">
         <x:v>46058</x:v>
       </x:c>
       <x:c r="J22" s="15" t="n">
-        <x:v>1216163</x:v>
+        <x:v>1216158</x:v>
       </x:c>
       <x:c r="K22" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L22" s="19">
-        <x:v>46090.3154976852</x:v>
+        <x:v>46090.2758680556</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
         <x:v>19</x:v>
@@ -14208,34 +14232,34 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>375</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E23" s="14" t="s">
-        <x:v>379</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="F23" s="14" t="s">
-        <x:v>380</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="G23" s="14" t="s">
-        <x:v>381</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46077.4722337963</x:v>
+        <x:v>46077.5191782407</x:v>
       </x:c>
       <x:c r="I23" s="17">
-        <x:v>46030</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J23" s="15" t="n">
-        <x:v>1216161</x:v>
+        <x:v>1216163</x:v>
       </x:c>
       <x:c r="K23" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L23" s="19">
-        <x:v>46090.2963078704</x:v>
+        <x:v>46090.3154976852</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>19</x:v>
@@ -14246,34 +14270,34 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>375</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="D24" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E24" s="14" t="s">
-        <x:v>382</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="F24" s="14" t="s">
-        <x:v>383</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="G24" s="14" t="s">
-        <x:v>384</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="H24" s="16">
-        <x:v>46077.2024189815</x:v>
+        <x:v>46077.4722337963</x:v>
       </x:c>
       <x:c r="I24" s="17">
-        <x:v>45948</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J24" s="15" t="n">
-        <x:v>1216154</x:v>
+        <x:v>1216161</x:v>
       </x:c>
       <x:c r="K24" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L24" s="19">
-        <x:v>46090.2495949074</x:v>
+        <x:v>46090.2963078704</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
         <x:v>19</x:v>
@@ -14284,34 +14308,34 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>124</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="D25" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="E25" s="14" t="s">
-        <x:v>125</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="F25" s="14" t="s">
-        <x:v>385</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="G25" s="14" t="s">
-        <x:v>386</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="H25" s="16">
-        <x:v>45988.1893402778</x:v>
+        <x:v>46077.2024189815</x:v>
       </x:c>
       <x:c r="I25" s="17">
-        <x:v>45973</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J25" s="15" t="n">
-        <x:v>1216173</x:v>
+        <x:v>1216154</x:v>
       </x:c>
       <x:c r="K25" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L25" s="19">
-        <x:v>46093.1383912037</x:v>
+        <x:v>46090.2495949074</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
         <x:v>19</x:v>
@@ -14319,14 +14343,16 @@
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B26" s="14" t="s">
-        <x:v>90</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C26" s="14" t="s">
-        <x:v>387</x:v>
-      </x:c>
-      <x:c r="D26" s="15" t="s"/>
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
       <x:c r="E26" s="14" t="s">
-        <x:v>388</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F26" s="14" t="s">
         <x:v>389</x:v>
@@ -14335,19 +14361,19 @@
         <x:v>390</x:v>
       </x:c>
       <x:c r="H26" s="16">
-        <x:v>46090.2854050926</x:v>
-      </x:c>
-      <x:c r="I26" s="16">
-        <x:v>46090.2854282407</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="s">
-        <x:v>390</x:v>
+        <x:v>45988.1893402778</x:v>
+      </x:c>
+      <x:c r="I26" s="17">
+        <x:v>45973</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="n">
+        <x:v>1216173</x:v>
       </x:c>
       <x:c r="K26" s="18" t="n">
-        <x:v>426</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L26" s="19">
-        <x:v>46094.0865740741</x:v>
+        <x:v>46093.1383912037</x:v>
       </x:c>
       <x:c r="M26" s="14" t="s">
         <x:v>19</x:v>
@@ -14371,19 +14397,19 @@
         <x:v>394</x:v>
       </x:c>
       <x:c r="H27" s="16">
-        <x:v>46090.2540972222</x:v>
+        <x:v>46090.2854050926</x:v>
       </x:c>
       <x:c r="I27" s="16">
-        <x:v>46090.2541203704</x:v>
-      </x:c>
-      <x:c r="J27" s="15" t="n">
-        <x:v>1216185</x:v>
+        <x:v>46090.2854282407</x:v>
+      </x:c>
+      <x:c r="J27" s="15" t="s">
+        <x:v>394</x:v>
       </x:c>
       <x:c r="K27" s="18" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L27" s="19">
-        <x:v>46094.0818981481</x:v>
+        <x:v>46094.0865740741</x:v>
       </x:c>
       <x:c r="M27" s="14" t="s">
         <x:v>19</x:v>
@@ -14398,28 +14424,28 @@
       </x:c>
       <x:c r="D28" s="15" t="s"/>
       <x:c r="E28" s="14" t="s">
-        <x:v>392</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="F28" s="14" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="G28" s="14" t="s">
-        <x:v>397</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="H28" s="16">
-        <x:v>46090.2349189815</x:v>
+        <x:v>46090.2540972222</x:v>
       </x:c>
       <x:c r="I28" s="16">
-        <x:v>46090.2349305556</x:v>
+        <x:v>46090.2541203704</x:v>
       </x:c>
       <x:c r="J28" s="15" t="n">
-        <x:v>1216187</x:v>
+        <x:v>1216185</x:v>
       </x:c>
       <x:c r="K28" s="18" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L28" s="19">
-        <x:v>46094.0939351852</x:v>
+        <x:v>46094.0818981481</x:v>
       </x:c>
       <x:c r="M28" s="14" t="s">
         <x:v>19</x:v>
@@ -14427,16 +14453,14 @@
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B29" s="14" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C29" s="14" t="s">
-        <x:v>398</x:v>
-      </x:c>
-      <x:c r="D29" s="15" t="s">
-        <x:v>26</x:v>
-      </x:c>
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="s"/>
       <x:c r="E29" s="14" t="s">
-        <x:v>399</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="F29" s="14" t="s">
         <x:v>400</x:v>
@@ -14445,19 +14469,19 @@
         <x:v>401</x:v>
       </x:c>
       <x:c r="H29" s="16">
-        <x:v>46077.2103587963</x:v>
-      </x:c>
-      <x:c r="I29" s="17">
-        <x:v>46042</x:v>
+        <x:v>46090.2349189815</x:v>
+      </x:c>
+      <x:c r="I29" s="16">
+        <x:v>46090.2349305556</x:v>
       </x:c>
       <x:c r="J29" s="15" t="n">
-        <x:v>1216155</x:v>
+        <x:v>1216187</x:v>
       </x:c>
       <x:c r="K29" s="18" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L29" s="19">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46094.0939351852</x:v>
       </x:c>
       <x:c r="M29" s="14" t="s">
         <x:v>19</x:v>
@@ -14483,19 +14507,19 @@
         <x:v>405</x:v>
       </x:c>
       <x:c r="H30" s="16">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46077.2103587963</x:v>
       </x:c>
       <x:c r="I30" s="17">
-        <x:v>45748</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J30" s="15" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216155</x:v>
       </x:c>
       <x:c r="K30" s="18" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L30" s="19">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46090.2536226852</x:v>
       </x:c>
       <x:c r="M30" s="14" t="s">
         <x:v>19</x:v>
@@ -14521,136 +14545,210 @@
         <x:v>409</x:v>
       </x:c>
       <x:c r="H31" s="16">
-        <x:v>46077.1834259259</x:v>
+        <x:v>46077.2683564815</x:v>
       </x:c>
       <x:c r="I31" s="17">
-        <x:v>46115</x:v>
+        <x:v>45748</x:v>
       </x:c>
       <x:c r="J31" s="15" t="n">
-        <x:v>1216166</x:v>
+        <x:v>1216159</x:v>
       </x:c>
       <x:c r="K31" s="18" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L31" s="19">
-        <x:v>46091.2388773148</x:v>
+        <x:v>46090.2806018519</x:v>
       </x:c>
       <x:c r="M31" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="34" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B34" s="20" t="s">
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="D32" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="H32" s="16">
+        <x:v>46077.1834259259</x:v>
+      </x:c>
+      <x:c r="I32" s="17">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J32" s="15" t="n">
+        <x:v>1216166</x:v>
+      </x:c>
+      <x:c r="K32" s="18" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L32" s="19">
+        <x:v>46091.2388773148</x:v>
+      </x:c>
+      <x:c r="M32" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E33" s="14" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="H33" s="16">
+        <x:v>46090.3681365741</x:v>
+      </x:c>
+      <x:c r="I33" s="17">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J33" s="15" t="n">
+        <x:v>1216192</x:v>
+      </x:c>
+      <x:c r="K33" s="18" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L33" s="19">
+        <x:v>46094.182662037</x:v>
+      </x:c>
+      <x:c r="M33" s="14" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B36" s="20" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C34" s="21" t="s"/>
-      <x:c r="D34" s="21" t="s"/>
-      <x:c r="E34" s="22" t="s"/>
-      <x:c r="F34" s="22" t="s"/>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B35" s="23" t="s">
+      <x:c r="C36" s="21" t="s"/>
+      <x:c r="D36" s="21" t="s"/>
+      <x:c r="E36" s="22" t="s"/>
+      <x:c r="F36" s="22" t="s"/>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B37" s="23" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C35" s="24" t="s"/>
-      <x:c r="D35" s="24" t="s"/>
-      <x:c r="E35" s="24" t="s"/>
-      <x:c r="F35" s="25" t="s">
+      <x:c r="C37" s="24" t="s"/>
+      <x:c r="D37" s="24" t="s"/>
+      <x:c r="E37" s="24" t="s"/>
+      <x:c r="F37" s="25" t="s">
         <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="26" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C36" s="27" t="s"/>
-      <x:c r="D36" s="27" t="s"/>
-      <x:c r="E36" s="27" t="s"/>
-      <x:c r="F36" s="28" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B37" s="26" t="s">
-        <x:v>331</x:v>
-      </x:c>
-      <x:c r="C37" s="27" t="s"/>
-      <x:c r="D37" s="27" t="s"/>
-      <x:c r="E37" s="27" t="s"/>
-      <x:c r="F37" s="28" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="18" customHeight="1">
       <x:c r="B38" s="26" t="s">
-        <x:v>151</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C38" s="27" t="s"/>
       <x:c r="D38" s="27" t="s"/>
       <x:c r="E38" s="27" t="s"/>
       <x:c r="F38" s="28" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="18" customHeight="1">
       <x:c r="B39" s="26" t="s">
-        <x:v>61</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C39" s="27" t="s"/>
       <x:c r="D39" s="27" t="s"/>
       <x:c r="E39" s="27" t="s"/>
       <x:c r="F39" s="28" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="18" customHeight="1">
       <x:c r="B40" s="26" t="s">
-        <x:v>29</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C40" s="27" t="s"/>
       <x:c r="D40" s="27" t="s"/>
       <x:c r="E40" s="27" t="s"/>
       <x:c r="F40" s="28" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="18" customHeight="1">
       <x:c r="B41" s="26" t="s">
-        <x:v>90</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C41" s="27" t="s"/>
       <x:c r="D41" s="27" t="s"/>
       <x:c r="E41" s="27" t="s"/>
       <x:c r="F41" s="28" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="18" customHeight="1">
       <x:c r="B42" s="26" t="s">
-        <x:v>100</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C42" s="27" t="s"/>
       <x:c r="D42" s="27" t="s"/>
       <x:c r="E42" s="27" t="s"/>
       <x:c r="F42" s="28" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B43" s="26" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C43" s="27" t="s"/>
+      <x:c r="D43" s="27" t="s"/>
+      <x:c r="E43" s="27" t="s"/>
+      <x:c r="F43" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B43" s="29" t="s">
+    <x:row r="44" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B44" s="26" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C44" s="27" t="s"/>
+      <x:c r="D44" s="27" t="s"/>
+      <x:c r="E44" s="27" t="s"/>
+      <x:c r="F44" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B45" s="29" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C43" s="30" t="s"/>
-      <x:c r="D43" s="30" t="s"/>
-      <x:c r="E43" s="30" t="s"/>
-      <x:c r="F43" s="31" t="n">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C45" s="30" t="s"/>
+      <x:c r="D45" s="30" t="s"/>
+      <x:c r="E45" s="30" t="s"/>
+      <x:c r="F45" s="31" t="n">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
     <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
@@ -15603,9 +15701,7 @@
   <x:mergeCells count="12">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B34:F34"/>
-    <x:mergeCell ref="B35:E35"/>
-    <x:mergeCell ref="B36:E36"/>
+    <x:mergeCell ref="B36:F36"/>
     <x:mergeCell ref="B37:E37"/>
     <x:mergeCell ref="B38:E38"/>
     <x:mergeCell ref="B39:E39"/>
@@ -15613,6 +15709,8 @@
     <x:mergeCell ref="B41:E41"/>
     <x:mergeCell ref="B42:E42"/>
     <x:mergeCell ref="B43:E43"/>
+    <x:mergeCell ref="B44:E44"/>
+    <x:mergeCell ref="B45:E45"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -1078,6 +1078,15 @@
     <x:t>AB GADGETZ ELECTRONIC GADGETS TRADING</x:t>
   </x:si>
   <x:si>
+    <x:t>POBLACION, Aurora, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-110615E-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1292-941</x:t>
+  </x:si>
+  <x:si>
     <x:t>SAN PEDRO, Pagadian City (Capital), Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -1087,15 +1096,6 @@
     <x:t>61-1-2026-1293-860</x:t>
   </x:si>
   <x:si>
-    <x:t>POBLACION, Aurora, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPRR-110615E-22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-1-2026-1292-941</x:t>
-  </x:si>
-  <x:si>
     <x:t>AB- GADGETZ MOBILE PHONES AND ACCESSORIES STORE</x:t>
   </x:si>
   <x:si>
@@ -1171,6 +1171,15 @@
     <x:t>REMEGIO T. BURBURAN JR.</x:t>
   </x:si>
   <x:si>
+    <x:t>N/A N/A, POBLACION, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1077-20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1367-348</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A PUROK DAISY 2, POBLACION, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -1178,15 +1187,6 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1369-049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N/A N/A, POBLACION, Margosatubig, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MS9/FV-1077-20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-2-2026-1367-348</x:t>
   </x:si>
   <x:si>
     <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
@@ -13943,19 +13943,19 @@
         <x:v>351</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46046.1309027778</x:v>
+        <x:v>46046.1237615741</x:v>
       </x:c>
       <x:c r="I15" s="17">
-        <x:v>46021</x:v>
+        <x:v>45991</x:v>
       </x:c>
       <x:c r="J15" s="15" t="n">
-        <x:v>1216181</x:v>
+        <x:v>1216180</x:v>
       </x:c>
       <x:c r="K15" s="18" t="n">
-        <x:v>5280</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L15" s="19">
-        <x:v>46093.273287037</x:v>
+        <x:v>46093.2636342593</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>19</x:v>
@@ -13981,19 +13981,19 @@
         <x:v>354</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46046.1237615741</x:v>
+        <x:v>46046.1309027778</x:v>
       </x:c>
       <x:c r="I16" s="17">
-        <x:v>45991</x:v>
+        <x:v>46021</x:v>
       </x:c>
       <x:c r="J16" s="15" t="n">
-        <x:v>1216180</x:v>
+        <x:v>1216181</x:v>
       </x:c>
       <x:c r="K16" s="18" t="n">
-        <x:v>3780</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="L16" s="19">
-        <x:v>46093.2636342593</x:v>
+        <x:v>46093.273287037</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>19</x:v>
@@ -14247,19 +14247,19 @@
         <x:v>382</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46077.5191782407</x:v>
+        <x:v>46077.4722337963</x:v>
       </x:c>
       <x:c r="I23" s="17">
-        <x:v>46058</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J23" s="15" t="n">
-        <x:v>1216163</x:v>
+        <x:v>1216161</x:v>
       </x:c>
       <x:c r="K23" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L23" s="19">
-        <x:v>46090.3154976852</x:v>
+        <x:v>46090.2963078704</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>19</x:v>
@@ -14285,19 +14285,19 @@
         <x:v>385</x:v>
       </x:c>
       <x:c r="H24" s="16">
-        <x:v>46077.4722337963</x:v>
+        <x:v>46077.5191782407</x:v>
       </x:c>
       <x:c r="I24" s="17">
-        <x:v>46030</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J24" s="15" t="n">
-        <x:v>1216161</x:v>
+        <x:v>1216163</x:v>
       </x:c>
       <x:c r="K24" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L24" s="19">
-        <x:v>46090.2963078704</x:v>
+        <x:v>46090.3154976852</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
         <x:v>19</x:v>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -2169,7 +2169,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -2239,7 +2239,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>2</x:v>
@@ -3619,7 +3619,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -3689,7 +3689,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>39</x:v>
@@ -5455,7 +5455,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -5525,7 +5525,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>50</x:v>
@@ -7043,7 +7043,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -7113,7 +7113,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>34</x:v>
@@ -8977,7 +8977,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -9047,7 +9047,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>50</x:v>
@@ -10501,7 +10501,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -10571,7 +10571,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>50</x:v>
@@ -12034,7 +12034,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -12104,7 +12104,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>18</x:v>
@@ -13632,7 +13632,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -13702,7 +13702,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>34</x:v>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -29,12 +29,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="422">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="434">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
   <x:si>
     <x:t>REYNALDO YBAÑEZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Restricted Radiotelephone Operator's Certificate for Land Mobile Station (NEW)</x:t>
@@ -1304,7 +1340,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -1349,21 +1385,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -1373,6 +1394,13 @@
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -1623,7 +1651,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -1634,10 +1662,16 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1646,68 +1680,53 @@
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="44">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1738,60 +1757,8 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1802,76 +1769,84 @@
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -2171,18 +2146,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2200,329 +2163,341 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45875.2668402778</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>45875.2668518519</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1215854</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>45877.2327314815</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E7" s="16" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F7" s="16" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G7" s="16" t="s">
+      <x:c r="L7" s="10" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="H7" s="17">
-        <x:v>45889.2616782407</x:v>
-      </x:c>
-      <x:c r="I7" s="17">
-        <x:v>45889.2616898148</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1215867</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>45891.1582986111</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
-        <x:v>8</x:v>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="19" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="19" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
+      <x:c r="D8" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="G8" s="19" t="s">
+      <x:c r="E8" s="11" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="H8" s="20">
+      <x:c r="F8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45875.2668402778</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>45875.2668518519</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1215854</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45877.2327314815</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45889.2616782407</x:v>
+      </x:c>
+      <x:c r="I9" s="12">
+        <x:v>45889.2616898148</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1215867</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45891.1582986111</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>45889.1521064815</x:v>
       </x:c>
-      <x:c r="I8" s="21">
+      <x:c r="I10" s="17">
         <x:v>44272</x:v>
       </x:c>
-      <x:c r="J8" s="19" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1215866</x:v>
       </x:c>
-      <x:c r="K8" s="22" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L10" s="19">
         <x:v>45891.153287037</x:v>
       </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="19" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
         <x:v>45887.5652430556</x:v>
       </x:c>
-      <x:c r="I9" s="21">
+      <x:c r="I11" s="17">
         <x:v>45851</x:v>
       </x:c>
-      <x:c r="J9" s="19" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>1215872</x:v>
       </x:c>
-      <x:c r="K9" s="22" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L11" s="19">
         <x:v>45896.2365393518</x:v>
       </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C10" s="23" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D10" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="23" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F10" s="23" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G10" s="23" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H10" s="25">
+      <x:c r="M11" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
         <x:v>45891.1735648148</x:v>
       </x:c>
-      <x:c r="I10" s="26">
+      <x:c r="I12" s="17">
         <x:v>45765</x:v>
       </x:c>
-      <x:c r="J10" s="24" t="n">
+      <x:c r="J12" s="15" t="n">
         <x:v>1215865</x:v>
       </x:c>
-      <x:c r="K10" s="27" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="28">
+      <x:c r="L12" s="19">
         <x:v>45898.0611111111</x:v>
       </x:c>
-      <x:c r="M10" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C11" s="23" t="s">
+      <x:c r="M12" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D11" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="23" t="s">
+      <x:c r="E13" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>45887.5590162037</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>45888</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="n">
+        <x:v>1215870</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>45896.237962963</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F11" s="23" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G11" s="23" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H11" s="25">
-        <x:v>45887.5590162037</x:v>
-      </x:c>
-      <x:c r="I11" s="26">
-        <x:v>45888</x:v>
-      </x:c>
-      <x:c r="J11" s="24" t="n">
-        <x:v>1215870</x:v>
-      </x:c>
-      <x:c r="K11" s="27" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L11" s="28">
-        <x:v>45896.237962963</x:v>
-      </x:c>
-      <x:c r="M11" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B12" s="29" t="s"/>
-      <x:c r="C12" s="29" t="s"/>
-      <x:c r="D12" s="29" t="s"/>
-      <x:c r="E12" s="29" t="s"/>
-      <x:c r="F12" s="29" t="s"/>
-      <x:c r="G12" s="29" t="s"/>
-      <x:c r="H12" s="29" t="s"/>
-      <x:c r="I12" s="29" t="s"/>
-      <x:c r="J12" s="29" t="s"/>
-      <x:c r="K12" s="29" t="s"/>
-      <x:c r="L12" s="29" t="s"/>
-      <x:c r="M12" s="29" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B13" s="29" t="s"/>
-      <x:c r="C13" s="29" t="s"/>
-      <x:c r="D13" s="29" t="s"/>
-      <x:c r="E13" s="29" t="s"/>
-      <x:c r="F13" s="29" t="s"/>
-      <x:c r="G13" s="29" t="s"/>
-      <x:c r="H13" s="29" t="s"/>
-      <x:c r="I13" s="29" t="s"/>
-      <x:c r="J13" s="29" t="s"/>
-      <x:c r="K13" s="29" t="s"/>
-      <x:c r="L13" s="29" t="s"/>
-      <x:c r="M13" s="29" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="30" t="s">
+      <x:c r="B16" s="20" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="22" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="26" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="26" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C16" s="31" t="s"/>
-      <x:c r="D16" s="31" t="s"/>
-      <x:c r="E16" s="32" t="s"/>
-      <x:c r="F16" s="32" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="33" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C17" s="34" t="s"/>
-      <x:c r="D17" s="34" t="s"/>
-      <x:c r="E17" s="34" t="s"/>
-      <x:c r="F17" s="35" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="36" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="37" t="s"/>
-      <x:c r="D18" s="37" t="s"/>
-      <x:c r="E18" s="37" t="s"/>
-      <x:c r="F18" s="38" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="36" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C19" s="37" t="s"/>
-      <x:c r="D19" s="37" t="s"/>
-      <x:c r="E19" s="37" t="s"/>
-      <x:c r="F19" s="38" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C20" s="37" t="s"/>
-      <x:c r="D20" s="37" t="s"/>
-      <x:c r="E20" s="37" t="s"/>
-      <x:c r="F20" s="38" t="n">
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="39" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C21" s="40" t="s"/>
-      <x:c r="D21" s="40" t="s"/>
-      <x:c r="E21" s="40" t="s"/>
-      <x:c r="F21" s="41" t="n">
+      <x:c r="B21" s="29" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C21" s="30" t="s"/>
+      <x:c r="D21" s="30" t="s"/>
+      <x:c r="E21" s="30" t="s"/>
+      <x:c r="F21" s="31" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -3621,18 +3596,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -3650,724 +3613,736 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45902.1777546296</x:v>
-      </x:c>
-      <x:c r="I6" s="42">
-        <x:v>45781</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1215887</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>45911.9486574074</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C7" s="16" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D7" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="16" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F7" s="16" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H7" s="17">
-        <x:v>45915.355787037</x:v>
-      </x:c>
-      <x:c r="I7" s="43">
-        <x:v>45851</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1215901</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>2550</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>45918.2339583333</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E8" s="19" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F8" s="19" t="s">
+      <x:c r="D8" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G8" s="19" t="s">
+      <x:c r="F8" s="11" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H8" s="20">
+      <x:c r="G8" s="11" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45902.1777546296</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
+        <x:v>45781</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1215887</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45911.9486574074</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45915.355787037</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>45851</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1215901</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45918.2339583333</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>45903.3849652778</x:v>
       </x:c>
-      <x:c r="I8" s="21">
+      <x:c r="I10" s="17">
         <x:v>45916</x:v>
       </x:c>
-      <x:c r="J8" s="19" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1215886</x:v>
       </x:c>
-      <x:c r="K8" s="22" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>3150</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L10" s="19">
         <x:v>45908.2848958333</x:v>
       </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="19" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
+      <x:c r="M10" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
         <x:v>45919.4023032407</x:v>
       </x:c>
-      <x:c r="I9" s="21">
+      <x:c r="I11" s="17">
         <x:v>45926</x:v>
       </x:c>
-      <x:c r="J9" s="19" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>1215905</x:v>
       </x:c>
-      <x:c r="K9" s="22" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L11" s="19">
         <x:v>45925.945150463</x:v>
       </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="23" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C10" s="23" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D10" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="23" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F10" s="23" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G10" s="23" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H10" s="25">
+      <x:c r="M11" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
         <x:v>45918.1053935185</x:v>
       </x:c>
-      <x:c r="I10" s="26">
+      <x:c r="I12" s="17">
         <x:v>45900</x:v>
       </x:c>
-      <x:c r="J10" s="24" t="n">
+      <x:c r="J12" s="15" t="n">
         <x:v>1215910</x:v>
       </x:c>
-      <x:c r="K10" s="27" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L10" s="28">
+      <x:c r="L12" s="19">
         <x:v>45929.2194097222</x:v>
       </x:c>
-      <x:c r="M10" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="23" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C11" s="23" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D11" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="23" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F11" s="23" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G11" s="23" t="s">
+      <x:c r="M12" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H11" s="25">
+      <x:c r="C13" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
         <x:v>45908.2183449074</x:v>
       </x:c>
-      <x:c r="I11" s="26">
+      <x:c r="I13" s="17">
         <x:v>45918</x:v>
       </x:c>
-      <x:c r="J11" s="24" t="n">
+      <x:c r="J13" s="15" t="n">
         <x:v>1215894</x:v>
       </x:c>
-      <x:c r="K11" s="27" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="28">
+      <x:c r="L13" s="19">
         <x:v>45912.1906134259</x:v>
       </x:c>
-      <x:c r="M11" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C12" s="23" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D12" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="23" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F12" s="23" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G12" s="23" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H12" s="25">
+      <x:c r="M13" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
         <x:v>45908.5003472222</x:v>
       </x:c>
-      <x:c r="I12" s="26">
+      <x:c r="I14" s="17">
         <x:v>45790</x:v>
       </x:c>
-      <x:c r="J12" s="24" t="n">
+      <x:c r="J14" s="15" t="n">
         <x:v>1215888</x:v>
       </x:c>
-      <x:c r="K12" s="27" t="n">
+      <x:c r="K14" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L12" s="28">
+      <x:c r="L14" s="19">
         <x:v>45911.952650463</x:v>
       </x:c>
-      <x:c r="M12" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D13" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="23" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F13" s="23" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G13" s="23" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H13" s="25">
+      <x:c r="M14" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
         <x:v>45916.1691666667</x:v>
       </x:c>
-      <x:c r="I13" s="26">
+      <x:c r="I15" s="17">
         <x:v>45949</x:v>
       </x:c>
-      <x:c r="J13" s="24" t="n">
+      <x:c r="J15" s="15" t="n">
         <x:v>1215908</x:v>
       </x:c>
-      <x:c r="K13" s="27" t="n">
+      <x:c r="K15" s="18" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L13" s="28">
+      <x:c r="L15" s="19">
         <x:v>45929.1383449074</x:v>
       </x:c>
-      <x:c r="M13" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D14" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E14" s="23" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F14" s="23" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="G14" s="23" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="H14" s="25">
+      <x:c r="M15" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
         <x:v>45888.154375</x:v>
       </x:c>
-      <x:c r="I14" s="26">
+      <x:c r="I16" s="17">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="J14" s="24" t="n">
+      <x:c r="J16" s="15" t="n">
         <x:v>1215874</x:v>
       </x:c>
-      <x:c r="K14" s="27" t="n">
+      <x:c r="K16" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="28">
+      <x:c r="L16" s="19">
         <x:v>45902.050775463</x:v>
       </x:c>
-      <x:c r="M14" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D15" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E15" s="23" t="s">
+      <x:c r="M16" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>45924.1162962963</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
+        <x:v>45902</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="n">
+        <x:v>1215911</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>45930.063912037</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s"/>
+      <x:c r="E18" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>45919.473287037</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>45919.4732986111</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="n">
+        <x:v>1215906</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="L18" s="19">
+        <x:v>45926.2586111111</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>45911.4396296296</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>45911.4396296296</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="n">
+        <x:v>1215899</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="L19" s="19">
+        <x:v>45918.0952083333</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>45925.3972453704</x:v>
+      </x:c>
+      <x:c r="I20" s="17">
+        <x:v>47021</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="n">
+        <x:v>1215915</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L20" s="19">
+        <x:v>45930.1169560185</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>45916.1769097222</x:v>
+      </x:c>
+      <x:c r="I21" s="17">
+        <x:v>45949</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="n">
+        <x:v>1215916</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L21" s="19">
+        <x:v>45930.1671643518</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="F15" s="23" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G15" s="23" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="H15" s="25">
-        <x:v>45924.1162962963</x:v>
-      </x:c>
-      <x:c r="I15" s="26">
-        <x:v>45902</x:v>
-      </x:c>
-      <x:c r="J15" s="24" t="n">
-        <x:v>1215911</x:v>
-      </x:c>
-      <x:c r="K15" s="27" t="n">
-        <x:v>2010</x:v>
-      </x:c>
-      <x:c r="L15" s="28">
-        <x:v>45930.063912037</x:v>
-      </x:c>
-      <x:c r="M15" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="23" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="23" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F16" s="23" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="G16" s="23" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="H16" s="25">
-        <x:v>45919.473287037</x:v>
-      </x:c>
-      <x:c r="I16" s="25">
-        <x:v>45919.4732986111</x:v>
-      </x:c>
-      <x:c r="J16" s="24" t="n">
-        <x:v>1215906</x:v>
-      </x:c>
-      <x:c r="K16" s="27" t="n">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="L16" s="28">
-        <x:v>45926.2586111111</x:v>
-      </x:c>
-      <x:c r="M16" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="23" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C17" s="23" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D17" s="24" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E17" s="23" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F17" s="23" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="G17" s="23" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="H17" s="25">
-        <x:v>45911.4396296296</x:v>
-      </x:c>
-      <x:c r="I17" s="25">
-        <x:v>45911.4396296296</x:v>
-      </x:c>
-      <x:c r="J17" s="24" t="n">
-        <x:v>1215899</x:v>
-      </x:c>
-      <x:c r="K17" s="27" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L17" s="28">
-        <x:v>45918.0952083333</x:v>
-      </x:c>
-      <x:c r="M17" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="23" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C18" s="23" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E18" s="23" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F18" s="23" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G18" s="23" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H18" s="25">
-        <x:v>45925.3972453704</x:v>
-      </x:c>
-      <x:c r="I18" s="26">
-        <x:v>47021</x:v>
-      </x:c>
-      <x:c r="J18" s="24" t="n">
-        <x:v>1215915</x:v>
-      </x:c>
-      <x:c r="K18" s="27" t="n">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="L18" s="28">
-        <x:v>45930.1169560185</x:v>
-      </x:c>
-      <x:c r="M18" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C19" s="23" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E19" s="23" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F19" s="23" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G19" s="23" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H19" s="25">
-        <x:v>45916.1769097222</x:v>
-      </x:c>
-      <x:c r="I19" s="26">
-        <x:v>45949</x:v>
-      </x:c>
-      <x:c r="J19" s="24" t="n">
-        <x:v>1215916</x:v>
-      </x:c>
-      <x:c r="K19" s="27" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L19" s="28">
-        <x:v>45930.1671643518</x:v>
-      </x:c>
-      <x:c r="M19" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="23" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C20" s="23" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D20" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E20" s="23" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F20" s="23" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="G20" s="23" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="H20" s="25">
+      <x:c r="F22" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
         <x:v>45912.47375</x:v>
       </x:c>
-      <x:c r="I20" s="26">
+      <x:c r="I22" s="17">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J20" s="24" t="n">
+      <x:c r="J22" s="15" t="n">
         <x:v>1215898</x:v>
       </x:c>
-      <x:c r="K20" s="27" t="n">
+      <x:c r="K22" s="18" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L20" s="28">
+      <x:c r="L22" s="19">
         <x:v>45918.0905787037</x:v>
       </x:c>
-      <x:c r="M20" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B21" s="29" t="s"/>
-      <x:c r="C21" s="29" t="s"/>
-      <x:c r="D21" s="29" t="s"/>
-      <x:c r="E21" s="29" t="s"/>
-      <x:c r="F21" s="29" t="s"/>
-      <x:c r="G21" s="29" t="s"/>
-      <x:c r="H21" s="29" t="s"/>
-      <x:c r="I21" s="29" t="s"/>
-      <x:c r="J21" s="29" t="s"/>
-      <x:c r="K21" s="29" t="s"/>
-      <x:c r="L21" s="29" t="s"/>
-      <x:c r="M21" s="29" t="s"/>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B22" s="29" t="s"/>
-      <x:c r="C22" s="29" t="s"/>
-      <x:c r="D22" s="29" t="s"/>
-      <x:c r="E22" s="29" t="s"/>
-      <x:c r="F22" s="29" t="s"/>
-      <x:c r="G22" s="29" t="s"/>
-      <x:c r="H22" s="29" t="s"/>
-      <x:c r="I22" s="29" t="s"/>
-      <x:c r="J22" s="29" t="s"/>
-      <x:c r="K22" s="29" t="s"/>
-      <x:c r="L22" s="29" t="s"/>
-      <x:c r="M22" s="29" t="s"/>
+      <x:c r="M22" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="30" t="s">
+      <x:c r="B25" s="20" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C25" s="21" t="s"/>
+      <x:c r="D25" s="21" t="s"/>
+      <x:c r="E25" s="22" t="s"/>
+      <x:c r="F25" s="22" t="s"/>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B26" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C26" s="24" t="s"/>
+      <x:c r="D26" s="24" t="s"/>
+      <x:c r="E26" s="24" t="s"/>
+      <x:c r="F26" s="25" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="26" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C27" s="27" t="s"/>
+      <x:c r="D27" s="27" t="s"/>
+      <x:c r="E27" s="27" t="s"/>
+      <x:c r="F27" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="26" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C28" s="27" t="s"/>
+      <x:c r="D28" s="27" t="s"/>
+      <x:c r="E28" s="27" t="s"/>
+      <x:c r="F28" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="26" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C29" s="27" t="s"/>
+      <x:c r="D29" s="27" t="s"/>
+      <x:c r="E29" s="27" t="s"/>
+      <x:c r="F29" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="26" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C30" s="27" t="s"/>
+      <x:c r="D30" s="27" t="s"/>
+      <x:c r="E30" s="27" t="s"/>
+      <x:c r="F30" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="26" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C25" s="31" t="s"/>
-      <x:c r="D25" s="31" t="s"/>
-      <x:c r="E25" s="32" t="s"/>
-      <x:c r="F25" s="32" t="s"/>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="33" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C26" s="34" t="s"/>
-      <x:c r="D26" s="34" t="s"/>
-      <x:c r="E26" s="34" t="s"/>
-      <x:c r="F26" s="35" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="36" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C27" s="37" t="s"/>
-      <x:c r="D27" s="37" t="s"/>
-      <x:c r="E27" s="37" t="s"/>
-      <x:c r="F27" s="38" t="n">
+      <x:c r="C31" s="27" t="s"/>
+      <x:c r="D31" s="27" t="s"/>
+      <x:c r="E31" s="27" t="s"/>
+      <x:c r="F31" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="26" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="36" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C28" s="37" t="s"/>
-      <x:c r="D28" s="37" t="s"/>
-      <x:c r="E28" s="37" t="s"/>
-      <x:c r="F28" s="38" t="n">
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="26" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C33" s="27" t="s"/>
+      <x:c r="D33" s="27" t="s"/>
+      <x:c r="E33" s="27" t="s"/>
+      <x:c r="F33" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="36" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C29" s="37" t="s"/>
-      <x:c r="D29" s="37" t="s"/>
-      <x:c r="E29" s="37" t="s"/>
-      <x:c r="F29" s="38" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="36" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C30" s="37" t="s"/>
-      <x:c r="D30" s="37" t="s"/>
-      <x:c r="E30" s="37" t="s"/>
-      <x:c r="F30" s="38" t="n">
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="26" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C34" s="27" t="s"/>
+      <x:c r="D34" s="27" t="s"/>
+      <x:c r="E34" s="27" t="s"/>
+      <x:c r="F34" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C31" s="37" t="s"/>
-      <x:c r="D31" s="37" t="s"/>
-      <x:c r="E31" s="37" t="s"/>
-      <x:c r="F31" s="38" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="36" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C32" s="37" t="s"/>
-      <x:c r="D32" s="37" t="s"/>
-      <x:c r="E32" s="37" t="s"/>
-      <x:c r="F32" s="38" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="36" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="C33" s="37" t="s"/>
-      <x:c r="D33" s="37" t="s"/>
-      <x:c r="E33" s="37" t="s"/>
-      <x:c r="F33" s="38" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="36" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C34" s="37" t="s"/>
-      <x:c r="D34" s="37" t="s"/>
-      <x:c r="E34" s="37" t="s"/>
-      <x:c r="F34" s="38" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
     <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="39" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C35" s="40" t="s"/>
-      <x:c r="D35" s="40" t="s"/>
-      <x:c r="E35" s="40" t="s"/>
-      <x:c r="F35" s="41" t="n">
+      <x:c r="B35" s="29" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C35" s="30" t="s"/>
+      <x:c r="D35" s="30" t="s"/>
+      <x:c r="E35" s="30" t="s"/>
+      <x:c r="F35" s="31" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -5457,18 +5432,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -5486,470 +5449,482 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45938.0053703704</x:v>
-      </x:c>
-      <x:c r="I6" s="42">
-        <x:v>45942</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1215952</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>45945.1196180556</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C7" s="16" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D7" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="16" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="F7" s="16" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="H7" s="17">
-        <x:v>45933.0884375</x:v>
-      </x:c>
-      <x:c r="I7" s="43">
-        <x:v>45932</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1215922</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>45936.014837963</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E8" s="19" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="G8" s="19" t="s">
+      <x:c r="C8" s="11" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H8" s="20">
+      <x:c r="D8" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45938.0053703704</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
+        <x:v>45942</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1215952</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45945.1196180556</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45933.0884375</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>45932</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1215922</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45936.014837963</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>45947.5768287037</x:v>
       </x:c>
-      <x:c r="I8" s="21">
+      <x:c r="I10" s="17">
         <x:v>43437</x:v>
       </x:c>
-      <x:c r="J8" s="19" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1215960</x:v>
       </x:c>
-      <x:c r="K8" s="22" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>17766</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L10" s="19">
         <x:v>45954.2191782407</x:v>
       </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="19" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s"/>
-      <x:c r="H9" s="20">
+      <x:c r="M10" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s"/>
+      <x:c r="H11" s="16">
         <x:v>45925.0601967593</x:v>
       </x:c>
-      <x:c r="I9" s="21">
+      <x:c r="I11" s="17">
         <x:v>45922</x:v>
       </x:c>
-      <x:c r="J9" s="19" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>1215919</x:v>
       </x:c>
-      <x:c r="K9" s="22" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L11" s="19">
         <x:v>45933.3037152778</x:v>
       </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C10" s="23" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="D10" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="23" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F10" s="23" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="G10" s="23" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="H10" s="25">
+      <x:c r="M11" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
         <x:v>45912.3032407407</x:v>
       </x:c>
-      <x:c r="I10" s="26">
+      <x:c r="I12" s="17">
         <x:v>45879</x:v>
       </x:c>
-      <x:c r="J10" s="24" t="n">
+      <x:c r="J12" s="15" t="n">
         <x:v>1215920</x:v>
       </x:c>
-      <x:c r="K10" s="27" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>4710</x:v>
       </x:c>
-      <x:c r="L10" s="28">
+      <x:c r="L12" s="19">
         <x:v>45933.3105324074</x:v>
       </x:c>
-      <x:c r="M10" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C11" s="23" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="D11" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="23" t="s">
+      <x:c r="M12" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>45931.5665277778</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46297</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="n">
+        <x:v>1215945</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>45940.1382060185</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="F11" s="23" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G11" s="23" t="s">
+      <x:c r="C14" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s"/>
+      <x:c r="E14" s="14" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>45928.9304513889</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>45928.9304861111</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="n">
+        <x:v>1215924</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>45938.0359375</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="H11" s="25">
-        <x:v>45931.5665277778</x:v>
-      </x:c>
-      <x:c r="I11" s="26">
-        <x:v>46297</x:v>
-      </x:c>
-      <x:c r="J11" s="24" t="n">
-        <x:v>1215945</x:v>
-      </x:c>
-      <x:c r="K11" s="27" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L11" s="28">
-        <x:v>45940.1382060185</x:v>
-      </x:c>
-      <x:c r="M11" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C12" s="23" t="s">
+      <x:c r="D15" s="15" t="s"/>
+      <x:c r="E15" s="14" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="23" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F12" s="23" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G12" s="23" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="H12" s="25">
-        <x:v>45928.9304513889</x:v>
-      </x:c>
-      <x:c r="I12" s="25">
-        <x:v>45928.9304861111</x:v>
-      </x:c>
-      <x:c r="J12" s="24" t="n">
-        <x:v>1215924</x:v>
-      </x:c>
-      <x:c r="K12" s="27" t="n">
+      <x:c r="F15" s="14" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>45926.4563888889</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>45926.4564351852</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="n">
+        <x:v>1215917</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L12" s="28">
-        <x:v>45938.0359375</x:v>
-      </x:c>
-      <x:c r="M12" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="23" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="F13" s="23" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="G13" s="23" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H13" s="25">
-        <x:v>45926.4563888889</x:v>
-      </x:c>
-      <x:c r="I13" s="25">
-        <x:v>45926.4564351852</x:v>
-      </x:c>
-      <x:c r="J13" s="24" t="n">
-        <x:v>1215917</x:v>
-      </x:c>
-      <x:c r="K13" s="27" t="n">
-        <x:v>456</x:v>
-      </x:c>
-      <x:c r="L13" s="28">
+      <x:c r="L15" s="19">
         <x:v>45932.239537037</x:v>
       </x:c>
-      <x:c r="M13" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D14" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E14" s="23" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="F14" s="23" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="G14" s="23" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="H14" s="25">
+      <x:c r="M15" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
         <x:v>45945.2727662037</x:v>
       </x:c>
-      <x:c r="I14" s="26">
+      <x:c r="I16" s="17">
         <x:v>45911</x:v>
       </x:c>
-      <x:c r="J14" s="24" t="n">
+      <x:c r="J16" s="15" t="n">
         <x:v>1215958</x:v>
       </x:c>
-      <x:c r="K14" s="27" t="n">
+      <x:c r="K16" s="18" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L14" s="28">
+      <x:c r="L16" s="19">
         <x:v>45953.151099537</x:v>
       </x:c>
-      <x:c r="M14" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B15" s="29" t="s"/>
-      <x:c r="C15" s="29" t="s"/>
-      <x:c r="D15" s="29" t="s"/>
-      <x:c r="E15" s="29" t="s"/>
-      <x:c r="F15" s="29" t="s"/>
-      <x:c r="G15" s="29" t="s"/>
-      <x:c r="H15" s="29" t="s"/>
-      <x:c r="I15" s="29" t="s"/>
-      <x:c r="J15" s="29" t="s"/>
-      <x:c r="K15" s="29" t="s"/>
-      <x:c r="L15" s="29" t="s"/>
-      <x:c r="M15" s="29" t="s"/>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B16" s="29" t="s"/>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="29" t="s"/>
-      <x:c r="G16" s="29" t="s"/>
-      <x:c r="H16" s="29" t="s"/>
-      <x:c r="I16" s="29" t="s"/>
-      <x:c r="J16" s="29" t="s"/>
-      <x:c r="K16" s="29" t="s"/>
-      <x:c r="L16" s="29" t="s"/>
-      <x:c r="M16" s="29" t="s"/>
+      <x:c r="M16" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="30" t="s">
+      <x:c r="B19" s="20" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C19" s="21" t="s"/>
+      <x:c r="D19" s="21" t="s"/>
+      <x:c r="E19" s="22" t="s"/>
+      <x:c r="F19" s="22" t="s"/>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B20" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C20" s="24" t="s"/>
+      <x:c r="D20" s="24" t="s"/>
+      <x:c r="E20" s="24" t="s"/>
+      <x:c r="F20" s="25" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="26" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="26" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="26" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="26" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C19" s="31" t="s"/>
-      <x:c r="D19" s="31" t="s"/>
-      <x:c r="E19" s="32" t="s"/>
-      <x:c r="F19" s="32" t="s"/>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="33" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C20" s="34" t="s"/>
-      <x:c r="D20" s="34" t="s"/>
-      <x:c r="E20" s="34" t="s"/>
-      <x:c r="F20" s="35" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="36" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C21" s="37" t="s"/>
-      <x:c r="D21" s="37" t="s"/>
-      <x:c r="E21" s="37" t="s"/>
-      <x:c r="F21" s="38" t="n">
+      <x:c r="C24" s="27" t="s"/>
+      <x:c r="D24" s="27" t="s"/>
+      <x:c r="E24" s="27" t="s"/>
+      <x:c r="F24" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="26" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C25" s="27" t="s"/>
+      <x:c r="D25" s="27" t="s"/>
+      <x:c r="E25" s="27" t="s"/>
+      <x:c r="F25" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="26" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C26" s="27" t="s"/>
+      <x:c r="D26" s="27" t="s"/>
+      <x:c r="E26" s="27" t="s"/>
+      <x:c r="F26" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="36" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C22" s="37" t="s"/>
-      <x:c r="D22" s="37" t="s"/>
-      <x:c r="E22" s="37" t="s"/>
-      <x:c r="F22" s="38" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="36" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="C23" s="37" t="s"/>
-      <x:c r="D23" s="37" t="s"/>
-      <x:c r="E23" s="37" t="s"/>
-      <x:c r="F23" s="38" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C24" s="37" t="s"/>
-      <x:c r="D24" s="37" t="s"/>
-      <x:c r="E24" s="37" t="s"/>
-      <x:c r="F24" s="38" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="36" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C25" s="37" t="s"/>
-      <x:c r="D25" s="37" t="s"/>
-      <x:c r="E25" s="37" t="s"/>
-      <x:c r="F25" s="38" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="36" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C26" s="37" t="s"/>
-      <x:c r="D26" s="37" t="s"/>
-      <x:c r="E26" s="37" t="s"/>
-      <x:c r="F26" s="38" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
     <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="39" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C27" s="40" t="s"/>
-      <x:c r="D27" s="40" t="s"/>
-      <x:c r="E27" s="40" t="s"/>
-      <x:c r="F27" s="41" t="n">
+      <x:c r="B27" s="29" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C27" s="30" t="s"/>
+      <x:c r="D27" s="30" t="s"/>
+      <x:c r="E27" s="30" t="s"/>
+      <x:c r="F27" s="31" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -7045,18 +7020,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -7074,825 +7037,837 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45954.1265625</x:v>
-      </x:c>
-      <x:c r="I6" s="42">
-        <x:v>45626</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1215975</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>45967.0018287037</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C7" s="16" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="D7" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="16" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="F7" s="16" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="H7" s="17">
-        <x:v>45965.2541435185</x:v>
-      </x:c>
-      <x:c r="I7" s="43">
-        <x:v>45971</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1215995</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>45971.1502199074</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="G8" s="19" t="s">
+      <x:c r="B8" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="H8" s="20">
+      <x:c r="D8" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45954.1265625</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
+        <x:v>45626</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1215975</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45967.0018287037</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45965.2541435185</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>45971</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1215995</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>45971.1502199074</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>45965.2736689815</x:v>
       </x:c>
-      <x:c r="I8" s="20">
+      <x:c r="I10" s="16">
         <x:v>45965.2736921296</x:v>
       </x:c>
-      <x:c r="J8" s="19" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1216000</x:v>
       </x:c>
-      <x:c r="K8" s="22" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L10" s="19">
         <x:v>45972.1539583333</x:v>
       </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="19" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
+      <x:c r="M10" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
         <x:v>45965.2661458333</x:v>
       </x:c>
-      <x:c r="I9" s="21">
+      <x:c r="I11" s="17">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J9" s="19" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>1215999</x:v>
       </x:c>
-      <x:c r="K9" s="22" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L11" s="19">
         <x:v>45972.1364236111</x:v>
       </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="23" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C10" s="23" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="D10" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="23" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="F10" s="23" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="G10" s="23" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="H10" s="25">
+      <x:c r="M11" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
         <x:v>45953.5328240741</x:v>
       </x:c>
-      <x:c r="I10" s="26">
+      <x:c r="I12" s="17">
         <x:v>45969</x:v>
       </x:c>
-      <x:c r="J10" s="24" t="n">
+      <x:c r="J12" s="15" t="n">
         <x:v>1215970</x:v>
       </x:c>
-      <x:c r="K10" s="27" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L10" s="28">
+      <x:c r="L12" s="19">
         <x:v>45966.0458101852</x:v>
       </x:c>
-      <x:c r="M10" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="23" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C11" s="23" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="D11" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="23" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="F11" s="23" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="G11" s="23" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="H11" s="25">
+      <x:c r="M12" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
         <x:v>45958.0724421296</x:v>
       </x:c>
-      <x:c r="I11" s="26">
+      <x:c r="I13" s="17">
         <x:v>45810</x:v>
       </x:c>
-      <x:c r="J11" s="24" t="n">
+      <x:c r="J13" s="15" t="n">
         <x:v>1216003</x:v>
       </x:c>
-      <x:c r="K11" s="27" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L11" s="28">
+      <x:c r="L13" s="19">
         <x:v>45973.0584490741</x:v>
       </x:c>
-      <x:c r="M11" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="C12" s="23" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="D12" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="23" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="F12" s="23" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="G12" s="23" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="H12" s="25">
+      <x:c r="M13" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
         <x:v>45973.1309375</x:v>
       </x:c>
-      <x:c r="I12" s="26">
+      <x:c r="I14" s="17">
         <x:v>45950</x:v>
       </x:c>
-      <x:c r="J12" s="24" t="n">
+      <x:c r="J14" s="15" t="n">
         <x:v>1216020</x:v>
       </x:c>
-      <x:c r="K12" s="27" t="n">
+      <x:c r="K14" s="18" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L12" s="28">
+      <x:c r="L14" s="19">
         <x:v>45985.2116666667</x:v>
       </x:c>
-      <x:c r="M12" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="D13" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="23" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="F13" s="23" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="G13" s="23" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="H13" s="25">
+      <x:c r="M14" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
         <x:v>45971.2436226852</x:v>
       </x:c>
-      <x:c r="I13" s="26">
+      <x:c r="I15" s="17">
         <x:v>45608</x:v>
       </x:c>
-      <x:c r="J13" s="24" t="n">
+      <x:c r="J15" s="15" t="n">
         <x:v>1216004</x:v>
       </x:c>
-      <x:c r="K13" s="27" t="n">
+      <x:c r="K15" s="18" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L13" s="28">
+      <x:c r="L15" s="19">
         <x:v>45973.2287268518</x:v>
       </x:c>
-      <x:c r="M13" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="D14" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E14" s="23" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F14" s="23" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="G14" s="23" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="H14" s="25">
+      <x:c r="M15" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
         <x:v>45974.6184490741</x:v>
       </x:c>
-      <x:c r="I14" s="26">
+      <x:c r="I16" s="17">
         <x:v>45682</x:v>
       </x:c>
-      <x:c r="J14" s="24" t="n">
+      <x:c r="J16" s="15" t="n">
         <x:v>1216021</x:v>
       </x:c>
-      <x:c r="K14" s="27" t="n">
+      <x:c r="K16" s="18" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L14" s="28">
+      <x:c r="L16" s="19">
         <x:v>45986.0239236111</x:v>
       </x:c>
-      <x:c r="M14" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="D15" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E15" s="23" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="F15" s="23" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="G15" s="23" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="H15" s="25">
+      <x:c r="M16" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
         <x:v>45965.4411342593</x:v>
       </x:c>
-      <x:c r="I15" s="26">
+      <x:c r="I17" s="17">
         <x:v>45974</x:v>
       </x:c>
-      <x:c r="J15" s="24" t="n">
+      <x:c r="J17" s="15" t="n">
         <x:v>1216001</x:v>
       </x:c>
-      <x:c r="K15" s="27" t="n">
+      <x:c r="K17" s="18" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L15" s="28">
+      <x:c r="L17" s="19">
         <x:v>45973.0179398148</x:v>
       </x:c>
-      <x:c r="M15" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="D16" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E16" s="23" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="F16" s="23" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="G16" s="23" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="H16" s="25">
+      <x:c r="M17" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
         <x:v>45971.2507291667</x:v>
       </x:c>
-      <x:c r="I16" s="26">
+      <x:c r="I18" s="17">
         <x:v>45991</x:v>
       </x:c>
-      <x:c r="J16" s="24" t="n">
+      <x:c r="J18" s="15" t="n">
         <x:v>1216006</x:v>
       </x:c>
-      <x:c r="K16" s="27" t="n">
+      <x:c r="K18" s="18" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L16" s="28">
+      <x:c r="L18" s="19">
         <x:v>45975.0756134259</x:v>
       </x:c>
-      <x:c r="M16" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C17" s="23" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="D17" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E17" s="23" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="F17" s="23" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="G17" s="23" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="H17" s="25">
+      <x:c r="M18" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
         <x:v>45958.3516898148</x:v>
       </x:c>
-      <x:c r="I17" s="26">
+      <x:c r="I19" s="17">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J17" s="24" t="n">
+      <x:c r="J19" s="15" t="n">
         <x:v>1215976</x:v>
       </x:c>
-      <x:c r="K17" s="27" t="n">
+      <x:c r="K19" s="18" t="n">
         <x:v>3990</x:v>
       </x:c>
-      <x:c r="L17" s="28">
+      <x:c r="L19" s="19">
         <x:v>45967.2412384259</x:v>
       </x:c>
-      <x:c r="M17" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C18" s="23" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E18" s="23" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="F18" s="23" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="G18" s="23" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="H18" s="25">
+      <x:c r="M19" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
         <x:v>45954.2913425926</x:v>
       </x:c>
-      <x:c r="I18" s="26">
+      <x:c r="I20" s="17">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J18" s="24" t="n">
+      <x:c r="J20" s="15" t="n">
         <x:v>1216013</x:v>
       </x:c>
-      <x:c r="K18" s="27" t="n">
+      <x:c r="K20" s="18" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L18" s="28">
+      <x:c r="L20" s="19">
         <x:v>45975.3213541667</x:v>
       </x:c>
-      <x:c r="M18" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C19" s="23" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E19" s="23" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="F19" s="23" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="G19" s="23" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="H19" s="25">
+      <x:c r="M20" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
         <x:v>45953.3174884259</x:v>
       </x:c>
-      <x:c r="I19" s="26">
+      <x:c r="I21" s="17">
         <x:v>45911</x:v>
       </x:c>
-      <x:c r="J19" s="24" t="n">
+      <x:c r="J21" s="15" t="n">
         <x:v>1215996</x:v>
       </x:c>
-      <x:c r="K19" s="27" t="n">
+      <x:c r="K21" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L19" s="28">
+      <x:c r="L21" s="19">
         <x:v>45971.2990162037</x:v>
       </x:c>
-      <x:c r="M19" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="23" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C20" s="23" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D20" s="24" t="s"/>
-      <x:c r="E20" s="23" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="F20" s="23" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="G20" s="23" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="H20" s="25">
+      <x:c r="M21" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s"/>
+      <x:c r="E22" s="14" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
         <x:v>45954.4189930556</x:v>
       </x:c>
-      <x:c r="I20" s="25">
+      <x:c r="I22" s="16">
         <x:v>45954.4190277778</x:v>
       </x:c>
-      <x:c r="J20" s="24" t="n">
+      <x:c r="J22" s="15" t="n">
         <x:v>1215987</x:v>
       </x:c>
-      <x:c r="K20" s="27" t="n">
+      <x:c r="K22" s="18" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L20" s="28">
+      <x:c r="L22" s="19">
         <x:v>45967.2850694444</x:v>
       </x:c>
-      <x:c r="M20" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="23" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C21" s="23" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="D21" s="24" t="s"/>
-      <x:c r="E21" s="23" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="F21" s="23" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="G21" s="23" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="H21" s="25">
+      <x:c r="M22" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s"/>
+      <x:c r="E23" s="14" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
         <x:v>45959.2592013889</x:v>
       </x:c>
-      <x:c r="I21" s="25">
+      <x:c r="I23" s="16">
         <x:v>45959.259224537</x:v>
       </x:c>
-      <x:c r="J21" s="24" t="n">
+      <x:c r="J23" s="15" t="n">
         <x:v>1216022</x:v>
       </x:c>
-      <x:c r="K21" s="27" t="n">
+      <x:c r="K23" s="18" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L21" s="28">
+      <x:c r="L23" s="19">
         <x:v>45986.1291898148</x:v>
       </x:c>
-      <x:c r="M21" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="23" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C22" s="23" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="D22" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E22" s="23" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="F22" s="23" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="G22" s="23" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="H22" s="25">
+      <x:c r="M23" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
         <x:v>45966.1203125</x:v>
       </x:c>
-      <x:c r="I22" s="26">
+      <x:c r="I24" s="17">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J22" s="24" t="n">
+      <x:c r="J24" s="15" t="n">
         <x:v>1216011</x:v>
       </x:c>
-      <x:c r="K22" s="27" t="n">
+      <x:c r="K24" s="18" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L22" s="28">
+      <x:c r="L24" s="19">
         <x:v>45975.3046180556</x:v>
       </x:c>
-      <x:c r="M22" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="23" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C23" s="23" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="D23" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E23" s="23" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="F23" s="23" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="G23" s="23" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="H23" s="25">
+      <x:c r="M24" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
         <x:v>45966.1218055556</x:v>
       </x:c>
-      <x:c r="I23" s="26">
+      <x:c r="I25" s="17">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J23" s="24" t="n">
+      <x:c r="J25" s="15" t="n">
         <x:v>1216012</x:v>
       </x:c>
-      <x:c r="K23" s="27" t="n">
+      <x:c r="K25" s="18" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L23" s="28">
+      <x:c r="L25" s="19">
         <x:v>45975.312349537</x:v>
       </x:c>
-      <x:c r="M23" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B24" s="29" t="s"/>
-      <x:c r="C24" s="29" t="s"/>
-      <x:c r="D24" s="29" t="s"/>
-      <x:c r="E24" s="29" t="s"/>
-      <x:c r="F24" s="29" t="s"/>
-      <x:c r="G24" s="29" t="s"/>
-      <x:c r="H24" s="29" t="s"/>
-      <x:c r="I24" s="29" t="s"/>
-      <x:c r="J24" s="29" t="s"/>
-      <x:c r="K24" s="29" t="s"/>
-      <x:c r="L24" s="29" t="s"/>
-      <x:c r="M24" s="29" t="s"/>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B25" s="29" t="s"/>
-      <x:c r="C25" s="29" t="s"/>
-      <x:c r="D25" s="29" t="s"/>
-      <x:c r="E25" s="29" t="s"/>
-      <x:c r="F25" s="29" t="s"/>
-      <x:c r="G25" s="29" t="s"/>
-      <x:c r="H25" s="29" t="s"/>
-      <x:c r="I25" s="29" t="s"/>
-      <x:c r="J25" s="29" t="s"/>
-      <x:c r="K25" s="29" t="s"/>
-      <x:c r="L25" s="29" t="s"/>
-      <x:c r="M25" s="29" t="s"/>
+      <x:c r="M25" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="30" t="s">
+      <x:c r="B28" s="20" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C28" s="21" t="s"/>
+      <x:c r="D28" s="21" t="s"/>
+      <x:c r="E28" s="22" t="s"/>
+      <x:c r="F28" s="22" t="s"/>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B29" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C29" s="24" t="s"/>
+      <x:c r="D29" s="24" t="s"/>
+      <x:c r="E29" s="24" t="s"/>
+      <x:c r="F29" s="25" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="26" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C30" s="27" t="s"/>
+      <x:c r="D30" s="27" t="s"/>
+      <x:c r="E30" s="27" t="s"/>
+      <x:c r="F30" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="26" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C31" s="27" t="s"/>
+      <x:c r="D31" s="27" t="s"/>
+      <x:c r="E31" s="27" t="s"/>
+      <x:c r="F31" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="26" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C32" s="27" t="s"/>
+      <x:c r="D32" s="27" t="s"/>
+      <x:c r="E32" s="27" t="s"/>
+      <x:c r="F32" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="26" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="C33" s="27" t="s"/>
+      <x:c r="D33" s="27" t="s"/>
+      <x:c r="E33" s="27" t="s"/>
+      <x:c r="F33" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="26" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C28" s="31" t="s"/>
-      <x:c r="D28" s="31" t="s"/>
-      <x:c r="E28" s="32" t="s"/>
-      <x:c r="F28" s="32" t="s"/>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B29" s="33" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C29" s="34" t="s"/>
-      <x:c r="D29" s="34" t="s"/>
-      <x:c r="E29" s="34" t="s"/>
-      <x:c r="F29" s="35" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="36" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C30" s="37" t="s"/>
-      <x:c r="D30" s="37" t="s"/>
-      <x:c r="E30" s="37" t="s"/>
-      <x:c r="F30" s="38" t="n">
+      <x:c r="C34" s="27" t="s"/>
+      <x:c r="D34" s="27" t="s"/>
+      <x:c r="E34" s="27" t="s"/>
+      <x:c r="F34" s="28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="26" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C35" s="27" t="s"/>
+      <x:c r="D35" s="27" t="s"/>
+      <x:c r="E35" s="27" t="s"/>
+      <x:c r="F35" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="36" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="C31" s="37" t="s"/>
-      <x:c r="D31" s="37" t="s"/>
-      <x:c r="E31" s="37" t="s"/>
-      <x:c r="F31" s="38" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="36" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C32" s="37" t="s"/>
-      <x:c r="D32" s="37" t="s"/>
-      <x:c r="E32" s="37" t="s"/>
-      <x:c r="F32" s="38" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="36" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="C33" s="37" t="s"/>
-      <x:c r="D33" s="37" t="s"/>
-      <x:c r="E33" s="37" t="s"/>
-      <x:c r="F33" s="38" t="n">
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="26" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C36" s="27" t="s"/>
+      <x:c r="D36" s="27" t="s"/>
+      <x:c r="E36" s="27" t="s"/>
+      <x:c r="F36" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C34" s="37" t="s"/>
-      <x:c r="D34" s="37" t="s"/>
-      <x:c r="E34" s="37" t="s"/>
-      <x:c r="F34" s="38" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="36" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C35" s="37" t="s"/>
-      <x:c r="D35" s="37" t="s"/>
-      <x:c r="E35" s="37" t="s"/>
-      <x:c r="F35" s="38" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="36" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C36" s="37" t="s"/>
-      <x:c r="D36" s="37" t="s"/>
-      <x:c r="E36" s="37" t="s"/>
-      <x:c r="F36" s="38" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
     <x:row r="37" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B37" s="39" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C37" s="40" t="s"/>
-      <x:c r="D37" s="40" t="s"/>
-      <x:c r="E37" s="40" t="s"/>
-      <x:c r="F37" s="41" t="n">
+      <x:c r="B37" s="29" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C37" s="30" t="s"/>
+      <x:c r="D37" s="30" t="s"/>
+      <x:c r="E37" s="30" t="s"/>
+      <x:c r="F37" s="31" t="n">
         <x:v>18</x:v>
       </x:c>
     </x:row>
@@ -8979,18 +8954,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -9008,405 +8971,417 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>45981.1374421296</x:v>
-      </x:c>
-      <x:c r="I6" s="42">
-        <x:v>45969</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216030</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>45996.1054282407</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C7" s="16" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="D7" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="16" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="F7" s="16" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="H7" s="17">
-        <x:v>45994.1029050926</x:v>
-      </x:c>
-      <x:c r="I7" s="43">
-        <x:v>45169</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1216035</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>12780</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>46006.2230439815</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
+      <x:c r="B8" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>45981.1374421296</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
+        <x:v>45969</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216030</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>45996.1054282407</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>45994.1029050926</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>45169</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1216035</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>12780</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46006.2230439815</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
+        <x:v>45973.2824074074</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>45964</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="n">
+        <x:v>1216029</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>45993.0810763889</x:v>
+      </x:c>
+      <x:c r="M10" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
+        <x:v>45988.1651388889</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>45974</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="n">
+        <x:v>1216036</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46006.2389583333</x:v>
+      </x:c>
+      <x:c r="M11" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
+        <x:v>45972.0386111111</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46337</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="n">
+        <x:v>1216033</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46006.0795717593</x:v>
+      </x:c>
+      <x:c r="M12" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
+        <x:v>45980.2173958333</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>45852</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="n">
+        <x:v>1216027</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>45992.1151851852</x:v>
+      </x:c>
+      <x:c r="M13" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
+        <x:v>45979.0549768519</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46007</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="n">
+        <x:v>1216037</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="D8" s="19" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="G8" s="19" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="H8" s="20">
-        <x:v>45973.2824074074</x:v>
-      </x:c>
-      <x:c r="I8" s="21">
-        <x:v>45964</x:v>
-      </x:c>
-      <x:c r="J8" s="19" t="n">
-        <x:v>1216029</x:v>
-      </x:c>
-      <x:c r="K8" s="22" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L8" s="20">
-        <x:v>45993.0810763889</x:v>
-      </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="19" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
-        <x:v>45988.1651388889</x:v>
-      </x:c>
-      <x:c r="I9" s="21">
-        <x:v>45974</x:v>
-      </x:c>
-      <x:c r="J9" s="19" t="n">
-        <x:v>1216036</x:v>
-      </x:c>
-      <x:c r="K9" s="22" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L9" s="20">
-        <x:v>46006.2389583333</x:v>
-      </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C10" s="23" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="D10" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="23" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="F10" s="23" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="G10" s="23" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="H10" s="25">
-        <x:v>45972.0386111111</x:v>
-      </x:c>
-      <x:c r="I10" s="26">
+      <x:c r="L14" s="19">
+        <x:v>46006.2690046296</x:v>
+      </x:c>
+      <x:c r="M14" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
+        <x:v>45972.2314236111</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
         <x:v>46337</x:v>
       </x:c>
-      <x:c r="J10" s="24" t="n">
-        <x:v>1216033</x:v>
-      </x:c>
-      <x:c r="K10" s="27" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L10" s="28">
-        <x:v>46006.0795717593</x:v>
-      </x:c>
-      <x:c r="M10" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C11" s="23" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="D11" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="23" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="F11" s="23" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="G11" s="23" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="H11" s="25">
-        <x:v>45980.2173958333</x:v>
-      </x:c>
-      <x:c r="I11" s="26">
-        <x:v>45852</x:v>
-      </x:c>
-      <x:c r="J11" s="24" t="n">
-        <x:v>1216027</x:v>
-      </x:c>
-      <x:c r="K11" s="27" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L11" s="28">
-        <x:v>45992.1151851852</x:v>
-      </x:c>
-      <x:c r="M11" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C12" s="23" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="D12" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="23" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="F12" s="23" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="G12" s="23" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="H12" s="25">
-        <x:v>45979.0549768519</x:v>
-      </x:c>
-      <x:c r="I12" s="26">
-        <x:v>46007</x:v>
-      </x:c>
-      <x:c r="J12" s="24" t="n">
-        <x:v>1216037</x:v>
-      </x:c>
-      <x:c r="K12" s="27" t="n">
+      <x:c r="J15" s="15" t="n">
+        <x:v>1216026</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L12" s="28">
-        <x:v>46006.2690046296</x:v>
-      </x:c>
-      <x:c r="M12" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="D13" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="23" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="F13" s="23" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="G13" s="23" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="H13" s="25">
-        <x:v>45972.2314236111</x:v>
-      </x:c>
-      <x:c r="I13" s="26">
-        <x:v>46337</x:v>
-      </x:c>
-      <x:c r="J13" s="24" t="n">
-        <x:v>1216026</x:v>
-      </x:c>
-      <x:c r="K13" s="27" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L13" s="28">
+      <x:c r="L15" s="19">
         <x:v>45992.0065509259</x:v>
       </x:c>
-      <x:c r="M13" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B14" s="29" t="s"/>
-      <x:c r="C14" s="29" t="s"/>
-      <x:c r="D14" s="29" t="s"/>
-      <x:c r="E14" s="29" t="s"/>
-      <x:c r="F14" s="29" t="s"/>
-      <x:c r="G14" s="29" t="s"/>
-      <x:c r="H14" s="29" t="s"/>
-      <x:c r="I14" s="29" t="s"/>
-      <x:c r="J14" s="29" t="s"/>
-      <x:c r="K14" s="29" t="s"/>
-      <x:c r="L14" s="29" t="s"/>
-      <x:c r="M14" s="29" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B15" s="29" t="s"/>
-      <x:c r="C15" s="29" t="s"/>
-      <x:c r="D15" s="29" t="s"/>
-      <x:c r="E15" s="29" t="s"/>
-      <x:c r="F15" s="29" t="s"/>
-      <x:c r="G15" s="29" t="s"/>
-      <x:c r="H15" s="29" t="s"/>
-      <x:c r="I15" s="29" t="s"/>
-      <x:c r="J15" s="29" t="s"/>
-      <x:c r="K15" s="29" t="s"/>
-      <x:c r="L15" s="29" t="s"/>
-      <x:c r="M15" s="29" t="s"/>
+      <x:c r="M15" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="30" t="s">
+      <x:c r="B18" s="20" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C18" s="21" t="s"/>
+      <x:c r="D18" s="21" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="22" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C19" s="24" t="s"/>
+      <x:c r="D19" s="24" t="s"/>
+      <x:c r="E19" s="24" t="s"/>
+      <x:c r="F19" s="25" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="26" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C18" s="31" t="s"/>
-      <x:c r="D18" s="31" t="s"/>
-      <x:c r="E18" s="32" t="s"/>
-      <x:c r="F18" s="32" t="s"/>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="33" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C19" s="34" t="s"/>
-      <x:c r="D19" s="34" t="s"/>
-      <x:c r="E19" s="34" t="s"/>
-      <x:c r="F19" s="35" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="36" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C20" s="37" t="s"/>
-      <x:c r="D20" s="37" t="s"/>
-      <x:c r="E20" s="37" t="s"/>
-      <x:c r="F20" s="38" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C21" s="37" t="s"/>
-      <x:c r="D21" s="37" t="s"/>
-      <x:c r="E21" s="37" t="s"/>
-      <x:c r="F21" s="38" t="n">
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="36" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C22" s="37" t="s"/>
-      <x:c r="D22" s="37" t="s"/>
-      <x:c r="E22" s="37" t="s"/>
-      <x:c r="F22" s="38" t="n">
+      <x:c r="B22" s="26" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="39" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C23" s="40" t="s"/>
-      <x:c r="D23" s="40" t="s"/>
-      <x:c r="E23" s="40" t="s"/>
-      <x:c r="F23" s="41" t="n">
+      <x:c r="B23" s="29" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C23" s="30" t="s"/>
+      <x:c r="D23" s="30" t="s"/>
+      <x:c r="E23" s="30" t="s"/>
+      <x:c r="F23" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -10503,18 +10478,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -10532,414 +10495,426 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46033.3509837963</x:v>
-      </x:c>
-      <x:c r="I6" s="42">
-        <x:v>46024</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216094</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46049.2368865741</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C7" s="16" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D7" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="16" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="F7" s="16" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="H7" s="17">
-        <x:v>46010.1939351852</x:v>
-      </x:c>
-      <x:c r="I7" s="43">
-        <x:v>46029</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1216062</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>3030</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>46034.111087963</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
-        <x:v>238</x:v>
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="G8" s="19" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="H8" s="20">
+      <x:c r="B8" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46033.3509837963</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
+        <x:v>46024</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216094</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46049.2368865741</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46010.1939351852</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>46029</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1216062</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46034.111087963</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>250</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>45989.0397222222</x:v>
       </x:c>
-      <x:c r="I8" s="21">
+      <x:c r="I10" s="17">
         <x:v>45597</x:v>
       </x:c>
-      <x:c r="J8" s="19" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1216078</x:v>
       </x:c>
-      <x:c r="K8" s="22" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>8280</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L10" s="19">
         <x:v>46043.2235069444</x:v>
       </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="19" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
+      <x:c r="M10" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
         <x:v>46007.1341435185</x:v>
       </x:c>
-      <x:c r="I9" s="21">
+      <x:c r="I11" s="17">
         <x:v>45942</x:v>
       </x:c>
-      <x:c r="J9" s="19" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>1216069</x:v>
       </x:c>
-      <x:c r="K9" s="22" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L11" s="19">
         <x:v>46035.3042476852</x:v>
       </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>238</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C10" s="23" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="D10" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="23" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F10" s="23" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="G10" s="23" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="H10" s="25">
+      <x:c r="M11" s="14" t="s">
+        <x:v>250</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
         <x:v>46014.1352083333</x:v>
       </x:c>
-      <x:c r="I10" s="26">
+      <x:c r="I12" s="17">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J10" s="24" t="n">
+      <x:c r="J12" s="15" t="n">
         <x:v>1216066</x:v>
       </x:c>
-      <x:c r="K10" s="27" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L10" s="28">
+      <x:c r="L12" s="19">
         <x:v>46035.0802662037</x:v>
       </x:c>
-      <x:c r="M10" s="23" t="s">
-        <x:v>238</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C11" s="23" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="D11" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="23" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="F11" s="23" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="G11" s="23" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="H11" s="25">
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
         <x:v>46014.4844097222</x:v>
       </x:c>
-      <x:c r="I11" s="26">
+      <x:c r="I13" s="17">
         <x:v>45786</x:v>
       </x:c>
-      <x:c r="J11" s="24" t="n">
+      <x:c r="J13" s="15" t="n">
         <x:v>1216060</x:v>
       </x:c>
-      <x:c r="K11" s="27" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>2430</x:v>
       </x:c>
-      <x:c r="L11" s="28">
+      <x:c r="L13" s="19">
         <x:v>46031.0514583333</x:v>
       </x:c>
-      <x:c r="M11" s="23" t="s">
-        <x:v>238</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C12" s="23" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="D12" s="24" t="s"/>
-      <x:c r="E12" s="23" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="F12" s="23" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="G12" s="23" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="H12" s="25">
+      <x:c r="M13" s="14" t="s">
+        <x:v>250</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s"/>
+      <x:c r="E14" s="14" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
         <x:v>46043.045474537</x:v>
       </x:c>
-      <x:c r="I12" s="25">
+      <x:c r="I14" s="16">
         <x:v>46043.0455092593</x:v>
       </x:c>
-      <x:c r="J12" s="24" t="n">
+      <x:c r="J14" s="15" t="n">
         <x:v>1216091</x:v>
       </x:c>
-      <x:c r="K12" s="27" t="n">
+      <x:c r="K14" s="18" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L12" s="28">
+      <x:c r="L14" s="19">
         <x:v>46048.2516435185</x:v>
       </x:c>
-      <x:c r="M12" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="D13" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="23" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="F13" s="23" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="G13" s="23" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="H13" s="25">
+      <x:c r="M14" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
         <x:v>46036.929224537</x:v>
       </x:c>
-      <x:c r="I13" s="26">
+      <x:c r="I15" s="17">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J13" s="24" t="n">
+      <x:c r="J15" s="15" t="n">
         <x:v>1216095</x:v>
       </x:c>
-      <x:c r="K13" s="27" t="n">
+      <x:c r="K15" s="18" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="L13" s="28">
+      <x:c r="L15" s="19">
         <x:v>46050.0472337963</x:v>
       </x:c>
-      <x:c r="M13" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B14" s="29" t="s"/>
-      <x:c r="C14" s="29" t="s"/>
-      <x:c r="D14" s="29" t="s"/>
-      <x:c r="E14" s="29" t="s"/>
-      <x:c r="F14" s="29" t="s"/>
-      <x:c r="G14" s="29" t="s"/>
-      <x:c r="H14" s="29" t="s"/>
-      <x:c r="I14" s="29" t="s"/>
-      <x:c r="J14" s="29" t="s"/>
-      <x:c r="K14" s="29" t="s"/>
-      <x:c r="L14" s="29" t="s"/>
-      <x:c r="M14" s="29" t="s"/>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B15" s="29" t="s"/>
-      <x:c r="C15" s="29" t="s"/>
-      <x:c r="D15" s="29" t="s"/>
-      <x:c r="E15" s="29" t="s"/>
-      <x:c r="F15" s="29" t="s"/>
-      <x:c r="G15" s="29" t="s"/>
-      <x:c r="H15" s="29" t="s"/>
-      <x:c r="I15" s="29" t="s"/>
-      <x:c r="J15" s="29" t="s"/>
-      <x:c r="K15" s="29" t="s"/>
-      <x:c r="L15" s="29" t="s"/>
-      <x:c r="M15" s="29" t="s"/>
+      <x:c r="M15" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="30" t="s">
+      <x:c r="B18" s="20" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C18" s="21" t="s"/>
+      <x:c r="D18" s="21" t="s"/>
+      <x:c r="E18" s="22" t="s"/>
+      <x:c r="F18" s="22" t="s"/>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B19" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C19" s="24" t="s"/>
+      <x:c r="D19" s="24" t="s"/>
+      <x:c r="E19" s="24" t="s"/>
+      <x:c r="F19" s="25" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="26" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C18" s="31" t="s"/>
-      <x:c r="D18" s="31" t="s"/>
-      <x:c r="E18" s="32" t="s"/>
-      <x:c r="F18" s="32" t="s"/>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="33" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C19" s="34" t="s"/>
-      <x:c r="D19" s="34" t="s"/>
-      <x:c r="E19" s="34" t="s"/>
-      <x:c r="F19" s="35" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="36" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C20" s="37" t="s"/>
-      <x:c r="D20" s="37" t="s"/>
-      <x:c r="E20" s="37" t="s"/>
-      <x:c r="F20" s="38" t="n">
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C21" s="37" t="s"/>
-      <x:c r="D21" s="37" t="s"/>
-      <x:c r="E21" s="37" t="s"/>
-      <x:c r="F21" s="38" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="36" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C22" s="37" t="s"/>
-      <x:c r="D22" s="37" t="s"/>
-      <x:c r="E22" s="37" t="s"/>
-      <x:c r="F22" s="38" t="n">
+      <x:c r="B22" s="26" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="36" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C23" s="37" t="s"/>
-      <x:c r="D23" s="37" t="s"/>
-      <x:c r="E23" s="37" t="s"/>
-      <x:c r="F23" s="38" t="n">
+      <x:c r="B23" s="26" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="39" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C24" s="40" t="s"/>
-      <x:c r="D24" s="40" t="s"/>
-      <x:c r="E24" s="40" t="s"/>
-      <x:c r="F24" s="41" t="n">
+      <x:c r="B24" s="29" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C24" s="30" t="s"/>
+      <x:c r="D24" s="30" t="s"/>
+      <x:c r="E24" s="30" t="s"/>
+      <x:c r="F24" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -12036,18 +12011,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -12065,481 +12028,493 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46051.2691319444</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46051.2691550926</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216103</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>2070</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46057.9587152778</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C7" s="16" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="D7" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="16" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="F7" s="16" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="H7" s="17">
-        <x:v>46051.1259722222</x:v>
-      </x:c>
-      <x:c r="I7" s="43">
-        <x:v>46053</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1216112</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>1470</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>46062.966400463</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="G8" s="19" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="H8" s="20">
+      <x:c r="C8" s="11" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46051.2691319444</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46051.2691550926</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216103</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>2070</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46057.9587152778</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46051.1259722222</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>46053</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1216112</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46062.966400463</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>46050.2853935185</x:v>
       </x:c>
-      <x:c r="I8" s="21">
+      <x:c r="I10" s="17">
         <x:v>45945</x:v>
       </x:c>
-      <x:c r="J8" s="19" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1216106</x:v>
       </x:c>
-      <x:c r="K8" s="22" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L10" s="19">
         <x:v>46058.0440046296</x:v>
       </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="19" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
+      <x:c r="M10" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
         <x:v>46057.2800462963</x:v>
       </x:c>
-      <x:c r="I9" s="21">
+      <x:c r="I11" s="17">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J9" s="19" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>1216117</x:v>
       </x:c>
-      <x:c r="K9" s="22" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L11" s="19">
         <x:v>46065.2796412037</x:v>
       </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C10" s="23" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="D10" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="23" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="F10" s="23" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="G10" s="23" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="H10" s="25">
+      <x:c r="M11" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
         <x:v>46057.272025463</x:v>
       </x:c>
-      <x:c r="I10" s="26">
+      <x:c r="I12" s="17">
         <x:v>46045</x:v>
       </x:c>
-      <x:c r="J10" s="24" t="n">
+      <x:c r="J12" s="15" t="n">
         <x:v>1216121</x:v>
       </x:c>
-      <x:c r="K10" s="27" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="28">
+      <x:c r="L12" s="19">
         <x:v>46065.2951388889</x:v>
       </x:c>
-      <x:c r="M10" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C11" s="23" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="D11" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E11" s="23" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="F11" s="23" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="G11" s="23" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="H11" s="25">
+      <x:c r="M12" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
         <x:v>46057.2657523148</x:v>
       </x:c>
-      <x:c r="I11" s="26">
+      <x:c r="I13" s="17">
         <x:v>46039</x:v>
       </x:c>
-      <x:c r="J11" s="24" t="n">
+      <x:c r="J13" s="15" t="n">
         <x:v>1216119</x:v>
       </x:c>
-      <x:c r="K11" s="27" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="28">
+      <x:c r="L13" s="19">
         <x:v>46065.285474537</x:v>
       </x:c>
-      <x:c r="M11" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C12" s="23" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="D12" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E12" s="23" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="F12" s="23" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="G12" s="23" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="H12" s="25">
+      <x:c r="M13" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
         <x:v>46056.1690046296</x:v>
       </x:c>
-      <x:c r="I12" s="26">
+      <x:c r="I14" s="17">
         <x:v>45716</x:v>
       </x:c>
-      <x:c r="J12" s="24" t="n">
+      <x:c r="J14" s="15" t="n">
         <x:v>1216107</x:v>
       </x:c>
-      <x:c r="K12" s="27" t="n">
+      <x:c r="K14" s="18" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L12" s="28">
+      <x:c r="L14" s="19">
         <x:v>46058.1034490741</x:v>
       </x:c>
-      <x:c r="M12" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="D13" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E13" s="23" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="F13" s="23" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="G13" s="23" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="H13" s="25">
+      <x:c r="M14" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
         <x:v>46065.2312962963</x:v>
       </x:c>
-      <x:c r="I13" s="26">
+      <x:c r="I15" s="17">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J13" s="24" t="n">
+      <x:c r="J15" s="15" t="n">
         <x:v>1216134</x:v>
       </x:c>
-      <x:c r="K13" s="27" t="n">
+      <x:c r="K15" s="18" t="n">
         <x:v>2190</x:v>
       </x:c>
-      <x:c r="L13" s="28">
+      <x:c r="L15" s="19">
         <x:v>46076.0858333333</x:v>
       </x:c>
-      <x:c r="M13" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="D14" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E14" s="23" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="F14" s="23" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="G14" s="23" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="H14" s="25">
+      <x:c r="M15" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
         <x:v>46063.0357060185</x:v>
       </x:c>
-      <x:c r="I14" s="26">
+      <x:c r="I16" s="17">
         <x:v>46066</x:v>
       </x:c>
-      <x:c r="J14" s="24" t="n">
+      <x:c r="J16" s="15" t="n">
         <x:v>1216123</x:v>
       </x:c>
-      <x:c r="K14" s="27" t="n">
+      <x:c r="K16" s="18" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L14" s="28">
+      <x:c r="L16" s="19">
         <x:v>46066.0203819444</x:v>
       </x:c>
-      <x:c r="M14" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="D15" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E15" s="23" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="F15" s="23" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="G15" s="23" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="H15" s="25">
+      <x:c r="M16" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
         <x:v>46051.2882638889</x:v>
       </x:c>
-      <x:c r="I15" s="26">
+      <x:c r="I17" s="17">
         <x:v>44445</x:v>
       </x:c>
-      <x:c r="J15" s="24" t="n">
+      <x:c r="J17" s="15" t="n">
         <x:v>1216104</x:v>
       </x:c>
-      <x:c r="K15" s="27" t="n">
+      <x:c r="K17" s="18" t="n">
         <x:v>960</x:v>
       </x:c>
-      <x:c r="L15" s="28">
+      <x:c r="L17" s="19">
         <x:v>46057.963587963</x:v>
       </x:c>
-      <x:c r="M15" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B16" s="29" t="s"/>
-      <x:c r="C16" s="29" t="s"/>
-      <x:c r="D16" s="29" t="s"/>
-      <x:c r="E16" s="29" t="s"/>
-      <x:c r="F16" s="29" t="s"/>
-      <x:c r="G16" s="29" t="s"/>
-      <x:c r="H16" s="29" t="s"/>
-      <x:c r="I16" s="29" t="s"/>
-      <x:c r="J16" s="29" t="s"/>
-      <x:c r="K16" s="29" t="s"/>
-      <x:c r="L16" s="29" t="s"/>
-      <x:c r="M16" s="29" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B17" s="29" t="s"/>
-      <x:c r="C17" s="29" t="s"/>
-      <x:c r="D17" s="29" t="s"/>
-      <x:c r="E17" s="29" t="s"/>
-      <x:c r="F17" s="29" t="s"/>
-      <x:c r="G17" s="29" t="s"/>
-      <x:c r="H17" s="29" t="s"/>
-      <x:c r="I17" s="29" t="s"/>
-      <x:c r="J17" s="29" t="s"/>
-      <x:c r="K17" s="29" t="s"/>
-      <x:c r="L17" s="29" t="s"/>
-      <x:c r="M17" s="29" t="s"/>
+      <x:c r="M17" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="30" t="s">
+      <x:c r="B20" s="20" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C20" s="21" t="s"/>
+      <x:c r="D20" s="21" t="s"/>
+      <x:c r="E20" s="22" t="s"/>
+      <x:c r="F20" s="22" t="s"/>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B21" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C21" s="24" t="s"/>
+      <x:c r="D21" s="24" t="s"/>
+      <x:c r="E21" s="24" t="s"/>
+      <x:c r="F21" s="25" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="26" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="26" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C20" s="31" t="s"/>
-      <x:c r="D20" s="31" t="s"/>
-      <x:c r="E20" s="32" t="s"/>
-      <x:c r="F20" s="32" t="s"/>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B21" s="33" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C21" s="34" t="s"/>
-      <x:c r="D21" s="34" t="s"/>
-      <x:c r="E21" s="34" t="s"/>
-      <x:c r="F21" s="35" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="36" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="C22" s="37" t="s"/>
-      <x:c r="D22" s="37" t="s"/>
-      <x:c r="E22" s="37" t="s"/>
-      <x:c r="F22" s="38" t="n">
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="26" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C24" s="27" t="s"/>
+      <x:c r="D24" s="27" t="s"/>
+      <x:c r="E24" s="27" t="s"/>
+      <x:c r="F24" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C23" s="37" t="s"/>
-      <x:c r="D23" s="37" t="s"/>
-      <x:c r="E23" s="37" t="s"/>
-      <x:c r="F23" s="38" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="36" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C24" s="37" t="s"/>
-      <x:c r="D24" s="37" t="s"/>
-      <x:c r="E24" s="37" t="s"/>
-      <x:c r="F24" s="38" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
     <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="39" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C25" s="40" t="s"/>
-      <x:c r="D25" s="40" t="s"/>
-      <x:c r="E25" s="40" t="s"/>
-      <x:c r="F25" s="41" t="n">
+      <x:c r="B25" s="29" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C25" s="30" t="s"/>
+      <x:c r="D25" s="30" t="s"/>
+      <x:c r="E25" s="30" t="s"/>
+      <x:c r="F25" s="31" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -13634,18 +13609,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -13663,1366 +13626,1378 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46065.33125</x:v>
-      </x:c>
-      <x:c r="I6" s="42">
-        <x:v>45700</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>1216139</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46084.1560763889</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C7" s="16" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="D7" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="16" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="F7" s="16" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="H7" s="17">
-        <x:v>46085.2764814815</x:v>
-      </x:c>
-      <x:c r="I7" s="43">
-        <x:v>44879</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>1216175</x:v>
-      </x:c>
-      <x:c r="K7" s="18" t="n">
-        <x:v>1290</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>46093.2000115741</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
         <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="10" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="19" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="D8" s="19" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="19" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="F8" s="19" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="G8" s="19" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="H8" s="20">
+      <x:c r="B8" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46065.33125</x:v>
+      </x:c>
+      <x:c r="I8" s="32">
+        <x:v>45700</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>1216139</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46084.1560763889</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46085.2764814815</x:v>
+      </x:c>
+      <x:c r="I9" s="32">
+        <x:v>44879</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>1216175</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>1290</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46093.2000115741</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>46065.2288541667</x:v>
       </x:c>
-      <x:c r="I8" s="21">
+      <x:c r="I10" s="17">
         <x:v>46070</x:v>
       </x:c>
-      <x:c r="J8" s="19" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>1216140</x:v>
       </x:c>
-      <x:c r="K8" s="22" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="20">
+      <x:c r="L10" s="19">
         <x:v>46084.1582175926</x:v>
       </x:c>
-      <x:c r="M8" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="19" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="19" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="F9" s="19" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="G9" s="19" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="H9" s="20">
+      <x:c r="M10" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="G11" s="14" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
         <x:v>46085.3007986111</x:v>
       </x:c>
-      <x:c r="I9" s="21">
+      <x:c r="I11" s="17">
         <x:v>46386</x:v>
       </x:c>
-      <x:c r="J9" s="19" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>1216177</x:v>
       </x:c>
-      <x:c r="K9" s="22" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L9" s="20">
+      <x:c r="L11" s="19">
         <x:v>46093.215162037</x:v>
       </x:c>
-      <x:c r="M9" s="19" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="23" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C10" s="23" t="s">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="D10" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="23" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="F10" s="23" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="G10" s="23" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="H10" s="25">
+      <x:c r="M11" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="14" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C12" s="14" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E12" s="14" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="G12" s="14" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="H12" s="16">
         <x:v>46085.2858333333</x:v>
       </x:c>
-      <x:c r="I10" s="26">
+      <x:c r="I12" s="17">
         <x:v>46096</x:v>
       </x:c>
-      <x:c r="J10" s="24" t="n">
+      <x:c r="J12" s="15" t="n">
         <x:v>1216176</x:v>
       </x:c>
-      <x:c r="K10" s="27" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L10" s="28">
+      <x:c r="L12" s="19">
         <x:v>46093.2057060185</x:v>
       </x:c>
-      <x:c r="M10" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="23" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="C11" s="23" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="D11" s="24" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E11" s="23" t="s">
-        <x:v>322</x:v>
-      </x:c>
-      <x:c r="F11" s="23" t="s">
-        <x:v>323</x:v>
-      </x:c>
-      <x:c r="G11" s="23" t="s">
-        <x:v>324</x:v>
-      </x:c>
-      <x:c r="H11" s="25">
+      <x:c r="M12" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="14" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E13" s="14" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="G13" s="14" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="H13" s="16">
         <x:v>46088.1798263889</x:v>
       </x:c>
-      <x:c r="I11" s="25">
+      <x:c r="I13" s="16">
         <x:v>46088.179837963</x:v>
       </x:c>
-      <x:c r="J11" s="24" t="n">
+      <x:c r="J13" s="15" t="n">
         <x:v>1216179</x:v>
       </x:c>
-      <x:c r="K11" s="27" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L11" s="28">
+      <x:c r="L13" s="19">
         <x:v>46093.2393865741</x:v>
       </x:c>
-      <x:c r="M11" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="23" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="C12" s="23" t="s">
-        <x:v>325</x:v>
-      </x:c>
-      <x:c r="D12" s="24" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E12" s="23" t="s">
-        <x:v>326</x:v>
-      </x:c>
-      <x:c r="F12" s="23" t="s">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c r="G12" s="23" t="s">
-        <x:v>328</x:v>
-      </x:c>
-      <x:c r="H12" s="25">
+      <x:c r="M13" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="14" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C14" s="14" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E14" s="14" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="G14" s="14" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="H14" s="16">
         <x:v>46076.2809953704</x:v>
       </x:c>
-      <x:c r="I12" s="25">
+      <x:c r="I14" s="16">
         <x:v>46076.2810185185</x:v>
       </x:c>
-      <x:c r="J12" s="24" t="n">
+      <x:c r="J14" s="15" t="n">
         <x:v>1216194</x:v>
       </x:c>
-      <x:c r="K12" s="27" t="n">
+      <x:c r="K14" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L12" s="28">
+      <x:c r="L14" s="19">
         <x:v>46097.2411111111</x:v>
       </x:c>
-      <x:c r="M12" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="23" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="C13" s="23" t="s">
-        <x:v>329</x:v>
-      </x:c>
-      <x:c r="D13" s="24" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E13" s="23" t="s">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="F13" s="23" t="s">
-        <x:v>331</x:v>
-      </x:c>
-      <x:c r="G13" s="23" t="s">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="H13" s="25">
+      <x:c r="M14" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="14" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C15" s="14" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="H15" s="16">
         <x:v>46076.2578009259</x:v>
       </x:c>
-      <x:c r="I13" s="25">
+      <x:c r="I15" s="16">
         <x:v>46076.2578240741</x:v>
       </x:c>
-      <x:c r="J13" s="24" t="n">
+      <x:c r="J15" s="15" t="n">
         <x:v>1216197</x:v>
       </x:c>
-      <x:c r="K13" s="27" t="n">
+      <x:c r="K15" s="18" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L13" s="28">
+      <x:c r="L15" s="19">
         <x:v>46097.2583912037</x:v>
       </x:c>
-      <x:c r="M13" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s">
-        <x:v>333</x:v>
-      </x:c>
-      <x:c r="D14" s="24" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E14" s="23" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="F14" s="23" t="s">
-        <x:v>335</x:v>
-      </x:c>
-      <x:c r="G14" s="23" t="s">
-        <x:v>336</x:v>
-      </x:c>
-      <x:c r="H14" s="25">
+      <x:c r="M15" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="14" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C16" s="14" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
         <x:v>46076.2633564815</x:v>
       </x:c>
-      <x:c r="I14" s="25">
+      <x:c r="I16" s="16">
         <x:v>46076.2633680556</x:v>
       </x:c>
-      <x:c r="J14" s="24" t="n">
+      <x:c r="J16" s="15" t="n">
         <x:v>1216188</x:v>
       </x:c>
-      <x:c r="K14" s="27" t="n">
+      <x:c r="K16" s="18" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L14" s="28">
+      <x:c r="L16" s="19">
         <x:v>46094.1562731481</x:v>
       </x:c>
-      <x:c r="M14" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s">
+      <x:c r="M16" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="14" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C17" s="14" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46076.3755324074</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>46076.3755439815</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="n">
+        <x:v>1216189</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>46094.1653935185</x:v>
+      </x:c>
+      <x:c r="M17" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46046.1343634259</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>45917</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="n">
+        <x:v>1216183</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L18" s="19">
+        <x:v>46093.2878703704</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46046.1309027778</x:v>
+      </x:c>
+      <x:c r="I19" s="17">
+        <x:v>46021</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="n">
+        <x:v>1216181</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>5280</x:v>
+      </x:c>
+      <x:c r="L19" s="19">
+        <x:v>46093.273287037</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46046.1237615741</x:v>
+      </x:c>
+      <x:c r="I20" s="17">
+        <x:v>45991</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="n">
+        <x:v>1216180</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L20" s="19">
+        <x:v>46093.2636342593</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46046.1140856482</x:v>
+      </x:c>
+      <x:c r="I21" s="17">
+        <x:v>46024</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="n">
+        <x:v>1216182</x:v>
+      </x:c>
+      <x:c r="K21" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L21" s="19">
+        <x:v>46093.2825231481</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46048.0974768518</x:v>
+      </x:c>
+      <x:c r="I22" s="17">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="n">
+        <x:v>1216184</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L22" s="19">
+        <x:v>46093.2926041667</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46076.318900463</x:v>
+      </x:c>
+      <x:c r="I23" s="17">
+        <x:v>46074</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="n">
+        <x:v>1216168</x:v>
+      </x:c>
+      <x:c r="K23" s="18" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L23" s="19">
+        <x:v>46092.1400231481</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
         <x:v>337</x:v>
       </x:c>
-      <x:c r="D15" s="24" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E15" s="23" t="s">
-        <x:v>338</x:v>
-      </x:c>
-      <x:c r="F15" s="23" t="s">
-        <x:v>339</x:v>
-      </x:c>
-      <x:c r="G15" s="23" t="s">
-        <x:v>340</x:v>
-      </x:c>
-      <x:c r="H15" s="25">
-        <x:v>46076.3755324074</x:v>
-      </x:c>
-      <x:c r="I15" s="25">
-        <x:v>46076.3755439815</x:v>
-      </x:c>
-      <x:c r="J15" s="24" t="n">
-        <x:v>1216189</x:v>
-      </x:c>
-      <x:c r="K15" s="27" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L15" s="28">
-        <x:v>46094.1653935185</x:v>
-      </x:c>
-      <x:c r="M15" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="23" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C16" s="23" t="s">
+      <x:c r="D24" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46079.2852546296</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
+        <x:v>46079.2852662037</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="n">
+        <x:v>1216195</x:v>
+      </x:c>
+      <x:c r="K24" s="18" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L24" s="19">
+        <x:v>46097.2459143518</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
         <x:v>341</x:v>
       </x:c>
-      <x:c r="D16" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E16" s="23" t="s">
-        <x:v>342</x:v>
-      </x:c>
-      <x:c r="F16" s="23" t="s">
-        <x:v>343</x:v>
-      </x:c>
-      <x:c r="G16" s="23" t="s">
-        <x:v>344</x:v>
-      </x:c>
-      <x:c r="H16" s="25">
-        <x:v>46046.1343634259</x:v>
-      </x:c>
-      <x:c r="I16" s="26">
-        <x:v>45917</x:v>
-      </x:c>
-      <x:c r="J16" s="24" t="n">
-        <x:v>1216183</x:v>
-      </x:c>
-      <x:c r="K16" s="27" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L16" s="28">
-        <x:v>46093.2878703704</x:v>
-      </x:c>
-      <x:c r="M16" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="23" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C17" s="23" t="s">
-        <x:v>345</x:v>
-      </x:c>
-      <x:c r="D17" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E17" s="23" t="s">
-        <x:v>346</x:v>
-      </x:c>
-      <x:c r="F17" s="23" t="s">
-        <x:v>347</x:v>
-      </x:c>
-      <x:c r="G17" s="23" t="s">
-        <x:v>348</x:v>
-      </x:c>
-      <x:c r="H17" s="25">
-        <x:v>46046.1309027778</x:v>
-      </x:c>
-      <x:c r="I17" s="26">
-        <x:v>46021</x:v>
-      </x:c>
-      <x:c r="J17" s="24" t="n">
-        <x:v>1216181</x:v>
-      </x:c>
-      <x:c r="K17" s="27" t="n">
-        <x:v>5280</x:v>
-      </x:c>
-      <x:c r="L17" s="28">
-        <x:v>46093.273287037</x:v>
-      </x:c>
-      <x:c r="M17" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="23" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C18" s="23" t="s">
-        <x:v>345</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E18" s="23" t="s">
-        <x:v>349</x:v>
-      </x:c>
-      <x:c r="F18" s="23" t="s">
-        <x:v>350</x:v>
-      </x:c>
-      <x:c r="G18" s="23" t="s">
-        <x:v>351</x:v>
-      </x:c>
-      <x:c r="H18" s="25">
-        <x:v>46046.1237615741</x:v>
-      </x:c>
-      <x:c r="I18" s="26">
-        <x:v>45991</x:v>
-      </x:c>
-      <x:c r="J18" s="24" t="n">
-        <x:v>1216180</x:v>
-      </x:c>
-      <x:c r="K18" s="27" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L18" s="28">
-        <x:v>46093.2636342593</x:v>
-      </x:c>
-      <x:c r="M18" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C19" s="23" t="s">
-        <x:v>352</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E19" s="23" t="s">
-        <x:v>353</x:v>
-      </x:c>
-      <x:c r="F19" s="23" t="s">
-        <x:v>354</x:v>
-      </x:c>
-      <x:c r="G19" s="23" t="s">
-        <x:v>355</x:v>
-      </x:c>
-      <x:c r="H19" s="25">
-        <x:v>46046.1140856482</x:v>
-      </x:c>
-      <x:c r="I19" s="26">
-        <x:v>46024</x:v>
-      </x:c>
-      <x:c r="J19" s="24" t="n">
-        <x:v>1216182</x:v>
-      </x:c>
-      <x:c r="K19" s="27" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L19" s="28">
-        <x:v>46093.2825231481</x:v>
-      </x:c>
-      <x:c r="M19" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="23" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C20" s="23" t="s">
-        <x:v>356</x:v>
-      </x:c>
-      <x:c r="D20" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E20" s="23" t="s">
-        <x:v>357</x:v>
-      </x:c>
-      <x:c r="F20" s="23" t="s">
-        <x:v>358</x:v>
-      </x:c>
-      <x:c r="G20" s="23" t="s">
-        <x:v>359</x:v>
-      </x:c>
-      <x:c r="H20" s="25">
-        <x:v>46048.0974768518</x:v>
-      </x:c>
-      <x:c r="I20" s="26">
-        <x:v>45883</x:v>
-      </x:c>
-      <x:c r="J20" s="24" t="n">
-        <x:v>1216184</x:v>
-      </x:c>
-      <x:c r="K20" s="27" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L20" s="28">
-        <x:v>46093.2926041667</x:v>
-      </x:c>
-      <x:c r="M20" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="23" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C21" s="23" t="s">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="D21" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E21" s="23" t="s">
-        <x:v>361</x:v>
-      </x:c>
-      <x:c r="F21" s="23" t="s">
-        <x:v>362</x:v>
-      </x:c>
-      <x:c r="G21" s="23" t="s">
-        <x:v>363</x:v>
-      </x:c>
-      <x:c r="H21" s="25">
-        <x:v>46076.318900463</x:v>
-      </x:c>
-      <x:c r="I21" s="26">
-        <x:v>46074</x:v>
-      </x:c>
-      <x:c r="J21" s="24" t="n">
-        <x:v>1216168</x:v>
-      </x:c>
-      <x:c r="K21" s="27" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L21" s="28">
-        <x:v>46092.1400231481</x:v>
-      </x:c>
-      <x:c r="M21" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="23" t="s">
-        <x:v>364</x:v>
-      </x:c>
-      <x:c r="C22" s="23" t="s">
-        <x:v>325</x:v>
-      </x:c>
-      <x:c r="D22" s="24" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E22" s="23" t="s">
-        <x:v>365</x:v>
-      </x:c>
-      <x:c r="F22" s="23" t="s">
-        <x:v>366</x:v>
-      </x:c>
-      <x:c r="G22" s="23" t="s">
-        <x:v>367</x:v>
-      </x:c>
-      <x:c r="H22" s="25">
-        <x:v>46079.2852546296</x:v>
-      </x:c>
-      <x:c r="I22" s="25">
-        <x:v>46079.2852662037</x:v>
-      </x:c>
-      <x:c r="J22" s="24" t="n">
-        <x:v>1216195</x:v>
-      </x:c>
-      <x:c r="K22" s="27" t="n">
+      <x:c r="D25" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46079.2747222222</x:v>
+      </x:c>
+      <x:c r="I25" s="16">
+        <x:v>46079.2747453704</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="n">
+        <x:v>1216196</x:v>
+      </x:c>
+      <x:c r="K25" s="18" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L22" s="28">
-        <x:v>46097.2459143518</x:v>
-      </x:c>
-      <x:c r="M22" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="23" t="s">
-        <x:v>364</x:v>
-      </x:c>
-      <x:c r="C23" s="23" t="s">
-        <x:v>329</x:v>
-      </x:c>
-      <x:c r="D23" s="24" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E23" s="23" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="F23" s="23" t="s">
-        <x:v>369</x:v>
-      </x:c>
-      <x:c r="G23" s="23" t="s">
-        <x:v>370</x:v>
-      </x:c>
-      <x:c r="H23" s="25">
-        <x:v>46079.2747222222</x:v>
-      </x:c>
-      <x:c r="I23" s="25">
-        <x:v>46079.2747453704</x:v>
-      </x:c>
-      <x:c r="J23" s="24" t="n">
-        <x:v>1216196</x:v>
-      </x:c>
-      <x:c r="K23" s="27" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L23" s="28">
+      <x:c r="L25" s="19">
         <x:v>46097.2536342593</x:v>
       </x:c>
-      <x:c r="M23" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C24" s="23" t="s">
-        <x:v>371</x:v>
-      </x:c>
-      <x:c r="D24" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E24" s="23" t="s">
-        <x:v>372</x:v>
-      </x:c>
-      <x:c r="F24" s="23" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="G24" s="23" t="s">
-        <x:v>374</x:v>
-      </x:c>
-      <x:c r="H24" s="25">
+      <x:c r="M25" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B26" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
         <x:v>46076.1792361111</x:v>
       </x:c>
-      <x:c r="I24" s="26">
+      <x:c r="I26" s="17">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J24" s="24" t="n">
+      <x:c r="J26" s="15" t="n">
         <x:v>1216147</x:v>
       </x:c>
-      <x:c r="K24" s="27" t="n">
+      <x:c r="K26" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L24" s="28">
+      <x:c r="L26" s="19">
         <x:v>46090.2042708333</x:v>
       </x:c>
-      <x:c r="M24" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C25" s="23" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="D25" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E25" s="23" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="F25" s="23" t="s">
-        <x:v>377</x:v>
-      </x:c>
-      <x:c r="G25" s="23" t="s">
-        <x:v>378</x:v>
-      </x:c>
-      <x:c r="H25" s="25">
+      <x:c r="M26" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B27" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="H27" s="16">
         <x:v>46076.1139583333</x:v>
       </x:c>
-      <x:c r="I25" s="26">
+      <x:c r="I27" s="17">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J25" s="24" t="n">
+      <x:c r="J27" s="15" t="n">
         <x:v>1216146</x:v>
       </x:c>
-      <x:c r="K25" s="27" t="n">
+      <x:c r="K27" s="18" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L25" s="28">
+      <x:c r="L27" s="19">
         <x:v>46090.1919444444</x:v>
       </x:c>
-      <x:c r="M25" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C26" s="23" t="s">
-        <x:v>379</x:v>
-      </x:c>
-      <x:c r="D26" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E26" s="23" t="s">
-        <x:v>380</x:v>
-      </x:c>
-      <x:c r="F26" s="23" t="s">
-        <x:v>381</x:v>
-      </x:c>
-      <x:c r="G26" s="23" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="H26" s="25">
+      <x:c r="M27" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B28" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="H28" s="16">
         <x:v>46077.2598726852</x:v>
       </x:c>
-      <x:c r="I26" s="26">
+      <x:c r="I28" s="17">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J26" s="24" t="n">
+      <x:c r="J28" s="15" t="n">
         <x:v>1216158</x:v>
       </x:c>
-      <x:c r="K26" s="27" t="n">
+      <x:c r="K28" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L26" s="28">
+      <x:c r="L28" s="19">
         <x:v>46090.2758680556</x:v>
       </x:c>
-      <x:c r="M26" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C27" s="23" t="s">
-        <x:v>383</x:v>
-      </x:c>
-      <x:c r="D27" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E27" s="23" t="s">
-        <x:v>384</x:v>
-      </x:c>
-      <x:c r="F27" s="23" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="G27" s="23" t="s">
-        <x:v>386</x:v>
-      </x:c>
-      <x:c r="H27" s="25">
+      <x:c r="M28" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B29" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="H29" s="16">
         <x:v>46077.4722337963</x:v>
       </x:c>
-      <x:c r="I27" s="26">
+      <x:c r="I29" s="17">
         <x:v>46030</x:v>
       </x:c>
-      <x:c r="J27" s="24" t="n">
+      <x:c r="J29" s="15" t="n">
         <x:v>1216161</x:v>
       </x:c>
-      <x:c r="K27" s="27" t="n">
+      <x:c r="K29" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L27" s="28">
+      <x:c r="L29" s="19">
         <x:v>46090.2963078704</x:v>
       </x:c>
-      <x:c r="M27" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C28" s="23" t="s">
-        <x:v>383</x:v>
-      </x:c>
-      <x:c r="D28" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E28" s="23" t="s">
-        <x:v>387</x:v>
-      </x:c>
-      <x:c r="F28" s="23" t="s">
-        <x:v>388</x:v>
-      </x:c>
-      <x:c r="G28" s="23" t="s">
-        <x:v>389</x:v>
-      </x:c>
-      <x:c r="H28" s="25">
+      <x:c r="M29" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B30" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="H30" s="16">
         <x:v>46077.5191782407</x:v>
       </x:c>
-      <x:c r="I28" s="26">
+      <x:c r="I30" s="17">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J28" s="24" t="n">
+      <x:c r="J30" s="15" t="n">
         <x:v>1216163</x:v>
       </x:c>
-      <x:c r="K28" s="27" t="n">
+      <x:c r="K30" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L28" s="28">
+      <x:c r="L30" s="19">
         <x:v>46090.3154976852</x:v>
       </x:c>
-      <x:c r="M28" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C29" s="23" t="s">
-        <x:v>383</x:v>
-      </x:c>
-      <x:c r="D29" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E29" s="23" t="s">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="F29" s="23" t="s">
-        <x:v>391</x:v>
-      </x:c>
-      <x:c r="G29" s="23" t="s">
-        <x:v>392</x:v>
-      </x:c>
-      <x:c r="H29" s="25">
+      <x:c r="M30" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B31" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C31" s="14" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E31" s="14" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="G31" s="14" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="H31" s="16">
         <x:v>46077.2024189815</x:v>
       </x:c>
-      <x:c r="I29" s="26">
+      <x:c r="I31" s="17">
         <x:v>45948</x:v>
       </x:c>
-      <x:c r="J29" s="24" t="n">
+      <x:c r="J31" s="15" t="n">
         <x:v>1216154</x:v>
       </x:c>
-      <x:c r="K29" s="27" t="n">
+      <x:c r="K31" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L29" s="28">
+      <x:c r="L31" s="19">
         <x:v>46090.2495949074</x:v>
       </x:c>
-      <x:c r="M29" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="23" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C30" s="23" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D30" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E30" s="23" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F30" s="23" t="s">
-        <x:v>393</x:v>
-      </x:c>
-      <x:c r="G30" s="23" t="s">
-        <x:v>394</x:v>
-      </x:c>
-      <x:c r="H30" s="25">
+      <x:c r="M31" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B32" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C32" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D32" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E32" s="14" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="G32" s="14" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="H32" s="16">
         <x:v>45988.1893402778</x:v>
       </x:c>
-      <x:c r="I30" s="26">
+      <x:c r="I32" s="17">
         <x:v>45973</x:v>
       </x:c>
-      <x:c r="J30" s="24" t="n">
+      <x:c r="J32" s="15" t="n">
         <x:v>1216173</x:v>
       </x:c>
-      <x:c r="K30" s="27" t="n">
+      <x:c r="K32" s="18" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L30" s="28">
+      <x:c r="L32" s="19">
         <x:v>46093.1383912037</x:v>
       </x:c>
-      <x:c r="M30" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="23" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C31" s="23" t="s">
-        <x:v>395</x:v>
-      </x:c>
-      <x:c r="D31" s="24" t="s"/>
-      <x:c r="E31" s="23" t="s">
-        <x:v>396</x:v>
-      </x:c>
-      <x:c r="F31" s="23" t="s">
-        <x:v>397</x:v>
-      </x:c>
-      <x:c r="G31" s="23" t="s">
-        <x:v>398</x:v>
-      </x:c>
-      <x:c r="H31" s="25">
+      <x:c r="M32" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B33" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C33" s="14" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="s"/>
+      <x:c r="E33" s="14" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="G33" s="14" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="H33" s="16">
         <x:v>46090.2854050926</x:v>
       </x:c>
-      <x:c r="I31" s="25">
+      <x:c r="I33" s="16">
         <x:v>46090.2854282407</x:v>
       </x:c>
-      <x:c r="J31" s="24" t="s">
-        <x:v>398</x:v>
-      </x:c>
-      <x:c r="K31" s="27" t="n">
+      <x:c r="J33" s="15" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="K33" s="18" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L31" s="28">
+      <x:c r="L33" s="19">
         <x:v>46094.0865740741</x:v>
       </x:c>
-      <x:c r="M31" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="23" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C32" s="23" t="s">
-        <x:v>399</x:v>
-      </x:c>
-      <x:c r="D32" s="24" t="s"/>
-      <x:c r="E32" s="23" t="s">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="F32" s="23" t="s">
-        <x:v>401</x:v>
-      </x:c>
-      <x:c r="G32" s="23" t="s">
-        <x:v>402</x:v>
-      </x:c>
-      <x:c r="H32" s="25">
+      <x:c r="M33" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B34" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C34" s="14" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="D34" s="15" t="s"/>
+      <x:c r="E34" s="14" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="G34" s="14" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="H34" s="16">
         <x:v>46090.2540972222</x:v>
       </x:c>
-      <x:c r="I32" s="25">
+      <x:c r="I34" s="16">
         <x:v>46090.2541203704</x:v>
       </x:c>
-      <x:c r="J32" s="24" t="n">
+      <x:c r="J34" s="15" t="n">
         <x:v>1216185</x:v>
       </x:c>
-      <x:c r="K32" s="27" t="n">
+      <x:c r="K34" s="18" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L32" s="28">
+      <x:c r="L34" s="19">
         <x:v>46094.0818981481</x:v>
       </x:c>
-      <x:c r="M32" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="23" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C33" s="23" t="s">
-        <x:v>403</x:v>
-      </x:c>
-      <x:c r="D33" s="24" t="s"/>
-      <x:c r="E33" s="23" t="s">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="F33" s="23" t="s">
-        <x:v>404</x:v>
-      </x:c>
-      <x:c r="G33" s="23" t="s">
-        <x:v>405</x:v>
-      </x:c>
-      <x:c r="H33" s="25">
+      <x:c r="M34" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B35" s="14" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C35" s="14" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="D35" s="15" t="s"/>
+      <x:c r="E35" s="14" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="G35" s="14" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="H35" s="16">
         <x:v>46090.2349189815</x:v>
       </x:c>
-      <x:c r="I33" s="25">
+      <x:c r="I35" s="16">
         <x:v>46090.2349305556</x:v>
       </x:c>
-      <x:c r="J33" s="24" t="n">
+      <x:c r="J35" s="15" t="n">
         <x:v>1216187</x:v>
       </x:c>
-      <x:c r="K33" s="27" t="n">
+      <x:c r="K35" s="18" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L33" s="28">
+      <x:c r="L35" s="19">
         <x:v>46094.0939351852</x:v>
       </x:c>
-      <x:c r="M33" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="23" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C34" s="23" t="s">
-        <x:v>406</x:v>
-      </x:c>
-      <x:c r="D34" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E34" s="23" t="s">
-        <x:v>407</x:v>
-      </x:c>
-      <x:c r="F34" s="23" t="s">
-        <x:v>408</x:v>
-      </x:c>
-      <x:c r="G34" s="23" t="s">
-        <x:v>409</x:v>
-      </x:c>
-      <x:c r="H34" s="25">
+      <x:c r="M35" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B36" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C36" s="14" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="D36" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E36" s="14" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="G36" s="14" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="H36" s="16">
         <x:v>46077.2103587963</x:v>
       </x:c>
-      <x:c r="I34" s="26">
+      <x:c r="I36" s="17">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J34" s="24" t="n">
+      <x:c r="J36" s="15" t="n">
         <x:v>1216155</x:v>
       </x:c>
-      <x:c r="K34" s="27" t="n">
+      <x:c r="K36" s="18" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L34" s="28">
+      <x:c r="L36" s="19">
         <x:v>46090.2536226852</x:v>
       </x:c>
-      <x:c r="M34" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="23" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C35" s="23" t="s">
-        <x:v>410</x:v>
-      </x:c>
-      <x:c r="D35" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E35" s="23" t="s">
-        <x:v>411</x:v>
-      </x:c>
-      <x:c r="F35" s="23" t="s">
-        <x:v>412</x:v>
-      </x:c>
-      <x:c r="G35" s="23" t="s">
-        <x:v>413</x:v>
-      </x:c>
-      <x:c r="H35" s="25">
+      <x:c r="M36" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B37" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C37" s="14" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="D37" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E37" s="14" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="G37" s="14" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="H37" s="16">
         <x:v>46077.2683564815</x:v>
       </x:c>
-      <x:c r="I35" s="26">
+      <x:c r="I37" s="17">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J35" s="24" t="n">
+      <x:c r="J37" s="15" t="n">
         <x:v>1216159</x:v>
       </x:c>
-      <x:c r="K35" s="27" t="n">
+      <x:c r="K37" s="18" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L35" s="28">
+      <x:c r="L37" s="19">
         <x:v>46090.2806018519</x:v>
       </x:c>
-      <x:c r="M35" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="23" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C36" s="23" t="s">
-        <x:v>414</x:v>
-      </x:c>
-      <x:c r="D36" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E36" s="23" t="s">
-        <x:v>415</x:v>
-      </x:c>
-      <x:c r="F36" s="23" t="s">
-        <x:v>416</x:v>
-      </x:c>
-      <x:c r="G36" s="23" t="s">
-        <x:v>417</x:v>
-      </x:c>
-      <x:c r="H36" s="25">
+      <x:c r="M37" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B38" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C38" s="14" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="D38" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E38" s="14" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="G38" s="14" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="H38" s="16">
         <x:v>46077.1834259259</x:v>
       </x:c>
-      <x:c r="I36" s="26">
+      <x:c r="I38" s="17">
         <x:v>46115</x:v>
       </x:c>
-      <x:c r="J36" s="24" t="n">
+      <x:c r="J38" s="15" t="n">
         <x:v>1216166</x:v>
       </x:c>
-      <x:c r="K36" s="27" t="n">
+      <x:c r="K38" s="18" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L36" s="28">
+      <x:c r="L38" s="19">
         <x:v>46091.2388773148</x:v>
       </x:c>
-      <x:c r="M36" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="23" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C37" s="23" t="s">
-        <x:v>418</x:v>
-      </x:c>
-      <x:c r="D37" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E37" s="23" t="s">
-        <x:v>419</x:v>
-      </x:c>
-      <x:c r="F37" s="23" t="s">
-        <x:v>420</x:v>
-      </x:c>
-      <x:c r="G37" s="23" t="s">
-        <x:v>421</x:v>
-      </x:c>
-      <x:c r="H37" s="25">
+      <x:c r="M38" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B39" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C39" s="14" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="D39" s="15" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E39" s="14" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="G39" s="14" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="H39" s="16">
         <x:v>46090.3681365741</x:v>
       </x:c>
-      <x:c r="I37" s="26">
+      <x:c r="I39" s="17">
         <x:v>46101</x:v>
       </x:c>
-      <x:c r="J37" s="24" t="n">
+      <x:c r="J39" s="15" t="n">
         <x:v>1216192</x:v>
       </x:c>
-      <x:c r="K37" s="27" t="n">
+      <x:c r="K39" s="18" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L37" s="28">
+      <x:c r="L39" s="19">
         <x:v>46094.182662037</x:v>
       </x:c>
-      <x:c r="M37" s="23" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B38" s="29" t="s"/>
-      <x:c r="C38" s="29" t="s"/>
-      <x:c r="D38" s="29" t="s"/>
-      <x:c r="E38" s="29" t="s"/>
-      <x:c r="F38" s="29" t="s"/>
-      <x:c r="G38" s="29" t="s"/>
-      <x:c r="H38" s="29" t="s"/>
-      <x:c r="I38" s="29" t="s"/>
-      <x:c r="J38" s="29" t="s"/>
-      <x:c r="K38" s="29" t="s"/>
-      <x:c r="L38" s="29" t="s"/>
-      <x:c r="M38" s="29" t="s"/>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B39" s="29" t="s"/>
-      <x:c r="C39" s="29" t="s"/>
-      <x:c r="D39" s="29" t="s"/>
-      <x:c r="E39" s="29" t="s"/>
-      <x:c r="F39" s="29" t="s"/>
-      <x:c r="G39" s="29" t="s"/>
-      <x:c r="H39" s="29" t="s"/>
-      <x:c r="I39" s="29" t="s"/>
-      <x:c r="J39" s="29" t="s"/>
-      <x:c r="K39" s="29" t="s"/>
-      <x:c r="L39" s="29" t="s"/>
-      <x:c r="M39" s="29" t="s"/>
+      <x:c r="M39" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="42" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B42" s="30" t="s">
+      <x:c r="B42" s="20" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C42" s="21" t="s"/>
+      <x:c r="D42" s="21" t="s"/>
+      <x:c r="E42" s="22" t="s"/>
+      <x:c r="F42" s="22" t="s"/>
+    </x:row>
+    <x:row r="43" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B43" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C43" s="24" t="s"/>
+      <x:c r="D43" s="24" t="s"/>
+      <x:c r="E43" s="24" t="s"/>
+      <x:c r="F43" s="25" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B44" s="26" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C44" s="27" t="s"/>
+      <x:c r="D44" s="27" t="s"/>
+      <x:c r="E44" s="27" t="s"/>
+      <x:c r="F44" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B45" s="26" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="C45" s="27" t="s"/>
+      <x:c r="D45" s="27" t="s"/>
+      <x:c r="E45" s="27" t="s"/>
+      <x:c r="F45" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B46" s="26" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C46" s="27" t="s"/>
+      <x:c r="D46" s="27" t="s"/>
+      <x:c r="E46" s="27" t="s"/>
+      <x:c r="F46" s="28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B47" s="26" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C47" s="27" t="s"/>
+      <x:c r="D47" s="27" t="s"/>
+      <x:c r="E47" s="27" t="s"/>
+      <x:c r="F47" s="28" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="26" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="C48" s="27" t="s"/>
+      <x:c r="D48" s="27" t="s"/>
+      <x:c r="E48" s="27" t="s"/>
+      <x:c r="F48" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="26" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C42" s="31" t="s"/>
-      <x:c r="D42" s="31" t="s"/>
-      <x:c r="E42" s="32" t="s"/>
-      <x:c r="F42" s="32" t="s"/>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B43" s="33" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C43" s="34" t="s"/>
-      <x:c r="D43" s="34" t="s"/>
-      <x:c r="E43" s="34" t="s"/>
-      <x:c r="F43" s="35" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B44" s="36" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C44" s="37" t="s"/>
-      <x:c r="D44" s="37" t="s"/>
-      <x:c r="E44" s="37" t="s"/>
-      <x:c r="F44" s="38" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B45" s="36" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="C45" s="37" t="s"/>
-      <x:c r="D45" s="37" t="s"/>
-      <x:c r="E45" s="37" t="s"/>
-      <x:c r="F45" s="38" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B46" s="36" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="C46" s="37" t="s"/>
-      <x:c r="D46" s="37" t="s"/>
-      <x:c r="E46" s="37" t="s"/>
-      <x:c r="F46" s="38" t="n">
+      <x:c r="C49" s="27" t="s"/>
+      <x:c r="D49" s="27" t="s"/>
+      <x:c r="E49" s="27" t="s"/>
+      <x:c r="F49" s="28" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="26" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C50" s="27" t="s"/>
+      <x:c r="D50" s="27" t="s"/>
+      <x:c r="E50" s="27" t="s"/>
+      <x:c r="F50" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="26" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C51" s="27" t="s"/>
+      <x:c r="D51" s="27" t="s"/>
+      <x:c r="E51" s="27" t="s"/>
+      <x:c r="F51" s="28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="36" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C47" s="37" t="s"/>
-      <x:c r="D47" s="37" t="s"/>
-      <x:c r="E47" s="37" t="s"/>
-      <x:c r="F47" s="38" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="36" t="s">
-        <x:v>364</x:v>
-      </x:c>
-      <x:c r="C48" s="37" t="s"/>
-      <x:c r="D48" s="37" t="s"/>
-      <x:c r="E48" s="37" t="s"/>
-      <x:c r="F48" s="38" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="36" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C49" s="37" t="s"/>
-      <x:c r="D49" s="37" t="s"/>
-      <x:c r="E49" s="37" t="s"/>
-      <x:c r="F49" s="38" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="36" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C50" s="37" t="s"/>
-      <x:c r="D50" s="37" t="s"/>
-      <x:c r="E50" s="37" t="s"/>
-      <x:c r="F50" s="38" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="36" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C51" s="37" t="s"/>
-      <x:c r="D51" s="37" t="s"/>
-      <x:c r="E51" s="37" t="s"/>
-      <x:c r="F51" s="38" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
     <x:row r="52" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B52" s="39" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C52" s="40" t="s"/>
-      <x:c r="D52" s="40" t="s"/>
-      <x:c r="E52" s="40" t="s"/>
-      <x:c r="F52" s="41" t="n">
+      <x:c r="B52" s="29" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C52" s="30" t="s"/>
+      <x:c r="D52" s="30" t="s"/>
+      <x:c r="E52" s="30" t="s"/>
+      <x:c r="F52" s="31" t="n">
         <x:v>32</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="434">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="442">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -37,6 +37,9 @@
     <x:t>REYNALDO YBAÑEZ</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | August 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>Application Type</x:t>
   </x:si>
   <x:si>
@@ -169,6 +172,9 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | September 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>Commercial Radio Operator Certificate (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -367,6 +373,9 @@
     <x:t>61-9-2025-1152</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | October 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>EDWIN ALMENDRAL ALCORIZA</x:t>
   </x:si>
   <x:si>
@@ -463,6 +472,9 @@
     <x:t>61-10-2025-1194</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | November 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARLYN TENIR PASCO</x:t>
   </x:si>
   <x:si>
@@ -673,6 +685,9 @@
     <x:t>61-11-2025-1228</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | December 2025</x:t>
+  </x:si>
+  <x:si>
     <x:t>AB GADGETS AND ACCESSORIES SHOP</x:t>
   </x:si>
   <x:si>
@@ -763,6 +778,9 @@
     <x:t>61-11-2025-1237</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | January 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A N/A, Poblacion, San Pablo, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -853,6 +871,9 @@
     <x:t>61-1-2026-1277-866</x:t>
   </x:si>
   <x:si>
+    <x:t>IX | February 2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ship Station License DOMESTIC Trade (NEW) (WITHOUT originally-installed equipment)</x:t>
   </x:si>
   <x:si>
@@ -965,6 +986,9 @@
   </x:si>
   <x:si>
     <x:t>61-1-2026-1302-574</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IX | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>FERNANDO B LAKAG</x:t>
@@ -1340,7 +1364,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -1380,6 +1404,30 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -1651,12 +1699,21 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -1671,62 +1728,62 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -1757,95 +1814,107 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -2074,58 +2143,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -2168,336 +2237,336 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="G8" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45875.2668402778</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>45875.2668518519</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1215854</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45877.2327314815</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>45889.2616782407</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>45889.2616898148</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="n">
+        <x:v>1215867</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="L9" s="15">
+        <x:v>45891.1582986111</x:v>
+      </x:c>
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="17" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
-        <x:v>45889.2616782407</x:v>
-      </x:c>
-      <x:c r="I9" s="12">
-        <x:v>45889.2616898148</x:v>
-      </x:c>
-      <x:c r="J9" s="11" t="n">
-        <x:v>1215867</x:v>
-      </x:c>
-      <x:c r="K9" s="13" t="n">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="L9" s="12">
-        <x:v>45891.1582986111</x:v>
-      </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="F10" s="17" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
+        <x:v>45889.1521064815</x:v>
+      </x:c>
+      <x:c r="I10" s="20">
+        <x:v>44272</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="n">
+        <x:v>1215866</x:v>
+      </x:c>
+      <x:c r="K10" s="21" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="L10" s="22">
+        <x:v>45891.153287037</x:v>
+      </x:c>
+      <x:c r="M10" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>45889.1521064815</x:v>
-      </x:c>
-      <x:c r="I10" s="17">
-        <x:v>44272</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>1215866</x:v>
-      </x:c>
-      <x:c r="K10" s="18" t="n">
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="L10" s="19">
-        <x:v>45891.153287037</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="E11" s="17" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>45887.5652430556</x:v>
+      </x:c>
+      <x:c r="I11" s="20">
+        <x:v>45851</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1215872</x:v>
+      </x:c>
+      <x:c r="K11" s="21" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L11" s="22">
+        <x:v>45896.2365393518</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="17" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="C12" s="17" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
+        <x:v>45891.1735648148</x:v>
+      </x:c>
+      <x:c r="I12" s="20">
+        <x:v>45765</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1215865</x:v>
+      </x:c>
+      <x:c r="K12" s="21" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L12" s="22">
+        <x:v>45898.0611111111</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>45887.5652430556</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>45851</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1215872</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>45896.2365393518</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>45891.1735648148</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>45765</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1215865</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>45898.0611111111</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="F13" s="17" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="H13" s="16">
+      <x:c r="G13" s="17" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
         <x:v>45887.5590162037</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="20">
         <x:v>45888</x:v>
       </x:c>
-      <x:c r="J13" s="15" t="n">
+      <x:c r="J13" s="18" t="n">
         <x:v>1215870</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="21" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="22">
         <x:v>45896.237962963</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M13" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="20" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="22" t="s"/>
+      <x:c r="B16" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="25" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="23" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="s">
+      <x:c r="B17" s="26" t="s">
         <x:v>44</x:v>
       </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="B18" s="29" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C18" s="30" t="s"/>
+      <x:c r="D18" s="30" t="s"/>
+      <x:c r="E18" s="30" t="s"/>
+      <x:c r="F18" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
+      <x:c r="B19" s="29" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C19" s="30" t="s"/>
+      <x:c r="D19" s="30" t="s"/>
+      <x:c r="E19" s="30" t="s"/>
+      <x:c r="F19" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="B20" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C20" s="30" t="s"/>
+      <x:c r="D20" s="30" t="s"/>
+      <x:c r="E20" s="30" t="s"/>
+      <x:c r="F20" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="29" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C21" s="30" t="s"/>
-      <x:c r="D21" s="30" t="s"/>
-      <x:c r="E21" s="30" t="s"/>
-      <x:c r="F21" s="31" t="n">
+      <x:c r="B21" s="32" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C21" s="33" t="s"/>
+      <x:c r="D21" s="33" t="s"/>
+      <x:c r="E21" s="33" t="s"/>
+      <x:c r="F21" s="34" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -3477,7 +3546,7 @@
   <x:mergeCells count="9">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B16:F16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
@@ -3524,58 +3593,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -3618,731 +3687,731 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="D8" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="F8" s="14" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45902.1777546296</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="35">
         <x:v>45781</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1215887</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45911.9486574074</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="D9" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="F9" s="14" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>45915.355787037</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="35">
         <x:v>45851</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1215901</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="16" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>45918.2339583333</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
+      <x:c r="B10" s="17" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="E10" s="14" t="s">
+      <x:c r="C10" s="17" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="D10" s="18" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="E10" s="17" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="F10" s="17" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
         <x:v>45903.3849652778</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="20">
         <x:v>45916</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="18" t="n">
         <x:v>1215886</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="21" t="n">
         <x:v>3150</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="22">
         <x:v>45908.2848958333</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M10" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="B11" s="17" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="C11" s="17" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="D11" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="H11" s="16">
+      <x:c r="F11" s="17" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
         <x:v>45919.4023032407</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="20">
         <x:v>45926</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
+      <x:c r="J11" s="18" t="n">
         <x:v>1215905</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="21" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="22">
         <x:v>45925.945150463</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M11" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="B12" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="D12" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="H12" s="16">
+      <x:c r="F12" s="17" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
         <x:v>45918.1053935185</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="20">
         <x:v>45900</x:v>
       </x:c>
-      <x:c r="J12" s="15" t="n">
+      <x:c r="J12" s="18" t="n">
         <x:v>1215910</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="21" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="22">
         <x:v>45929.2194097222</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M12" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="B13" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="D13" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="H13" s="16">
+      <x:c r="F13" s="17" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
         <x:v>45908.2183449074</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="20">
         <x:v>45918</x:v>
       </x:c>
-      <x:c r="J13" s="15" t="n">
+      <x:c r="J13" s="18" t="n">
         <x:v>1215894</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="21" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="22">
         <x:v>45912.1906134259</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M13" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="B14" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="D14" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="H14" s="16">
+      <x:c r="F14" s="17" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
         <x:v>45908.5003472222</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="20">
         <x:v>45790</x:v>
       </x:c>
-      <x:c r="J14" s="15" t="n">
+      <x:c r="J14" s="18" t="n">
         <x:v>1215888</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="21" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="22">
         <x:v>45911.952650463</x:v>
       </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M14" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="B15" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="D15" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="H15" s="16">
+      <x:c r="F15" s="17" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
         <x:v>45916.1691666667</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="20">
         <x:v>45949</x:v>
       </x:c>
-      <x:c r="J15" s="15" t="n">
+      <x:c r="J15" s="18" t="n">
         <x:v>1215908</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="21" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="22">
         <x:v>45929.1383449074</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M15" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="B16" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
+      <x:c r="D16" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="H16" s="16">
+      <x:c r="F16" s="17" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H16" s="19">
         <x:v>45888.154375</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="20">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="J16" s="15" t="n">
+      <x:c r="J16" s="18" t="n">
         <x:v>1215874</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="21" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="22">
         <x:v>45902.050775463</x:v>
       </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M16" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
+      <x:c r="B17" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="G17" s="14" t="s">
+      <x:c r="D17" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E17" s="17" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="H17" s="16">
+      <x:c r="F17" s="17" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H17" s="19">
         <x:v>45924.1162962963</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="20">
         <x:v>45902</x:v>
       </x:c>
-      <x:c r="J17" s="15" t="n">
+      <x:c r="J17" s="18" t="n">
         <x:v>1215911</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="21" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="22">
         <x:v>45930.063912037</x:v>
       </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M17" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s"/>
-      <x:c r="E18" s="14" t="s">
+      <x:c r="B18" s="17" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="s">
+      <x:c r="C18" s="17" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="s">
+      <x:c r="D18" s="18" t="s"/>
+      <x:c r="E18" s="17" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="H18" s="16">
+      <x:c r="F18" s="17" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="H18" s="19">
         <x:v>45919.473287037</x:v>
       </x:c>
-      <x:c r="I18" s="16">
+      <x:c r="I18" s="19">
         <x:v>45919.4732986111</x:v>
       </x:c>
-      <x:c r="J18" s="15" t="n">
+      <x:c r="J18" s="18" t="n">
         <x:v>1215906</x:v>
       </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="K18" s="21" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L18" s="19">
+      <x:c r="L18" s="22">
         <x:v>45926.2586111111</x:v>
       </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M18" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
+      <x:c r="B19" s="17" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="s">
+      <x:c r="C19" s="17" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="G19" s="14" t="s">
+      <x:c r="D19" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E19" s="17" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="H19" s="16">
+      <x:c r="F19" s="17" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H19" s="19">
         <x:v>45911.4396296296</x:v>
       </x:c>
-      <x:c r="I19" s="16">
+      <x:c r="I19" s="19">
         <x:v>45911.4396296296</x:v>
       </x:c>
-      <x:c r="J19" s="15" t="n">
+      <x:c r="J19" s="18" t="n">
         <x:v>1215899</x:v>
       </x:c>
-      <x:c r="K19" s="18" t="n">
+      <x:c r="K19" s="21" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L19" s="19">
+      <x:c r="L19" s="22">
         <x:v>45918.0952083333</x:v>
       </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M19" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
+      <x:c r="B20" s="17" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="F20" s="14" t="s">
+      <x:c r="C20" s="17" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G20" s="14" t="s">
+      <x:c r="D20" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="H20" s="16">
+      <x:c r="F20" s="17" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="H20" s="19">
         <x:v>45925.3972453704</x:v>
       </x:c>
-      <x:c r="I20" s="17">
+      <x:c r="I20" s="20">
         <x:v>47021</x:v>
       </x:c>
-      <x:c r="J20" s="15" t="n">
+      <x:c r="J20" s="18" t="n">
         <x:v>1215915</x:v>
       </x:c>
-      <x:c r="K20" s="18" t="n">
+      <x:c r="K20" s="21" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L20" s="19">
+      <x:c r="L20" s="22">
         <x:v>45930.1169560185</x:v>
       </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M20" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
+      <x:c r="B21" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="H21" s="16">
+      <x:c r="D21" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E21" s="17" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H21" s="19">
         <x:v>45916.1769097222</x:v>
       </x:c>
-      <x:c r="I21" s="17">
+      <x:c r="I21" s="20">
         <x:v>45949</x:v>
       </x:c>
-      <x:c r="J21" s="15" t="n">
+      <x:c r="J21" s="18" t="n">
         <x:v>1215916</x:v>
       </x:c>
-      <x:c r="K21" s="18" t="n">
+      <x:c r="K21" s="21" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L21" s="19">
+      <x:c r="L21" s="22">
         <x:v>45930.1671643518</x:v>
       </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M21" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
+      <x:c r="B22" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="H22" s="16">
+      <x:c r="D22" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E22" s="17" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="G22" s="17" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H22" s="19">
         <x:v>45912.47375</x:v>
       </x:c>
-      <x:c r="I22" s="17">
+      <x:c r="I22" s="20">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J22" s="15" t="n">
+      <x:c r="J22" s="18" t="n">
         <x:v>1215898</x:v>
       </x:c>
-      <x:c r="K22" s="18" t="n">
+      <x:c r="K22" s="21" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L22" s="19">
+      <x:c r="L22" s="22">
         <x:v>45918.0905787037</x:v>
       </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M22" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="20" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C25" s="21" t="s"/>
-      <x:c r="D25" s="21" t="s"/>
-      <x:c r="E25" s="22" t="s"/>
-      <x:c r="F25" s="22" t="s"/>
+      <x:c r="B25" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C25" s="24" t="s"/>
+      <x:c r="D25" s="24" t="s"/>
+      <x:c r="E25" s="25" t="s"/>
+      <x:c r="F25" s="25" t="s"/>
     </x:row>
     <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="23" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C26" s="24" t="s"/>
-      <x:c r="D26" s="24" t="s"/>
-      <x:c r="E26" s="24" t="s"/>
-      <x:c r="F26" s="25" t="s">
+      <x:c r="B26" s="26" t="s">
         <x:v>44</x:v>
       </x:c>
+      <x:c r="C26" s="27" t="s"/>
+      <x:c r="D26" s="27" t="s"/>
+      <x:c r="E26" s="27" t="s"/>
+      <x:c r="F26" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="26" t="s">
+      <x:c r="B27" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C27" s="30" t="s"/>
+      <x:c r="D27" s="30" t="s"/>
+      <x:c r="E27" s="30" t="s"/>
+      <x:c r="F27" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="29" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C28" s="30" t="s"/>
+      <x:c r="D28" s="30" t="s"/>
+      <x:c r="E28" s="30" t="s"/>
+      <x:c r="F28" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="29" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C29" s="30" t="s"/>
+      <x:c r="D29" s="30" t="s"/>
+      <x:c r="E29" s="30" t="s"/>
+      <x:c r="F29" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="29" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C30" s="30" t="s"/>
+      <x:c r="D30" s="30" t="s"/>
+      <x:c r="E30" s="30" t="s"/>
+      <x:c r="F30" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C31" s="30" t="s"/>
+      <x:c r="D31" s="30" t="s"/>
+      <x:c r="E31" s="30" t="s"/>
+      <x:c r="F31" s="31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="29" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C32" s="30" t="s"/>
+      <x:c r="D32" s="30" t="s"/>
+      <x:c r="E32" s="30" t="s"/>
+      <x:c r="F32" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="29" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C33" s="30" t="s"/>
+      <x:c r="D33" s="30" t="s"/>
+      <x:c r="E33" s="30" t="s"/>
+      <x:c r="F33" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="29" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C34" s="30" t="s"/>
+      <x:c r="D34" s="30" t="s"/>
+      <x:c r="E34" s="30" t="s"/>
+      <x:c r="F34" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B35" s="32" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C27" s="27" t="s"/>
-      <x:c r="D27" s="27" t="s"/>
-      <x:c r="E27" s="27" t="s"/>
-      <x:c r="F27" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="26" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C28" s="27" t="s"/>
-      <x:c r="D28" s="27" t="s"/>
-      <x:c r="E28" s="27" t="s"/>
-      <x:c r="F28" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="26" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C29" s="27" t="s"/>
-      <x:c r="D29" s="27" t="s"/>
-      <x:c r="E29" s="27" t="s"/>
-      <x:c r="F29" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="26" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C34" s="27" t="s"/>
-      <x:c r="D34" s="27" t="s"/>
-      <x:c r="E34" s="27" t="s"/>
-      <x:c r="F34" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="29" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C35" s="30" t="s"/>
-      <x:c r="D35" s="30" t="s"/>
-      <x:c r="E35" s="30" t="s"/>
-      <x:c r="F35" s="31" t="n">
+      <x:c r="C35" s="33" t="s"/>
+      <x:c r="D35" s="33" t="s"/>
+      <x:c r="E35" s="33" t="s"/>
+      <x:c r="F35" s="34" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -5308,7 +5377,7 @@
   <x:mergeCells count="14">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B25:F25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
@@ -5360,58 +5429,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -5454,477 +5523,477 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="B8" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="D8" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45938.0053703704</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="35">
         <x:v>45942</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1215952</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45945.1196180556</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="B9" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="D9" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>45933.0884375</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="35">
         <x:v>45932</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1215922</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>45936.014837963</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="B10" s="17" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="C10" s="17" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="D10" s="18" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
         <x:v>45947.5768287037</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="20">
         <x:v>43437</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="18" t="n">
         <x:v>1215960</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="21" t="n">
         <x:v>17766</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="22">
         <x:v>45954.2191782407</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M10" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
+      <x:c r="B11" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s"/>
+      <x:c r="H11" s="19">
+        <x:v>45925.0601967593</x:v>
+      </x:c>
+      <x:c r="I11" s="20">
+        <x:v>45922</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1215919</x:v>
+      </x:c>
+      <x:c r="K11" s="21" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L11" s="22">
+        <x:v>45933.3037152778</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B12" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
+        <x:v>45912.3032407407</x:v>
+      </x:c>
+      <x:c r="I12" s="20">
+        <x:v>45879</x:v>
+      </x:c>
+      <x:c r="J12" s="18" t="n">
+        <x:v>1215920</x:v>
+      </x:c>
+      <x:c r="K12" s="21" t="n">
+        <x:v>4710</x:v>
+      </x:c>
+      <x:c r="L12" s="22">
+        <x:v>45933.3105324074</x:v>
+      </x:c>
+      <x:c r="M12" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B13" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
+        <x:v>45931.5665277778</x:v>
+      </x:c>
+      <x:c r="I13" s="20">
+        <x:v>46297</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>1215945</x:v>
+      </x:c>
+      <x:c r="K13" s="21" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L13" s="22">
+        <x:v>45940.1382060185</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="17" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="s"/>
+      <x:c r="E14" s="17" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
+        <x:v>45928.9304513889</x:v>
+      </x:c>
+      <x:c r="I14" s="19">
+        <x:v>45928.9304861111</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="n">
+        <x:v>1215924</x:v>
+      </x:c>
+      <x:c r="K14" s="21" t="n">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="L14" s="22">
+        <x:v>45938.0359375</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="17" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s"/>
+      <x:c r="E15" s="17" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s"/>
-      <x:c r="H11" s="16">
-        <x:v>45925.0601967593</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>45922</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1215919</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>45933.3037152778</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>45912.3032407407</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>45879</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="n">
-        <x:v>1215920</x:v>
-      </x:c>
-      <x:c r="K12" s="18" t="n">
-        <x:v>4710</x:v>
-      </x:c>
-      <x:c r="L12" s="19">
-        <x:v>45933.3105324074</x:v>
-      </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
+      <x:c r="F15" s="17" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
+        <x:v>45926.4563888889</x:v>
+      </x:c>
+      <x:c r="I15" s="19">
+        <x:v>45926.4564351852</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="n">
+        <x:v>1215917</x:v>
+      </x:c>
+      <x:c r="K15" s="21" t="n">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="L15" s="22">
+        <x:v>45932.239537037</x:v>
+      </x:c>
+      <x:c r="M15" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B16" s="17" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>45931.5665277778</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>46297</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>1215945</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>45940.1382060185</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s"/>
-      <x:c r="E14" s="14" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>45928.9304513889</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>45928.9304861111</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>1215924</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
-        <x:v>456</x:v>
-      </x:c>
-      <x:c r="L14" s="19">
-        <x:v>45938.0359375</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s"/>
-      <x:c r="E15" s="14" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>45926.4563888889</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>45926.4564351852</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>1215917</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>456</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
-        <x:v>45932.239537037</x:v>
-      </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
+      <x:c r="C16" s="17" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="H16" s="16">
+      <x:c r="D16" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="H16" s="19">
         <x:v>45945.2727662037</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="20">
         <x:v>45911</x:v>
       </x:c>
-      <x:c r="J16" s="15" t="n">
+      <x:c r="J16" s="18" t="n">
         <x:v>1215958</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="21" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="22">
         <x:v>45953.151099537</x:v>
       </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M16" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="20" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C19" s="21" t="s"/>
-      <x:c r="D19" s="21" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="22" t="s"/>
+      <x:c r="B19" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C19" s="24" t="s"/>
+      <x:c r="D19" s="24" t="s"/>
+      <x:c r="E19" s="25" t="s"/>
+      <x:c r="F19" s="25" t="s"/>
     </x:row>
     <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="23" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C20" s="24" t="s"/>
-      <x:c r="D20" s="24" t="s"/>
-      <x:c r="E20" s="24" t="s"/>
-      <x:c r="F20" s="25" t="s">
+      <x:c r="B20" s="26" t="s">
         <x:v>44</x:v>
       </x:c>
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
+      <x:c r="B21" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C21" s="30" t="s"/>
+      <x:c r="D21" s="30" t="s"/>
+      <x:c r="E21" s="30" t="s"/>
+      <x:c r="F21" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="29" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C22" s="30" t="s"/>
+      <x:c r="D22" s="30" t="s"/>
+      <x:c r="E22" s="30" t="s"/>
+      <x:c r="F22" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="29" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="C23" s="30" t="s"/>
+      <x:c r="D23" s="30" t="s"/>
+      <x:c r="E23" s="30" t="s"/>
+      <x:c r="F23" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C24" s="30" t="s"/>
+      <x:c r="D24" s="30" t="s"/>
+      <x:c r="E24" s="30" t="s"/>
+      <x:c r="F24" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="29" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C25" s="30" t="s"/>
+      <x:c r="D25" s="30" t="s"/>
+      <x:c r="E25" s="30" t="s"/>
+      <x:c r="F25" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="29" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C26" s="30" t="s"/>
+      <x:c r="D26" s="30" t="s"/>
+      <x:c r="E26" s="30" t="s"/>
+      <x:c r="F26" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B27" s="32" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="26" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="26" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C26" s="27" t="s"/>
-      <x:c r="D26" s="27" t="s"/>
-      <x:c r="E26" s="27" t="s"/>
-      <x:c r="F26" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="29" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C27" s="30" t="s"/>
-      <x:c r="D27" s="30" t="s"/>
-      <x:c r="E27" s="30" t="s"/>
-      <x:c r="F27" s="31" t="n">
+      <x:c r="C27" s="33" t="s"/>
+      <x:c r="D27" s="33" t="s"/>
+      <x:c r="E27" s="33" t="s"/>
+      <x:c r="F27" s="34" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -6898,7 +6967,7 @@
   <x:mergeCells count="12">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B19:F19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
@@ -6948,58 +7017,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -7042,832 +7111,832 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="B8" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45954.1265625</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="35">
         <x:v>45626</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1215975</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>510</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45967.0018287037</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="B9" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>45965.2541435185</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="35">
         <x:v>45971</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1215995</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="16" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>45971.1502199074</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="B10" s="17" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="C10" s="17" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
         <x:v>45965.2736689815</x:v>
       </x:c>
-      <x:c r="I10" s="16">
+      <x:c r="I10" s="19">
         <x:v>45965.2736921296</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="18" t="n">
         <x:v>1216000</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="21" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="22">
         <x:v>45972.1539583333</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M10" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
+      <x:c r="B11" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
         <x:v>45965.2661458333</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="20">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
+      <x:c r="J11" s="18" t="n">
         <x:v>1215999</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="21" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="22">
         <x:v>45972.1364236111</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M11" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
+      <x:c r="B12" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
         <x:v>45953.5328240741</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="20">
         <x:v>45969</x:v>
       </x:c>
-      <x:c r="J12" s="15" t="n">
+      <x:c r="J12" s="18" t="n">
         <x:v>1215970</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="21" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="22">
         <x:v>45966.0458101852</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M12" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
+      <x:c r="B13" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
         <x:v>45958.0724421296</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="20">
         <x:v>45810</x:v>
       </x:c>
-      <x:c r="J13" s="15" t="n">
+      <x:c r="J13" s="18" t="n">
         <x:v>1216003</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="21" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="22">
         <x:v>45973.0584490741</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M13" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="B14" s="17" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="H14" s="16">
+      <x:c r="C14" s="17" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
         <x:v>45973.1309375</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="20">
         <x:v>45950</x:v>
       </x:c>
-      <x:c r="J14" s="15" t="n">
+      <x:c r="J14" s="18" t="n">
         <x:v>1216020</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="21" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="22">
         <x:v>45985.2116666667</x:v>
       </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M14" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
+      <x:c r="B15" s="17" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
         <x:v>45971.2436226852</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="20">
         <x:v>45608</x:v>
       </x:c>
-      <x:c r="J15" s="15" t="n">
+      <x:c r="J15" s="18" t="n">
         <x:v>1216004</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="21" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="22">
         <x:v>45973.2287268518</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M15" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
+      <x:c r="B16" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="H16" s="19">
         <x:v>45974.6184490741</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="20">
         <x:v>45682</x:v>
       </x:c>
-      <x:c r="J16" s="15" t="n">
+      <x:c r="J16" s="18" t="n">
         <x:v>1216021</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="21" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="22">
         <x:v>45986.0239236111</x:v>
       </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M16" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
+      <x:c r="B17" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E17" s="17" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="F17" s="17" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="H17" s="19">
         <x:v>45965.4411342593</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="20">
         <x:v>45974</x:v>
       </x:c>
-      <x:c r="J17" s="15" t="n">
+      <x:c r="J17" s="18" t="n">
         <x:v>1216001</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="21" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="22">
         <x:v>45973.0179398148</x:v>
       </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M17" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
+      <x:c r="B18" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="H18" s="19">
         <x:v>45971.2507291667</x:v>
       </x:c>
-      <x:c r="I18" s="17">
+      <x:c r="I18" s="20">
         <x:v>45991</x:v>
       </x:c>
-      <x:c r="J18" s="15" t="n">
+      <x:c r="J18" s="18" t="n">
         <x:v>1216006</x:v>
       </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="K18" s="21" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L18" s="19">
+      <x:c r="L18" s="22">
         <x:v>45975.0756134259</x:v>
       </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M18" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
+      <x:c r="B19" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C19" s="17" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E19" s="17" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="F19" s="17" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="H19" s="19">
         <x:v>45958.3516898148</x:v>
       </x:c>
-      <x:c r="I19" s="17">
+      <x:c r="I19" s="20">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J19" s="15" t="n">
+      <x:c r="J19" s="18" t="n">
         <x:v>1215976</x:v>
       </x:c>
-      <x:c r="K19" s="18" t="n">
+      <x:c r="K19" s="21" t="n">
         <x:v>3990</x:v>
       </x:c>
-      <x:c r="L19" s="19">
+      <x:c r="L19" s="22">
         <x:v>45967.2412384259</x:v>
       </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M19" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
+      <x:c r="B20" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H20" s="19">
         <x:v>45954.2913425926</x:v>
       </x:c>
-      <x:c r="I20" s="17">
+      <x:c r="I20" s="20">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J20" s="15" t="n">
+      <x:c r="J20" s="18" t="n">
         <x:v>1216013</x:v>
       </x:c>
-      <x:c r="K20" s="18" t="n">
+      <x:c r="K20" s="21" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L20" s="19">
+      <x:c r="L20" s="22">
         <x:v>45975.3213541667</x:v>
       </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M20" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
+      <x:c r="B21" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E21" s="17" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="H21" s="19">
         <x:v>45953.3174884259</x:v>
       </x:c>
-      <x:c r="I21" s="17">
+      <x:c r="I21" s="20">
         <x:v>45911</x:v>
       </x:c>
-      <x:c r="J21" s="15" t="n">
+      <x:c r="J21" s="18" t="n">
         <x:v>1215996</x:v>
       </x:c>
-      <x:c r="K21" s="18" t="n">
+      <x:c r="K21" s="21" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L21" s="19">
+      <x:c r="L21" s="22">
         <x:v>45971.2990162037</x:v>
       </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M21" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s"/>
-      <x:c r="E22" s="14" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
+      <x:c r="B22" s="17" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="s"/>
+      <x:c r="E22" s="17" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G22" s="17" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="H22" s="19">
         <x:v>45954.4189930556</x:v>
       </x:c>
-      <x:c r="I22" s="16">
+      <x:c r="I22" s="19">
         <x:v>45954.4190277778</x:v>
       </x:c>
-      <x:c r="J22" s="15" t="n">
+      <x:c r="J22" s="18" t="n">
         <x:v>1215987</x:v>
       </x:c>
-      <x:c r="K22" s="18" t="n">
+      <x:c r="K22" s="21" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L22" s="19">
+      <x:c r="L22" s="22">
         <x:v>45967.2850694444</x:v>
       </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M22" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s"/>
-      <x:c r="E23" s="14" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
+      <x:c r="B23" s="17" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="s"/>
+      <x:c r="E23" s="17" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="F23" s="17" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="G23" s="17" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="H23" s="19">
         <x:v>45959.2592013889</x:v>
       </x:c>
-      <x:c r="I23" s="16">
+      <x:c r="I23" s="19">
         <x:v>45959.259224537</x:v>
       </x:c>
-      <x:c r="J23" s="15" t="n">
+      <x:c r="J23" s="18" t="n">
         <x:v>1216022</x:v>
       </x:c>
-      <x:c r="K23" s="18" t="n">
+      <x:c r="K23" s="21" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L23" s="19">
+      <x:c r="L23" s="22">
         <x:v>45986.1291898148</x:v>
       </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M23" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
+      <x:c r="B24" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E24" s="17" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="G24" s="17" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="H24" s="19">
+        <x:v>45966.1203125</x:v>
+      </x:c>
+      <x:c r="I24" s="20">
+        <x:v>45975</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="n">
+        <x:v>1216011</x:v>
+      </x:c>
+      <x:c r="K24" s="21" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="H24" s="16">
-        <x:v>45966.1203125</x:v>
-      </x:c>
-      <x:c r="I24" s="17">
+      <x:c r="L24" s="22">
+        <x:v>45975.3046180556</x:v>
+      </x:c>
+      <x:c r="M24" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E25" s="17" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="F25" s="17" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G25" s="17" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="H25" s="19">
+        <x:v>45966.1218055556</x:v>
+      </x:c>
+      <x:c r="I25" s="20">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J24" s="15" t="n">
-        <x:v>1216011</x:v>
-      </x:c>
-      <x:c r="K24" s="18" t="n">
+      <x:c r="J25" s="18" t="n">
+        <x:v>1216012</x:v>
+      </x:c>
+      <x:c r="K25" s="21" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L24" s="19">
-        <x:v>45975.3046180556</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>45966.1218055556</x:v>
-      </x:c>
-      <x:c r="I25" s="17">
-        <x:v>45975</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="n">
-        <x:v>1216012</x:v>
-      </x:c>
-      <x:c r="K25" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L25" s="19">
+      <x:c r="L25" s="22">
         <x:v>45975.312349537</x:v>
       </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M25" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="20" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C28" s="21" t="s"/>
-      <x:c r="D28" s="21" t="s"/>
-      <x:c r="E28" s="22" t="s"/>
-      <x:c r="F28" s="22" t="s"/>
+      <x:c r="B28" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C28" s="24" t="s"/>
+      <x:c r="D28" s="24" t="s"/>
+      <x:c r="E28" s="25" t="s"/>
+      <x:c r="F28" s="25" t="s"/>
     </x:row>
     <x:row r="29" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B29" s="23" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C29" s="24" t="s"/>
-      <x:c r="D29" s="24" t="s"/>
-      <x:c r="E29" s="24" t="s"/>
-      <x:c r="F29" s="25" t="s">
+      <x:c r="B29" s="26" t="s">
         <x:v>44</x:v>
       </x:c>
+      <x:c r="C29" s="27" t="s"/>
+      <x:c r="D29" s="27" t="s"/>
+      <x:c r="E29" s="27" t="s"/>
+      <x:c r="F29" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
+      <x:c r="B30" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C30" s="30" t="s"/>
+      <x:c r="D30" s="30" t="s"/>
+      <x:c r="E30" s="30" t="s"/>
+      <x:c r="F30" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="29" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C31" s="30" t="s"/>
+      <x:c r="D31" s="30" t="s"/>
+      <x:c r="E31" s="30" t="s"/>
+      <x:c r="F31" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="29" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C32" s="30" t="s"/>
+      <x:c r="D32" s="30" t="s"/>
+      <x:c r="E32" s="30" t="s"/>
+      <x:c r="F32" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="29" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C33" s="30" t="s"/>
+      <x:c r="D33" s="30" t="s"/>
+      <x:c r="E33" s="30" t="s"/>
+      <x:c r="F33" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C34" s="30" t="s"/>
+      <x:c r="D34" s="30" t="s"/>
+      <x:c r="E34" s="30" t="s"/>
+      <x:c r="F34" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="29" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C35" s="30" t="s"/>
+      <x:c r="D35" s="30" t="s"/>
+      <x:c r="E35" s="30" t="s"/>
+      <x:c r="F35" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="29" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C36" s="30" t="s"/>
+      <x:c r="D36" s="30" t="s"/>
+      <x:c r="E36" s="30" t="s"/>
+      <x:c r="F36" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B37" s="32" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C34" s="27" t="s"/>
-      <x:c r="D34" s="27" t="s"/>
-      <x:c r="E34" s="27" t="s"/>
-      <x:c r="F34" s="28" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="26" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C35" s="27" t="s"/>
-      <x:c r="D35" s="27" t="s"/>
-      <x:c r="E35" s="27" t="s"/>
-      <x:c r="F35" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="26" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C36" s="27" t="s"/>
-      <x:c r="D36" s="27" t="s"/>
-      <x:c r="E36" s="27" t="s"/>
-      <x:c r="F36" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B37" s="29" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C37" s="30" t="s"/>
-      <x:c r="D37" s="30" t="s"/>
-      <x:c r="E37" s="30" t="s"/>
-      <x:c r="F37" s="31" t="n">
+      <x:c r="C37" s="33" t="s"/>
+      <x:c r="D37" s="33" t="s"/>
+      <x:c r="E37" s="33" t="s"/>
+      <x:c r="F37" s="34" t="n">
         <x:v>18</x:v>
       </x:c>
     </x:row>
@@ -8831,7 +8900,7 @@
   <x:mergeCells count="13">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B28:F28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
@@ -8882,58 +8951,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -8976,412 +9045,412 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="B8" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>45981.1374421296</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="35">
         <x:v>45969</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1216030</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>45996.1054282407</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="B9" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>45994.1029050926</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="35">
         <x:v>45169</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1216035</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="16" t="n">
         <x:v>12780</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>46006.2230439815</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="B10" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
         <x:v>45973.2824074074</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="20">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="18" t="n">
         <x:v>1216029</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="21" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="22">
         <x:v>45993.0810763889</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M10" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
+      <x:c r="B11" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
         <x:v>45988.1651388889</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="20">
         <x:v>45974</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
+      <x:c r="J11" s="18" t="n">
         <x:v>1216036</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="21" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="22">
         <x:v>46006.2389583333</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M11" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
+      <x:c r="B12" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
         <x:v>45972.0386111111</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="20">
         <x:v>46337</x:v>
       </x:c>
-      <x:c r="J12" s="15" t="n">
+      <x:c r="J12" s="18" t="n">
         <x:v>1216033</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="21" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="22">
         <x:v>46006.0795717593</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M12" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="B13" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
+        <x:v>45980.2173958333</x:v>
+      </x:c>
+      <x:c r="I13" s="20">
+        <x:v>45852</x:v>
+      </x:c>
+      <x:c r="J13" s="18" t="n">
+        <x:v>1216027</x:v>
+      </x:c>
+      <x:c r="K13" s="21" t="n">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="L13" s="22">
+        <x:v>45992.1151851852</x:v>
+      </x:c>
+      <x:c r="M13" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B14" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
+        <x:v>45979.0549768519</x:v>
+      </x:c>
+      <x:c r="I14" s="20">
+        <x:v>46007</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="n">
+        <x:v>1216037</x:v>
+      </x:c>
+      <x:c r="K14" s="21" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L14" s="22">
+        <x:v>46006.2690046296</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B15" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="H13" s="16">
-        <x:v>45980.2173958333</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>45852</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="n">
-        <x:v>1216027</x:v>
-      </x:c>
-      <x:c r="K13" s="18" t="n">
-        <x:v>1830</x:v>
-      </x:c>
-      <x:c r="L13" s="19">
-        <x:v>45992.1151851852</x:v>
-      </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>45979.0549768519</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>46007</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="n">
-        <x:v>1216037</x:v>
-      </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="F15" s="17" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
+        <x:v>45972.2314236111</x:v>
+      </x:c>
+      <x:c r="I15" s="20">
+        <x:v>46337</x:v>
+      </x:c>
+      <x:c r="J15" s="18" t="n">
+        <x:v>1216026</x:v>
+      </x:c>
+      <x:c r="K15" s="21" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L14" s="19">
-        <x:v>46006.2690046296</x:v>
-      </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>45972.2314236111</x:v>
-      </x:c>
-      <x:c r="I15" s="17">
-        <x:v>46337</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="n">
-        <x:v>1216026</x:v>
-      </x:c>
-      <x:c r="K15" s="18" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="22">
         <x:v>45992.0065509259</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M15" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="20" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C18" s="21" t="s"/>
-      <x:c r="D18" s="21" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="22" t="s"/>
+      <x:c r="B18" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C18" s="24" t="s"/>
+      <x:c r="D18" s="24" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="25" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="s">
+      <x:c r="B19" s="26" t="s">
         <x:v>44</x:v>
       </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="B20" s="29" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C20" s="30" t="s"/>
+      <x:c r="D20" s="30" t="s"/>
+      <x:c r="E20" s="30" t="s"/>
+      <x:c r="F20" s="31" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+      <x:c r="B21" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C21" s="30" t="s"/>
+      <x:c r="D21" s="30" t="s"/>
+      <x:c r="E21" s="30" t="s"/>
+      <x:c r="F21" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="B22" s="29" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C22" s="30" t="s"/>
+      <x:c r="D22" s="30" t="s"/>
+      <x:c r="E22" s="30" t="s"/>
+      <x:c r="F22" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="29" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C23" s="30" t="s"/>
-      <x:c r="D23" s="30" t="s"/>
-      <x:c r="E23" s="30" t="s"/>
-      <x:c r="F23" s="31" t="n">
+      <x:c r="B23" s="32" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C23" s="33" t="s"/>
+      <x:c r="D23" s="33" t="s"/>
+      <x:c r="E23" s="33" t="s"/>
+      <x:c r="F23" s="34" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -10359,7 +10428,7 @@
   <x:mergeCells count="9">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
@@ -10406,58 +10475,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -10500,421 +10569,421 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="B8" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46033.3509837963</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="35">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1216094</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46049.2368865741</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="B9" s="14" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>46010.1939351852</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="35">
         <x:v>46029</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1216062</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>46034.111087963</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>250</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="B10" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
         <x:v>45989.0397222222</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="20">
         <x:v>45597</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="18" t="n">
         <x:v>1216078</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="21" t="n">
         <x:v>8280</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="22">
         <x:v>46043.2235069444</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M10" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
+      <x:c r="B11" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
+        <x:v>46007.1341435185</x:v>
+      </x:c>
+      <x:c r="I11" s="20">
+        <x:v>45942</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1216069</x:v>
+      </x:c>
+      <x:c r="K11" s="21" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="L11" s="22">
+        <x:v>46035.3042476852</x:v>
+      </x:c>
+      <x:c r="M11" s="17" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46007.1341435185</x:v>
-      </x:c>
-      <x:c r="I11" s="17">
-        <x:v>45942</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>1216069</x:v>
-      </x:c>
-      <x:c r="K11" s="18" t="n">
-        <x:v>2010</x:v>
-      </x:c>
-      <x:c r="L11" s="19">
-        <x:v>46035.3042476852</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>250</x:v>
-      </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
+      <x:c r="B12" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
         <x:v>46014.1352083333</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="20">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J12" s="15" t="n">
+      <x:c r="J12" s="18" t="n">
         <x:v>1216066</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="21" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="22">
         <x:v>46035.0802662037</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>250</x:v>
+      <x:c r="M12" s="17" t="s">
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
+      <x:c r="B13" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
         <x:v>46014.4844097222</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="20">
         <x:v>45786</x:v>
       </x:c>
-      <x:c r="J13" s="15" t="n">
+      <x:c r="J13" s="18" t="n">
         <x:v>1216060</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="21" t="n">
         <x:v>2430</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="22">
         <x:v>46031.0514583333</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>250</x:v>
+      <x:c r="M13" s="17" t="s">
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s"/>
-      <x:c r="E14" s="14" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
+      <x:c r="B14" s="17" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="s"/>
+      <x:c r="E14" s="17" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
         <x:v>46043.045474537</x:v>
       </x:c>
-      <x:c r="I14" s="16">
+      <x:c r="I14" s="19">
         <x:v>46043.0455092593</x:v>
       </x:c>
-      <x:c r="J14" s="15" t="n">
+      <x:c r="J14" s="18" t="n">
         <x:v>1216091</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="21" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="22">
         <x:v>46048.2516435185</x:v>
       </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M14" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
+      <x:c r="B15" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
         <x:v>46036.929224537</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="20">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J15" s="15" t="n">
+      <x:c r="J15" s="18" t="n">
         <x:v>1216095</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="21" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="22">
         <x:v>46050.0472337963</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M15" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="20" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C18" s="21" t="s"/>
-      <x:c r="D18" s="21" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="22" t="s"/>
+      <x:c r="B18" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C18" s="24" t="s"/>
+      <x:c r="D18" s="24" t="s"/>
+      <x:c r="E18" s="25" t="s"/>
+      <x:c r="F18" s="25" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="23" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="s">
+      <x:c r="B19" s="26" t="s">
         <x:v>44</x:v>
       </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="B20" s="29" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C20" s="30" t="s"/>
+      <x:c r="D20" s="30" t="s"/>
+      <x:c r="E20" s="30" t="s"/>
+      <x:c r="F20" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+      <x:c r="B21" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C21" s="30" t="s"/>
+      <x:c r="D21" s="30" t="s"/>
+      <x:c r="E21" s="30" t="s"/>
+      <x:c r="F21" s="31" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="B22" s="29" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C22" s="30" t="s"/>
+      <x:c r="D22" s="30" t="s"/>
+      <x:c r="E22" s="30" t="s"/>
+      <x:c r="F22" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
+      <x:c r="B23" s="29" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C23" s="30" t="s"/>
+      <x:c r="D23" s="30" t="s"/>
+      <x:c r="E23" s="30" t="s"/>
+      <x:c r="F23" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="29" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C24" s="30" t="s"/>
-      <x:c r="D24" s="30" t="s"/>
-      <x:c r="E24" s="30" t="s"/>
-      <x:c r="F24" s="31" t="n">
+      <x:c r="B24" s="32" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C24" s="33" t="s"/>
+      <x:c r="D24" s="33" t="s"/>
+      <x:c r="E24" s="33" t="s"/>
+      <x:c r="F24" s="34" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -11891,7 +11960,7 @@
   <x:mergeCells count="10">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B18:F18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
@@ -11939,58 +12008,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -12033,488 +12102,488 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="B8" s="14" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46051.2691319444</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="15">
         <x:v>46051.2691550926</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1216103</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>2070</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46057.9587152778</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="B9" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>46051.1259722222</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="35">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1216112</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="16" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>46062.966400463</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="B10" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
         <x:v>46050.2853935185</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="20">
         <x:v>45945</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="18" t="n">
         <x:v>1216106</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="21" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="22">
         <x:v>46058.0440046296</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M10" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
+      <x:c r="B11" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
         <x:v>46057.2800462963</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="20">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
+      <x:c r="J11" s="18" t="n">
         <x:v>1216117</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="21" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="22">
         <x:v>46065.2796412037</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M11" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
+      <x:c r="B12" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
         <x:v>46057.272025463</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="20">
         <x:v>46045</x:v>
       </x:c>
-      <x:c r="J12" s="15" t="n">
+      <x:c r="J12" s="18" t="n">
         <x:v>1216121</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="21" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="22">
         <x:v>46065.2951388889</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M12" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="B13" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
+      <x:c r="D13" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
         <x:v>46057.2657523148</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="20">
         <x:v>46039</x:v>
       </x:c>
-      <x:c r="J13" s="15" t="n">
+      <x:c r="J13" s="18" t="n">
         <x:v>1216119</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="21" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="22">
         <x:v>46065.285474537</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M13" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
+      <x:c r="B14" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
         <x:v>46056.1690046296</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="20">
         <x:v>45716</x:v>
       </x:c>
-      <x:c r="J14" s="15" t="n">
+      <x:c r="J14" s="18" t="n">
         <x:v>1216107</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="21" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="22">
         <x:v>46058.1034490741</x:v>
       </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M14" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
+      <x:c r="B15" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
         <x:v>46065.2312962963</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="20">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J15" s="15" t="n">
+      <x:c r="J15" s="18" t="n">
         <x:v>1216134</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="21" t="n">
         <x:v>2190</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="22">
         <x:v>46076.0858333333</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M15" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
+      <x:c r="B16" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="H16" s="19">
         <x:v>46063.0357060185</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="20">
         <x:v>46066</x:v>
       </x:c>
-      <x:c r="J16" s="15" t="n">
+      <x:c r="J16" s="18" t="n">
         <x:v>1216123</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="21" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="22">
         <x:v>46066.0203819444</x:v>
       </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M16" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
+      <x:c r="B17" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E17" s="17" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="F17" s="17" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="H17" s="19">
         <x:v>46051.2882638889</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="20">
         <x:v>44445</x:v>
       </x:c>
-      <x:c r="J17" s="15" t="n">
+      <x:c r="J17" s="18" t="n">
         <x:v>1216104</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="21" t="n">
         <x:v>960</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="22">
         <x:v>46057.963587963</x:v>
       </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M17" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="20" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C20" s="21" t="s"/>
-      <x:c r="D20" s="21" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="22" t="s"/>
+      <x:c r="B20" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C20" s="24" t="s"/>
+      <x:c r="D20" s="24" t="s"/>
+      <x:c r="E20" s="25" t="s"/>
+      <x:c r="F20" s="25" t="s"/>
     </x:row>
     <x:row r="21" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B21" s="23" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C21" s="24" t="s"/>
-      <x:c r="D21" s="24" t="s"/>
-      <x:c r="E21" s="24" t="s"/>
-      <x:c r="F21" s="25" t="s">
+      <x:c r="B21" s="26" t="s">
         <x:v>44</x:v>
       </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="B22" s="29" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="C22" s="30" t="s"/>
+      <x:c r="D22" s="30" t="s"/>
+      <x:c r="E22" s="30" t="s"/>
+      <x:c r="F22" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
+      <x:c r="B23" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C23" s="30" t="s"/>
+      <x:c r="D23" s="30" t="s"/>
+      <x:c r="E23" s="30" t="s"/>
+      <x:c r="F23" s="31" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
+      <x:c r="B24" s="29" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C24" s="30" t="s"/>
+      <x:c r="D24" s="30" t="s"/>
+      <x:c r="E24" s="30" t="s"/>
+      <x:c r="F24" s="31" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="29" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C25" s="30" t="s"/>
-      <x:c r="D25" s="30" t="s"/>
-      <x:c r="E25" s="30" t="s"/>
-      <x:c r="F25" s="31" t="n">
+      <x:c r="B25" s="32" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C25" s="33" t="s"/>
+      <x:c r="D25" s="33" t="s"/>
+      <x:c r="E25" s="33" t="s"/>
+      <x:c r="F25" s="34" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -13490,7 +13559,7 @@
   <x:mergeCells count="9">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B20:F20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
@@ -13537,58 +13606,58 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s">
+      <x:c r="B2" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="12" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s"/>
+      <x:c r="D3" s="12" t="s"/>
+      <x:c r="E3" s="12" t="s"/>
+      <x:c r="F3" s="12" t="s"/>
+      <x:c r="G3" s="12" t="s"/>
+      <x:c r="H3" s="12" t="s"/>
+      <x:c r="I3" s="12" t="s"/>
+      <x:c r="J3" s="12" t="s"/>
+      <x:c r="K3" s="12" t="s"/>
+      <x:c r="L3" s="12" t="s"/>
+      <x:c r="M3" s="12" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
@@ -13631,1373 +13700,1373 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>13</x:v>
+      </x:c>
+      <x:c r="M7" s="13" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="B8" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="H8" s="15">
         <x:v>46065.33125</x:v>
       </x:c>
-      <x:c r="I8" s="32">
+      <x:c r="I8" s="35">
         <x:v>45700</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="14" t="n">
         <x:v>1216139</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="16" t="n">
         <x:v>510</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="15">
         <x:v>46084.1560763889</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M8" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="s">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="B9" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C9" s="14" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="G9" s="14" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>46085.2764814815</x:v>
       </x:c>
-      <x:c r="I9" s="32">
+      <x:c r="I9" s="35">
         <x:v>44879</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="14" t="n">
         <x:v>1216175</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="16" t="n">
         <x:v>1290</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="15">
         <x:v>46093.2000115741</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
-        <x:v>20</x:v>
+      <x:c r="M9" s="14" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>322</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>323</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
+      <x:c r="B10" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C10" s="17" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E10" s="17" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="F10" s="17" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="G10" s="17" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="H10" s="19">
         <x:v>46065.2288541667</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="20">
         <x:v>46070</x:v>
       </x:c>
-      <x:c r="J10" s="15" t="n">
+      <x:c r="J10" s="18" t="n">
         <x:v>1216140</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="21" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="22">
         <x:v>46084.1582175926</x:v>
       </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M10" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>324</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>325</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="s">
-        <x:v>326</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
+      <x:c r="B11" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C11" s="17" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E11" s="17" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="F11" s="17" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="G11" s="17" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="H11" s="19">
         <x:v>46085.3007986111</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="20">
         <x:v>46386</x:v>
       </x:c>
-      <x:c r="J11" s="15" t="n">
+      <x:c r="J11" s="18" t="n">
         <x:v>1216177</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="21" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="22">
         <x:v>46093.215162037</x:v>
       </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M11" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B12" s="14" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C12" s="14" t="s">
-        <x:v>328</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E12" s="14" t="s">
-        <x:v>329</x:v>
-      </x:c>
-      <x:c r="F12" s="14" t="s">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="G12" s="14" t="s">
-        <x:v>331</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
+      <x:c r="B12" s="17" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C12" s="17" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E12" s="17" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="F12" s="17" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="G12" s="17" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="H12" s="19">
         <x:v>46085.2858333333</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="20">
         <x:v>46096</x:v>
       </x:c>
-      <x:c r="J12" s="15" t="n">
+      <x:c r="J12" s="18" t="n">
         <x:v>1216176</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="21" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="22">
         <x:v>46093.2057060185</x:v>
       </x:c>
-      <x:c r="M12" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M12" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B13" s="14" t="s">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="C13" s="14" t="s">
-        <x:v>333</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>335</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>336</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
+      <x:c r="B13" s="17" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="17" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="F13" s="17" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="G13" s="17" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="H13" s="19">
         <x:v>46088.1798263889</x:v>
       </x:c>
-      <x:c r="I13" s="16">
+      <x:c r="I13" s="19">
         <x:v>46088.179837963</x:v>
       </x:c>
-      <x:c r="J13" s="15" t="n">
+      <x:c r="J13" s="18" t="n">
         <x:v>1216179</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="21" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="22">
         <x:v>46093.2393865741</x:v>
       </x:c>
-      <x:c r="M13" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M13" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B14" s="14" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C14" s="14" t="s">
-        <x:v>337</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
-        <x:v>338</x:v>
-      </x:c>
-      <x:c r="F14" s="14" t="s">
-        <x:v>339</x:v>
-      </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>340</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
+      <x:c r="B14" s="17" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="H14" s="19">
         <x:v>46076.2809953704</x:v>
       </x:c>
-      <x:c r="I14" s="16">
+      <x:c r="I14" s="19">
         <x:v>46076.2810185185</x:v>
       </x:c>
-      <x:c r="J14" s="15" t="n">
+      <x:c r="J14" s="18" t="n">
         <x:v>1216194</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="21" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="22">
         <x:v>46097.2411111111</x:v>
       </x:c>
-      <x:c r="M14" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M14" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B15" s="14" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C15" s="14" t="s">
-        <x:v>341</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
-        <x:v>342</x:v>
-      </x:c>
-      <x:c r="F15" s="14" t="s">
-        <x:v>343</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>344</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
+      <x:c r="B15" s="17" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C15" s="17" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="17" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="F15" s="17" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="G15" s="17" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="H15" s="19">
         <x:v>46076.2578009259</x:v>
       </x:c>
-      <x:c r="I15" s="16">
+      <x:c r="I15" s="19">
         <x:v>46076.2578240741</x:v>
       </x:c>
-      <x:c r="J15" s="15" t="n">
+      <x:c r="J15" s="18" t="n">
         <x:v>1216197</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="21" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="22">
         <x:v>46097.2583912037</x:v>
       </x:c>
-      <x:c r="M15" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M15" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B16" s="14" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C16" s="14" t="s">
+      <x:c r="B16" s="17" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C16" s="17" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="17" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="F16" s="17" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="G16" s="17" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="H16" s="19">
+        <x:v>46076.2633564815</x:v>
+      </x:c>
+      <x:c r="I16" s="19">
+        <x:v>46076.2633680556</x:v>
+      </x:c>
+      <x:c r="J16" s="18" t="n">
+        <x:v>1216188</x:v>
+      </x:c>
+      <x:c r="K16" s="21" t="n">
+        <x:v>4530</x:v>
+      </x:c>
+      <x:c r="L16" s="22">
+        <x:v>46094.1562731481</x:v>
+      </x:c>
+      <x:c r="M16" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B17" s="17" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C17" s="17" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="17" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="F17" s="17" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="G17" s="17" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="H17" s="19">
+        <x:v>46076.3755324074</x:v>
+      </x:c>
+      <x:c r="I17" s="19">
+        <x:v>46076.3755439815</x:v>
+      </x:c>
+      <x:c r="J17" s="18" t="n">
+        <x:v>1216189</x:v>
+      </x:c>
+      <x:c r="K17" s="21" t="n">
+        <x:v>3530</x:v>
+      </x:c>
+      <x:c r="L17" s="22">
+        <x:v>46094.1653935185</x:v>
+      </x:c>
+      <x:c r="M17" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B18" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="H18" s="19">
+        <x:v>46046.1343634259</x:v>
+      </x:c>
+      <x:c r="I18" s="20">
+        <x:v>45917</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="n">
+        <x:v>1216183</x:v>
+      </x:c>
+      <x:c r="K18" s="21" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L18" s="22">
+        <x:v>46093.2878703704</x:v>
+      </x:c>
+      <x:c r="M18" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B19" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C19" s="17" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E19" s="17" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="F19" s="17" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="G19" s="17" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="H19" s="19">
+        <x:v>46046.1309027778</x:v>
+      </x:c>
+      <x:c r="I19" s="20">
+        <x:v>46021</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="n">
+        <x:v>1216181</x:v>
+      </x:c>
+      <x:c r="K19" s="21" t="n">
+        <x:v>5280</x:v>
+      </x:c>
+      <x:c r="L19" s="22">
+        <x:v>46093.273287037</x:v>
+      </x:c>
+      <x:c r="M19" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B20" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C20" s="17" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="G20" s="17" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="H20" s="19">
+        <x:v>46046.1237615741</x:v>
+      </x:c>
+      <x:c r="I20" s="20">
+        <x:v>45991</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="n">
+        <x:v>1216180</x:v>
+      </x:c>
+      <x:c r="K20" s="21" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L20" s="22">
+        <x:v>46093.2636342593</x:v>
+      </x:c>
+      <x:c r="M20" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B21" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C21" s="17" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E21" s="17" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="F21" s="17" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="G21" s="17" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="H21" s="19">
+        <x:v>46046.1140856482</x:v>
+      </x:c>
+      <x:c r="I21" s="20">
+        <x:v>46024</x:v>
+      </x:c>
+      <x:c r="J21" s="18" t="n">
+        <x:v>1216182</x:v>
+      </x:c>
+      <x:c r="K21" s="21" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L21" s="22">
+        <x:v>46093.2825231481</x:v>
+      </x:c>
+      <x:c r="M21" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B22" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C22" s="17" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E22" s="17" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="F22" s="17" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="G22" s="17" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="H22" s="19">
+        <x:v>46048.0974768518</x:v>
+      </x:c>
+      <x:c r="I22" s="20">
+        <x:v>45883</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="n">
+        <x:v>1216184</x:v>
+      </x:c>
+      <x:c r="K22" s="21" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L22" s="22">
+        <x:v>46093.2926041667</x:v>
+      </x:c>
+      <x:c r="M22" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B23" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C23" s="17" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E23" s="17" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="F23" s="17" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="G23" s="17" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="H23" s="19">
+        <x:v>46076.318900463</x:v>
+      </x:c>
+      <x:c r="I23" s="20">
+        <x:v>46074</x:v>
+      </x:c>
+      <x:c r="J23" s="18" t="n">
+        <x:v>1216168</x:v>
+      </x:c>
+      <x:c r="K23" s="21" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="L23" s="22">
+        <x:v>46092.1400231481</x:v>
+      </x:c>
+      <x:c r="M23" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B24" s="17" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="s">
         <x:v>345</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>346</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>347</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>348</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46076.2633564815</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46076.2633680556</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="n">
-        <x:v>1216188</x:v>
-      </x:c>
-      <x:c r="K16" s="18" t="n">
-        <x:v>4530</x:v>
-      </x:c>
-      <x:c r="L16" s="19">
-        <x:v>46094.1562731481</x:v>
-      </x:c>
-      <x:c r="M16" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B17" s="14" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C17" s="14" t="s">
+      <x:c r="D24" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E24" s="17" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="F24" s="17" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="G24" s="17" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="H24" s="19">
+        <x:v>46079.2852546296</x:v>
+      </x:c>
+      <x:c r="I24" s="19">
+        <x:v>46079.2852662037</x:v>
+      </x:c>
+      <x:c r="J24" s="18" t="n">
+        <x:v>1216195</x:v>
+      </x:c>
+      <x:c r="K24" s="21" t="n">
+        <x:v>2130</x:v>
+      </x:c>
+      <x:c r="L24" s="22">
+        <x:v>46097.2459143518</x:v>
+      </x:c>
+      <x:c r="M24" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B25" s="17" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C25" s="17" t="s">
         <x:v>349</x:v>
       </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>350</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>351</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>352</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46076.3755324074</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>46076.3755439815</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="n">
-        <x:v>1216189</x:v>
-      </x:c>
-      <x:c r="K17" s="18" t="n">
-        <x:v>3530</x:v>
-      </x:c>
-      <x:c r="L17" s="19">
-        <x:v>46094.1653935185</x:v>
-      </x:c>
-      <x:c r="M17" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B18" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C18" s="14" t="s">
-        <x:v>353</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E18" s="14" t="s">
-        <x:v>354</x:v>
-      </x:c>
-      <x:c r="F18" s="14" t="s">
-        <x:v>355</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="s">
-        <x:v>356</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46046.1343634259</x:v>
-      </x:c>
-      <x:c r="I18" s="17">
-        <x:v>45917</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="n">
-        <x:v>1216183</x:v>
-      </x:c>
-      <x:c r="K18" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L18" s="19">
-        <x:v>46093.2878703704</x:v>
-      </x:c>
-      <x:c r="M18" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B19" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C19" s="14" t="s">
-        <x:v>357</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
-        <x:v>358</x:v>
-      </x:c>
-      <x:c r="F19" s="14" t="s">
-        <x:v>359</x:v>
-      </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46046.1309027778</x:v>
-      </x:c>
-      <x:c r="I19" s="17">
-        <x:v>46021</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="n">
-        <x:v>1216181</x:v>
-      </x:c>
-      <x:c r="K19" s="18" t="n">
-        <x:v>5280</x:v>
-      </x:c>
-      <x:c r="L19" s="19">
-        <x:v>46093.273287037</x:v>
-      </x:c>
-      <x:c r="M19" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B20" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>357</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E20" s="14" t="s">
-        <x:v>361</x:v>
-      </x:c>
-      <x:c r="F20" s="14" t="s">
-        <x:v>362</x:v>
-      </x:c>
-      <x:c r="G20" s="14" t="s">
-        <x:v>363</x:v>
-      </x:c>
-      <x:c r="H20" s="16">
-        <x:v>46046.1237615741</x:v>
-      </x:c>
-      <x:c r="I20" s="17">
-        <x:v>45991</x:v>
-      </x:c>
-      <x:c r="J20" s="15" t="n">
-        <x:v>1216180</x:v>
-      </x:c>
-      <x:c r="K20" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L20" s="19">
-        <x:v>46093.2636342593</x:v>
-      </x:c>
-      <x:c r="M20" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B21" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C21" s="14" t="s">
-        <x:v>364</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E21" s="14" t="s">
-        <x:v>365</x:v>
-      </x:c>
-      <x:c r="F21" s="14" t="s">
-        <x:v>366</x:v>
-      </x:c>
-      <x:c r="G21" s="14" t="s">
-        <x:v>367</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46046.1140856482</x:v>
-      </x:c>
-      <x:c r="I21" s="17">
-        <x:v>46024</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="n">
-        <x:v>1216182</x:v>
-      </x:c>
-      <x:c r="K21" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L21" s="19">
-        <x:v>46093.2825231481</x:v>
-      </x:c>
-      <x:c r="M21" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B22" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C22" s="14" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
-        <x:v>369</x:v>
-      </x:c>
-      <x:c r="F22" s="14" t="s">
-        <x:v>370</x:v>
-      </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>371</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46048.0974768518</x:v>
-      </x:c>
-      <x:c r="I22" s="17">
-        <x:v>45883</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="n">
-        <x:v>1216184</x:v>
-      </x:c>
-      <x:c r="K22" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L22" s="19">
-        <x:v>46093.2926041667</x:v>
-      </x:c>
-      <x:c r="M22" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B23" s="14" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C23" s="14" t="s">
-        <x:v>372</x:v>
-      </x:c>
-      <x:c r="D23" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E23" s="14" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="s">
-        <x:v>374</x:v>
-      </x:c>
-      <x:c r="G23" s="14" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46076.318900463</x:v>
-      </x:c>
-      <x:c r="I23" s="17">
-        <x:v>46074</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="n">
-        <x:v>1216168</x:v>
-      </x:c>
-      <x:c r="K23" s="18" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="L23" s="19">
-        <x:v>46092.1400231481</x:v>
-      </x:c>
-      <x:c r="M23" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B24" s="14" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>337</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>377</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>378</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>379</x:v>
-      </x:c>
-      <x:c r="H24" s="16">
-        <x:v>46079.2852546296</x:v>
-      </x:c>
-      <x:c r="I24" s="16">
-        <x:v>46079.2852662037</x:v>
-      </x:c>
-      <x:c r="J24" s="15" t="n">
-        <x:v>1216195</x:v>
-      </x:c>
-      <x:c r="K24" s="18" t="n">
+      <x:c r="D25" s="18" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E25" s="17" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="F25" s="17" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="G25" s="17" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="H25" s="19">
+        <x:v>46079.2747222222</x:v>
+      </x:c>
+      <x:c r="I25" s="19">
+        <x:v>46079.2747453704</x:v>
+      </x:c>
+      <x:c r="J25" s="18" t="n">
+        <x:v>1216196</x:v>
+      </x:c>
+      <x:c r="K25" s="21" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L24" s="19">
-        <x:v>46097.2459143518</x:v>
-      </x:c>
-      <x:c r="M24" s="14" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B25" s="14" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="C25" s="14" t="s">
-        <x:v>341</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E25" s="14" t="s">
-        <x:v>380</x:v>
-      </x:c>
-      <x:c r="F25" s="14" t="s">
-        <x:v>381</x:v>
-      </x:c>
-      <x:c r="G25" s="14" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46079.2747222222</x:v>
-      </x:c>
-      <x:c r="I25" s="16">
-        <x:v>46079.2747453704</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="n">
-        <x:v>1216196</x:v>
-      </x:c>
-      <x:c r="K25" s="18" t="n">
-        <x:v>2130</x:v>
-      </x:c>
-      <x:c r="L25" s="19">
+      <x:c r="L25" s="22">
         <x:v>46097.2536342593</x:v>
       </x:c>
-      <x:c r="M25" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M25" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B26" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C26" s="14" t="s">
-        <x:v>383</x:v>
-      </x:c>
-      <x:c r="D26" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E26" s="14" t="s">
-        <x:v>384</x:v>
-      </x:c>
-      <x:c r="F26" s="14" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="G26" s="14" t="s">
-        <x:v>386</x:v>
-      </x:c>
-      <x:c r="H26" s="16">
+      <x:c r="B26" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C26" s="17" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="D26" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E26" s="17" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="F26" s="17" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="G26" s="17" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="H26" s="19">
         <x:v>46076.1792361111</x:v>
       </x:c>
-      <x:c r="I26" s="17">
+      <x:c r="I26" s="20">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J26" s="15" t="n">
+      <x:c r="J26" s="18" t="n">
         <x:v>1216147</x:v>
       </x:c>
-      <x:c r="K26" s="18" t="n">
+      <x:c r="K26" s="21" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L26" s="19">
+      <x:c r="L26" s="22">
         <x:v>46090.2042708333</x:v>
       </x:c>
-      <x:c r="M26" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M26" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B27" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C27" s="14" t="s">
-        <x:v>387</x:v>
-      </x:c>
-      <x:c r="D27" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E27" s="14" t="s">
-        <x:v>388</x:v>
-      </x:c>
-      <x:c r="F27" s="14" t="s">
-        <x:v>389</x:v>
-      </x:c>
-      <x:c r="G27" s="14" t="s">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="H27" s="16">
+      <x:c r="B27" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C27" s="17" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="D27" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E27" s="17" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="F27" s="17" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="G27" s="17" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="H27" s="19">
         <x:v>46076.1139583333</x:v>
       </x:c>
-      <x:c r="I27" s="17">
+      <x:c r="I27" s="20">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J27" s="15" t="n">
+      <x:c r="J27" s="18" t="n">
         <x:v>1216146</x:v>
       </x:c>
-      <x:c r="K27" s="18" t="n">
+      <x:c r="K27" s="21" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L27" s="19">
+      <x:c r="L27" s="22">
         <x:v>46090.1919444444</x:v>
       </x:c>
-      <x:c r="M27" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M27" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B28" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C28" s="14" t="s">
-        <x:v>391</x:v>
-      </x:c>
-      <x:c r="D28" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E28" s="14" t="s">
-        <x:v>392</x:v>
-      </x:c>
-      <x:c r="F28" s="14" t="s">
-        <x:v>393</x:v>
-      </x:c>
-      <x:c r="G28" s="14" t="s">
-        <x:v>394</x:v>
-      </x:c>
-      <x:c r="H28" s="16">
+      <x:c r="B28" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C28" s="17" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="D28" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E28" s="17" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="F28" s="17" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="G28" s="17" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="H28" s="19">
         <x:v>46077.2598726852</x:v>
       </x:c>
-      <x:c r="I28" s="17">
+      <x:c r="I28" s="20">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J28" s="15" t="n">
+      <x:c r="J28" s="18" t="n">
         <x:v>1216158</x:v>
       </x:c>
-      <x:c r="K28" s="18" t="n">
+      <x:c r="K28" s="21" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L28" s="19">
+      <x:c r="L28" s="22">
         <x:v>46090.2758680556</x:v>
       </x:c>
-      <x:c r="M28" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M28" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B29" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C29" s="14" t="s">
-        <x:v>395</x:v>
-      </x:c>
-      <x:c r="D29" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E29" s="14" t="s">
-        <x:v>396</x:v>
-      </x:c>
-      <x:c r="F29" s="14" t="s">
-        <x:v>397</x:v>
-      </x:c>
-      <x:c r="G29" s="14" t="s">
-        <x:v>398</x:v>
-      </x:c>
-      <x:c r="H29" s="16">
+      <x:c r="B29" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C29" s="17" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="D29" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E29" s="17" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="F29" s="17" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="G29" s="17" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="H29" s="19">
         <x:v>46077.4722337963</x:v>
       </x:c>
-      <x:c r="I29" s="17">
+      <x:c r="I29" s="20">
         <x:v>46030</x:v>
       </x:c>
-      <x:c r="J29" s="15" t="n">
+      <x:c r="J29" s="18" t="n">
         <x:v>1216161</x:v>
       </x:c>
-      <x:c r="K29" s="18" t="n">
+      <x:c r="K29" s="21" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L29" s="19">
+      <x:c r="L29" s="22">
         <x:v>46090.2963078704</x:v>
       </x:c>
-      <x:c r="M29" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M29" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B30" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C30" s="14" t="s">
-        <x:v>395</x:v>
-      </x:c>
-      <x:c r="D30" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E30" s="14" t="s">
-        <x:v>399</x:v>
-      </x:c>
-      <x:c r="F30" s="14" t="s">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="G30" s="14" t="s">
-        <x:v>401</x:v>
-      </x:c>
-      <x:c r="H30" s="16">
+      <x:c r="B30" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C30" s="17" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="D30" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E30" s="17" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="F30" s="17" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="G30" s="17" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="H30" s="19">
         <x:v>46077.5191782407</x:v>
       </x:c>
-      <x:c r="I30" s="17">
+      <x:c r="I30" s="20">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J30" s="15" t="n">
+      <x:c r="J30" s="18" t="n">
         <x:v>1216163</x:v>
       </x:c>
-      <x:c r="K30" s="18" t="n">
+      <x:c r="K30" s="21" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L30" s="19">
+      <x:c r="L30" s="22">
         <x:v>46090.3154976852</x:v>
       </x:c>
-      <x:c r="M30" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M30" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B31" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C31" s="14" t="s">
-        <x:v>395</x:v>
-      </x:c>
-      <x:c r="D31" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E31" s="14" t="s">
-        <x:v>402</x:v>
-      </x:c>
-      <x:c r="F31" s="14" t="s">
+      <x:c r="B31" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C31" s="17" t="s">
         <x:v>403</x:v>
       </x:c>
-      <x:c r="G31" s="14" t="s">
-        <x:v>404</x:v>
-      </x:c>
-      <x:c r="H31" s="16">
+      <x:c r="D31" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E31" s="17" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="F31" s="17" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="G31" s="17" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="H31" s="19">
         <x:v>46077.2024189815</x:v>
       </x:c>
-      <x:c r="I31" s="17">
+      <x:c r="I31" s="20">
         <x:v>45948</x:v>
       </x:c>
-      <x:c r="J31" s="15" t="n">
+      <x:c r="J31" s="18" t="n">
         <x:v>1216154</x:v>
       </x:c>
-      <x:c r="K31" s="18" t="n">
+      <x:c r="K31" s="21" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L31" s="19">
+      <x:c r="L31" s="22">
         <x:v>46090.2495949074</x:v>
       </x:c>
-      <x:c r="M31" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M31" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B32" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C32" s="14" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="D32" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E32" s="14" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="F32" s="14" t="s">
-        <x:v>405</x:v>
-      </x:c>
-      <x:c r="G32" s="14" t="s">
-        <x:v>406</x:v>
-      </x:c>
-      <x:c r="H32" s="16">
+      <x:c r="B32" s="17" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C32" s="17" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D32" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E32" s="17" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="F32" s="17" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="G32" s="17" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="H32" s="19">
         <x:v>45988.1893402778</x:v>
       </x:c>
-      <x:c r="I32" s="17">
+      <x:c r="I32" s="20">
         <x:v>45973</x:v>
       </x:c>
-      <x:c r="J32" s="15" t="n">
+      <x:c r="J32" s="18" t="n">
         <x:v>1216173</x:v>
       </x:c>
-      <x:c r="K32" s="18" t="n">
+      <x:c r="K32" s="21" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L32" s="19">
+      <x:c r="L32" s="22">
         <x:v>46093.1383912037</x:v>
       </x:c>
-      <x:c r="M32" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M32" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B33" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C33" s="14" t="s">
-        <x:v>407</x:v>
-      </x:c>
-      <x:c r="D33" s="15" t="s"/>
-      <x:c r="E33" s="14" t="s">
-        <x:v>408</x:v>
-      </x:c>
-      <x:c r="F33" s="14" t="s">
-        <x:v>409</x:v>
-      </x:c>
-      <x:c r="G33" s="14" t="s">
-        <x:v>410</x:v>
-      </x:c>
-      <x:c r="H33" s="16">
+      <x:c r="B33" s="17" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C33" s="17" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="D33" s="18" t="s"/>
+      <x:c r="E33" s="17" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="F33" s="17" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="G33" s="17" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="H33" s="19">
         <x:v>46090.2854050926</x:v>
       </x:c>
-      <x:c r="I33" s="16">
+      <x:c r="I33" s="19">
         <x:v>46090.2854282407</x:v>
       </x:c>
-      <x:c r="J33" s="15" t="s">
-        <x:v>410</x:v>
-      </x:c>
-      <x:c r="K33" s="18" t="n">
+      <x:c r="J33" s="18" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="K33" s="21" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L33" s="19">
+      <x:c r="L33" s="22">
         <x:v>46094.0865740741</x:v>
       </x:c>
-      <x:c r="M33" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M33" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B34" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C34" s="14" t="s">
-        <x:v>411</x:v>
-      </x:c>
-      <x:c r="D34" s="15" t="s"/>
-      <x:c r="E34" s="14" t="s">
-        <x:v>412</x:v>
-      </x:c>
-      <x:c r="F34" s="14" t="s">
-        <x:v>413</x:v>
-      </x:c>
-      <x:c r="G34" s="14" t="s">
-        <x:v>414</x:v>
-      </x:c>
-      <x:c r="H34" s="16">
+      <x:c r="B34" s="17" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C34" s="17" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="D34" s="18" t="s"/>
+      <x:c r="E34" s="17" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="F34" s="17" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="G34" s="17" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="H34" s="19">
         <x:v>46090.2540972222</x:v>
       </x:c>
-      <x:c r="I34" s="16">
+      <x:c r="I34" s="19">
         <x:v>46090.2541203704</x:v>
       </x:c>
-      <x:c r="J34" s="15" t="n">
+      <x:c r="J34" s="18" t="n">
         <x:v>1216185</x:v>
       </x:c>
-      <x:c r="K34" s="18" t="n">
+      <x:c r="K34" s="21" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L34" s="19">
+      <x:c r="L34" s="22">
         <x:v>46094.0818981481</x:v>
       </x:c>
-      <x:c r="M34" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M34" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B35" s="14" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C35" s="14" t="s">
-        <x:v>415</x:v>
-      </x:c>
-      <x:c r="D35" s="15" t="s"/>
-      <x:c r="E35" s="14" t="s">
-        <x:v>412</x:v>
-      </x:c>
-      <x:c r="F35" s="14" t="s">
-        <x:v>416</x:v>
-      </x:c>
-      <x:c r="G35" s="14" t="s">
-        <x:v>417</x:v>
-      </x:c>
-      <x:c r="H35" s="16">
+      <x:c r="B35" s="17" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C35" s="17" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="D35" s="18" t="s"/>
+      <x:c r="E35" s="17" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="F35" s="17" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="G35" s="17" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="H35" s="19">
         <x:v>46090.2349189815</x:v>
       </x:c>
-      <x:c r="I35" s="16">
+      <x:c r="I35" s="19">
         <x:v>46090.2349305556</x:v>
       </x:c>
-      <x:c r="J35" s="15" t="n">
+      <x:c r="J35" s="18" t="n">
         <x:v>1216187</x:v>
       </x:c>
-      <x:c r="K35" s="18" t="n">
+      <x:c r="K35" s="21" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L35" s="19">
+      <x:c r="L35" s="22">
         <x:v>46094.0939351852</x:v>
       </x:c>
-      <x:c r="M35" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M35" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B36" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C36" s="14" t="s">
-        <x:v>418</x:v>
-      </x:c>
-      <x:c r="D36" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E36" s="14" t="s">
-        <x:v>419</x:v>
-      </x:c>
-      <x:c r="F36" s="14" t="s">
-        <x:v>420</x:v>
-      </x:c>
-      <x:c r="G36" s="14" t="s">
-        <x:v>421</x:v>
-      </x:c>
-      <x:c r="H36" s="16">
+      <x:c r="B36" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C36" s="17" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="D36" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E36" s="17" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="F36" s="17" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="G36" s="17" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="H36" s="19">
         <x:v>46077.2103587963</x:v>
       </x:c>
-      <x:c r="I36" s="17">
+      <x:c r="I36" s="20">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J36" s="15" t="n">
+      <x:c r="J36" s="18" t="n">
         <x:v>1216155</x:v>
       </x:c>
-      <x:c r="K36" s="18" t="n">
+      <x:c r="K36" s="21" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L36" s="19">
+      <x:c r="L36" s="22">
         <x:v>46090.2536226852</x:v>
       </x:c>
-      <x:c r="M36" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M36" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B37" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C37" s="14" t="s">
-        <x:v>422</x:v>
-      </x:c>
-      <x:c r="D37" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E37" s="14" t="s">
-        <x:v>423</x:v>
-      </x:c>
-      <x:c r="F37" s="14" t="s">
-        <x:v>424</x:v>
-      </x:c>
-      <x:c r="G37" s="14" t="s">
-        <x:v>425</x:v>
-      </x:c>
-      <x:c r="H37" s="16">
+      <x:c r="B37" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C37" s="17" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="D37" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E37" s="17" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="F37" s="17" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="G37" s="17" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="H37" s="19">
         <x:v>46077.2683564815</x:v>
       </x:c>
-      <x:c r="I37" s="17">
+      <x:c r="I37" s="20">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J37" s="15" t="n">
+      <x:c r="J37" s="18" t="n">
         <x:v>1216159</x:v>
       </x:c>
-      <x:c r="K37" s="18" t="n">
+      <x:c r="K37" s="21" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L37" s="19">
+      <x:c r="L37" s="22">
         <x:v>46090.2806018519</x:v>
       </x:c>
-      <x:c r="M37" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M37" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B38" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C38" s="14" t="s">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="D38" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E38" s="14" t="s">
-        <x:v>427</x:v>
-      </x:c>
-      <x:c r="F38" s="14" t="s">
-        <x:v>428</x:v>
-      </x:c>
-      <x:c r="G38" s="14" t="s">
-        <x:v>429</x:v>
-      </x:c>
-      <x:c r="H38" s="16">
+      <x:c r="B38" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C38" s="17" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="D38" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E38" s="17" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="F38" s="17" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="G38" s="17" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="H38" s="19">
         <x:v>46077.1834259259</x:v>
       </x:c>
-      <x:c r="I38" s="17">
+      <x:c r="I38" s="20">
         <x:v>46115</x:v>
       </x:c>
-      <x:c r="J38" s="15" t="n">
+      <x:c r="J38" s="18" t="n">
         <x:v>1216166</x:v>
       </x:c>
-      <x:c r="K38" s="18" t="n">
+      <x:c r="K38" s="21" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L38" s="19">
+      <x:c r="L38" s="22">
         <x:v>46091.2388773148</x:v>
       </x:c>
-      <x:c r="M38" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M38" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B39" s="14" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C39" s="14" t="s">
-        <x:v>430</x:v>
-      </x:c>
-      <x:c r="D39" s="15" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E39" s="14" t="s">
-        <x:v>431</x:v>
-      </x:c>
-      <x:c r="F39" s="14" t="s">
-        <x:v>432</x:v>
-      </x:c>
-      <x:c r="G39" s="14" t="s">
-        <x:v>433</x:v>
-      </x:c>
-      <x:c r="H39" s="16">
+      <x:c r="B39" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C39" s="17" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="D39" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E39" s="17" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="F39" s="17" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="G39" s="17" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="H39" s="19">
         <x:v>46090.3681365741</x:v>
       </x:c>
-      <x:c r="I39" s="17">
+      <x:c r="I39" s="20">
         <x:v>46101</x:v>
       </x:c>
-      <x:c r="J39" s="15" t="n">
+      <x:c r="J39" s="18" t="n">
         <x:v>1216192</x:v>
       </x:c>
-      <x:c r="K39" s="18" t="n">
+      <x:c r="K39" s="21" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L39" s="19">
+      <x:c r="L39" s="22">
         <x:v>46094.182662037</x:v>
       </x:c>
-      <x:c r="M39" s="14" t="s">
-        <x:v>20</x:v>
+      <x:c r="M39" s="17" t="s">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="42" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B42" s="20" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C42" s="21" t="s"/>
-      <x:c r="D42" s="21" t="s"/>
-      <x:c r="E42" s="22" t="s"/>
-      <x:c r="F42" s="22" t="s"/>
+      <x:c r="B42" s="23" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C42" s="24" t="s"/>
+      <x:c r="D42" s="24" t="s"/>
+      <x:c r="E42" s="25" t="s"/>
+      <x:c r="F42" s="25" t="s"/>
     </x:row>
     <x:row r="43" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B43" s="23" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C43" s="24" t="s"/>
-      <x:c r="D43" s="24" t="s"/>
-      <x:c r="E43" s="24" t="s"/>
-      <x:c r="F43" s="25" t="s">
+      <x:c r="B43" s="26" t="s">
         <x:v>44</x:v>
       </x:c>
+      <x:c r="C43" s="27" t="s"/>
+      <x:c r="D43" s="27" t="s"/>
+      <x:c r="E43" s="27" t="s"/>
+      <x:c r="F43" s="28" t="s">
+        <x:v>45</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B44" s="26" t="s">
+      <x:c r="B44" s="29" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C44" s="30" t="s"/>
+      <x:c r="D44" s="30" t="s"/>
+      <x:c r="E44" s="30" t="s"/>
+      <x:c r="F44" s="31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B45" s="29" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="C45" s="30" t="s"/>
+      <x:c r="D45" s="30" t="s"/>
+      <x:c r="E45" s="30" t="s"/>
+      <x:c r="F45" s="31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B46" s="29" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C46" s="30" t="s"/>
+      <x:c r="D46" s="30" t="s"/>
+      <x:c r="E46" s="30" t="s"/>
+      <x:c r="F46" s="31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B47" s="29" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C47" s="30" t="s"/>
+      <x:c r="D47" s="30" t="s"/>
+      <x:c r="E47" s="30" t="s"/>
+      <x:c r="F47" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B48" s="29" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C48" s="30" t="s"/>
+      <x:c r="D48" s="30" t="s"/>
+      <x:c r="E48" s="30" t="s"/>
+      <x:c r="F48" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B49" s="29" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C49" s="30" t="s"/>
+      <x:c r="D49" s="30" t="s"/>
+      <x:c r="E49" s="30" t="s"/>
+      <x:c r="F49" s="31" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B50" s="29" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C50" s="30" t="s"/>
+      <x:c r="D50" s="30" t="s"/>
+      <x:c r="E50" s="30" t="s"/>
+      <x:c r="F50" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B51" s="29" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C51" s="30" t="s"/>
+      <x:c r="D51" s="30" t="s"/>
+      <x:c r="E51" s="30" t="s"/>
+      <x:c r="F51" s="31" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B52" s="32" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C44" s="27" t="s"/>
-      <x:c r="D44" s="27" t="s"/>
-      <x:c r="E44" s="27" t="s"/>
-      <x:c r="F44" s="28" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B45" s="26" t="s">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="C45" s="27" t="s"/>
-      <x:c r="D45" s="27" t="s"/>
-      <x:c r="E45" s="27" t="s"/>
-      <x:c r="F45" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B46" s="26" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C46" s="27" t="s"/>
-      <x:c r="D46" s="27" t="s"/>
-      <x:c r="E46" s="27" t="s"/>
-      <x:c r="F46" s="28" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="26" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C47" s="27" t="s"/>
-      <x:c r="D47" s="27" t="s"/>
-      <x:c r="E47" s="27" t="s"/>
-      <x:c r="F47" s="28" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="26" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="C48" s="27" t="s"/>
-      <x:c r="D48" s="27" t="s"/>
-      <x:c r="E48" s="27" t="s"/>
-      <x:c r="F48" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="26" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C49" s="27" t="s"/>
-      <x:c r="D49" s="27" t="s"/>
-      <x:c r="E49" s="27" t="s"/>
-      <x:c r="F49" s="28" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="26" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C50" s="27" t="s"/>
-      <x:c r="D50" s="27" t="s"/>
-      <x:c r="E50" s="27" t="s"/>
-      <x:c r="F50" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="26" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C51" s="27" t="s"/>
-      <x:c r="D51" s="27" t="s"/>
-      <x:c r="E51" s="27" t="s"/>
-      <x:c r="F51" s="28" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B52" s="29" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C52" s="30" t="s"/>
-      <x:c r="D52" s="30" t="s"/>
-      <x:c r="E52" s="30" t="s"/>
-      <x:c r="F52" s="31" t="n">
+      <x:c r="C52" s="33" t="s"/>
+      <x:c r="D52" s="33" t="s"/>
+      <x:c r="E52" s="33" t="s"/>
+      <x:c r="F52" s="34" t="n">
         <x:v>32</x:v>
       </x:c>
     </x:row>
@@ -15946,7 +16015,7 @@
   <x:mergeCells count="14">
     <x:mergeCell ref="B1:M1"/>
     <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B42:F42"/>
     <x:mergeCell ref="B43:E43"/>
     <x:mergeCell ref="B44:E44"/>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="442">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="446">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -1112,6 +1112,18 @@
   </x:si>
   <x:si>
     <x:t>61-2-2026-1360-023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3D'S&amp;B CELLPHONE AND ACCESORIES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gumahan, Poblacion, Josefina, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09073370000-0052</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1377-766</x:t>
   </x:si>
   <x:si>
     <x:t>A &amp; B - GADGETZ CELLPHONE AND ACCESSORIES STORE</x:t>
@@ -14228,19 +14240,19 @@
         <x:v>364</x:v>
       </x:c>
       <x:c r="H18" s="19">
-        <x:v>46046.1343634259</x:v>
+        <x:v>46083.2965972222</x:v>
       </x:c>
       <x:c r="I18" s="19">
-        <x:v>45917</x:v>
+        <x:v>46387</x:v>
       </x:c>
       <x:c r="J18" s="18" t="n">
-        <x:v>1216183</x:v>
+        <x:v>1216198</x:v>
       </x:c>
       <x:c r="K18" s="20" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L18" s="21">
-        <x:v>46093.2878703704</x:v>
+        <x:v>46098.2996296296</x:v>
       </x:c>
       <x:c r="M18" s="17" t="s">
         <x:v>21</x:v>
@@ -14266,19 +14278,19 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="H19" s="19">
-        <x:v>46046.1309027778</x:v>
+        <x:v>46046.1343634259</x:v>
       </x:c>
       <x:c r="I19" s="19">
-        <x:v>46021</x:v>
+        <x:v>45917</x:v>
       </x:c>
       <x:c r="J19" s="18" t="n">
-        <x:v>1216181</x:v>
+        <x:v>1216183</x:v>
       </x:c>
       <x:c r="K19" s="20" t="n">
-        <x:v>5280</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L19" s="21">
-        <x:v>46093.273287037</x:v>
+        <x:v>46093.2878703704</x:v>
       </x:c>
       <x:c r="M19" s="17" t="s">
         <x:v>21</x:v>
@@ -14289,34 +14301,34 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="C20" s="17" t="s">
-        <x:v>365</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="D20" s="18" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E20" s="17" t="s">
-        <x:v>369</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="F20" s="17" t="s">
-        <x:v>370</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="G20" s="17" t="s">
-        <x:v>371</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="H20" s="19">
-        <x:v>46046.1237615741</x:v>
+        <x:v>46046.1309027778</x:v>
       </x:c>
       <x:c r="I20" s="19">
-        <x:v>45991</x:v>
+        <x:v>46021</x:v>
       </x:c>
       <x:c r="J20" s="18" t="n">
-        <x:v>1216180</x:v>
+        <x:v>1216181</x:v>
       </x:c>
       <x:c r="K20" s="20" t="n">
-        <x:v>3780</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="L20" s="21">
-        <x:v>46093.2636342593</x:v>
+        <x:v>46093.273287037</x:v>
       </x:c>
       <x:c r="M20" s="17" t="s">
         <x:v>21</x:v>
@@ -14327,7 +14339,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="C21" s="17" t="s">
-        <x:v>372</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="D21" s="18" t="s">
         <x:v>28</x:v>
@@ -14342,19 +14354,19 @@
         <x:v>375</x:v>
       </x:c>
       <x:c r="H21" s="19">
-        <x:v>46046.1140856482</x:v>
+        <x:v>46046.1237615741</x:v>
       </x:c>
       <x:c r="I21" s="19">
-        <x:v>46024</x:v>
+        <x:v>45991</x:v>
       </x:c>
       <x:c r="J21" s="18" t="n">
-        <x:v>1216182</x:v>
+        <x:v>1216180</x:v>
       </x:c>
       <x:c r="K21" s="20" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L21" s="21">
-        <x:v>46093.2825231481</x:v>
+        <x:v>46093.2636342593</x:v>
       </x:c>
       <x:c r="M21" s="17" t="s">
         <x:v>21</x:v>
@@ -14380,19 +14392,19 @@
         <x:v>379</x:v>
       </x:c>
       <x:c r="H22" s="19">
-        <x:v>46048.0974768518</x:v>
+        <x:v>46046.1140856482</x:v>
       </x:c>
       <x:c r="I22" s="19">
-        <x:v>45883</x:v>
+        <x:v>46024</x:v>
       </x:c>
       <x:c r="J22" s="18" t="n">
-        <x:v>1216184</x:v>
+        <x:v>1216182</x:v>
       </x:c>
       <x:c r="K22" s="20" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L22" s="21">
-        <x:v>46093.2926041667</x:v>
+        <x:v>46093.2825231481</x:v>
       </x:c>
       <x:c r="M22" s="17" t="s">
         <x:v>21</x:v>
@@ -14418,19 +14430,19 @@
         <x:v>383</x:v>
       </x:c>
       <x:c r="H23" s="19">
-        <x:v>46076.318900463</x:v>
+        <x:v>46048.0974768518</x:v>
       </x:c>
       <x:c r="I23" s="19">
-        <x:v>46074</x:v>
+        <x:v>45883</x:v>
       </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>1216168</x:v>
+        <x:v>1216184</x:v>
       </x:c>
       <x:c r="K23" s="20" t="n">
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L23" s="21">
-        <x:v>46092.1400231481</x:v>
+        <x:v>46093.2926041667</x:v>
       </x:c>
       <x:c r="M23" s="17" t="s">
         <x:v>21</x:v>
@@ -14438,13 +14450,13 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B24" s="17" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C24" s="17" t="s">
         <x:v>384</x:v>
       </x:c>
-      <x:c r="C24" s="17" t="s">
-        <x:v>345</x:v>
-      </x:c>
       <x:c r="D24" s="18" t="s">
-        <x:v>17</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E24" s="17" t="s">
         <x:v>385</x:v>
@@ -14456,19 +14468,19 @@
         <x:v>387</x:v>
       </x:c>
       <x:c r="H24" s="19">
-        <x:v>46079.2852546296</x:v>
+        <x:v>46076.318900463</x:v>
       </x:c>
       <x:c r="I24" s="19">
-        <x:v>46079.2852662037</x:v>
+        <x:v>46074</x:v>
       </x:c>
       <x:c r="J24" s="18" t="n">
-        <x:v>1216195</x:v>
+        <x:v>1216168</x:v>
       </x:c>
       <x:c r="K24" s="20" t="n">
-        <x:v>2130</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L24" s="21">
-        <x:v>46097.2459143518</x:v>
+        <x:v>46092.1400231481</x:v>
       </x:c>
       <x:c r="M24" s="17" t="s">
         <x:v>21</x:v>
@@ -14476,37 +14488,37 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B25" s="17" t="s">
-        <x:v>384</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="C25" s="17" t="s">
-        <x:v>349</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="D25" s="18" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E25" s="17" t="s">
-        <x:v>388</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="F25" s="17" t="s">
-        <x:v>389</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="G25" s="17" t="s">
-        <x:v>390</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="H25" s="19">
-        <x:v>46079.2747222222</x:v>
+        <x:v>46079.2852546296</x:v>
       </x:c>
       <x:c r="I25" s="19">
-        <x:v>46079.2747453704</x:v>
+        <x:v>46079.2852662037</x:v>
       </x:c>
       <x:c r="J25" s="18" t="n">
-        <x:v>1216196</x:v>
+        <x:v>1216195</x:v>
       </x:c>
       <x:c r="K25" s="20" t="n">
         <x:v>2130</x:v>
       </x:c>
       <x:c r="L25" s="21">
-        <x:v>46097.2536342593</x:v>
+        <x:v>46097.2459143518</x:v>
       </x:c>
       <x:c r="M25" s="17" t="s">
         <x:v>21</x:v>
@@ -14514,13 +14526,13 @@
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B26" s="17" t="s">
-        <x:v>31</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="C26" s="17" t="s">
-        <x:v>391</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="D26" s="18" t="s">
-        <x:v>28</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E26" s="17" t="s">
         <x:v>392</x:v>
@@ -14532,19 +14544,19 @@
         <x:v>394</x:v>
       </x:c>
       <x:c r="H26" s="19">
-        <x:v>46076.1792361111</x:v>
+        <x:v>46079.2747222222</x:v>
       </x:c>
       <x:c r="I26" s="19">
-        <x:v>46058</x:v>
+        <x:v>46079.2747453704</x:v>
       </x:c>
       <x:c r="J26" s="18" t="n">
-        <x:v>1216147</x:v>
+        <x:v>1216196</x:v>
       </x:c>
       <x:c r="K26" s="20" t="n">
-        <x:v>1830</x:v>
+        <x:v>2130</x:v>
       </x:c>
       <x:c r="L26" s="21">
-        <x:v>46090.2042708333</x:v>
+        <x:v>46097.2536342593</x:v>
       </x:c>
       <x:c r="M26" s="17" t="s">
         <x:v>21</x:v>
@@ -14570,19 +14582,19 @@
         <x:v>398</x:v>
       </x:c>
       <x:c r="H27" s="19">
-        <x:v>46076.1139583333</x:v>
+        <x:v>46076.1792361111</x:v>
       </x:c>
       <x:c r="I27" s="19">
-        <x:v>46084</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J27" s="18" t="n">
-        <x:v>1216146</x:v>
+        <x:v>1216147</x:v>
       </x:c>
       <x:c r="K27" s="20" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L27" s="21">
-        <x:v>46090.1919444444</x:v>
+        <x:v>46090.2042708333</x:v>
       </x:c>
       <x:c r="M27" s="17" t="s">
         <x:v>21</x:v>
@@ -14608,19 +14620,19 @@
         <x:v>402</x:v>
       </x:c>
       <x:c r="H28" s="19">
-        <x:v>46077.2598726852</x:v>
+        <x:v>46076.1139583333</x:v>
       </x:c>
       <x:c r="I28" s="19">
-        <x:v>46058</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J28" s="18" t="n">
-        <x:v>1216158</x:v>
+        <x:v>1216146</x:v>
       </x:c>
       <x:c r="K28" s="20" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L28" s="21">
-        <x:v>46090.2758680556</x:v>
+        <x:v>46090.1919444444</x:v>
       </x:c>
       <x:c r="M28" s="17" t="s">
         <x:v>21</x:v>
@@ -14646,19 +14658,19 @@
         <x:v>406</x:v>
       </x:c>
       <x:c r="H29" s="19">
-        <x:v>46077.4722337963</x:v>
+        <x:v>46077.2598726852</x:v>
       </x:c>
       <x:c r="I29" s="19">
-        <x:v>46030</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J29" s="18" t="n">
-        <x:v>1216161</x:v>
+        <x:v>1216158</x:v>
       </x:c>
       <x:c r="K29" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L29" s="21">
-        <x:v>46090.2963078704</x:v>
+        <x:v>46090.2758680556</x:v>
       </x:c>
       <x:c r="M29" s="17" t="s">
         <x:v>21</x:v>
@@ -14669,34 +14681,34 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C30" s="17" t="s">
-        <x:v>403</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D30" s="18" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E30" s="17" t="s">
-        <x:v>407</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="F30" s="17" t="s">
-        <x:v>408</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="G30" s="17" t="s">
-        <x:v>409</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="H30" s="19">
-        <x:v>46077.5191782407</x:v>
+        <x:v>46077.4722337963</x:v>
       </x:c>
       <x:c r="I30" s="19">
-        <x:v>46058</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J30" s="18" t="n">
-        <x:v>1216163</x:v>
+        <x:v>1216161</x:v>
       </x:c>
       <x:c r="K30" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L30" s="21">
-        <x:v>46090.3154976852</x:v>
+        <x:v>46090.2963078704</x:v>
       </x:c>
       <x:c r="M30" s="17" t="s">
         <x:v>21</x:v>
@@ -14707,34 +14719,34 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C31" s="17" t="s">
-        <x:v>403</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D31" s="18" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E31" s="17" t="s">
-        <x:v>410</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="F31" s="17" t="s">
-        <x:v>411</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="G31" s="17" t="s">
-        <x:v>412</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="H31" s="19">
-        <x:v>46077.2024189815</x:v>
+        <x:v>46077.5191782407</x:v>
       </x:c>
       <x:c r="I31" s="19">
-        <x:v>45948</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J31" s="18" t="n">
-        <x:v>1216154</x:v>
+        <x:v>1216163</x:v>
       </x:c>
       <x:c r="K31" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L31" s="21">
-        <x:v>46090.2495949074</x:v>
+        <x:v>46090.3154976852</x:v>
       </x:c>
       <x:c r="M31" s="17" t="s">
         <x:v>21</x:v>
@@ -14745,34 +14757,34 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C32" s="17" t="s">
-        <x:v>128</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="D32" s="18" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E32" s="17" t="s">
-        <x:v>129</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="F32" s="17" t="s">
-        <x:v>413</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="G32" s="17" t="s">
-        <x:v>414</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="H32" s="19">
-        <x:v>45988.1893402778</x:v>
+        <x:v>46077.2024189815</x:v>
       </x:c>
       <x:c r="I32" s="19">
-        <x:v>45973</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J32" s="18" t="n">
-        <x:v>1216173</x:v>
+        <x:v>1216154</x:v>
       </x:c>
       <x:c r="K32" s="20" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L32" s="21">
-        <x:v>46093.1383912037</x:v>
+        <x:v>46090.2495949074</x:v>
       </x:c>
       <x:c r="M32" s="17" t="s">
         <x:v>21</x:v>
@@ -14780,14 +14792,16 @@
     </x:row>
     <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B33" s="17" t="s">
-        <x:v>93</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C33" s="17" t="s">
-        <x:v>415</x:v>
-      </x:c>
-      <x:c r="D33" s="18" t="s"/>
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D33" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
       <x:c r="E33" s="17" t="s">
-        <x:v>416</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F33" s="17" t="s">
         <x:v>417</x:v>
@@ -14796,19 +14810,19 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="H33" s="19">
-        <x:v>46090.2854050926</x:v>
+        <x:v>45988.1893402778</x:v>
       </x:c>
       <x:c r="I33" s="19">
-        <x:v>46090.2854282407</x:v>
-      </x:c>
-      <x:c r="J33" s="18" t="s">
-        <x:v>418</x:v>
+        <x:v>45973</x:v>
+      </x:c>
+      <x:c r="J33" s="18" t="n">
+        <x:v>1216173</x:v>
       </x:c>
       <x:c r="K33" s="20" t="n">
-        <x:v>426</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L33" s="21">
-        <x:v>46094.0865740741</x:v>
+        <x:v>46093.1383912037</x:v>
       </x:c>
       <x:c r="M33" s="17" t="s">
         <x:v>21</x:v>
@@ -14832,19 +14846,19 @@
         <x:v>422</x:v>
       </x:c>
       <x:c r="H34" s="19">
-        <x:v>46090.2540972222</x:v>
+        <x:v>46090.2854050926</x:v>
       </x:c>
       <x:c r="I34" s="19">
-        <x:v>46090.2541203704</x:v>
-      </x:c>
-      <x:c r="J34" s="18" t="n">
-        <x:v>1216185</x:v>
+        <x:v>46090.2854282407</x:v>
+      </x:c>
+      <x:c r="J34" s="18" t="s">
+        <x:v>422</x:v>
       </x:c>
       <x:c r="K34" s="20" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L34" s="21">
-        <x:v>46094.0818981481</x:v>
+        <x:v>46094.0865740741</x:v>
       </x:c>
       <x:c r="M34" s="17" t="s">
         <x:v>21</x:v>
@@ -14859,28 +14873,28 @@
       </x:c>
       <x:c r="D35" s="18" t="s"/>
       <x:c r="E35" s="17" t="s">
-        <x:v>420</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="F35" s="17" t="s">
-        <x:v>424</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="G35" s="17" t="s">
-        <x:v>425</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="H35" s="19">
-        <x:v>46090.2349189815</x:v>
+        <x:v>46090.2540972222</x:v>
       </x:c>
       <x:c r="I35" s="19">
-        <x:v>46090.2349305556</x:v>
+        <x:v>46090.2541203704</x:v>
       </x:c>
       <x:c r="J35" s="18" t="n">
-        <x:v>1216187</x:v>
+        <x:v>1216185</x:v>
       </x:c>
       <x:c r="K35" s="20" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L35" s="21">
-        <x:v>46094.0939351852</x:v>
+        <x:v>46094.0818981481</x:v>
       </x:c>
       <x:c r="M35" s="17" t="s">
         <x:v>21</x:v>
@@ -14888,16 +14902,14 @@
     </x:row>
     <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B36" s="17" t="s">
-        <x:v>103</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C36" s="17" t="s">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="D36" s="18" t="s">
-        <x:v>28</x:v>
-      </x:c>
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="D36" s="18" t="s"/>
       <x:c r="E36" s="17" t="s">
-        <x:v>427</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="F36" s="17" t="s">
         <x:v>428</x:v>
@@ -14906,19 +14918,19 @@
         <x:v>429</x:v>
       </x:c>
       <x:c r="H36" s="19">
-        <x:v>46077.2103587963</x:v>
+        <x:v>46090.2349189815</x:v>
       </x:c>
       <x:c r="I36" s="19">
-        <x:v>46042</x:v>
+        <x:v>46090.2349305556</x:v>
       </x:c>
       <x:c r="J36" s="18" t="n">
-        <x:v>1216155</x:v>
+        <x:v>1216187</x:v>
       </x:c>
       <x:c r="K36" s="20" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L36" s="21">
-        <x:v>46090.2536226852</x:v>
+        <x:v>46094.0939351852</x:v>
       </x:c>
       <x:c r="M36" s="17" t="s">
         <x:v>21</x:v>
@@ -14944,19 +14956,19 @@
         <x:v>433</x:v>
       </x:c>
       <x:c r="H37" s="19">
-        <x:v>46077.2683564815</x:v>
+        <x:v>46077.2103587963</x:v>
       </x:c>
       <x:c r="I37" s="19">
-        <x:v>45748</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J37" s="18" t="n">
-        <x:v>1216159</x:v>
+        <x:v>1216155</x:v>
       </x:c>
       <x:c r="K37" s="20" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L37" s="21">
-        <x:v>46090.2806018519</x:v>
+        <x:v>46090.2536226852</x:v>
       </x:c>
       <x:c r="M37" s="17" t="s">
         <x:v>21</x:v>
@@ -14982,19 +14994,19 @@
         <x:v>437</x:v>
       </x:c>
       <x:c r="H38" s="19">
-        <x:v>46077.1834259259</x:v>
+        <x:v>46077.2683564815</x:v>
       </x:c>
       <x:c r="I38" s="19">
-        <x:v>46115</x:v>
+        <x:v>45748</x:v>
       </x:c>
       <x:c r="J38" s="18" t="n">
-        <x:v>1216166</x:v>
+        <x:v>1216159</x:v>
       </x:c>
       <x:c r="K38" s="20" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L38" s="21">
-        <x:v>46091.2388773148</x:v>
+        <x:v>46090.2806018519</x:v>
       </x:c>
       <x:c r="M38" s="17" t="s">
         <x:v>21</x:v>
@@ -15020,146 +15032,183 @@
         <x:v>441</x:v>
       </x:c>
       <x:c r="H39" s="19">
-        <x:v>46090.3681365741</x:v>
+        <x:v>46077.1834259259</x:v>
       </x:c>
       <x:c r="I39" s="19">
-        <x:v>46101</x:v>
+        <x:v>46115</x:v>
       </x:c>
       <x:c r="J39" s="18" t="n">
-        <x:v>1216192</x:v>
+        <x:v>1216166</x:v>
       </x:c>
       <x:c r="K39" s="20" t="n">
         <x:v>210</x:v>
       </x:c>
       <x:c r="L39" s="21">
-        <x:v>46094.182662037</x:v>
+        <x:v>46091.2388773148</x:v>
       </x:c>
       <x:c r="M39" s="17" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B40" s="17" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C40" s="17" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="D40" s="18" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E40" s="17" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="F40" s="17" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="G40" s="17" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="H40" s="19">
+        <x:v>46090.3681365741</x:v>
+      </x:c>
+      <x:c r="I40" s="19">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J40" s="18" t="n">
+        <x:v>1216192</x:v>
+      </x:c>
+      <x:c r="K40" s="20" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L40" s="21">
+        <x:v>46094.182662037</x:v>
+      </x:c>
+      <x:c r="M40" s="17" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="42" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B42" s="22" t="s">
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B43" s="22" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="C42" s="23" t="s"/>
-      <x:c r="D42" s="23" t="s"/>
-      <x:c r="E42" s="24" t="s"/>
-      <x:c r="F42" s="24" t="s"/>
-    </x:row>
-    <x:row r="43" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B43" s="25" t="s">
+      <x:c r="C43" s="23" t="s"/>
+      <x:c r="D43" s="23" t="s"/>
+      <x:c r="E43" s="24" t="s"/>
+      <x:c r="F43" s="24" t="s"/>
+    </x:row>
+    <x:row r="44" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B44" s="25" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C43" s="26" t="s"/>
-      <x:c r="D43" s="26" t="s"/>
-      <x:c r="E43" s="26" t="s"/>
-      <x:c r="F43" s="27" t="s">
+      <x:c r="C44" s="26" t="s"/>
+      <x:c r="D44" s="26" t="s"/>
+      <x:c r="E44" s="26" t="s"/>
+      <x:c r="F44" s="27" t="s">
         <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B44" s="28" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C44" s="29" t="s"/>
-      <x:c r="D44" s="29" t="s"/>
-      <x:c r="E44" s="29" t="s"/>
-      <x:c r="F44" s="30" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:28" ht="18" customHeight="1">
       <x:c r="B45" s="28" t="s">
-        <x:v>340</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C45" s="29" t="s"/>
       <x:c r="D45" s="29" t="s"/>
       <x:c r="E45" s="29" t="s"/>
       <x:c r="F45" s="30" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:28" ht="18" customHeight="1">
       <x:c r="B46" s="28" t="s">
-        <x:v>156</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C46" s="29" t="s"/>
       <x:c r="D46" s="29" t="s"/>
       <x:c r="E46" s="29" t="s"/>
       <x:c r="F46" s="30" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="18" customHeight="1">
       <x:c r="B47" s="28" t="s">
-        <x:v>64</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C47" s="29" t="s"/>
       <x:c r="D47" s="29" t="s"/>
       <x:c r="E47" s="29" t="s"/>
       <x:c r="F47" s="30" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
       <x:c r="B48" s="28" t="s">
-        <x:v>384</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C48" s="29" t="s"/>
       <x:c r="D48" s="29" t="s"/>
       <x:c r="E48" s="29" t="s"/>
       <x:c r="F48" s="30" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="18" customHeight="1">
       <x:c r="B49" s="28" t="s">
-        <x:v>31</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="C49" s="29" t="s"/>
       <x:c r="D49" s="29" t="s"/>
       <x:c r="E49" s="29" t="s"/>
       <x:c r="F49" s="30" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
       <x:c r="B50" s="28" t="s">
-        <x:v>93</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C50" s="29" t="s"/>
       <x:c r="D50" s="29" t="s"/>
       <x:c r="E50" s="29" t="s"/>
       <x:c r="F50" s="30" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="18" customHeight="1">
       <x:c r="B51" s="28" t="s">
-        <x:v>103</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C51" s="29" t="s"/>
       <x:c r="D51" s="29" t="s"/>
       <x:c r="E51" s="29" t="s"/>
       <x:c r="F51" s="30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B52" s="28" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C52" s="29" t="s"/>
+      <x:c r="D52" s="29" t="s"/>
+      <x:c r="E52" s="29" t="s"/>
+      <x:c r="F52" s="30" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B52" s="31" t="s">
+    <x:row r="53" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B53" s="31" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C52" s="32" t="s"/>
-      <x:c r="D52" s="32" t="s"/>
-      <x:c r="E52" s="32" t="s"/>
-      <x:c r="F52" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C53" s="32" t="s"/>
+      <x:c r="D53" s="32" t="s"/>
+      <x:c r="E53" s="32" t="s"/>
+      <x:c r="F53" s="33" t="n">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
     <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
@@ -16106,8 +16155,7 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B42:F42"/>
-    <x:mergeCell ref="B43:E43"/>
+    <x:mergeCell ref="B43:F43"/>
     <x:mergeCell ref="B44:E44"/>
     <x:mergeCell ref="B45:E45"/>
     <x:mergeCell ref="B46:E46"/>
@@ -16117,6 +16165,7 @@
     <x:mergeCell ref="B50:E50"/>
     <x:mergeCell ref="B51:E51"/>
     <x:mergeCell ref="B52:E52"/>
+    <x:mergeCell ref="B53:E53"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="557">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
   <x:si>
     <x:t>EVALUATOR SUMMARY</x:t>
   </x:si>
@@ -1322,6 +1322,21 @@
     <x:t>1216179</x:t>
   </x:si>
   <x:si>
+    <x:t>PMC EXPRESS HUB INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unit no. 227, Robinson Pagadian Mall, F.S. Pajares Ave., Cor. P.L. Urro St., Cor Vincenzo, Sagun St.,, San Francisco, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-II0618A-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1391-148</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216201</x:t>
+  </x:si>
+  <x:si>
     <x:t>COMPRO COMPUTER SHOP</x:t>
   </x:si>
   <x:si>
@@ -1559,6 +1574,18 @@
     <x:t>REMEGIO T. BURBURAN JR.</x:t>
   </x:si>
   <x:si>
+    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS-4878-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-2-2026-1362-288</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216154</x:t>
+  </x:si>
+  <x:si>
     <x:t>N/A N/A, POBLACION, Margosatubig, Zamboanga Del Sur</x:t>
   </x:si>
   <x:si>
@@ -1581,18 +1608,6 @@
   </x:si>
   <x:si>
     <x:t>1216163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N/A Prk. Daisy-2, Poblacion, Margosatubig, Zamboanga Del Sur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MS-4878-23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-2-2026-1362-288</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1216154</x:t>
   </x:si>
   <x:si>
     <x:t>MS9/FV-1283-23</x:t>
@@ -14414,13 +14429,13 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>188</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
         <x:v>430</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
         <x:v>431</x:v>
@@ -14432,19 +14447,19 @@
         <x:v>433</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46076.2810036343</x:v>
+        <x:v>46091.1989145023</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46076.2810195833</x:v>
+        <x:v>46101</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
         <x:v>434</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>4030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46097.2411206366</x:v>
+        <x:v>46106.1492534144</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>22</x:v>
@@ -14470,10 +14485,10 @@
         <x:v>438</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46076.2578122338</x:v>
+        <x:v>46076.2810036343</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46076.2578276505</x:v>
+        <x:v>46076.2810195833</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
         <x:v>439</x:v>
@@ -14482,7 +14497,7 @@
         <x:v>3530</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46097.2583940162</x:v>
+        <x:v>46097.2411206366</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>22</x:v>
@@ -14508,19 +14523,19 @@
         <x:v>443</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46076.263358912</x:v>
+        <x:v>46076.2578122338</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46076.2633790625</x:v>
+        <x:v>46076.2578276505</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
         <x:v>444</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
-        <x:v>4530</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46094.1562770949</x:v>
+        <x:v>46097.2583940162</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>22</x:v>
@@ -14546,19 +14561,19 @@
         <x:v>448</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46076.3755334722</x:v>
+        <x:v>46076.263358912</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46076.3755506134</x:v>
+        <x:v>46076.2633790625</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
         <x:v>449</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46094.1653946759</x:v>
+        <x:v>46094.1562770949</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>22</x:v>
@@ -14566,13 +14581,13 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>73</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
         <x:v>450</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
-        <x:v>30</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E19" s="14" t="s">
         <x:v>451</x:v>
@@ -14584,19 +14599,19 @@
         <x:v>453</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46083.2966067014</x:v>
+        <x:v>46076.3755334722</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46387</x:v>
+        <x:v>46076.3755506134</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
         <x:v>454</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46098.2996351505</x:v>
+        <x:v>46094.1653946759</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>22</x:v>
@@ -14622,10 +14637,10 @@
         <x:v>458</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46046.1343687731</x:v>
+        <x:v>46083.2966067014</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>45917</x:v>
+        <x:v>46387</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
         <x:v>459</x:v>
@@ -14634,7 +14649,7 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46093.2878737037</x:v>
+        <x:v>46098.2996351505</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
         <x:v>22</x:v>
@@ -14660,19 +14675,19 @@
         <x:v>463</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46046.1309132176</x:v>
+        <x:v>46046.1343687731</x:v>
       </x:c>
       <x:c r="I21" s="16">
-        <x:v>46021</x:v>
+        <x:v>45917</x:v>
       </x:c>
       <x:c r="J21" s="15" t="s">
         <x:v>464</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
-        <x:v>5280</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46093.2732890162</x:v>
+        <x:v>46093.2878737037</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>22</x:v>
@@ -14683,34 +14698,34 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>460</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E22" s="14" t="s">
-        <x:v>465</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="F22" s="14" t="s">
-        <x:v>466</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="G22" s="14" t="s">
-        <x:v>467</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46046.1237709144</x:v>
+        <x:v>46046.1309132176</x:v>
       </x:c>
       <x:c r="I22" s="16">
-        <x:v>45991</x:v>
+        <x:v>46021</x:v>
       </x:c>
       <x:c r="J22" s="15" t="s">
-        <x:v>468</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>5280</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46093.2636364931</x:v>
+        <x:v>46093.2732890162</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
         <x:v>22</x:v>
@@ -14721,7 +14736,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>469</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
         <x:v>30</x:v>
@@ -14736,10 +14751,10 @@
         <x:v>472</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46046.1140924306</x:v>
+        <x:v>46046.1237709144</x:v>
       </x:c>
       <x:c r="I23" s="16">
-        <x:v>46024</x:v>
+        <x:v>45991</x:v>
       </x:c>
       <x:c r="J23" s="15" t="s">
         <x:v>473</x:v>
@@ -14748,7 +14763,7 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46093.2825289005</x:v>
+        <x:v>46093.2636364931</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>22</x:v>
@@ -14774,10 +14789,10 @@
         <x:v>477</x:v>
       </x:c>
       <x:c r="H24" s="16">
-        <x:v>46048.0974875347</x:v>
+        <x:v>46046.1140924306</x:v>
       </x:c>
       <x:c r="I24" s="16">
-        <x:v>45883</x:v>
+        <x:v>46024</x:v>
       </x:c>
       <x:c r="J24" s="15" t="s">
         <x:v>478</x:v>
@@ -14786,7 +14801,7 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46093.2926065278</x:v>
+        <x:v>46093.2825289005</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
         <x:v>22</x:v>
@@ -14812,10 +14827,10 @@
         <x:v>482</x:v>
       </x:c>
       <x:c r="H25" s="16">
-        <x:v>46076.3189094676</x:v>
+        <x:v>46048.0974875347</x:v>
       </x:c>
       <x:c r="I25" s="16">
-        <x:v>46074</x:v>
+        <x:v>45883</x:v>
       </x:c>
       <x:c r="J25" s="15" t="s">
         <x:v>483</x:v>
@@ -14824,7 +14839,7 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="L25" s="18">
-        <x:v>46092.1400343403</x:v>
+        <x:v>46093.2926065278</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
         <x:v>22</x:v>
@@ -14832,13 +14847,13 @@
     </x:row>
     <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B26" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
         <x:v>484</x:v>
       </x:c>
-      <x:c r="C26" s="14" t="s">
-        <x:v>430</x:v>
-      </x:c>
       <x:c r="D26" s="15" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E26" s="14" t="s">
         <x:v>485</x:v>
@@ -14850,19 +14865,19 @@
         <x:v>487</x:v>
       </x:c>
       <x:c r="H26" s="16">
-        <x:v>46079.2852568981</x:v>
+        <x:v>46076.3189094676</x:v>
       </x:c>
       <x:c r="I26" s="16">
-        <x:v>46079.2852718981</x:v>
+        <x:v>46074</x:v>
       </x:c>
       <x:c r="J26" s="15" t="s">
         <x:v>488</x:v>
       </x:c>
       <x:c r="K26" s="17" t="n">
-        <x:v>2130</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L26" s="18">
-        <x:v>46097.2459243171</x:v>
+        <x:v>46092.1400343403</x:v>
       </x:c>
       <x:c r="M26" s="14" t="s">
         <x:v>22</x:v>
@@ -14870,7 +14885,7 @@
     </x:row>
     <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B27" s="14" t="s">
-        <x:v>484</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="C27" s="14" t="s">
         <x:v>435</x:v>
@@ -14879,28 +14894,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E27" s="14" t="s">
-        <x:v>489</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="F27" s="14" t="s">
-        <x:v>490</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="G27" s="14" t="s">
-        <x:v>491</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="H27" s="16">
-        <x:v>46079.2747337153</x:v>
+        <x:v>46079.2852568981</x:v>
       </x:c>
       <x:c r="I27" s="16">
-        <x:v>46079.2747495718</x:v>
+        <x:v>46079.2852718981</x:v>
       </x:c>
       <x:c r="J27" s="15" t="s">
-        <x:v>492</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="K27" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
       <x:c r="L27" s="18">
-        <x:v>46097.2536368518</x:v>
+        <x:v>46097.2459243171</x:v>
       </x:c>
       <x:c r="M27" s="14" t="s">
         <x:v>22</x:v>
@@ -14908,13 +14923,13 @@
     </x:row>
     <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B28" s="14" t="s">
-        <x:v>34</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="C28" s="14" t="s">
-        <x:v>493</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="D28" s="15" t="s">
-        <x:v>30</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E28" s="14" t="s">
         <x:v>494</x:v>
@@ -14926,19 +14941,19 @@
         <x:v>496</x:v>
       </x:c>
       <x:c r="H28" s="16">
-        <x:v>46076.1792420602</x:v>
+        <x:v>46079.2747337153</x:v>
       </x:c>
       <x:c r="I28" s="16">
-        <x:v>46058</x:v>
+        <x:v>46079.2747495718</x:v>
       </x:c>
       <x:c r="J28" s="15" t="s">
         <x:v>497</x:v>
       </x:c>
       <x:c r="K28" s="17" t="n">
-        <x:v>1830</x:v>
+        <x:v>2130</x:v>
       </x:c>
       <x:c r="L28" s="18">
-        <x:v>46090.204281088</x:v>
+        <x:v>46097.2536368518</x:v>
       </x:c>
       <x:c r="M28" s="14" t="s">
         <x:v>22</x:v>
@@ -14964,19 +14979,19 @@
         <x:v>501</x:v>
       </x:c>
       <x:c r="H29" s="16">
-        <x:v>46076.1139638194</x:v>
+        <x:v>46076.1792420602</x:v>
       </x:c>
       <x:c r="I29" s="16">
-        <x:v>46084</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J29" s="15" t="s">
         <x:v>502</x:v>
       </x:c>
       <x:c r="K29" s="17" t="n">
-        <x:v>1470</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L29" s="18">
-        <x:v>46090.1919488889</x:v>
+        <x:v>46090.204281088</x:v>
       </x:c>
       <x:c r="M29" s="14" t="s">
         <x:v>22</x:v>
@@ -15002,19 +15017,19 @@
         <x:v>506</x:v>
       </x:c>
       <x:c r="H30" s="16">
-        <x:v>46077.2598841551</x:v>
+        <x:v>46076.1139638194</x:v>
       </x:c>
       <x:c r="I30" s="16">
-        <x:v>46058</x:v>
+        <x:v>46084</x:v>
       </x:c>
       <x:c r="J30" s="15" t="s">
         <x:v>507</x:v>
       </x:c>
       <x:c r="K30" s="17" t="n">
-        <x:v>1830</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L30" s="18">
-        <x:v>46090.2758708681</x:v>
+        <x:v>46090.1919488889</x:v>
       </x:c>
       <x:c r="M30" s="14" t="s">
         <x:v>22</x:v>
@@ -15040,10 +15055,10 @@
         <x:v>511</x:v>
       </x:c>
       <x:c r="H31" s="16">
-        <x:v>46077.4722378472</x:v>
+        <x:v>46077.2598841551</x:v>
       </x:c>
       <x:c r="I31" s="16">
-        <x:v>46030</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J31" s="15" t="s">
         <x:v>512</x:v>
@@ -15052,7 +15067,7 @@
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L31" s="18">
-        <x:v>46090.2963156019</x:v>
+        <x:v>46090.2758708681</x:v>
       </x:c>
       <x:c r="M31" s="14" t="s">
         <x:v>22</x:v>
@@ -15063,34 +15078,34 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C32" s="14" t="s">
-        <x:v>508</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="D32" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E32" s="14" t="s">
-        <x:v>513</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="F32" s="14" t="s">
-        <x:v>514</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="G32" s="14" t="s">
-        <x:v>515</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="H32" s="16">
-        <x:v>46077.5191885417</x:v>
+        <x:v>46077.2024189931</x:v>
       </x:c>
       <x:c r="I32" s="16">
-        <x:v>46058</x:v>
+        <x:v>45948</x:v>
       </x:c>
       <x:c r="J32" s="15" t="s">
-        <x:v>516</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="K32" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L32" s="18">
-        <x:v>46090.3155018056</x:v>
+        <x:v>46090.2496018056</x:v>
       </x:c>
       <x:c r="M32" s="14" t="s">
         <x:v>22</x:v>
@@ -15101,34 +15116,34 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C33" s="14" t="s">
-        <x:v>508</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="D33" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E33" s="14" t="s">
-        <x:v>517</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="F33" s="14" t="s">
-        <x:v>518</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="G33" s="14" t="s">
-        <x:v>519</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="H33" s="16">
-        <x:v>46077.2024189931</x:v>
+        <x:v>46077.4722378472</x:v>
       </x:c>
       <x:c r="I33" s="16">
-        <x:v>45948</x:v>
+        <x:v>46030</x:v>
       </x:c>
       <x:c r="J33" s="15" t="s">
-        <x:v>520</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="K33" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L33" s="18">
-        <x:v>46090.2496018056</x:v>
+        <x:v>46090.2963156019</x:v>
       </x:c>
       <x:c r="M33" s="14" t="s">
         <x:v>22</x:v>
@@ -15139,34 +15154,34 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C34" s="14" t="s">
-        <x:v>152</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="D34" s="15" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E34" s="14" t="s">
-        <x:v>153</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="F34" s="14" t="s">
-        <x:v>521</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="G34" s="14" t="s">
-        <x:v>522</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="H34" s="16">
-        <x:v>45988.189350544</x:v>
+        <x:v>46077.5191885417</x:v>
       </x:c>
       <x:c r="I34" s="16">
-        <x:v>45973</x:v>
+        <x:v>46058</x:v>
       </x:c>
       <x:c r="J34" s="15" t="s">
-        <x:v>523</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="K34" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
       <x:c r="L34" s="18">
-        <x:v>46093.1383928935</x:v>
+        <x:v>46090.3155018056</x:v>
       </x:c>
       <x:c r="M34" s="14" t="s">
         <x:v>22</x:v>
@@ -15174,14 +15189,16 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B35" s="14" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C35" s="14" t="s">
-        <x:v>524</x:v>
-      </x:c>
-      <x:c r="D35" s="15" t="s"/>
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D35" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="E35" s="14" t="s">
-        <x:v>525</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="F35" s="14" t="s">
         <x:v>526</x:v>
@@ -15190,19 +15207,19 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="H35" s="16">
-        <x:v>46090.2854096643</x:v>
+        <x:v>45988.189350544</x:v>
       </x:c>
       <x:c r="I35" s="16">
-        <x:v>46090.2854287153</x:v>
+        <x:v>45973</x:v>
       </x:c>
       <x:c r="J35" s="15" t="s">
-        <x:v>527</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="K35" s="17" t="n">
-        <x:v>426</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="L35" s="18">
-        <x:v>46094.0865837153</x:v>
+        <x:v>46093.1383928935</x:v>
       </x:c>
       <x:c r="M35" s="14" t="s">
         <x:v>22</x:v>
@@ -15213,23 +15230,23 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="C36" s="14" t="s">
-        <x:v>528</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="D36" s="15" t="s"/>
       <x:c r="E36" s="14" t="s">
-        <x:v>529</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="F36" s="14" t="s">
-        <x:v>530</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="G36" s="14" t="s">
-        <x:v>531</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="H36" s="16">
-        <x:v>46090.2541037731</x:v>
+        <x:v>46090.2854096643</x:v>
       </x:c>
       <x:c r="I36" s="16">
-        <x:v>46090.2541222106</x:v>
+        <x:v>46090.2854287153</x:v>
       </x:c>
       <x:c r="J36" s="15" t="s">
         <x:v>532</x:v>
@@ -15238,7 +15255,7 @@
         <x:v>426</x:v>
       </x:c>
       <x:c r="L36" s="18">
-        <x:v>46094.0819034491</x:v>
+        <x:v>46094.0865837153</x:v>
       </x:c>
       <x:c r="M36" s="14" t="s">
         <x:v>22</x:v>
@@ -15253,28 +15270,28 @@
       </x:c>
       <x:c r="D37" s="15" t="s"/>
       <x:c r="E37" s="14" t="s">
-        <x:v>529</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="F37" s="14" t="s">
-        <x:v>534</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="G37" s="14" t="s">
-        <x:v>535</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="H37" s="16">
-        <x:v>46090.2349194444</x:v>
+        <x:v>46090.2541037731</x:v>
       </x:c>
       <x:c r="I37" s="16">
-        <x:v>46090.2349374884</x:v>
+        <x:v>46090.2541222106</x:v>
       </x:c>
       <x:c r="J37" s="15" t="s">
-        <x:v>536</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="K37" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
       <x:c r="L37" s="18">
-        <x:v>46094.093939213</x:v>
+        <x:v>46094.0819034491</x:v>
       </x:c>
       <x:c r="M37" s="14" t="s">
         <x:v>22</x:v>
@@ -15282,16 +15299,14 @@
     </x:row>
     <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B38" s="14" t="s">
-        <x:v>121</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C38" s="14" t="s">
-        <x:v>537</x:v>
-      </x:c>
-      <x:c r="D38" s="15" t="s">
-        <x:v>30</x:v>
-      </x:c>
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="D38" s="15" t="s"/>
       <x:c r="E38" s="14" t="s">
-        <x:v>538</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="F38" s="14" t="s">
         <x:v>539</x:v>
@@ -15300,19 +15315,19 @@
         <x:v>540</x:v>
       </x:c>
       <x:c r="H38" s="16">
-        <x:v>46077.2103691435</x:v>
+        <x:v>46090.2349194444</x:v>
       </x:c>
       <x:c r="I38" s="16">
-        <x:v>46042</x:v>
+        <x:v>46090.2349374884</x:v>
       </x:c>
       <x:c r="J38" s="15" t="s">
         <x:v>541</x:v>
       </x:c>
       <x:c r="K38" s="17" t="n">
-        <x:v>240</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="L38" s="18">
-        <x:v>46090.253629537</x:v>
+        <x:v>46094.093939213</x:v>
       </x:c>
       <x:c r="M38" s="14" t="s">
         <x:v>22</x:v>
@@ -15338,19 +15353,19 @@
         <x:v>545</x:v>
       </x:c>
       <x:c r="H39" s="16">
-        <x:v>46077.2683575231</x:v>
+        <x:v>46077.2103691435</x:v>
       </x:c>
       <x:c r="I39" s="16">
-        <x:v>45748</x:v>
+        <x:v>46042</x:v>
       </x:c>
       <x:c r="J39" s="15" t="s">
         <x:v>546</x:v>
       </x:c>
       <x:c r="K39" s="17" t="n">
-        <x:v>270</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L39" s="18">
-        <x:v>46090.2806125347</x:v>
+        <x:v>46090.253629537</x:v>
       </x:c>
       <x:c r="M39" s="14" t="s">
         <x:v>22</x:v>
@@ -15376,19 +15391,19 @@
         <x:v>550</x:v>
       </x:c>
       <x:c r="H40" s="16">
-        <x:v>46077.1834319213</x:v>
+        <x:v>46077.2683575231</x:v>
       </x:c>
       <x:c r="I40" s="16">
-        <x:v>46115</x:v>
+        <x:v>45748</x:v>
       </x:c>
       <x:c r="J40" s="15" t="s">
         <x:v>551</x:v>
       </x:c>
       <x:c r="K40" s="17" t="n">
-        <x:v>210</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="L40" s="18">
-        <x:v>46091.2388780324</x:v>
+        <x:v>46090.2806125347</x:v>
       </x:c>
       <x:c r="M40" s="14" t="s">
         <x:v>22</x:v>
@@ -15414,10 +15429,10 @@
         <x:v>555</x:v>
       </x:c>
       <x:c r="H41" s="16">
-        <x:v>46090.3681394907</x:v>
+        <x:v>46077.1834319213</x:v>
       </x:c>
       <x:c r="I41" s="16">
-        <x:v>46101</x:v>
+        <x:v>46115</x:v>
       </x:c>
       <x:c r="J41" s="15" t="s">
         <x:v>556</x:v>
@@ -15426,92 +15441,119 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="L41" s="18">
-        <x:v>46094.1826630093</x:v>
+        <x:v>46091.2388780324</x:v>
       </x:c>
       <x:c r="M41" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B42" s="14" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C42" s="14" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="D42" s="15" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E42" s="14" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="G42" s="14" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="H42" s="16">
+        <x:v>46090.3681394907</x:v>
+      </x:c>
+      <x:c r="I42" s="16">
+        <x:v>46101</x:v>
+      </x:c>
+      <x:c r="J42" s="15" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="K42" s="17" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L42" s="18">
+        <x:v>46094.1826630093</x:v>
+      </x:c>
+      <x:c r="M42" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="44" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B44" s="19" t="s">
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B45" s="19" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C44" s="20" t="s"/>
-      <x:c r="D44" s="20" t="s"/>
-      <x:c r="E44" s="21" t="s"/>
-      <x:c r="F44" s="21" t="s"/>
-    </x:row>
-    <x:row r="45" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B45" s="22" t="s">
+      <x:c r="C45" s="20" t="s"/>
+      <x:c r="D45" s="20" t="s"/>
+      <x:c r="E45" s="21" t="s"/>
+      <x:c r="F45" s="21" t="s"/>
+    </x:row>
+    <x:row r="46" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B46" s="22" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="C45" s="23" t="s"/>
-      <x:c r="D45" s="23" t="s"/>
-      <x:c r="E45" s="23" t="s"/>
-      <x:c r="F45" s="24" t="s">
+      <x:c r="C46" s="23" t="s"/>
+      <x:c r="D46" s="23" t="s"/>
+      <x:c r="E46" s="23" t="s"/>
+      <x:c r="F46" s="24" t="s">
         <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B46" s="25" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C46" s="26" t="s"/>
-      <x:c r="D46" s="26" t="s"/>
-      <x:c r="E46" s="26" t="s"/>
-      <x:c r="F46" s="27" t="n">
-        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="18" customHeight="1">
       <x:c r="B47" s="25" t="s">
-        <x:v>424</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C47" s="26" t="s"/>
       <x:c r="D47" s="26" t="s"/>
       <x:c r="E47" s="26" t="s"/>
       <x:c r="F47" s="27" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
       <x:c r="B48" s="25" t="s">
-        <x:v>188</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="C48" s="26" t="s"/>
       <x:c r="D48" s="26" t="s"/>
       <x:c r="E48" s="26" t="s"/>
       <x:c r="F48" s="27" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="18" customHeight="1">
       <x:c r="B49" s="25" t="s">
-        <x:v>73</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C49" s="26" t="s"/>
       <x:c r="D49" s="26" t="s"/>
       <x:c r="E49" s="26" t="s"/>
       <x:c r="F49" s="27" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
       <x:c r="B50" s="25" t="s">
-        <x:v>484</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C50" s="26" t="s"/>
       <x:c r="D50" s="26" t="s"/>
       <x:c r="E50" s="26" t="s"/>
       <x:c r="F50" s="27" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="18" customHeight="1">
       <x:c r="B51" s="25" t="s">
-        <x:v>34</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C51" s="26" t="s"/>
       <x:c r="D51" s="26" t="s"/>
@@ -15522,39 +15564,59 @@
     </x:row>
     <x:row r="52" spans="1:28" ht="18" customHeight="1">
       <x:c r="B52" s="25" t="s">
-        <x:v>109</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="C52" s="26" t="s"/>
       <x:c r="D52" s="26" t="s"/>
       <x:c r="E52" s="26" t="s"/>
       <x:c r="F52" s="27" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="18" customHeight="1">
       <x:c r="B53" s="25" t="s">
-        <x:v>121</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C53" s="26" t="s"/>
       <x:c r="D53" s="26" t="s"/>
       <x:c r="E53" s="26" t="s"/>
       <x:c r="F53" s="27" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B54" s="25" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C54" s="26" t="s"/>
+      <x:c r="D54" s="26" t="s"/>
+      <x:c r="E54" s="26" t="s"/>
+      <x:c r="F54" s="27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B55" s="25" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C55" s="26" t="s"/>
+      <x:c r="D55" s="26" t="s"/>
+      <x:c r="E55" s="26" t="s"/>
+      <x:c r="F55" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B54" s="28" t="s">
+    <x:row r="56" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B56" s="28" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C54" s="29" t="s"/>
-      <x:c r="D54" s="29" t="s"/>
-      <x:c r="E54" s="29" t="s"/>
-      <x:c r="F54" s="30" t="n">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C56" s="29" t="s"/>
+      <x:c r="D56" s="29" t="s"/>
+      <x:c r="E56" s="29" t="s"/>
+      <x:c r="F56" s="30" t="n">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
     <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
@@ -16493,13 +16555,12 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="15">
+  <x:mergeCells count="16">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B44:F44"/>
-    <x:mergeCell ref="B45:E45"/>
+    <x:mergeCell ref="B45:F45"/>
     <x:mergeCell ref="B46:E46"/>
     <x:mergeCell ref="B47:E47"/>
     <x:mergeCell ref="B48:E48"/>
@@ -16509,6 +16570,8 @@
     <x:mergeCell ref="B52:E52"/>
     <x:mergeCell ref="B53:E53"/>
     <x:mergeCell ref="B54:E54"/>
+    <x:mergeCell ref="B55:E55"/>
+    <x:mergeCell ref="B56:E56"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -2566,7 +2566,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -2606,7 +2606,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>15</x:v>
@@ -2645,7 +2645,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -2683,7 +2683,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -2721,7 +2721,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -2759,7 +2759,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -2797,7 +2797,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -4029,7 +4029,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -4069,7 +4069,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>54</x:v>
@@ -4108,7 +4108,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
@@ -4146,7 +4146,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>66</x:v>
       </x:c>
@@ -4184,7 +4184,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -4222,7 +4222,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -4260,7 +4260,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -4298,7 +4298,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -4336,7 +4336,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -4374,7 +4374,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -4412,7 +4412,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -4450,7 +4450,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
         <x:v>109</x:v>
       </x:c>
@@ -4486,7 +4486,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
         <x:v>115</x:v>
       </x:c>
@@ -4524,7 +4524,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
@@ -4562,7 +4562,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
@@ -4600,7 +4600,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
@@ -5878,7 +5878,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -5918,7 +5918,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>54</x:v>
@@ -5957,7 +5957,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -5995,7 +5995,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>146</x:v>
       </x:c>
@@ -6033,7 +6033,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -6069,7 +6069,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -6107,7 +6107,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -6145,7 +6145,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>109</x:v>
       </x:c>
@@ -6181,7 +6181,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>109</x:v>
       </x:c>
@@ -6217,7 +6217,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
@@ -7479,7 +7479,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -7519,7 +7519,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>54</x:v>
@@ -7558,7 +7558,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
@@ -7596,7 +7596,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>188</x:v>
       </x:c>
@@ -7634,7 +7634,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -7672,7 +7672,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -7710,7 +7710,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -7748,7 +7748,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>209</x:v>
       </x:c>
@@ -7786,7 +7786,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>209</x:v>
       </x:c>
@@ -7824,7 +7824,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -7862,7 +7862,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -7900,7 +7900,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -7938,7 +7938,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -7976,7 +7976,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -8014,7 +8014,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -8052,7 +8052,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
         <x:v>109</x:v>
       </x:c>
@@ -8088,7 +8088,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
         <x:v>109</x:v>
       </x:c>
@@ -8124,7 +8124,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
@@ -8162,7 +8162,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
@@ -9426,7 +9426,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -9466,7 +9466,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>73</x:v>
@@ -9505,7 +9505,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -9543,7 +9543,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -9581,7 +9581,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -9619,7 +9619,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -9657,7 +9657,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -9695,7 +9695,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
@@ -9733,7 +9733,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
@@ -10963,7 +10963,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -11003,7 +11003,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>73</x:v>
@@ -11042,7 +11042,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -11080,7 +11080,7 @@
         <x:v>314</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -11118,7 +11118,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -11156,7 +11156,7 @@
         <x:v>314</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -11194,7 +11194,7 @@
         <x:v>314</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -11232,7 +11232,7 @@
         <x:v>314</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>109</x:v>
       </x:c>
@@ -11268,7 +11268,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
@@ -12509,7 +12509,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -12549,7 +12549,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>345</x:v>
@@ -12588,7 +12588,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -12626,7 +12626,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -12664,7 +12664,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -12702,7 +12702,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -12740,7 +12740,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -12778,7 +12778,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -12816,7 +12816,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="33.597656" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -12854,7 +12854,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -12892,7 +12892,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
@@ -14120,7 +14120,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="13" t="s">
         <x:v>3</x:v>
@@ -14160,7 +14160,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="14" t="s">
         <x:v>54</x:v>
@@ -14199,7 +14199,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
@@ -14237,7 +14237,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
@@ -14275,7 +14275,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
@@ -14313,7 +14313,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
@@ -14351,7 +14351,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
@@ -14389,7 +14389,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
         <x:v>424</x:v>
       </x:c>
@@ -14427,7 +14427,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
@@ -14465,7 +14465,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
         <x:v>188</x:v>
       </x:c>
@@ -14503,7 +14503,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
         <x:v>188</x:v>
       </x:c>
@@ -14541,7 +14541,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
         <x:v>188</x:v>
       </x:c>
@@ -14579,7 +14579,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
         <x:v>188</x:v>
       </x:c>
@@ -14617,7 +14617,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -14655,7 +14655,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -14693,7 +14693,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -14731,7 +14731,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -14769,7 +14769,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -14807,7 +14807,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -14845,7 +14845,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
@@ -14883,7 +14883,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="14" t="s">
         <x:v>489</x:v>
       </x:c>
@@ -14921,7 +14921,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
       <x:c r="B28" s="14" t="s">
         <x:v>489</x:v>
       </x:c>
@@ -14959,7 +14959,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
       <x:c r="B29" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -14997,7 +14997,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
       <x:c r="B30" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -15035,7 +15035,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="31" spans="1:28" ht="30" customHeight="1">
       <x:c r="B31" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -15073,7 +15073,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="32" spans="1:28" ht="30" customHeight="1">
       <x:c r="B32" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -15111,7 +15111,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="33" spans="1:28" ht="30" customHeight="1">
       <x:c r="B33" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -15149,7 +15149,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="34" spans="1:28" ht="30" customHeight="1">
       <x:c r="B34" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -15187,7 +15187,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="35" spans="1:28" ht="30" customHeight="1">
       <x:c r="B35" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
@@ -15225,7 +15225,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="36" spans="1:28" ht="30" customHeight="1">
       <x:c r="B36" s="14" t="s">
         <x:v>109</x:v>
       </x:c>
@@ -15261,7 +15261,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="37" spans="1:28" ht="30" customHeight="1">
       <x:c r="B37" s="14" t="s">
         <x:v>109</x:v>
       </x:c>
@@ -15297,7 +15297,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="38" spans="1:28" ht="30" customHeight="1">
       <x:c r="B38" s="14" t="s">
         <x:v>109</x:v>
       </x:c>
@@ -15333,7 +15333,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="39" spans="1:28" ht="30" customHeight="1">
       <x:c r="B39" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
@@ -15371,7 +15371,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="40" spans="1:28" ht="30" customHeight="1">
       <x:c r="B40" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
@@ -15409,7 +15409,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="41" spans="1:28" ht="30" customHeight="1">
       <x:c r="B41" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
@@ -15447,7 +15447,7 @@
         <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="42" spans="1:28" ht="30" customHeight="1">
       <x:c r="B42" s="14" t="s">
         <x:v>121</x:v>
       </x:c>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
   <x:si>
-    <x:t>EVALUATOR SUMMARY</x:t>
+    <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
   <x:si>
     <x:t>REYNALDO YBAÑEZ</x:t>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -14,6 +14,7 @@
     <x:sheet name="January 2026" sheetId="12" r:id="rId12"/>
     <x:sheet name="February 2026" sheetId="13" r:id="rId13"/>
     <x:sheet name="March 2026" sheetId="14" r:id="rId14"/>
+    <x:sheet name="April 2026" sheetId="15" r:id="rId15"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="554">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="564">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -1692,6 +1693,36 @@
   </x:si>
   <x:si>
     <x:t>1216192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHRISTOPHER P. RODA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A Prk. Kahayag, Dumagoc, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-0719-17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1411-353</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBEN S. TAMULA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DISTRICT KAWASHI, POBLACION, Tabina, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1316-24(REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1394-597</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216214</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2419,6 +2450,1299 @@
     </a:fmtScheme>
   </a:themeElements>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="12">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s"/>
+      <x:c r="D5" s="13" t="s"/>
+      <x:c r="E5" s="13" t="s"/>
+      <x:c r="F5" s="13" t="s"/>
+      <x:c r="G5" s="13" t="s"/>
+      <x:c r="H5" s="13" t="s"/>
+      <x:c r="I5" s="13" t="s"/>
+      <x:c r="J5" s="13" t="s"/>
+      <x:c r="K5" s="13" t="s"/>
+      <x:c r="L5" s="13" t="s"/>
+      <x:c r="M5" s="13" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E7" s="14" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L7" s="14" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="H8" s="17">
+        <x:v>46100.1333120023</x:v>
+      </x:c>
+      <x:c r="I8" s="17">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="K8" s="18" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L8" s="19">
+        <x:v>46118.9999416204</x:v>
+      </x:c>
+      <x:c r="M8" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="s">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="H9" s="17">
+        <x:v>46093.1047457407</x:v>
+      </x:c>
+      <x:c r="I9" s="17">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L9" s="19">
+        <x:v>46119.1181697338</x:v>
+      </x:c>
+      <x:c r="M9" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="20" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="22" t="s"/>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="23" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="26" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B15" s="29" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C15" s="30" t="s"/>
+      <x:c r="D15" s="30" t="s"/>
+      <x:c r="E15" s="30" t="s"/>
+      <x:c r="F15" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B5:M5"/>
+    <x:mergeCell ref="B12:F12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="564">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="569">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -1693,6 +1693,21 @@
   </x:si>
   <x:si>
     <x:t>1216192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MINZZ GADGETS AND ACCESSORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Yoho Building Purok tambis, Sanito, Ipil (Capital), Zamboanga Sibugay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRRP-ROIX-07290-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1402-161</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216210</x:t>
   </x:si>
   <x:si>
     <x:t>CHRISTOPHER P. RODA</x:t>
@@ -2623,13 +2638,13 @@
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="15" t="s">
-        <x:v>33</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
         <x:v>554</x:v>
       </x:c>
       <x:c r="D8" s="16" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E8" s="15" t="s">
         <x:v>555</x:v>
@@ -2641,19 +2656,19 @@
         <x:v>557</x:v>
       </x:c>
       <x:c r="H8" s="17">
-        <x:v>46100.1333120023</x:v>
+        <x:v>46097.2931531944</x:v>
       </x:c>
       <x:c r="I8" s="17">
-        <x:v>46115</x:v>
+        <x:v>46097.2931710069</x:v>
       </x:c>
       <x:c r="J8" s="16" t="s">
         <x:v>558</x:v>
       </x:c>
       <x:c r="K8" s="18" t="n">
-        <x:v>1590</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L8" s="19">
-        <x:v>46118.9999416204</x:v>
+        <x:v>46119.1505964699</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
@@ -2679,10 +2694,10 @@
         <x:v>562</x:v>
       </x:c>
       <x:c r="H9" s="17">
-        <x:v>46093.1047457407</x:v>
+        <x:v>46100.1333120023</x:v>
       </x:c>
       <x:c r="I9" s="17">
-        <x:v>46123</x:v>
+        <x:v>46115</x:v>
       </x:c>
       <x:c r="J9" s="16" t="s">
         <x:v>563</x:v>
@@ -2691,58 +2706,105 @@
         <x:v>1590</x:v>
       </x:c>
       <x:c r="L9" s="19">
-        <x:v>46119.1181697338</x:v>
+        <x:v>46118.9999416204</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="s">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="H10" s="17">
+        <x:v>46093.1047457407</x:v>
+      </x:c>
+      <x:c r="I10" s="17">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="K10" s="18" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L10" s="19">
+        <x:v>46119.1181697338</x:v>
+      </x:c>
+      <x:c r="M10" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="20" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="22" t="s"/>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="23" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="26" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="29" t="s">
+    <x:row r="17" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B17" s="29" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C15" s="30" t="s"/>
-      <x:c r="D15" s="30" t="s"/>
-      <x:c r="E15" s="30" t="s"/>
-      <x:c r="F15" s="31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C17" s="30" t="s"/>
+      <x:c r="D17" s="30" t="s"/>
+      <x:c r="E17" s="30" t="s"/>
+      <x:c r="F17" s="31" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3720,15 +3782,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="569">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="580">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -1695,6 +1695,24 @@
     <x:t>1216192</x:t>
   </x:si>
   <x:si>
+    <x:t>Amateur Radio Station License (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LEONILO V. MARTEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N/A PUROK SANTAN, BALANGASAN, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AT-II-91634-18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1415-279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216220</x:t>
+  </x:si>
+  <x:si>
     <x:t>MINZZ GADGETS AND ACCESSORIES SHOP</x:t>
   </x:si>
   <x:si>
@@ -1708,6 +1726,21 @@
   </x:si>
   <x:si>
     <x:t>1216210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMCOR, INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JVR bldg. Rizal avenue, San francisco, Pagadian City (Capital), Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPRR-II0716-17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-1-2026-1296-085</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216221</x:t>
   </x:si>
   <x:si>
     <x:t>CHRISTOPHER P. RODA</x:t>
@@ -2638,37 +2671,37 @@
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="15" t="s">
-        <x:v>184</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="C8" s="15" t="s">
-        <x:v>554</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="D8" s="16" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E8" s="15" t="s">
-        <x:v>555</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="F8" s="15" t="s">
-        <x:v>556</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="G8" s="15" t="s">
-        <x:v>557</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="H8" s="17">
-        <x:v>46097.2931531944</x:v>
+        <x:v>46104.0644558912</x:v>
       </x:c>
       <x:c r="I8" s="17">
-        <x:v>46097.2931710069</x:v>
+        <x:v>45902</x:v>
       </x:c>
       <x:c r="J8" s="16" t="s">
-        <x:v>558</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="K8" s="18" t="n">
-        <x:v>3530</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="L8" s="19">
-        <x:v>46119.1505964699</x:v>
+        <x:v>46120.3413710417</x:v>
       </x:c>
       <x:c r="M8" s="15" t="s">
         <x:v>21</x:v>
@@ -2676,37 +2709,37 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="15" t="s">
-        <x:v>33</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
-        <x:v>559</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="D9" s="16" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="15" t="s">
-        <x:v>560</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="F9" s="15" t="s">
-        <x:v>561</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="G9" s="15" t="s">
-        <x:v>562</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="H9" s="17">
-        <x:v>46100.1333120023</x:v>
+        <x:v>46097.2931531944</x:v>
       </x:c>
       <x:c r="I9" s="17">
-        <x:v>46115</x:v>
+        <x:v>46097.2931710069</x:v>
       </x:c>
       <x:c r="J9" s="16" t="s">
-        <x:v>563</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="K9" s="18" t="n">
-        <x:v>1590</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L9" s="19">
-        <x:v>46118.9999416204</x:v>
+        <x:v>46119.1505964699</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>21</x:v>
@@ -2714,101 +2747,195 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="15" t="s">
-        <x:v>33</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
-        <x:v>564</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="D10" s="16" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E10" s="15" t="s">
-        <x:v>565</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="F10" s="15" t="s">
-        <x:v>566</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="G10" s="15" t="s">
-        <x:v>567</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="H10" s="17">
-        <x:v>46093.1047457407</x:v>
+        <x:v>46049.1592238657</x:v>
       </x:c>
       <x:c r="I10" s="17">
-        <x:v>46123</x:v>
+        <x:v>45939</x:v>
       </x:c>
       <x:c r="J10" s="16" t="s">
-        <x:v>568</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="K10" s="18" t="n">
-        <x:v>1590</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L10" s="19">
-        <x:v>46119.1181697338</x:v>
+        <x:v>46120.3467831597</x:v>
       </x:c>
       <x:c r="M10" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="20" t="s">
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="s">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="H11" s="17">
+        <x:v>46100.1333120023</x:v>
+      </x:c>
+      <x:c r="I11" s="17">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L11" s="19">
+        <x:v>46118.9999416204</x:v>
+      </x:c>
+      <x:c r="M11" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="s">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="s">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="s">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="H12" s="17">
+        <x:v>46093.1047457407</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="K12" s="18" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L12" s="19">
+        <x:v>46119.1181697338</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="20" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="22" t="s"/>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="23" t="s">
+      <x:c r="C15" s="21" t="s"/>
+      <x:c r="D15" s="21" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="22" t="s"/>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B16" s="23" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="s">
+      <x:c r="C16" s="24" t="s"/>
+      <x:c r="D16" s="24" t="s"/>
+      <x:c r="E16" s="24" t="s"/>
+      <x:c r="F16" s="25" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="26" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="s"/>
+      <x:c r="D17" s="27" t="s"/>
+      <x:c r="E17" s="27" t="s"/>
+      <x:c r="F17" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B18" s="26" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="C18" s="27" t="s"/>
+      <x:c r="D18" s="27" t="s"/>
+      <x:c r="E18" s="27" t="s"/>
+      <x:c r="F18" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="26" t="s">
+    <x:row r="19" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B19" s="26" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="s"/>
+      <x:c r="D19" s="27" t="s"/>
+      <x:c r="E19" s="27" t="s"/>
+      <x:c r="F19" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B20" s="26" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
+      <x:c r="C20" s="27" t="s"/>
+      <x:c r="D20" s="27" t="s"/>
+      <x:c r="E20" s="27" t="s"/>
+      <x:c r="F20" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="29" t="s">
+    <x:row r="21" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B21" s="29" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C17" s="30" t="s"/>
-      <x:c r="D17" s="30" t="s"/>
-      <x:c r="E17" s="30" t="s"/>
-      <x:c r="F17" s="31" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C21" s="30" t="s"/>
+      <x:c r="D21" s="30" t="s"/>
+      <x:c r="E21" s="30" t="s"/>
+      <x:c r="F21" s="31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3782,16 +3909,18 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
+  <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B13:F13"/>
-    <x:mergeCell ref="B14:E14"/>
-    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B15:F15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="580">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="585">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -1711,6 +1711,21 @@
   </x:si>
   <x:si>
     <x:t>1216220</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MINZZ GADGETS AND ACCESORIES SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Central Hypermarket Rizal Avenue, Blancia, Molave, Zamboanga Del Sur</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROIX-07277-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1400-190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216222</x:t>
   </x:si>
   <x:si>
     <x:t>MINZZ GADGETS AND ACCESSORIES SHOP</x:t>
@@ -2709,7 +2724,7 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="15" t="s">
-        <x:v>184</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C9" s="15" t="s">
         <x:v>560</x:v>
@@ -2727,19 +2742,19 @@
         <x:v>563</x:v>
       </x:c>
       <x:c r="H9" s="17">
-        <x:v>46097.2931531944</x:v>
+        <x:v>46097.2573180208</x:v>
       </x:c>
       <x:c r="I9" s="17">
-        <x:v>46097.2931710069</x:v>
+        <x:v>46097.2573345602</x:v>
       </x:c>
       <x:c r="J9" s="16" t="s">
         <x:v>564</x:v>
       </x:c>
       <x:c r="K9" s="18" t="n">
-        <x:v>3530</x:v>
+        <x:v>4530</x:v>
       </x:c>
       <x:c r="L9" s="19">
-        <x:v>46119.1505964699</x:v>
+        <x:v>46125.2485400116</x:v>
       </x:c>
       <x:c r="M9" s="15" t="s">
         <x:v>21</x:v>
@@ -2747,13 +2762,13 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="15" t="s">
-        <x:v>71</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C10" s="15" t="s">
         <x:v>565</x:v>
       </x:c>
       <x:c r="D10" s="16" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E10" s="15" t="s">
         <x:v>566</x:v>
@@ -2765,19 +2780,19 @@
         <x:v>568</x:v>
       </x:c>
       <x:c r="H10" s="17">
-        <x:v>46049.1592238657</x:v>
+        <x:v>46097.2931531944</x:v>
       </x:c>
       <x:c r="I10" s="17">
-        <x:v>45939</x:v>
+        <x:v>46097.2931710069</x:v>
       </x:c>
       <x:c r="J10" s="16" t="s">
         <x:v>569</x:v>
       </x:c>
       <x:c r="K10" s="18" t="n">
-        <x:v>3780</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L10" s="19">
-        <x:v>46120.3467831597</x:v>
+        <x:v>46119.1505964699</x:v>
       </x:c>
       <x:c r="M10" s="15" t="s">
         <x:v>21</x:v>
@@ -2785,7 +2800,7 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="15" t="s">
-        <x:v>33</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C11" s="15" t="s">
         <x:v>570</x:v>
@@ -2803,19 +2818,19 @@
         <x:v>573</x:v>
       </x:c>
       <x:c r="H11" s="17">
-        <x:v>46100.1333120023</x:v>
+        <x:v>46049.1592238657</x:v>
       </x:c>
       <x:c r="I11" s="17">
-        <x:v>46115</x:v>
+        <x:v>45939</x:v>
       </x:c>
       <x:c r="J11" s="16" t="s">
         <x:v>574</x:v>
       </x:c>
       <x:c r="K11" s="18" t="n">
-        <x:v>1590</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L11" s="19">
-        <x:v>46118.9999416204</x:v>
+        <x:v>46120.3467831597</x:v>
       </x:c>
       <x:c r="M11" s="15" t="s">
         <x:v>21</x:v>
@@ -2841,10 +2856,10 @@
         <x:v>578</x:v>
       </x:c>
       <x:c r="H12" s="17">
-        <x:v>46093.1047457407</x:v>
+        <x:v>46100.1333120023</x:v>
       </x:c>
       <x:c r="I12" s="17">
-        <x:v>46123</x:v>
+        <x:v>46115</x:v>
       </x:c>
       <x:c r="J12" s="16" t="s">
         <x:v>579</x:v>
@@ -2853,48 +2868,75 @@
         <x:v>1590</x:v>
       </x:c>
       <x:c r="L12" s="19">
-        <x:v>46119.1181697338</x:v>
+        <x:v>46118.9999416204</x:v>
       </x:c>
       <x:c r="M12" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46093.1047457407</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="K13" s="18" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L13" s="19">
+        <x:v>46119.1181697338</x:v>
+      </x:c>
+      <x:c r="M13" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="20" t="s">
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="20" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C15" s="21" t="s"/>
-      <x:c r="D15" s="21" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="22" t="s"/>
-    </x:row>
-    <x:row r="16" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B16" s="23" t="s">
+      <x:c r="C16" s="21" t="s"/>
+      <x:c r="D16" s="21" t="s"/>
+      <x:c r="E16" s="22" t="s"/>
+      <x:c r="F16" s="22" t="s"/>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B17" s="23" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C16" s="24" t="s"/>
-      <x:c r="D16" s="24" t="s"/>
-      <x:c r="E16" s="24" t="s"/>
-      <x:c r="F16" s="25" t="s">
+      <x:c r="C17" s="24" t="s"/>
+      <x:c r="D17" s="24" t="s"/>
+      <x:c r="E17" s="24" t="s"/>
+      <x:c r="F17" s="25" t="s">
         <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="26" t="s">
-        <x:v>554</x:v>
-      </x:c>
-      <x:c r="C17" s="27" t="s"/>
-      <x:c r="D17" s="27" t="s"/>
-      <x:c r="E17" s="27" t="s"/>
-      <x:c r="F17" s="28" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
       <x:c r="B18" s="26" t="s">
-        <x:v>184</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="C18" s="27" t="s"/>
       <x:c r="D18" s="27" t="s"/>
@@ -2905,7 +2947,7 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
       <x:c r="B19" s="26" t="s">
-        <x:v>71</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C19" s="27" t="s"/>
       <x:c r="D19" s="27" t="s"/>
@@ -2916,28 +2958,48 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
       <x:c r="B20" s="26" t="s">
-        <x:v>33</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C20" s="27" t="s"/>
       <x:c r="D20" s="27" t="s"/>
       <x:c r="E20" s="27" t="s"/>
       <x:c r="F20" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="26" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="s"/>
+      <x:c r="D21" s="27" t="s"/>
+      <x:c r="E21" s="27" t="s"/>
+      <x:c r="F21" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="26" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="s"/>
+      <x:c r="D22" s="27" t="s"/>
+      <x:c r="E22" s="27" t="s"/>
+      <x:c r="F22" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="29" t="s">
+    <x:row r="23" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B23" s="29" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C21" s="30" t="s"/>
-      <x:c r="D21" s="30" t="s"/>
-      <x:c r="E21" s="30" t="s"/>
-      <x:c r="F21" s="31" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C23" s="30" t="s"/>
+      <x:c r="D23" s="30" t="s"/>
+      <x:c r="E23" s="30" t="s"/>
+      <x:c r="F23" s="31" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3909,18 +3971,19 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="11">
+  <x:mergeCells count="12">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B15:F15"/>
-    <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B16:F16"/>
     <x:mergeCell ref="B17:E17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="585">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="589">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -1771,6 +1771,18 @@
   </x:si>
   <x:si>
     <x:t>1216212</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NOEMA M.MORGIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1022-19(MOD)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1429-605</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216224</x:t>
   </x:si>
   <x:si>
     <x:t>RUBEN S. TAMULA</x:t>
@@ -2885,69 +2897,96 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="E13" s="15" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="s">
         <x:v>581</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="G13" s="15" t="s">
         <x:v>582</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="H13" s="17">
+        <x:v>46107.098771794</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46161</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
         <x:v>583</x:v>
       </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46093.1047457407</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>46123</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="s">
-        <x:v>584</x:v>
-      </x:c>
       <x:c r="K13" s="18" t="n">
-        <x:v>1590</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L13" s="19">
-        <x:v>46119.1181697338</x:v>
+        <x:v>46126.1382984606</x:v>
       </x:c>
       <x:c r="M13" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46093.1047457407</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L14" s="19">
+        <x:v>46119.1181697338</x:v>
+      </x:c>
+      <x:c r="M14" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="20" t="s">
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="20" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="22" t="s"/>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="23" t="s">
+      <x:c r="C17" s="21" t="s"/>
+      <x:c r="D17" s="21" t="s"/>
+      <x:c r="E17" s="22" t="s"/>
+      <x:c r="F17" s="22" t="s"/>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B18" s="23" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="s">
+      <x:c r="C18" s="24" t="s"/>
+      <x:c r="D18" s="24" t="s"/>
+      <x:c r="E18" s="24" t="s"/>
+      <x:c r="F18" s="25" t="s">
         <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
-        <x:v>554</x:v>
-      </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
       <x:c r="B19" s="26" t="s">
-        <x:v>416</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="C19" s="27" t="s"/>
       <x:c r="D19" s="27" t="s"/>
@@ -2958,7 +2997,7 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
       <x:c r="B20" s="26" t="s">
-        <x:v>184</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C20" s="27" t="s"/>
       <x:c r="D20" s="27" t="s"/>
@@ -2969,7 +3008,7 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
       <x:c r="B21" s="26" t="s">
-        <x:v>71</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C21" s="27" t="s"/>
       <x:c r="D21" s="27" t="s"/>
@@ -2980,27 +3019,37 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="26" t="s">
-        <x:v>33</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C22" s="27" t="s"/>
       <x:c r="D22" s="27" t="s"/>
       <x:c r="E22" s="27" t="s"/>
       <x:c r="F22" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="29" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="26" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="s"/>
+      <x:c r="D23" s="27" t="s"/>
+      <x:c r="E23" s="27" t="s"/>
+      <x:c r="F23" s="28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B24" s="29" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C23" s="30" t="s"/>
-      <x:c r="D23" s="30" t="s"/>
-      <x:c r="E23" s="30" t="s"/>
-      <x:c r="F23" s="31" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C24" s="30" t="s"/>
+      <x:c r="D24" s="30" t="s"/>
+      <x:c r="E24" s="30" t="s"/>
+      <x:c r="F24" s="31" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3976,14 +4025,14 @@
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B16:F16"/>
-    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B17:F17"/>
     <x:mergeCell ref="B18:E18"/>
     <x:mergeCell ref="B19:E19"/>
     <x:mergeCell ref="B20:E20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="589">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="611">
   <x:si>
     <x:t>Application Summary Report by Evaluator</x:t>
   </x:si>
@@ -1758,6 +1758,39 @@
     <x:t>1216221</x:t>
   </x:si>
   <x:si>
+    <x:t>AMANUDIN U.BALATUCAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1020-19(REN.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1431-614</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216228</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1017-19(REN/MOD)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1418-218</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216227</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMANUDIN UNGAD BALATUCAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1018-19(REN.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1413-402</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216223</x:t>
+  </x:si>
+  <x:si>
     <x:t>CHRISTOPHER P. RODA</x:t>
   </x:si>
   <x:si>
@@ -1773,6 +1806,27 @@
     <x:t>1216212</x:t>
   </x:si>
   <x:si>
+    <x:t>NOEMA M.BALATUCAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1019-19(REN.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1430-444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216225</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MS9/FV-1016-19(DUP/REN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1419-204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216226</x:t>
+  </x:si>
+  <x:si>
     <x:t>NOEMA M.MORGIA</x:t>
   </x:si>
   <x:si>
@@ -1798,6 +1852,18 @@
   </x:si>
   <x:si>
     <x:t>1216214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOHNRIN ROSALIJOS GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21-SROPIX-13838</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1432-568</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1216229</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2859,28 +2925,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="E12" s="15" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="s">
         <x:v>576</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="G12" s="15" t="s">
         <x:v>577</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="H12" s="17">
+        <x:v>46107.1169023495</x:v>
+      </x:c>
+      <x:c r="I12" s="17">
+        <x:v>46127</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="s">
         <x:v>578</x:v>
-      </x:c>
-      <x:c r="H12" s="17">
-        <x:v>46100.1333120023</x:v>
-      </x:c>
-      <x:c r="I12" s="17">
-        <x:v>46115</x:v>
-      </x:c>
-      <x:c r="J12" s="16" t="s">
-        <x:v>579</x:v>
       </x:c>
       <x:c r="K12" s="18" t="n">
         <x:v>1590</x:v>
       </x:c>
       <x:c r="L12" s="19">
-        <x:v>46118.9999416204</x:v>
+        <x:v>46126.1914953241</x:v>
       </x:c>
       <x:c r="M12" s="15" t="s">
         <x:v>21</x:v>
@@ -2891,7 +2957,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C13" s="15" t="s">
-        <x:v>580</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D13" s="16" t="s">
         <x:v>29</x:v>
@@ -2900,25 +2966,25 @@
         <x:v>329</x:v>
       </x:c>
       <x:c r="F13" s="15" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="H13" s="17">
+        <x:v>46105.2495215509</x:v>
+      </x:c>
+      <x:c r="I13" s="17">
+        <x:v>46127</x:v>
+      </x:c>
+      <x:c r="J13" s="16" t="s">
         <x:v>581</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
-        <x:v>582</x:v>
-      </x:c>
-      <x:c r="H13" s="17">
-        <x:v>46107.098771794</x:v>
-      </x:c>
-      <x:c r="I13" s="17">
-        <x:v>46161</x:v>
-      </x:c>
-      <x:c r="J13" s="16" t="s">
-        <x:v>583</x:v>
-      </x:c>
       <x:c r="K13" s="18" t="n">
-        <x:v>1470</x:v>
+        <x:v>1590</x:v>
       </x:c>
       <x:c r="L13" s="19">
-        <x:v>46126.1382984606</x:v>
+        <x:v>46126.1951014005</x:v>
       </x:c>
       <x:c r="M13" s="15" t="s">
         <x:v>21</x:v>
@@ -2929,134 +2995,366 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="C14" s="15" t="s">
-        <x:v>584</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="D14" s="16" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="E14" s="15" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="H14" s="17">
+        <x:v>46102.5247719444</x:v>
+      </x:c>
+      <x:c r="I14" s="17">
+        <x:v>46127</x:v>
+      </x:c>
+      <x:c r="J14" s="16" t="s">
         <x:v>585</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
-        <x:v>586</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="s">
-        <x:v>587</x:v>
-      </x:c>
-      <x:c r="H14" s="17">
-        <x:v>46093.1047457407</x:v>
-      </x:c>
-      <x:c r="I14" s="17">
-        <x:v>46123</x:v>
-      </x:c>
-      <x:c r="J14" s="16" t="s">
-        <x:v>588</x:v>
-      </x:c>
       <x:c r="K14" s="18" t="n">
-        <x:v>1590</x:v>
+        <x:v>1470</x:v>
       </x:c>
       <x:c r="L14" s="19">
-        <x:v>46119.1181697338</x:v>
+        <x:v>46126.1550669907</x:v>
       </x:c>
       <x:c r="M14" s="15" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="H15" s="17">
+        <x:v>46100.1333120023</x:v>
+      </x:c>
+      <x:c r="I15" s="17">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="K15" s="18" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L15" s="19">
+        <x:v>46118.9999416204</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="H16" s="17">
+        <x:v>46107.1054781366</x:v>
+      </x:c>
+      <x:c r="I16" s="17">
+        <x:v>46127</x:v>
+      </x:c>
+      <x:c r="J16" s="16" t="s">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="K16" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L16" s="19">
+        <x:v>46126.1858600463</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="20" t="s">
+      <x:c r="B17" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="s">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="H17" s="17">
+        <x:v>46107.0809005093</x:v>
+      </x:c>
+      <x:c r="I17" s="17">
+        <x:v>46127</x:v>
+      </x:c>
+      <x:c r="J17" s="16" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="K17" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L17" s="19">
+        <x:v>46126.1597197801</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="s">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="H18" s="17">
+        <x:v>46107.098771794</x:v>
+      </x:c>
+      <x:c r="I18" s="17">
+        <x:v>46161</x:v>
+      </x:c>
+      <x:c r="J18" s="16" t="s">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="K18" s="18" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+      <x:c r="L18" s="19">
+        <x:v>46126.1382984606</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="15" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="s">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="s">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="H19" s="17">
+        <x:v>46093.1047457407</x:v>
+      </x:c>
+      <x:c r="I19" s="17">
+        <x:v>46123</x:v>
+      </x:c>
+      <x:c r="J19" s="16" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>1590</x:v>
+      </x:c>
+      <x:c r="L19" s="19">
+        <x:v>46119.1181697338</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="15" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="H20" s="17">
+        <x:v>46107.1249875579</x:v>
+      </x:c>
+      <x:c r="I20" s="17">
+        <x:v>45842</x:v>
+      </x:c>
+      <x:c r="J20" s="16" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="K20" s="18" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="L20" s="19">
+        <x:v>46126.1994933218</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B23" s="20" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C17" s="21" t="s"/>
-      <x:c r="D17" s="21" t="s"/>
-      <x:c r="E17" s="22" t="s"/>
-      <x:c r="F17" s="22" t="s"/>
-    </x:row>
-    <x:row r="18" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B18" s="23" t="s">
+      <x:c r="C23" s="21" t="s"/>
+      <x:c r="D23" s="21" t="s"/>
+      <x:c r="E23" s="22" t="s"/>
+      <x:c r="F23" s="22" t="s"/>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B24" s="23" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C18" s="24" t="s"/>
-      <x:c r="D18" s="24" t="s"/>
-      <x:c r="E18" s="24" t="s"/>
-      <x:c r="F18" s="25" t="s">
+      <x:c r="C24" s="24" t="s"/>
+      <x:c r="D24" s="24" t="s"/>
+      <x:c r="E24" s="24" t="s"/>
+      <x:c r="F24" s="25" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="26" t="s">
         <x:v>554</x:v>
       </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
+      <x:c r="C25" s="27" t="s"/>
+      <x:c r="D25" s="27" t="s"/>
+      <x:c r="E25" s="27" t="s"/>
+      <x:c r="F25" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="26" t="s">
         <x:v>416</x:v>
       </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="C26" s="27" t="s"/>
+      <x:c r="D26" s="27" t="s"/>
+      <x:c r="E26" s="27" t="s"/>
+      <x:c r="F26" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="26" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+      <x:c r="C27" s="27" t="s"/>
+      <x:c r="D27" s="27" t="s"/>
+      <x:c r="E27" s="27" t="s"/>
+      <x:c r="F27" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="26" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="C28" s="27" t="s"/>
+      <x:c r="D28" s="27" t="s"/>
+      <x:c r="E28" s="27" t="s"/>
+      <x:c r="F28" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="26" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="29" t="s">
+      <x:c r="C29" s="27" t="s"/>
+      <x:c r="D29" s="27" t="s"/>
+      <x:c r="E29" s="27" t="s"/>
+      <x:c r="F29" s="28" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="26" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C30" s="27" t="s"/>
+      <x:c r="D30" s="27" t="s"/>
+      <x:c r="E30" s="27" t="s"/>
+      <x:c r="F30" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B31" s="29" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C24" s="30" t="s"/>
-      <x:c r="D24" s="30" t="s"/>
-      <x:c r="E24" s="30" t="s"/>
-      <x:c r="F24" s="31" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C31" s="30" t="s"/>
+      <x:c r="D31" s="30" t="s"/>
+      <x:c r="E31" s="30" t="s"/>
+      <x:c r="F31" s="31" t="n">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4020,19 +4318,20 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="12">
+  <x:mergeCells count="13">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
     <x:mergeCell ref="B5:M5"/>
-    <x:mergeCell ref="B17:F17"/>
-    <x:mergeCell ref="B18:E18"/>
-    <x:mergeCell ref="B19:E19"/>
-    <x:mergeCell ref="B20:E20"/>
-    <x:mergeCell ref="B21:E21"/>
-    <x:mergeCell ref="B22:E22"/>
-    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B23:F23"/>
     <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B31:E31"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
+++ b/reports/service-tracking-report-REYNALDO-YBAÑEZ-evaluator-cache-serviceTracking-REYNALDO-YBAÑEZ-IX-202501-202612.xlsx
@@ -1875,7 +1875,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -1915,14 +1915,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -2195,7 +2187,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -2206,16 +2198,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -2227,53 +2216,53 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -2308,87 +2297,83 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -2690,17 +2675,17 @@
       <x:c r="B5" s="12">
         <x:v>46113</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -2723,635 +2708,635 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>554</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>555</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>556</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>557</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>558</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46104.0644558912</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45902</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>559</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>798</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46120.3413710417</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>416</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>560</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>561</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>562</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>563</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46097.2573180208</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46097.2573345602</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>564</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46125.2485400116</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>565</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>566</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>567</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>568</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46097.2931531944</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>46097.2931710069</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>569</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46119.1505964699</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>570</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>571</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>572</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>573</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46049.1592238657</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45939</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>574</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46120.3467831597</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>575</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>576</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>577</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46107.1169023495</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>46127</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>578</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46126.1914953241</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>575</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>579</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>580</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>46105.2495215509</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46127</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>581</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>46126.1951014005</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>582</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>583</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>584</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>46102.5247719444</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>46127</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>585</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>46126.1550669907</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>586</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>587</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>588</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>589</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>46100.1333120023</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>46115</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>46118.9999416204</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>591</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>592</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>593</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>46107.1054781366</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>46127</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>594</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>46126.1858600463</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>591</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="14" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>595</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>596</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="16">
         <x:v>46107.0809005093</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="16">
         <x:v>46127</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>597</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="18">
         <x:v>46126.1597197801</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="14" t="s">
         <x:v>598</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s">
+      <x:c r="D18" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="E18" s="14" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>599</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="16">
         <x:v>46107.098771794</x:v>
       </x:c>
-      <x:c r="I18" s="17">
+      <x:c r="I18" s="16">
         <x:v>46161</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="s">
+      <x:c r="J18" s="15" t="s">
         <x:v>601</x:v>
       </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L18" s="19">
+      <x:c r="L18" s="18">
         <x:v>46126.1382984606</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="15" t="s">
+      <x:c r="B19" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="s">
+      <x:c r="C19" s="14" t="s">
         <x:v>602</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="s">
+      <x:c r="D19" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="s">
+      <x:c r="E19" s="14" t="s">
         <x:v>603</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="s">
+      <x:c r="F19" s="14" t="s">
         <x:v>604</x:v>
       </x:c>
-      <x:c r="G19" s="15" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>605</x:v>
       </x:c>
-      <x:c r="H19" s="17">
+      <x:c r="H19" s="16">
         <x:v>46093.1047457407</x:v>
       </x:c>
-      <x:c r="I19" s="17">
+      <x:c r="I19" s="16">
         <x:v>46123</x:v>
       </x:c>
-      <x:c r="J19" s="16" t="s">
+      <x:c r="J19" s="15" t="s">
         <x:v>606</x:v>
       </x:c>
-      <x:c r="K19" s="18" t="n">
+      <x:c r="K19" s="17" t="n">
         <x:v>1590</x:v>
       </x:c>
-      <x:c r="L19" s="19">
+      <x:c r="L19" s="18">
         <x:v>46119.1181697338</x:v>
       </x:c>
-      <x:c r="M19" s="15" t="s">
+      <x:c r="M19" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="15" t="s">
+      <x:c r="B20" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="s">
+      <x:c r="C20" s="14" t="s">
         <x:v>607</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="s">
+      <x:c r="D20" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="s">
+      <x:c r="E20" s="14" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="s">
+      <x:c r="F20" s="14" t="s">
         <x:v>608</x:v>
       </x:c>
-      <x:c r="G20" s="15" t="s">
+      <x:c r="G20" s="14" t="s">
         <x:v>609</x:v>
       </x:c>
-      <x:c r="H20" s="17">
+      <x:c r="H20" s="16">
         <x:v>46107.1249875579</x:v>
       </x:c>
-      <x:c r="I20" s="17">
+      <x:c r="I20" s="16">
         <x:v>45842</x:v>
       </x:c>
-      <x:c r="J20" s="16" t="s">
+      <x:c r="J20" s="15" t="s">
         <x:v>610</x:v>
       </x:c>
-      <x:c r="K20" s="18" t="n">
+      <x:c r="K20" s="17" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L20" s="19">
+      <x:c r="L20" s="18">
         <x:v>46126.1994933218</x:v>
       </x:c>
-      <x:c r="M20" s="15" t="s">
+      <x:c r="M20" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="20" t="s">
+      <x:c r="B23" s="19" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C23" s="21" t="s"/>
-      <x:c r="D23" s="21" t="s"/>
-      <x:c r="E23" s="22" t="s"/>
-      <x:c r="F23" s="22" t="s"/>
+      <x:c r="C23" s="20" t="s"/>
+      <x:c r="D23" s="20" t="s"/>
+      <x:c r="E23" s="21" t="s"/>
+      <x:c r="F23" s="21" t="s"/>
     </x:row>
     <x:row r="24" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B24" s="23" t="s">
+      <x:c r="B24" s="22" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C24" s="24" t="s"/>
-      <x:c r="D24" s="24" t="s"/>
-      <x:c r="E24" s="24" t="s"/>
-      <x:c r="F24" s="25" t="s">
+      <x:c r="C24" s="23" t="s"/>
+      <x:c r="D24" s="23" t="s"/>
+      <x:c r="E24" s="23" t="s"/>
+      <x:c r="F24" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="26" t="s">
+      <x:c r="B25" s="25" t="s">
         <x:v>554</x:v>
       </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="n">
+      <x:c r="C25" s="26" t="s"/>
+      <x:c r="D25" s="26" t="s"/>
+      <x:c r="E25" s="26" t="s"/>
+      <x:c r="F25" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="26" t="s">
+      <x:c r="B26" s="25" t="s">
         <x:v>416</x:v>
       </x:c>
-      <x:c r="C26" s="27" t="s"/>
-      <x:c r="D26" s="27" t="s"/>
-      <x:c r="E26" s="27" t="s"/>
-      <x:c r="F26" s="28" t="n">
+      <x:c r="C26" s="26" t="s"/>
+      <x:c r="D26" s="26" t="s"/>
+      <x:c r="E26" s="26" t="s"/>
+      <x:c r="F26" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="26" t="s">
+      <x:c r="B27" s="25" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="C27" s="27" t="s"/>
-      <x:c r="D27" s="27" t="s"/>
-      <x:c r="E27" s="27" t="s"/>
-      <x:c r="F27" s="28" t="n">
+      <x:c r="C27" s="26" t="s"/>
+      <x:c r="D27" s="26" t="s"/>
+      <x:c r="E27" s="26" t="s"/>
+      <x:c r="F27" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="26" t="s">
+      <x:c r="B28" s="25" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C28" s="27" t="s"/>
-      <x:c r="D28" s="27" t="s"/>
-      <x:c r="E28" s="27" t="s"/>
-      <x:c r="F28" s="28" t="n">
+      <x:c r="C28" s="26" t="s"/>
+      <x:c r="D28" s="26" t="s"/>
+      <x:c r="E28" s="26" t="s"/>
+      <x:c r="F28" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="26" t="s">
+      <x:c r="B29" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C29" s="27" t="s"/>
-      <x:c r="D29" s="27" t="s"/>
-      <x:c r="E29" s="27" t="s"/>
-      <x:c r="F29" s="28" t="n">
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
+      <x:c r="B30" s="25" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
+      <x:c r="C30" s="26" t="s"/>
+      <x:c r="D30" s="26" t="s"/>
+      <x:c r="E30" s="26" t="s"/>
+      <x:c r="F30" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B31" s="29" t="s">
+      <x:c r="B31" s="28" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C31" s="30" t="s"/>
-      <x:c r="D31" s="30" t="s"/>
-      <x:c r="E31" s="30" t="s"/>
-      <x:c r="F31" s="31" t="n">
+      <x:c r="C31" s="29" t="s"/>
+      <x:c r="D31" s="29" t="s"/>
+      <x:c r="E31" s="29" t="s"/>
+      <x:c r="F31" s="30" t="n">
         <x:v>13</x:v>
       </x:c>
     </x:row>
@@ -4445,17 +4430,17 @@
       <x:c r="B5" s="12">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -4478,336 +4463,336 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45875.2668430556</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45875.2668525</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45877.2327351852</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45889.2616895949</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45889.2616989468</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45891.1583043171</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45889.1521108681</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>44272</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45891.1532978241</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45887.5652509954</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45851</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45896.2365416898</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>45891.1735682407</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>45765</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>45898.0611189931</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>45887.559024537</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>45888</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>45896.2379658681</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="20" t="s">
+      <x:c r="B16" s="19" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C16" s="21" t="s"/>
-      <x:c r="D16" s="21" t="s"/>
-      <x:c r="E16" s="22" t="s"/>
-      <x:c r="F16" s="22" t="s"/>
+      <x:c r="C16" s="20" t="s"/>
+      <x:c r="D16" s="20" t="s"/>
+      <x:c r="E16" s="21" t="s"/>
+      <x:c r="F16" s="21" t="s"/>
     </x:row>
     <x:row r="17" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B17" s="23" t="s">
+      <x:c r="B17" s="22" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C17" s="24" t="s"/>
-      <x:c r="D17" s="24" t="s"/>
-      <x:c r="E17" s="24" t="s"/>
-      <x:c r="F17" s="25" t="s">
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B18" s="26" t="s">
+      <x:c r="B18" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" s="27" t="s"/>
-      <x:c r="D18" s="27" t="s"/>
-      <x:c r="E18" s="27" t="s"/>
-      <x:c r="F18" s="28" t="n">
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B19" s="26" t="s">
+      <x:c r="B19" s="25" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C19" s="27" t="s"/>
-      <x:c r="D19" s="27" t="s"/>
-      <x:c r="E19" s="27" t="s"/>
-      <x:c r="F19" s="28" t="n">
+      <x:c r="C19" s="26" t="s"/>
+      <x:c r="D19" s="26" t="s"/>
+      <x:c r="E19" s="26" t="s"/>
+      <x:c r="F19" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
+      <x:c r="B20" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B21" s="29" t="s">
+      <x:c r="B21" s="28" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C21" s="30" t="s"/>
-      <x:c r="D21" s="30" t="s"/>
-      <x:c r="E21" s="30" t="s"/>
-      <x:c r="F21" s="31" t="n">
+      <x:c r="C21" s="29" t="s"/>
+      <x:c r="D21" s="29" t="s"/>
+      <x:c r="E21" s="29" t="s"/>
+      <x:c r="F21" s="30" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -5908,17 +5893,17 @@
       <x:c r="B5" s="12">
         <x:v>45901</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -5941,731 +5926,731 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45902.1777587269</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45781</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45911.9486641782</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45915.3557896528</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45851</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45918.2339584606</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45903.3849758912</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45916</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3150</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45908.2848985301</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45919.4023076505</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45926</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45925.9451511111</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>45918.1054021528</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>45900</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>45929.2194160764</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>45908.2183496296</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>45918</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>45912.190615463</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>45908.5003548611</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>45790</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>45911.9526579514</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>45916.1691749537</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>45949</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>45929.1383451968</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>45888.1543781134</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>45870</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>45902.0507853472</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="14" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="16">
         <x:v>45924.1163046412</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="16">
         <x:v>45902</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="18">
         <x:v>45930.0639154051</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="14" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s"/>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="D18" s="15" t="s"/>
+      <x:c r="E18" s="14" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="16">
         <x:v>45919.4732912847</x:v>
       </x:c>
-      <x:c r="I18" s="17">
+      <x:c r="I18" s="16">
         <x:v>45919.4733016088</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="s">
+      <x:c r="J18" s="15" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L18" s="19">
+      <x:c r="L18" s="18">
         <x:v>45926.2586175694</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="15" t="s">
+      <x:c r="B19" s="14" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="s">
+      <x:c r="C19" s="14" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="s">
+      <x:c r="D19" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="s">
+      <x:c r="E19" s="14" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="s">
+      <x:c r="F19" s="14" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="G19" s="15" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="H19" s="17">
+      <x:c r="H19" s="16">
         <x:v>45911.4396314699</x:v>
       </x:c>
-      <x:c r="I19" s="17">
+      <x:c r="I19" s="16">
         <x:v>45911.4396406018</x:v>
       </x:c>
-      <x:c r="J19" s="16" t="s">
+      <x:c r="J19" s="15" t="s">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="K19" s="18" t="n">
+      <x:c r="K19" s="17" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="L19" s="19">
+      <x:c r="L19" s="18">
         <x:v>45918.0952106019</x:v>
       </x:c>
-      <x:c r="M19" s="15" t="s">
+      <x:c r="M19" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="15" t="s">
+      <x:c r="B20" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="s">
+      <x:c r="C20" s="14" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="s">
+      <x:c r="D20" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="s">
+      <x:c r="E20" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="s">
+      <x:c r="F20" s="14" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="G20" s="15" t="s">
+      <x:c r="G20" s="14" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="H20" s="17">
+      <x:c r="H20" s="16">
         <x:v>45925.397251713</x:v>
       </x:c>
-      <x:c r="I20" s="17">
+      <x:c r="I20" s="16">
         <x:v>47021</x:v>
       </x:c>
-      <x:c r="J20" s="16" t="s">
+      <x:c r="J20" s="15" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="K20" s="18" t="n">
+      <x:c r="K20" s="17" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L20" s="19">
+      <x:c r="L20" s="18">
         <x:v>45930.1169604282</x:v>
       </x:c>
-      <x:c r="M20" s="15" t="s">
+      <x:c r="M20" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="15" t="s">
+      <x:c r="B21" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="s">
+      <x:c r="C21" s="14" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="D21" s="16" t="s">
+      <x:c r="D21" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="s">
+      <x:c r="E21" s="14" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="s">
+      <x:c r="F21" s="14" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="G21" s="15" t="s">
+      <x:c r="G21" s="14" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="H21" s="17">
+      <x:c r="H21" s="16">
         <x:v>45916.1769203588</x:v>
       </x:c>
-      <x:c r="I21" s="17">
+      <x:c r="I21" s="16">
         <x:v>45949</x:v>
       </x:c>
-      <x:c r="J21" s="16" t="s">
+      <x:c r="J21" s="15" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="K21" s="18" t="n">
+      <x:c r="K21" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L21" s="19">
+      <x:c r="L21" s="18">
         <x:v>45930.1671706366</x:v>
       </x:c>
-      <x:c r="M21" s="15" t="s">
+      <x:c r="M21" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="15" t="s">
+      <x:c r="B22" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="s">
+      <x:c r="C22" s="14" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="D22" s="16" t="s">
+      <x:c r="D22" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="s">
+      <x:c r="E22" s="14" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="s">
+      <x:c r="F22" s="14" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="s">
+      <x:c r="G22" s="14" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="H22" s="17">
+      <x:c r="H22" s="16">
         <x:v>45912.4737565972</x:v>
       </x:c>
-      <x:c r="I22" s="17">
+      <x:c r="I22" s="16">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J22" s="16" t="s">
+      <x:c r="J22" s="15" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="K22" s="18" t="n">
+      <x:c r="K22" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L22" s="19">
+      <x:c r="L22" s="18">
         <x:v>45918.0905875926</x:v>
       </x:c>
-      <x:c r="M22" s="15" t="s">
+      <x:c r="M22" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="20" t="s">
+      <x:c r="B25" s="19" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C25" s="21" t="s"/>
-      <x:c r="D25" s="21" t="s"/>
-      <x:c r="E25" s="22" t="s"/>
-      <x:c r="F25" s="22" t="s"/>
+      <x:c r="C25" s="20" t="s"/>
+      <x:c r="D25" s="20" t="s"/>
+      <x:c r="E25" s="21" t="s"/>
+      <x:c r="F25" s="21" t="s"/>
     </x:row>
     <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="23" t="s">
+      <x:c r="B26" s="22" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C26" s="24" t="s"/>
-      <x:c r="D26" s="24" t="s"/>
-      <x:c r="E26" s="24" t="s"/>
-      <x:c r="F26" s="25" t="s">
+      <x:c r="C26" s="23" t="s"/>
+      <x:c r="D26" s="23" t="s"/>
+      <x:c r="E26" s="23" t="s"/>
+      <x:c r="F26" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="26" t="s">
+      <x:c r="B27" s="25" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C27" s="27" t="s"/>
-      <x:c r="D27" s="27" t="s"/>
-      <x:c r="E27" s="27" t="s"/>
-      <x:c r="F27" s="28" t="n">
+      <x:c r="C27" s="26" t="s"/>
+      <x:c r="D27" s="26" t="s"/>
+      <x:c r="E27" s="26" t="s"/>
+      <x:c r="F27" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="26" t="s">
+      <x:c r="B28" s="25" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C28" s="27" t="s"/>
-      <x:c r="D28" s="27" t="s"/>
-      <x:c r="E28" s="27" t="s"/>
-      <x:c r="F28" s="28" t="n">
+      <x:c r="C28" s="26" t="s"/>
+      <x:c r="D28" s="26" t="s"/>
+      <x:c r="E28" s="26" t="s"/>
+      <x:c r="F28" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="26" t="s">
+      <x:c r="B29" s="25" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C29" s="27" t="s"/>
-      <x:c r="D29" s="27" t="s"/>
-      <x:c r="E29" s="27" t="s"/>
-      <x:c r="F29" s="28" t="n">
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
+      <x:c r="B30" s="25" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
+      <x:c r="C30" s="26" t="s"/>
+      <x:c r="D30" s="26" t="s"/>
+      <x:c r="E30" s="26" t="s"/>
+      <x:c r="F30" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
+      <x:c r="B31" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
+      <x:c r="C31" s="26" t="s"/>
+      <x:c r="D31" s="26" t="s"/>
+      <x:c r="E31" s="26" t="s"/>
+      <x:c r="F31" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
+      <x:c r="B32" s="25" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
+      <x:c r="C32" s="26" t="s"/>
+      <x:c r="D32" s="26" t="s"/>
+      <x:c r="E32" s="26" t="s"/>
+      <x:c r="F32" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
+      <x:c r="B33" s="25" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
+      <x:c r="C33" s="26" t="s"/>
+      <x:c r="D33" s="26" t="s"/>
+      <x:c r="E33" s="26" t="s"/>
+      <x:c r="F33" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="26" t="s">
+      <x:c r="B34" s="25" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C34" s="27" t="s"/>
-      <x:c r="D34" s="27" t="s"/>
-      <x:c r="E34" s="27" t="s"/>
-      <x:c r="F34" s="28" t="n">
+      <x:c r="C34" s="26" t="s"/>
+      <x:c r="D34" s="26" t="s"/>
+      <x:c r="E34" s="26" t="s"/>
+      <x:c r="F34" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B35" s="29" t="s">
+      <x:c r="B35" s="28" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C35" s="30" t="s"/>
-      <x:c r="D35" s="30" t="s"/>
-      <x:c r="E35" s="30" t="s"/>
-      <x:c r="F35" s="31" t="n">
+      <x:c r="C35" s="29" t="s"/>
+      <x:c r="D35" s="29" t="s"/>
+      <x:c r="E35" s="29" t="s"/>
+      <x:c r="F35" s="30" t="n">
         <x:v>15</x:v>
       </x:c>
     </x:row>
@@ -7757,17 +7742,17 @@
       <x:c r="B5" s="12">
         <x:v>45931</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -7790,477 +7775,477 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45938.0053813889</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45942</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45945.1196250694</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45933.0884397222</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45932</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45936.0148412269</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45947.5768402431</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>43437</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>17766</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45954.219187662</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>151</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s"/>
-      <x:c r="H11" s="17">
+      <x:c r="G11" s="14" t="s"/>
+      <x:c r="H11" s="16">
         <x:v>45925.0602006481</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45922</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45933.3037187384</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>153</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>45912.3032409491</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>45879</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>4710</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>45933.3105378819</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>158</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>45931.5665387384</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46297</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>45940.1382142824</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s"/>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="D14" s="15" t="s"/>
+      <x:c r="E14" s="14" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>164</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>45928.9304539583</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>45928.9304922454</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>45938.035947419</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s"/>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="D15" s="15" t="s"/>
+      <x:c r="E15" s="14" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>45926.4563998264</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>45926.4564372454</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>168</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>45932.2395375463</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>170</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>45945.2727709838</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>45911</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>45953.1511070255</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="20" t="s">
+      <x:c r="B19" s="19" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C19" s="21" t="s"/>
-      <x:c r="D19" s="21" t="s"/>
-      <x:c r="E19" s="22" t="s"/>
-      <x:c r="F19" s="22" t="s"/>
+      <x:c r="C19" s="20" t="s"/>
+      <x:c r="D19" s="20" t="s"/>
+      <x:c r="E19" s="21" t="s"/>
+      <x:c r="F19" s="21" t="s"/>
     </x:row>
     <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="23" t="s">
+      <x:c r="B20" s="22" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C20" s="24" t="s"/>
-      <x:c r="D20" s="24" t="s"/>
-      <x:c r="E20" s="24" t="s"/>
-      <x:c r="F20" s="25" t="s">
+      <x:c r="C20" s="23" t="s"/>
+      <x:c r="D20" s="23" t="s"/>
+      <x:c r="E20" s="23" t="s"/>
+      <x:c r="F20" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
+      <x:c r="B21" s="25" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
+      <x:c r="B22" s="25" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
+      <x:c r="B23" s="25" t="s">
         <x:v>143</x:v>
       </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
+      <x:c r="B24" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
+      <x:c r="C24" s="26" t="s"/>
+      <x:c r="D24" s="26" t="s"/>
+      <x:c r="E24" s="26" t="s"/>
+      <x:c r="F24" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="26" t="s">
+      <x:c r="B25" s="25" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C25" s="27" t="s"/>
-      <x:c r="D25" s="27" t="s"/>
-      <x:c r="E25" s="27" t="s"/>
-      <x:c r="F25" s="28" t="n">
+      <x:c r="C25" s="26" t="s"/>
+      <x:c r="D25" s="26" t="s"/>
+      <x:c r="E25" s="26" t="s"/>
+      <x:c r="F25" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="26" t="s">
+      <x:c r="B26" s="25" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C26" s="27" t="s"/>
-      <x:c r="D26" s="27" t="s"/>
-      <x:c r="E26" s="27" t="s"/>
-      <x:c r="F26" s="28" t="n">
+      <x:c r="C26" s="26" t="s"/>
+      <x:c r="D26" s="26" t="s"/>
+      <x:c r="E26" s="26" t="s"/>
+      <x:c r="F26" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="29" t="s">
+      <x:c r="B27" s="28" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C27" s="30" t="s"/>
-      <x:c r="D27" s="30" t="s"/>
-      <x:c r="E27" s="30" t="s"/>
-      <x:c r="F27" s="31" t="n">
+      <x:c r="C27" s="29" t="s"/>
+      <x:c r="D27" s="29" t="s"/>
+      <x:c r="E27" s="29" t="s"/>
+      <x:c r="F27" s="30" t="n">
         <x:v>9</x:v>
       </x:c>
     </x:row>
@@ -9358,17 +9343,17 @@
       <x:c r="B5" s="12">
         <x:v>45962</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -9391,832 +9376,832 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45954.1265640162</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45626</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>510</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45967.0018301736</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45965.2541525</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45971</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>45971.1502294097</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>186</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45965.2736735764</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45965.2736975579</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45972.1539687153</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45965.2661516088</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>45972.1364239815</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>45953.5328279861</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>45969</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>199</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>45966.0458205787</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>45958.0724435648</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>45810</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>45973.0584535069</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>45973.1309431481</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>45950</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>2550</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>45985.2116720486</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>211</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>45971.2436290394</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>45608</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>215</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>45973.2287349769</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>217</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>45974.6184602778</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>45682</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>45986.0239280787</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="14" t="s">
         <x:v>221</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="16">
         <x:v>45965.4411408796</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="16">
         <x:v>45974</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="18">
         <x:v>45973.017945463</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="14" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s">
+      <x:c r="D18" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="E18" s="14" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="16">
         <x:v>45971.2507406366</x:v>
       </x:c>
-      <x:c r="I18" s="17">
+      <x:c r="I18" s="16">
         <x:v>45991</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="s">
+      <x:c r="J18" s="15" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L18" s="19">
+      <x:c r="L18" s="18">
         <x:v>45975.0756137384</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="15" t="s">
+      <x:c r="B19" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="s">
+      <x:c r="C19" s="14" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="s">
+      <x:c r="D19" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="s">
+      <x:c r="E19" s="14" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="s">
+      <x:c r="F19" s="14" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="G19" s="15" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="H19" s="17">
+      <x:c r="H19" s="16">
         <x:v>45958.3516981366</x:v>
       </x:c>
-      <x:c r="I19" s="17">
+      <x:c r="I19" s="16">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J19" s="16" t="s">
+      <x:c r="J19" s="15" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="K19" s="18" t="n">
+      <x:c r="K19" s="17" t="n">
         <x:v>3990</x:v>
       </x:c>
-      <x:c r="L19" s="19">
+      <x:c r="L19" s="18">
         <x:v>45967.2412429051</x:v>
       </x:c>
-      <x:c r="M19" s="15" t="s">
+      <x:c r="M19" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="15" t="s">
+      <x:c r="B20" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="s">
+      <x:c r="C20" s="14" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="s">
+      <x:c r="D20" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="s">
+      <x:c r="E20" s="14" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="s">
+      <x:c r="F20" s="14" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="G20" s="15" t="s">
+      <x:c r="G20" s="14" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="H20" s="17">
+      <x:c r="H20" s="16">
         <x:v>45954.2913455787</x:v>
       </x:c>
-      <x:c r="I20" s="17">
+      <x:c r="I20" s="16">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J20" s="16" t="s">
+      <x:c r="J20" s="15" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="K20" s="18" t="n">
+      <x:c r="K20" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L20" s="19">
+      <x:c r="L20" s="18">
         <x:v>45975.3213612153</x:v>
       </x:c>
-      <x:c r="M20" s="15" t="s">
+      <x:c r="M20" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="15" t="s">
+      <x:c r="B21" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="s">
+      <x:c r="C21" s="14" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="D21" s="16" t="s">
+      <x:c r="D21" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="s">
+      <x:c r="E21" s="14" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="s">
+      <x:c r="F21" s="14" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="G21" s="15" t="s">
+      <x:c r="G21" s="14" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="H21" s="17">
+      <x:c r="H21" s="16">
         <x:v>45953.3174921644</x:v>
       </x:c>
-      <x:c r="I21" s="17">
+      <x:c r="I21" s="16">
         <x:v>45911</x:v>
       </x:c>
-      <x:c r="J21" s="16" t="s">
+      <x:c r="J21" s="15" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="K21" s="18" t="n">
+      <x:c r="K21" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L21" s="19">
+      <x:c r="L21" s="18">
         <x:v>45971.2990240856</x:v>
       </x:c>
-      <x:c r="M21" s="15" t="s">
+      <x:c r="M21" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="15" t="s">
+      <x:c r="B22" s="14" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="s">
+      <x:c r="C22" s="14" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="D22" s="16" t="s"/>
-      <x:c r="E22" s="15" t="s">
+      <x:c r="D22" s="15" t="s"/>
+      <x:c r="E22" s="14" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="s">
+      <x:c r="F22" s="14" t="s">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="s">
+      <x:c r="G22" s="14" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="H22" s="17">
+      <x:c r="H22" s="16">
         <x:v>45954.4190024884</x:v>
       </x:c>
-      <x:c r="I22" s="17">
+      <x:c r="I22" s="16">
         <x:v>45954.4190340741</x:v>
       </x:c>
-      <x:c r="J22" s="16" t="s">
+      <x:c r="J22" s="15" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="K22" s="18" t="n">
+      <x:c r="K22" s="17" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L22" s="19">
+      <x:c r="L22" s="18">
         <x:v>45967.2850746528</x:v>
       </x:c>
-      <x:c r="M22" s="15" t="s">
+      <x:c r="M22" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="15" t="s">
+      <x:c r="B23" s="14" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C23" s="15" t="s">
+      <x:c r="C23" s="14" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="D23" s="16" t="s"/>
-      <x:c r="E23" s="15" t="s">
+      <x:c r="D23" s="15" t="s"/>
+      <x:c r="E23" s="14" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="F23" s="15" t="s">
+      <x:c r="F23" s="14" t="s">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="G23" s="15" t="s">
+      <x:c r="G23" s="14" t="s">
         <x:v>251</x:v>
       </x:c>
-      <x:c r="H23" s="17">
+      <x:c r="H23" s="16">
         <x:v>45959.2592067593</x:v>
       </x:c>
-      <x:c r="I23" s="17">
+      <x:c r="I23" s="16">
         <x:v>45959.2592354861</x:v>
       </x:c>
-      <x:c r="J23" s="16" t="s">
+      <x:c r="J23" s="15" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="K23" s="18" t="n">
+      <x:c r="K23" s="17" t="n">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="L23" s="19">
+      <x:c r="L23" s="18">
         <x:v>45986.1291977315</x:v>
       </x:c>
-      <x:c r="M23" s="15" t="s">
+      <x:c r="M23" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="15" t="s">
+      <x:c r="B24" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C24" s="15" t="s">
+      <x:c r="C24" s="14" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="D24" s="16" t="s">
+      <x:c r="D24" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E24" s="15" t="s">
+      <x:c r="E24" s="14" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="F24" s="15" t="s">
+      <x:c r="F24" s="14" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="G24" s="15" t="s">
+      <x:c r="G24" s="14" t="s">
         <x:v>256</x:v>
       </x:c>
-      <x:c r="H24" s="17">
+      <x:c r="H24" s="16">
         <x:v>45966.1203235417</x:v>
       </x:c>
-      <x:c r="I24" s="17">
+      <x:c r="I24" s="16">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J24" s="16" t="s">
+      <x:c r="J24" s="15" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="K24" s="18" t="n">
+      <x:c r="K24" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L24" s="19">
+      <x:c r="L24" s="18">
         <x:v>45975.3046220602</x:v>
       </x:c>
-      <x:c r="M24" s="15" t="s">
+      <x:c r="M24" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="15" t="s">
+      <x:c r="B25" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C25" s="15" t="s">
+      <x:c r="C25" s="14" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="D25" s="16" t="s">
+      <x:c r="D25" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E25" s="15" t="s">
+      <x:c r="E25" s="14" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="F25" s="15" t="s">
+      <x:c r="F25" s="14" t="s">
         <x:v>259</x:v>
       </x:c>
-      <x:c r="G25" s="15" t="s">
+      <x:c r="G25" s="14" t="s">
         <x:v>260</x:v>
       </x:c>
-      <x:c r="H25" s="17">
+      <x:c r="H25" s="16">
         <x:v>45966.1218093634</x:v>
       </x:c>
-      <x:c r="I25" s="17">
+      <x:c r="I25" s="16">
         <x:v>45975</x:v>
       </x:c>
-      <x:c r="J25" s="16" t="s">
+      <x:c r="J25" s="15" t="s">
         <x:v>261</x:v>
       </x:c>
-      <x:c r="K25" s="18" t="n">
+      <x:c r="K25" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L25" s="19">
+      <x:c r="L25" s="18">
         <x:v>45975.3123537269</x:v>
       </x:c>
-      <x:c r="M25" s="15" t="s">
+      <x:c r="M25" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="20" t="s">
+      <x:c r="B28" s="19" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C28" s="21" t="s"/>
-      <x:c r="D28" s="21" t="s"/>
-      <x:c r="E28" s="22" t="s"/>
-      <x:c r="F28" s="22" t="s"/>
+      <x:c r="C28" s="20" t="s"/>
+      <x:c r="D28" s="20" t="s"/>
+      <x:c r="E28" s="21" t="s"/>
+      <x:c r="F28" s="21" t="s"/>
     </x:row>
     <x:row r="29" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B29" s="23" t="s">
+      <x:c r="B29" s="22" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C29" s="24" t="s"/>
-      <x:c r="D29" s="24" t="s"/>
-      <x:c r="E29" s="24" t="s"/>
-      <x:c r="F29" s="25" t="s">
+      <x:c r="C29" s="23" t="s"/>
+      <x:c r="D29" s="23" t="s"/>
+      <x:c r="E29" s="23" t="s"/>
+      <x:c r="F29" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="26" t="s">
+      <x:c r="B30" s="25" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C30" s="27" t="s"/>
-      <x:c r="D30" s="27" t="s"/>
-      <x:c r="E30" s="27" t="s"/>
-      <x:c r="F30" s="28" t="n">
+      <x:c r="C30" s="26" t="s"/>
+      <x:c r="D30" s="26" t="s"/>
+      <x:c r="E30" s="26" t="s"/>
+      <x:c r="F30" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="26" t="s">
+      <x:c r="B31" s="25" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="C31" s="27" t="s"/>
-      <x:c r="D31" s="27" t="s"/>
-      <x:c r="E31" s="27" t="s"/>
-      <x:c r="F31" s="28" t="n">
+      <x:c r="C31" s="26" t="s"/>
+      <x:c r="D31" s="26" t="s"/>
+      <x:c r="E31" s="26" t="s"/>
+      <x:c r="F31" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="26" t="s">
+      <x:c r="B32" s="25" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C32" s="27" t="s"/>
-      <x:c r="D32" s="27" t="s"/>
-      <x:c r="E32" s="27" t="s"/>
-      <x:c r="F32" s="28" t="n">
+      <x:c r="C32" s="26" t="s"/>
+      <x:c r="D32" s="26" t="s"/>
+      <x:c r="E32" s="26" t="s"/>
+      <x:c r="F32" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="26" t="s">
+      <x:c r="B33" s="25" t="s">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="C33" s="27" t="s"/>
-      <x:c r="D33" s="27" t="s"/>
-      <x:c r="E33" s="27" t="s"/>
-      <x:c r="F33" s="28" t="n">
+      <x:c r="C33" s="26" t="s"/>
+      <x:c r="D33" s="26" t="s"/>
+      <x:c r="E33" s="26" t="s"/>
+      <x:c r="F33" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="26" t="s">
+      <x:c r="B34" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C34" s="27" t="s"/>
-      <x:c r="D34" s="27" t="s"/>
-      <x:c r="E34" s="27" t="s"/>
-      <x:c r="F34" s="28" t="n">
+      <x:c r="C34" s="26" t="s"/>
+      <x:c r="D34" s="26" t="s"/>
+      <x:c r="E34" s="26" t="s"/>
+      <x:c r="F34" s="27" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B35" s="26" t="s">
+      <x:c r="B35" s="25" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C35" s="27" t="s"/>
-      <x:c r="D35" s="27" t="s"/>
-      <x:c r="E35" s="27" t="s"/>
-      <x:c r="F35" s="28" t="n">
+      <x:c r="C35" s="26" t="s"/>
+      <x:c r="D35" s="26" t="s"/>
+      <x:c r="E35" s="26" t="s"/>
+      <x:c r="F35" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B36" s="26" t="s">
+      <x:c r="B36" s="25" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C36" s="27" t="s"/>
-      <x:c r="D36" s="27" t="s"/>
-      <x:c r="E36" s="27" t="s"/>
-      <x:c r="F36" s="28" t="n">
+      <x:c r="C36" s="26" t="s"/>
+      <x:c r="D36" s="26" t="s"/>
+      <x:c r="E36" s="26" t="s"/>
+      <x:c r="F36" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B37" s="29" t="s">
+      <x:c r="B37" s="28" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C37" s="30" t="s"/>
-      <x:c r="D37" s="30" t="s"/>
-      <x:c r="E37" s="30" t="s"/>
-      <x:c r="F37" s="31" t="n">
+      <x:c r="C37" s="29" t="s"/>
+      <x:c r="D37" s="29" t="s"/>
+      <x:c r="E37" s="29" t="s"/>
+      <x:c r="F37" s="30" t="n">
         <x:v>18</x:v>
       </x:c>
     </x:row>
@@ -11305,17 +11290,17 @@
       <x:c r="B5" s="12">
         <x:v>45992</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -11338,412 +11323,412 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>263</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>264</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>265</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>45981.1374423611</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>45969</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>266</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>45996.1054321181</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>267</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>268</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>45994.1029113889</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45169</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>12780</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46006.2230459028</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>273</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>274</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45973.282415625</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45964</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>45993.0810788889</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>279</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>280</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>45988.1651420255</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45974</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46006.238966169</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>45972.0386162384</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>46337</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>286</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46006.0795786111</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>288</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>289</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>45980.2174048843</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>45852</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>290</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>45992.1151937269</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>291</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>45979.0549779514</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>46007</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>295</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>46006.269013287</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>296</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>297</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>298</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>45972.2314280556</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>46337</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>299</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>45992.0065612963</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="20" t="s">
+      <x:c r="B18" s="19" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C18" s="21" t="s"/>
-      <x:c r="D18" s="21" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="22" t="s"/>
+      <x:c r="C18" s="20" t="s"/>
+      <x:c r="D18" s="20" t="s"/>
+      <x:c r="E18" s="21" t="s"/>
+      <x:c r="F18" s="21" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="23" t="s">
+      <x:c r="B19" s="22" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="s">
+      <x:c r="C19" s="23" t="s"/>
+      <x:c r="D19" s="23" t="s"/>
+      <x:c r="E19" s="23" t="s"/>
+      <x:c r="F19" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
+      <x:c r="B20" s="25" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
+      <x:c r="B21" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
+      <x:c r="B22" s="25" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="29" t="s">
+      <x:c r="B23" s="28" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C23" s="30" t="s"/>
-      <x:c r="D23" s="30" t="s"/>
-      <x:c r="E23" s="30" t="s"/>
-      <x:c r="F23" s="31" t="n">
+      <x:c r="C23" s="29" t="s"/>
+      <x:c r="D23" s="29" t="s"/>
+      <x:c r="E23" s="29" t="s"/>
+      <x:c r="F23" s="30" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -12842,17 +12827,17 @@
       <x:c r="B5" s="12">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -12875,421 +12860,421 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>301</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46033.3509841319</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>303</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46049.2368941319</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>262</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>305</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>306</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46010.1939375579</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46029</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>307</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46034.111096713</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>309</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>311</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>312</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>45989.0397289236</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45597</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>313</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>8280</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46043.2235160301</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>314</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>315</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>316</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>317</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46007.1341463773</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>45942</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>318</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46035.3042477199</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>319</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>321</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46014.1352096759</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>322</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46035.0802777199</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>323</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>324</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>325</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>46014.4844165162</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>45786</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>327</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>2430</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>46031.0514651852</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s"/>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="D14" s="15" t="s"/>
+      <x:c r="E14" s="14" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>331</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>46043.0454792477</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>46043.0455093056</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>332</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>46048.2516543634</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>333</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>334</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>335</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>46036.9292262963</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>337</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>46050.0472434028</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="20" t="s">
+      <x:c r="B18" s="19" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C18" s="21" t="s"/>
-      <x:c r="D18" s="21" t="s"/>
-      <x:c r="E18" s="22" t="s"/>
-      <x:c r="F18" s="22" t="s"/>
+      <x:c r="C18" s="20" t="s"/>
+      <x:c r="D18" s="20" t="s"/>
+      <x:c r="E18" s="21" t="s"/>
+      <x:c r="F18" s="21" t="s"/>
     </x:row>
     <x:row r="19" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B19" s="23" t="s">
+      <x:c r="B19" s="22" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C19" s="24" t="s"/>
-      <x:c r="D19" s="24" t="s"/>
-      <x:c r="E19" s="24" t="s"/>
-      <x:c r="F19" s="25" t="s">
+      <x:c r="C19" s="23" t="s"/>
+      <x:c r="D19" s="23" t="s"/>
+      <x:c r="E19" s="23" t="s"/>
+      <x:c r="F19" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B20" s="26" t="s">
+      <x:c r="B20" s="25" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C20" s="27" t="s"/>
-      <x:c r="D20" s="27" t="s"/>
-      <x:c r="E20" s="27" t="s"/>
-      <x:c r="F20" s="28" t="n">
+      <x:c r="C20" s="26" t="s"/>
+      <x:c r="D20" s="26" t="s"/>
+      <x:c r="E20" s="26" t="s"/>
+      <x:c r="F20" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="26" t="s">
+      <x:c r="B21" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C21" s="27" t="s"/>
-      <x:c r="D21" s="27" t="s"/>
-      <x:c r="E21" s="27" t="s"/>
-      <x:c r="F21" s="28" t="n">
+      <x:c r="C21" s="26" t="s"/>
+      <x:c r="D21" s="26" t="s"/>
+      <x:c r="E21" s="26" t="s"/>
+      <x:c r="F21" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
+      <x:c r="B22" s="25" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
+      <x:c r="B23" s="25" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="29" t="s">
+      <x:c r="B24" s="28" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C24" s="30" t="s"/>
-      <x:c r="D24" s="30" t="s"/>
-      <x:c r="E24" s="30" t="s"/>
-      <x:c r="F24" s="31" t="n">
+      <x:c r="C24" s="29" t="s"/>
+      <x:c r="D24" s="29" t="s"/>
+      <x:c r="E24" s="29" t="s"/>
+      <x:c r="F24" s="30" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -14388,17 +14373,17 @@
       <x:c r="B5" s="12">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -14421,488 +14406,488 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>339</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>341</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>342</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46051.2691346181</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46051.2691569676</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>343</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>2070</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46057.9587264699</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>345</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>346</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46051.1259765394</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46062.9664110648</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>349</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>350</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>352</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46050.2853992708</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>45945</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46058.044006875</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>354</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>355</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>356</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>357</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46057.2800557755</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46052</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>358</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>2010</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46065.279651412</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>354</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>355</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>359</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46057.2720317477</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>46045</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>361</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46065.2951402431</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>354</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>362</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>363</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>364</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>46057.2657532407</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46039</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>365</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>46065.2854801042</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>366</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>367</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>368</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>369</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>46056.1690134606</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>45716</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>370</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>3630</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>46058.1034575694</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>373</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>46065.2313001968</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>46053</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>375</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>2190</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>46076.0858435648</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>376</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>377</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>378</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>46063.0357172222</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>46066</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>46066.0203850694</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>381</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="14" t="s">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>383</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>384</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="16">
         <x:v>46051.2882746759</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="16">
         <x:v>44445</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>960</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="18">
         <x:v>46057.9635980093</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="20" t="s">
+      <x:c r="B20" s="19" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C20" s="21" t="s"/>
-      <x:c r="D20" s="21" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="22" t="s"/>
+      <x:c r="C20" s="20" t="s"/>
+      <x:c r="D20" s="20" t="s"/>
+      <x:c r="E20" s="21" t="s"/>
+      <x:c r="F20" s="21" t="s"/>
     </x:row>
     <x:row r="21" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B21" s="23" t="s">
+      <x:c r="B21" s="22" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C21" s="24" t="s"/>
-      <x:c r="D21" s="24" t="s"/>
-      <x:c r="E21" s="24" t="s"/>
-      <x:c r="F21" s="25" t="s">
+      <x:c r="C21" s="23" t="s"/>
+      <x:c r="D21" s="23" t="s"/>
+      <x:c r="E21" s="23" t="s"/>
+      <x:c r="F21" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="26" t="s">
+      <x:c r="B22" s="25" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="C22" s="27" t="s"/>
-      <x:c r="D22" s="27" t="s"/>
-      <x:c r="E22" s="27" t="s"/>
-      <x:c r="F22" s="28" t="n">
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="26" t="s">
+      <x:c r="B23" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C23" s="27" t="s"/>
-      <x:c r="D23" s="27" t="s"/>
-      <x:c r="E23" s="27" t="s"/>
-      <x:c r="F23" s="28" t="n">
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="26" t="s">
+      <x:c r="B24" s="25" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C24" s="27" t="s"/>
-      <x:c r="D24" s="27" t="s"/>
-      <x:c r="E24" s="27" t="s"/>
-      <x:c r="F24" s="28" t="n">
+      <x:c r="C24" s="26" t="s"/>
+      <x:c r="D24" s="26" t="s"/>
+      <x:c r="E24" s="26" t="s"/>
+      <x:c r="F24" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B25" s="29" t="s">
+      <x:c r="B25" s="28" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C25" s="30" t="s"/>
-      <x:c r="D25" s="30" t="s"/>
-      <x:c r="E25" s="30" t="s"/>
-      <x:c r="F25" s="31" t="n">
+      <x:c r="C25" s="29" t="s"/>
+      <x:c r="D25" s="29" t="s"/>
+      <x:c r="E25" s="29" t="s"/>
+      <x:c r="F25" s="30" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -15999,17 +15984,17 @@
       <x:c r="B5" s="12">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -16032,1498 +16017,1498 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>386</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>387</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>388</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46062.3800913889</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46054</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46104.0851025694</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>391</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>394</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46065.3312544444</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>45700</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>395</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>510</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46084.1560858449</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C10" s="15" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>397</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>398</x:v>
       </x:c>
-      <x:c r="G10" s="15" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>399</x:v>
       </x:c>
-      <x:c r="H10" s="17">
+      <x:c r="H10" s="16">
         <x:v>46085.2764846181</x:v>
       </x:c>
-      <x:c r="I10" s="17">
+      <x:c r="I10" s="16">
         <x:v>44879</x:v>
       </x:c>
-      <x:c r="J10" s="16" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="K10" s="18" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>1290</x:v>
       </x:c>
-      <x:c r="L10" s="19">
+      <x:c r="L10" s="18">
         <x:v>46093.2000157407</x:v>
       </x:c>
-      <x:c r="M10" s="15" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="15" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C11" s="15" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>401</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>402</x:v>
       </x:c>
-      <x:c r="F11" s="15" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>403</x:v>
       </x:c>
-      <x:c r="G11" s="15" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>404</x:v>
       </x:c>
-      <x:c r="H11" s="17">
+      <x:c r="H11" s="16">
         <x:v>46065.2288648495</x:v>
       </x:c>
-      <x:c r="I11" s="17">
+      <x:c r="I11" s="16">
         <x:v>46070</x:v>
       </x:c>
-      <x:c r="J11" s="16" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>405</x:v>
       </x:c>
-      <x:c r="K11" s="18" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L11" s="19">
+      <x:c r="L11" s="18">
         <x:v>46084.1582202315</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C12" s="15" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>406</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>407</x:v>
       </x:c>
-      <x:c r="F12" s="15" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>408</x:v>
       </x:c>
-      <x:c r="G12" s="15" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="H12" s="17">
+      <x:c r="H12" s="16">
         <x:v>46085.3008007755</x:v>
       </x:c>
-      <x:c r="I12" s="17">
+      <x:c r="I12" s="16">
         <x:v>46386</x:v>
       </x:c>
-      <x:c r="J12" s="16" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>410</x:v>
       </x:c>
-      <x:c r="K12" s="18" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L12" s="19">
+      <x:c r="L12" s="18">
         <x:v>46093.2151637732</x:v>
       </x:c>
-      <x:c r="M12" s="15" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="15" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>411</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>412</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>413</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>414</x:v>
       </x:c>
-      <x:c r="H13" s="17">
+      <x:c r="H13" s="16">
         <x:v>46085.2858432523</x:v>
       </x:c>
-      <x:c r="I13" s="17">
+      <x:c r="I13" s="16">
         <x:v>46096</x:v>
       </x:c>
-      <x:c r="J13" s="16" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>415</x:v>
       </x:c>
-      <x:c r="K13" s="18" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="L13" s="19">
+      <x:c r="L13" s="18">
         <x:v>46093.2057128819</x:v>
       </x:c>
-      <x:c r="M13" s="15" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="15" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>416</x:v>
       </x:c>
-      <x:c r="C14" s="15" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>417</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>418</x:v>
       </x:c>
-      <x:c r="F14" s="15" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>419</x:v>
       </x:c>
-      <x:c r="G14" s="15" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>420</x:v>
       </x:c>
-      <x:c r="H14" s="17">
+      <x:c r="H14" s="16">
         <x:v>46088.1798280556</x:v>
       </x:c>
-      <x:c r="I14" s="17">
+      <x:c r="I14" s="16">
         <x:v>46088.1798485995</x:v>
       </x:c>
-      <x:c r="J14" s="16" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>421</x:v>
       </x:c>
-      <x:c r="K14" s="18" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L14" s="19">
+      <x:c r="L14" s="18">
         <x:v>46093.2393924884</x:v>
       </x:c>
-      <x:c r="M14" s="15" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="15" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C15" s="15" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>422</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>423</x:v>
       </x:c>
-      <x:c r="F15" s="15" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>424</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>425</x:v>
       </x:c>
-      <x:c r="H15" s="17">
+      <x:c r="H15" s="16">
         <x:v>46091.1989145023</x:v>
       </x:c>
-      <x:c r="I15" s="17">
+      <x:c r="I15" s="16">
         <x:v>46101</x:v>
       </x:c>
-      <x:c r="J15" s="16" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="K15" s="18" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>4030</x:v>
       </x:c>
-      <x:c r="L15" s="19">
+      <x:c r="L15" s="18">
         <x:v>46106.1492534144</x:v>
       </x:c>
-      <x:c r="M15" s="15" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="15" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="C16" s="15" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>427</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>428</x:v>
       </x:c>
-      <x:c r="F16" s="15" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>429</x:v>
       </x:c>
-      <x:c r="G16" s="15" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>430</x:v>
       </x:c>
-      <x:c r="H16" s="17">
+      <x:c r="H16" s="16">
         <x:v>46076.2810036343</x:v>
       </x:c>
-      <x:c r="I16" s="17">
+      <x:c r="I16" s="16">
         <x:v>46076.2810195833</x:v>
       </x:c>
-      <x:c r="J16" s="16" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>431</x:v>
       </x:c>
-      <x:c r="K16" s="18" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L16" s="19">
+      <x:c r="L16" s="18">
         <x:v>46097.2411206366</x:v>
       </x:c>
-      <x:c r="M16" s="15" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="15" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="C17" s="15" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>432</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="s">
+      <x:c r="D17" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="s">
+      <x:c r="E17" s="14" t="s">
         <x:v>433</x:v>
       </x:c>
-      <x:c r="F17" s="15" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>434</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>435</x:v>
       </x:c>
-      <x:c r="H17" s="17">
+      <x:c r="H17" s="16">
         <x:v>46076.2578122338</x:v>
       </x:c>
-      <x:c r="I17" s="17">
+      <x:c r="I17" s="16">
         <x:v>46076.2578276505</x:v>
       </x:c>
-      <x:c r="J17" s="16" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>436</x:v>
       </x:c>
-      <x:c r="K17" s="18" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L17" s="19">
+      <x:c r="L17" s="18">
         <x:v>46097.2583940162</x:v>
       </x:c>
-      <x:c r="M17" s="15" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B18" s="15" t="s">
+      <x:c r="B18" s="14" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="C18" s="15" t="s">
+      <x:c r="C18" s="14" t="s">
         <x:v>437</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="s">
+      <x:c r="D18" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="s">
+      <x:c r="E18" s="14" t="s">
         <x:v>438</x:v>
       </x:c>
-      <x:c r="F18" s="15" t="s">
+      <x:c r="F18" s="14" t="s">
         <x:v>439</x:v>
       </x:c>
-      <x:c r="G18" s="15" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>440</x:v>
       </x:c>
-      <x:c r="H18" s="17">
+      <x:c r="H18" s="16">
         <x:v>46076.263358912</x:v>
       </x:c>
-      <x:c r="I18" s="17">
+      <x:c r="I18" s="16">
         <x:v>46076.2633790625</x:v>
       </x:c>
-      <x:c r="J18" s="16" t="s">
+      <x:c r="J18" s="15" t="s">
         <x:v>441</x:v>
       </x:c>
-      <x:c r="K18" s="18" t="n">
+      <x:c r="K18" s="17" t="n">
         <x:v>4530</x:v>
       </x:c>
-      <x:c r="L18" s="19">
+      <x:c r="L18" s="18">
         <x:v>46094.1562770949</x:v>
       </x:c>
-      <x:c r="M18" s="15" t="s">
+      <x:c r="M18" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="15" t="s">
+      <x:c r="B19" s="14" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="C19" s="15" t="s">
+      <x:c r="C19" s="14" t="s">
         <x:v>442</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="s">
+      <x:c r="D19" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="s">
+      <x:c r="E19" s="14" t="s">
         <x:v>443</x:v>
       </x:c>
-      <x:c r="F19" s="15" t="s">
+      <x:c r="F19" s="14" t="s">
         <x:v>444</x:v>
       </x:c>
-      <x:c r="G19" s="15" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>445</x:v>
       </x:c>
-      <x:c r="H19" s="17">
+      <x:c r="H19" s="16">
         <x:v>46076.3755334722</x:v>
       </x:c>
-      <x:c r="I19" s="17">
+      <x:c r="I19" s="16">
         <x:v>46076.3755506134</x:v>
       </x:c>
-      <x:c r="J19" s="16" t="s">
+      <x:c r="J19" s="15" t="s">
         <x:v>446</x:v>
       </x:c>
-      <x:c r="K19" s="18" t="n">
+      <x:c r="K19" s="17" t="n">
         <x:v>3530</x:v>
       </x:c>
-      <x:c r="L19" s="19">
+      <x:c r="L19" s="18">
         <x:v>46094.1653946759</x:v>
       </x:c>
-      <x:c r="M19" s="15" t="s">
+      <x:c r="M19" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="15" t="s">
+      <x:c r="B20" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C20" s="15" t="s">
+      <x:c r="C20" s="14" t="s">
         <x:v>447</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="s">
+      <x:c r="D20" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="s">
+      <x:c r="E20" s="14" t="s">
         <x:v>448</x:v>
       </x:c>
-      <x:c r="F20" s="15" t="s">
+      <x:c r="F20" s="14" t="s">
         <x:v>449</x:v>
       </x:c>
-      <x:c r="G20" s="15" t="s">
+      <x:c r="G20" s="14" t="s">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="H20" s="17">
+      <x:c r="H20" s="16">
         <x:v>46083.2966067014</x:v>
       </x:c>
-      <x:c r="I20" s="17">
+      <x:c r="I20" s="16">
         <x:v>46387</x:v>
       </x:c>
-      <x:c r="J20" s="16" t="s">
+      <x:c r="J20" s="15" t="s">
         <x:v>451</x:v>
       </x:c>
-      <x:c r="K20" s="18" t="n">
+      <x:c r="K20" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L20" s="19">
+      <x:c r="L20" s="18">
         <x:v>46098.2996351505</x:v>
       </x:c>
-      <x:c r="M20" s="15" t="s">
+      <x:c r="M20" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="15" t="s">
+      <x:c r="B21" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C21" s="15" t="s">
+      <x:c r="C21" s="14" t="s">
         <x:v>452</x:v>
       </x:c>
-      <x:c r="D21" s="16" t="s">
+      <x:c r="D21" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="s">
+      <x:c r="E21" s="14" t="s">
         <x:v>453</x:v>
       </x:c>
-      <x:c r="F21" s="15" t="s">
+      <x:c r="F21" s="14" t="s">
         <x:v>454</x:v>
       </x:c>
-      <x:c r="G21" s="15" t="s">
+      <x:c r="G21" s="14" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="H21" s="17">
+      <x:c r="H21" s="16">
         <x:v>46046.1343687731</x:v>
       </x:c>
-      <x:c r="I21" s="17">
+      <x:c r="I21" s="16">
         <x:v>45917</x:v>
       </x:c>
-      <x:c r="J21" s="16" t="s">
+      <x:c r="J21" s="15" t="s">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="K21" s="18" t="n">
+      <x:c r="K21" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L21" s="19">
+      <x:c r="L21" s="18">
         <x:v>46093.2878737037</x:v>
       </x:c>
-      <x:c r="M21" s="15" t="s">
+      <x:c r="M21" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="15" t="s">
+      <x:c r="B22" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C22" s="15" t="s">
+      <x:c r="C22" s="14" t="s">
         <x:v>457</x:v>
       </x:c>
-      <x:c r="D22" s="16" t="s">
+      <x:c r="D22" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="s">
+      <x:c r="E22" s="14" t="s">
         <x:v>458</x:v>
       </x:c>
-      <x:c r="F22" s="15" t="s">
+      <x:c r="F22" s="14" t="s">
         <x:v>459</x:v>
       </x:c>
-      <x:c r="G22" s="15" t="s">
+      <x:c r="G22" s="14" t="s">
         <x:v>460</x:v>
       </x:c>
-      <x:c r="H22" s="17">
+      <x:c r="H22" s="16">
         <x:v>46046.1309132176</x:v>
       </x:c>
-      <x:c r="I22" s="17">
+      <x:c r="I22" s="16">
         <x:v>46021</x:v>
       </x:c>
-      <x:c r="J22" s="16" t="s">
+      <x:c r="J22" s="15" t="s">
         <x:v>461</x:v>
       </x:c>
-      <x:c r="K22" s="18" t="n">
+      <x:c r="K22" s="17" t="n">
         <x:v>5280</x:v>
       </x:c>
-      <x:c r="L22" s="19">
+      <x:c r="L22" s="18">
         <x:v>46093.2732890162</x:v>
       </x:c>
-      <x:c r="M22" s="15" t="s">
+      <x:c r="M22" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="15" t="s">
+      <x:c r="B23" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C23" s="15" t="s">
+      <x:c r="C23" s="14" t="s">
         <x:v>457</x:v>
       </x:c>
-      <x:c r="D23" s="16" t="s">
+      <x:c r="D23" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E23" s="15" t="s">
+      <x:c r="E23" s="14" t="s">
         <x:v>462</x:v>
       </x:c>
-      <x:c r="F23" s="15" t="s">
+      <x:c r="F23" s="14" t="s">
         <x:v>463</x:v>
       </x:c>
-      <x:c r="G23" s="15" t="s">
+      <x:c r="G23" s="14" t="s">
         <x:v>464</x:v>
       </x:c>
-      <x:c r="H23" s="17">
+      <x:c r="H23" s="16">
         <x:v>46046.1237709144</x:v>
       </x:c>
-      <x:c r="I23" s="17">
+      <x:c r="I23" s="16">
         <x:v>45991</x:v>
       </x:c>
-      <x:c r="J23" s="16" t="s">
+      <x:c r="J23" s="15" t="s">
         <x:v>465</x:v>
       </x:c>
-      <x:c r="K23" s="18" t="n">
+      <x:c r="K23" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L23" s="19">
+      <x:c r="L23" s="18">
         <x:v>46093.2636364931</x:v>
       </x:c>
-      <x:c r="M23" s="15" t="s">
+      <x:c r="M23" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B24" s="15" t="s">
+      <x:c r="B24" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C24" s="15" t="s">
+      <x:c r="C24" s="14" t="s">
         <x:v>466</x:v>
       </x:c>
-      <x:c r="D24" s="16" t="s">
+      <x:c r="D24" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E24" s="15" t="s">
+      <x:c r="E24" s="14" t="s">
         <x:v>467</x:v>
       </x:c>
-      <x:c r="F24" s="15" t="s">
+      <x:c r="F24" s="14" t="s">
         <x:v>468</x:v>
       </x:c>
-      <x:c r="G24" s="15" t="s">
+      <x:c r="G24" s="14" t="s">
         <x:v>469</x:v>
       </x:c>
-      <x:c r="H24" s="17">
+      <x:c r="H24" s="16">
         <x:v>46046.1140924306</x:v>
       </x:c>
-      <x:c r="I24" s="17">
+      <x:c r="I24" s="16">
         <x:v>46024</x:v>
       </x:c>
-      <x:c r="J24" s="16" t="s">
+      <x:c r="J24" s="15" t="s">
         <x:v>470</x:v>
       </x:c>
-      <x:c r="K24" s="18" t="n">
+      <x:c r="K24" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L24" s="19">
+      <x:c r="L24" s="18">
         <x:v>46093.2825289005</x:v>
       </x:c>
-      <x:c r="M24" s="15" t="s">
+      <x:c r="M24" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="15" t="s">
+      <x:c r="B25" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C25" s="15" t="s">
+      <x:c r="C25" s="14" t="s">
         <x:v>471</x:v>
       </x:c>
-      <x:c r="D25" s="16" t="s">
+      <x:c r="D25" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E25" s="15" t="s">
+      <x:c r="E25" s="14" t="s">
         <x:v>472</x:v>
       </x:c>
-      <x:c r="F25" s="15" t="s">
+      <x:c r="F25" s="14" t="s">
         <x:v>473</x:v>
       </x:c>
-      <x:c r="G25" s="15" t="s">
+      <x:c r="G25" s="14" t="s">
         <x:v>474</x:v>
       </x:c>
-      <x:c r="H25" s="17">
+      <x:c r="H25" s="16">
         <x:v>46048.0974875347</x:v>
       </x:c>
-      <x:c r="I25" s="17">
+      <x:c r="I25" s="16">
         <x:v>45883</x:v>
       </x:c>
-      <x:c r="J25" s="16" t="s">
+      <x:c r="J25" s="15" t="s">
         <x:v>475</x:v>
       </x:c>
-      <x:c r="K25" s="18" t="n">
+      <x:c r="K25" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L25" s="19">
+      <x:c r="L25" s="18">
         <x:v>46093.2926065278</x:v>
       </x:c>
-      <x:c r="M25" s="15" t="s">
+      <x:c r="M25" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B26" s="15" t="s">
+      <x:c r="B26" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C26" s="15" t="s">
+      <x:c r="C26" s="14" t="s">
         <x:v>476</x:v>
       </x:c>
-      <x:c r="D26" s="16" t="s">
+      <x:c r="D26" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E26" s="15" t="s">
+      <x:c r="E26" s="14" t="s">
         <x:v>477</x:v>
       </x:c>
-      <x:c r="F26" s="15" t="s">
+      <x:c r="F26" s="14" t="s">
         <x:v>478</x:v>
       </x:c>
-      <x:c r="G26" s="15" t="s">
+      <x:c r="G26" s="14" t="s">
         <x:v>479</x:v>
       </x:c>
-      <x:c r="H26" s="17">
+      <x:c r="H26" s="16">
         <x:v>46076.3189094676</x:v>
       </x:c>
-      <x:c r="I26" s="17">
+      <x:c r="I26" s="16">
         <x:v>46074</x:v>
       </x:c>
-      <x:c r="J26" s="16" t="s">
+      <x:c r="J26" s="15" t="s">
         <x:v>480</x:v>
       </x:c>
-      <x:c r="K26" s="18" t="n">
+      <x:c r="K26" s="17" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="L26" s="19">
+      <x:c r="L26" s="18">
         <x:v>46092.1400343403</x:v>
       </x:c>
-      <x:c r="M26" s="15" t="s">
+      <x:c r="M26" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="15" t="s">
+      <x:c r="B27" s="14" t="s">
         <x:v>481</x:v>
       </x:c>
-      <x:c r="C27" s="15" t="s">
+      <x:c r="C27" s="14" t="s">
         <x:v>427</x:v>
       </x:c>
-      <x:c r="D27" s="16" t="s">
+      <x:c r="D27" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E27" s="15" t="s">
+      <x:c r="E27" s="14" t="s">
         <x:v>482</x:v>
       </x:c>
-      <x:c r="F27" s="15" t="s">
+      <x:c r="F27" s="14" t="s">
         <x:v>483</x:v>
       </x:c>
-      <x:c r="G27" s="15" t="s">
+      <x:c r="G27" s="14" t="s">
         <x:v>484</x:v>
       </x:c>
-      <x:c r="H27" s="17">
+      <x:c r="H27" s="16">
         <x:v>46079.2852568981</x:v>
       </x:c>
-      <x:c r="I27" s="17">
+      <x:c r="I27" s="16">
         <x:v>46079.2852718981</x:v>
       </x:c>
-      <x:c r="J27" s="16" t="s">
+      <x:c r="J27" s="15" t="s">
         <x:v>485</x:v>
       </x:c>
-      <x:c r="K27" s="18" t="n">
+      <x:c r="K27" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L27" s="19">
+      <x:c r="L27" s="18">
         <x:v>46097.2459243171</x:v>
       </x:c>
-      <x:c r="M27" s="15" t="s">
+      <x:c r="M27" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="15" t="s">
+      <x:c r="B28" s="14" t="s">
         <x:v>481</x:v>
       </x:c>
-      <x:c r="C28" s="15" t="s">
+      <x:c r="C28" s="14" t="s">
         <x:v>432</x:v>
       </x:c>
-      <x:c r="D28" s="16" t="s">
+      <x:c r="D28" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E28" s="15" t="s">
+      <x:c r="E28" s="14" t="s">
         <x:v>486</x:v>
       </x:c>
-      <x:c r="F28" s="15" t="s">
+      <x:c r="F28" s="14" t="s">
         <x:v>487</x:v>
       </x:c>
-      <x:c r="G28" s="15" t="s">
+      <x:c r="G28" s="14" t="s">
         <x:v>488</x:v>
       </x:c>
-      <x:c r="H28" s="17">
+      <x:c r="H28" s="16">
         <x:v>46079.2747337153</x:v>
       </x:c>
-      <x:c r="I28" s="17">
+      <x:c r="I28" s="16">
         <x:v>46079.2747495718</x:v>
       </x:c>
-      <x:c r="J28" s="16" t="s">
+      <x:c r="J28" s="15" t="s">
         <x:v>489</x:v>
       </x:c>
-      <x:c r="K28" s="18" t="n">
+      <x:c r="K28" s="17" t="n">
         <x:v>2130</x:v>
       </x:c>
-      <x:c r="L28" s="19">
+      <x:c r="L28" s="18">
         <x:v>46097.2536368518</x:v>
       </x:c>
-      <x:c r="M28" s="15" t="s">
+      <x:c r="M28" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B29" s="15" t="s">
+      <x:c r="B29" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C29" s="15" t="s">
+      <x:c r="C29" s="14" t="s">
         <x:v>490</x:v>
       </x:c>
-      <x:c r="D29" s="16" t="s">
+      <x:c r="D29" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E29" s="15" t="s">
+      <x:c r="E29" s="14" t="s">
         <x:v>491</x:v>
       </x:c>
-      <x:c r="F29" s="15" t="s">
+      <x:c r="F29" s="14" t="s">
         <x:v>492</x:v>
       </x:c>
-      <x:c r="G29" s="15" t="s">
+      <x:c r="G29" s="14" t="s">
         <x:v>493</x:v>
       </x:c>
-      <x:c r="H29" s="17">
+      <x:c r="H29" s="16">
         <x:v>46076.1792420602</x:v>
       </x:c>
-      <x:c r="I29" s="17">
+      <x:c r="I29" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J29" s="16" t="s">
+      <x:c r="J29" s="15" t="s">
         <x:v>494</x:v>
       </x:c>
-      <x:c r="K29" s="18" t="n">
+      <x:c r="K29" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L29" s="19">
+      <x:c r="L29" s="18">
         <x:v>46090.204281088</x:v>
       </x:c>
-      <x:c r="M29" s="15" t="s">
+      <x:c r="M29" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B30" s="15" t="s">
+      <x:c r="B30" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C30" s="15" t="s">
+      <x:c r="C30" s="14" t="s">
         <x:v>495</x:v>
       </x:c>
-      <x:c r="D30" s="16" t="s">
+      <x:c r="D30" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E30" s="15" t="s">
+      <x:c r="E30" s="14" t="s">
         <x:v>496</x:v>
       </x:c>
-      <x:c r="F30" s="15" t="s">
+      <x:c r="F30" s="14" t="s">
         <x:v>497</x:v>
       </x:c>
-      <x:c r="G30" s="15" t="s">
+      <x:c r="G30" s="14" t="s">
         <x:v>498</x:v>
       </x:c>
-      <x:c r="H30" s="17">
+      <x:c r="H30" s="16">
         <x:v>46076.1139638194</x:v>
       </x:c>
-      <x:c r="I30" s="17">
+      <x:c r="I30" s="16">
         <x:v>46084</x:v>
       </x:c>
-      <x:c r="J30" s="16" t="s">
+      <x:c r="J30" s="15" t="s">
         <x:v>499</x:v>
       </x:c>
-      <x:c r="K30" s="18" t="n">
+      <x:c r="K30" s="17" t="n">
         <x:v>1470</x:v>
       </x:c>
-      <x:c r="L30" s="19">
+      <x:c r="L30" s="18">
         <x:v>46090.1919488889</x:v>
       </x:c>
-      <x:c r="M30" s="15" t="s">
+      <x:c r="M30" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B31" s="15" t="s">
+      <x:c r="B31" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C31" s="15" t="s">
+      <x:c r="C31" s="14" t="s">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="D31" s="16" t="s">
+      <x:c r="D31" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E31" s="15" t="s">
+      <x:c r="E31" s="14" t="s">
         <x:v>501</x:v>
       </x:c>
-      <x:c r="F31" s="15" t="s">
+      <x:c r="F31" s="14" t="s">
         <x:v>502</x:v>
       </x:c>
-      <x:c r="G31" s="15" t="s">
+      <x:c r="G31" s="14" t="s">
         <x:v>503</x:v>
       </x:c>
-      <x:c r="H31" s="17">
+      <x:c r="H31" s="16">
         <x:v>46077.2598841551</x:v>
       </x:c>
-      <x:c r="I31" s="17">
+      <x:c r="I31" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J31" s="16" t="s">
+      <x:c r="J31" s="15" t="s">
         <x:v>504</x:v>
       </x:c>
-      <x:c r="K31" s="18" t="n">
+      <x:c r="K31" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L31" s="19">
+      <x:c r="L31" s="18">
         <x:v>46090.2758708681</x:v>
       </x:c>
-      <x:c r="M31" s="15" t="s">
+      <x:c r="M31" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B32" s="15" t="s">
+      <x:c r="B32" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C32" s="15" t="s">
+      <x:c r="C32" s="14" t="s">
         <x:v>505</x:v>
       </x:c>
-      <x:c r="D32" s="16" t="s">
+      <x:c r="D32" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E32" s="15" t="s">
+      <x:c r="E32" s="14" t="s">
         <x:v>506</x:v>
       </x:c>
-      <x:c r="F32" s="15" t="s">
+      <x:c r="F32" s="14" t="s">
         <x:v>507</x:v>
       </x:c>
-      <x:c r="G32" s="15" t="s">
+      <x:c r="G32" s="14" t="s">
         <x:v>508</x:v>
       </x:c>
-      <x:c r="H32" s="17">
+      <x:c r="H32" s="16">
         <x:v>46077.2024189931</x:v>
       </x:c>
-      <x:c r="I32" s="17">
+      <x:c r="I32" s="16">
         <x:v>45948</x:v>
       </x:c>
-      <x:c r="J32" s="16" t="s">
+      <x:c r="J32" s="15" t="s">
         <x:v>509</x:v>
       </x:c>
-      <x:c r="K32" s="18" t="n">
+      <x:c r="K32" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L32" s="19">
+      <x:c r="L32" s="18">
         <x:v>46090.2496018056</x:v>
       </x:c>
-      <x:c r="M32" s="15" t="s">
+      <x:c r="M32" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B33" s="15" t="s">
+      <x:c r="B33" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C33" s="15" t="s">
+      <x:c r="C33" s="14" t="s">
         <x:v>505</x:v>
       </x:c>
-      <x:c r="D33" s="16" t="s">
+      <x:c r="D33" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E33" s="15" t="s">
+      <x:c r="E33" s="14" t="s">
         <x:v>510</x:v>
       </x:c>
-      <x:c r="F33" s="15" t="s">
+      <x:c r="F33" s="14" t="s">
         <x:v>511</x:v>
       </x:c>
-      <x:c r="G33" s="15" t="s">
+      <x:c r="G33" s="14" t="s">
         <x:v>512</x:v>
       </x:c>
-      <x:c r="H33" s="17">
+      <x:c r="H33" s="16">
         <x:v>46077.4722378472</x:v>
       </x:c>
-      <x:c r="I33" s="17">
+      <x:c r="I33" s="16">
         <x:v>46030</x:v>
       </x:c>
-      <x:c r="J33" s="16" t="s">
+      <x:c r="J33" s="15" t="s">
         <x:v>513</x:v>
       </x:c>
-      <x:c r="K33" s="18" t="n">
+      <x:c r="K33" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L33" s="19">
+      <x:c r="L33" s="18">
         <x:v>46090.2963156019</x:v>
       </x:c>
-      <x:c r="M33" s="15" t="s">
+      <x:c r="M33" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B34" s="15" t="s">
+      <x:c r="B34" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C34" s="15" t="s">
+      <x:c r="C34" s="14" t="s">
         <x:v>505</x:v>
       </x:c>
-      <x:c r="D34" s="16" t="s">
+      <x:c r="D34" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E34" s="15" t="s">
+      <x:c r="E34" s="14" t="s">
         <x:v>514</x:v>
       </x:c>
-      <x:c r="F34" s="15" t="s">
+      <x:c r="F34" s="14" t="s">
         <x:v>515</x:v>
       </x:c>
-      <x:c r="G34" s="15" t="s">
+      <x:c r="G34" s="14" t="s">
         <x:v>516</x:v>
       </x:c>
-      <x:c r="H34" s="17">
+      <x:c r="H34" s="16">
         <x:v>46077.5191885417</x:v>
       </x:c>
-      <x:c r="I34" s="17">
+      <x:c r="I34" s="16">
         <x:v>46058</x:v>
       </x:c>
-      <x:c r="J34" s="16" t="s">
+      <x:c r="J34" s="15" t="s">
         <x:v>517</x:v>
       </x:c>
-      <x:c r="K34" s="18" t="n">
+      <x:c r="K34" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L34" s="19">
+      <x:c r="L34" s="18">
         <x:v>46090.3155018056</x:v>
       </x:c>
-      <x:c r="M34" s="15" t="s">
+      <x:c r="M34" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B35" s="15" t="s">
+      <x:c r="B35" s="14" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C35" s="15" t="s">
+      <x:c r="C35" s="14" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="D35" s="16" t="s">
+      <x:c r="D35" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E35" s="15" t="s">
+      <x:c r="E35" s="14" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="F35" s="15" t="s">
+      <x:c r="F35" s="14" t="s">
         <x:v>518</x:v>
       </x:c>
-      <x:c r="G35" s="15" t="s">
+      <x:c r="G35" s="14" t="s">
         <x:v>519</x:v>
       </x:c>
-      <x:c r="H35" s="17">
+      <x:c r="H35" s="16">
         <x:v>45988.189350544</x:v>
       </x:c>
-      <x:c r="I35" s="17">
+      <x:c r="I35" s="16">
         <x:v>45973</x:v>
       </x:c>
-      <x:c r="J35" s="16" t="s">
+      <x:c r="J35" s="15" t="s">
         <x:v>520</x:v>
       </x:c>
-      <x:c r="K35" s="18" t="n">
+      <x:c r="K35" s="17" t="n">
         <x:v>1830</x:v>
       </x:c>
-      <x:c r="L35" s="19">
+      <x:c r="L35" s="18">
         <x:v>46093.1383928935</x:v>
       </x:c>
-      <x:c r="M35" s="15" t="s">
+      <x:c r="M35" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B36" s="15" t="s">
+      <x:c r="B36" s="14" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C36" s="15" t="s">
+      <x:c r="C36" s="14" t="s">
         <x:v>521</x:v>
       </x:c>
-      <x:c r="D36" s="16" t="s"/>
-      <x:c r="E36" s="15" t="s">
+      <x:c r="D36" s="15" t="s"/>
+      <x:c r="E36" s="14" t="s">
         <x:v>522</x:v>
       </x:c>
-      <x:c r="F36" s="15" t="s">
+      <x:c r="F36" s="14" t="s">
         <x:v>523</x:v>
       </x:c>
-      <x:c r="G36" s="15" t="s">
+      <x:c r="G36" s="14" t="s">
         <x:v>524</x:v>
       </x:c>
-      <x:c r="H36" s="17">
+      <x:c r="H36" s="16">
         <x:v>46090.2854096643</x:v>
       </x:c>
-      <x:c r="I36" s="17">
+      <x:c r="I36" s="16">
         <x:v>46090.2854287153</x:v>
       </x:c>
-      <x:c r="J36" s="16" t="s">
+      <x:c r="J36" s="15" t="s">
         <x:v>524</x:v>
       </x:c>
-      <x:c r="K36" s="18" t="n">
+      <x:c r="K36" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L36" s="19">
+      <x:c r="L36" s="18">
         <x:v>46094.0865837153</x:v>
       </x:c>
-      <x:c r="M36" s="15" t="s">
+      <x:c r="M36" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B37" s="15" t="s">
+      <x:c r="B37" s="14" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C37" s="15" t="s">
+      <x:c r="C37" s="14" t="s">
         <x:v>525</x:v>
       </x:c>
-      <x:c r="D37" s="16" t="s"/>
-      <x:c r="E37" s="15" t="s">
+      <x:c r="D37" s="15" t="s"/>
+      <x:c r="E37" s="14" t="s">
         <x:v>526</x:v>
       </x:c>
-      <x:c r="F37" s="15" t="s">
+      <x:c r="F37" s="14" t="s">
         <x:v>527</x:v>
       </x:c>
-      <x:c r="G37" s="15" t="s">
+      <x:c r="G37" s="14" t="s">
         <x:v>528</x:v>
       </x:c>
-      <x:c r="H37" s="17">
+      <x:c r="H37" s="16">
         <x:v>46090.2541037731</x:v>
       </x:c>
-      <x:c r="I37" s="17">
+      <x:c r="I37" s="16">
         <x:v>46090.2541222106</x:v>
       </x:c>
-      <x:c r="J37" s="16" t="s">
+      <x:c r="J37" s="15" t="s">
         <x:v>529</x:v>
       </x:c>
-      <x:c r="K37" s="18" t="n">
+      <x:c r="K37" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L37" s="19">
+      <x:c r="L37" s="18">
         <x:v>46094.0819034491</x:v>
       </x:c>
-      <x:c r="M37" s="15" t="s">
+      <x:c r="M37" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B38" s="15" t="s">
+      <x:c r="B38" s="14" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C38" s="15" t="s">
+      <x:c r="C38" s="14" t="s">
         <x:v>530</x:v>
       </x:c>
-      <x:c r="D38" s="16" t="s"/>
-      <x:c r="E38" s="15" t="s">
+      <x:c r="D38" s="15" t="s"/>
+      <x:c r="E38" s="14" t="s">
         <x:v>526</x:v>
       </x:c>
-      <x:c r="F38" s="15" t="s">
+      <x:c r="F38" s="14" t="s">
         <x:v>531</x:v>
       </x:c>
-      <x:c r="G38" s="15" t="s">
+      <x:c r="G38" s="14" t="s">
         <x:v>532</x:v>
       </x:c>
-      <x:c r="H38" s="17">
+      <x:c r="H38" s="16">
         <x:v>46090.2349194444</x:v>
       </x:c>
-      <x:c r="I38" s="17">
+      <x:c r="I38" s="16">
         <x:v>46090.2349374884</x:v>
       </x:c>
-      <x:c r="J38" s="16" t="s">
+      <x:c r="J38" s="15" t="s">
         <x:v>533</x:v>
       </x:c>
-      <x:c r="K38" s="18" t="n">
+      <x:c r="K38" s="17" t="n">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="L38" s="19">
+      <x:c r="L38" s="18">
         <x:v>46094.093939213</x:v>
       </x:c>
-      <x:c r="M38" s="15" t="s">
+      <x:c r="M38" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B39" s="15" t="s">
+      <x:c r="B39" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C39" s="15" t="s">
+      <x:c r="C39" s="14" t="s">
         <x:v>534</x:v>
       </x:c>
-      <x:c r="D39" s="16" t="s">
+      <x:c r="D39" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E39" s="15" t="s">
+      <x:c r="E39" s="14" t="s">
         <x:v>535</x:v>
       </x:c>
-      <x:c r="F39" s="15" t="s">
+      <x:c r="F39" s="14" t="s">
         <x:v>536</x:v>
       </x:c>
-      <x:c r="G39" s="15" t="s">
+      <x:c r="G39" s="14" t="s">
         <x:v>537</x:v>
       </x:c>
-      <x:c r="H39" s="17">
+      <x:c r="H39" s="16">
         <x:v>46077.2103691435</x:v>
       </x:c>
-      <x:c r="I39" s="17">
+      <x:c r="I39" s="16">
         <x:v>46042</x:v>
       </x:c>
-      <x:c r="J39" s="16" t="s">
+      <x:c r="J39" s="15" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="K39" s="18" t="n">
+      <x:c r="K39" s="17" t="n">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="L39" s="19">
+      <x:c r="L39" s="18">
         <x:v>46090.253629537</x:v>
       </x:c>
-      <x:c r="M39" s="15" t="s">
+      <x:c r="M39" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B40" s="15" t="s">
+      <x:c r="B40" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C40" s="15" t="s">
+      <x:c r="C40" s="14" t="s">
         <x:v>539</x:v>
       </x:c>
-      <x:c r="D40" s="16" t="s">
+      <x:c r="D40" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E40" s="15" t="s">
+      <x:c r="E40" s="14" t="s">
         <x:v>540</x:v>
       </x:c>
-      <x:c r="F40" s="15" t="s">
+      <x:c r="F40" s="14" t="s">
         <x:v>541</x:v>
       </x:c>
-      <x:c r="G40" s="15" t="s">
+      <x:c r="G40" s="14" t="s">
         <x:v>542</x:v>
       </x:c>
-      <x:c r="H40" s="17">
+      <x:c r="H40" s="16">
         <x:v>46077.2683575231</x:v>
       </x:c>
-      <x:c r="I40" s="17">
+      <x:c r="I40" s="16">
         <x:v>45748</x:v>
       </x:c>
-      <x:c r="J40" s="16" t="s">
+      <x:c r="J40" s="15" t="s">
         <x:v>543</x:v>
       </x:c>
-      <x:c r="K40" s="18" t="n">
+      <x:c r="K40" s="17" t="n">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="L40" s="19">
+      <x:c r="L40" s="18">
         <x:v>46090.2806125347</x:v>
       </x:c>
-      <x:c r="M40" s="15" t="s">
+      <x:c r="M40" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B41" s="15" t="s">
+      <x:c r="B41" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C41" s="15" t="s">
+      <x:c r="C41" s="14" t="s">
         <x:v>544</x:v>
       </x:c>
-      <x:c r="D41" s="16" t="s">
+      <x:c r="D41" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E41" s="15" t="s">
+      <x:c r="E41" s="14" t="s">
         <x:v>545</x:v>
       </x:c>
-      <x:c r="F41" s="15" t="s">
+      <x:c r="F41" s="14" t="s">
         <x:v>546</x:v>
       </x:c>
-      <x:c r="G41" s="15" t="s">
+      <x:c r="G41" s="14" t="s">
         <x:v>547</x:v>
       </x:c>
-      <x:c r="H41" s="17">
+      <x:c r="H41" s="16">
         <x:v>46077.1834319213</x:v>
       </x:c>
-      <x:c r="I41" s="17">
+      <x:c r="I41" s="16">
         <x:v>46115</x:v>
       </x:c>
-      <x:c r="J41" s="16" t="s">
+      <x:c r="J41" s="15" t="s">
         <x:v>548</x:v>
       </x:c>
-      <x:c r="K41" s="18" t="n">
+      <x:c r="K41" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L41" s="19">
+      <x:c r="L41" s="18">
         <x:v>46091.2388780324</x:v>
       </x:c>
-      <x:c r="M41" s="15" t="s">
+      <x:c r="M41" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B42" s="15" t="s">
+      <x:c r="B42" s="14" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C42" s="15" t="s">
+      <x:c r="C42" s="14" t="s">
         <x:v>549</x:v>
       </x:c>
-      <x:c r="D42" s="16" t="s">
+      <x:c r="D42" s="15" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E42" s="15" t="s">
+      <x:c r="E42" s="14" t="s">
         <x:v>550</x:v>
       </x:c>
-      <x:c r="F42" s="15" t="s">
+      <x:c r="F42" s="14" t="s">
         <x:v>551</x:v>
       </x:c>
-      <x:c r="G42" s="15" t="s">
+      <x:c r="G42" s="14" t="s">
         <x:v>552</x:v>
       </x:c>
-      <x:c r="H42" s="17">
+      <x:c r="H42" s="16">
         <x:v>46090.3681394907</x:v>
       </x:c>
-      <x:c r="I42" s="17">
+      <x:c r="I42" s="16">
         <x:v>46101</x:v>
       </x:c>
-      <x:c r="J42" s="16" t="s">
+      <x:c r="J42" s="15" t="s">
         <x:v>553</x:v>
       </x:c>
-      <x:c r="K42" s="18" t="n">
+      <x:c r="K42" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L42" s="19">
+      <x:c r="L42" s="18">
         <x:v>46094.1826630093</x:v>
       </x:c>
-      <x:c r="M42" s="15" t="s">
+      <x:c r="M42" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="45" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B45" s="20" t="s">
+      <x:c r="B45" s="19" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C45" s="21" t="s"/>
-      <x:c r="D45" s="21" t="s"/>
-      <x:c r="E45" s="22" t="s"/>
-      <x:c r="F45" s="22" t="s"/>
+      <x:c r="C45" s="20" t="s"/>
+      <x:c r="D45" s="20" t="s"/>
+      <x:c r="E45" s="21" t="s"/>
+      <x:c r="F45" s="21" t="s"/>
     </x:row>
     <x:row r="46" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B46" s="23" t="s">
+      <x:c r="B46" s="22" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="C46" s="24" t="s"/>
-      <x:c r="D46" s="24" t="s"/>
-      <x:c r="E46" s="24" t="s"/>
-      <x:c r="F46" s="25" t="s">
+      <x:c r="C46" s="23" t="s"/>
+      <x:c r="D46" s="23" t="s"/>
+      <x:c r="E46" s="23" t="s"/>
+      <x:c r="F46" s="24" t="s">
         <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B47" s="26" t="s">
+      <x:c r="B47" s="25" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C47" s="27" t="s"/>
-      <x:c r="D47" s="27" t="s"/>
-      <x:c r="E47" s="27" t="s"/>
-      <x:c r="F47" s="28" t="n">
+      <x:c r="C47" s="26" t="s"/>
+      <x:c r="D47" s="26" t="s"/>
+      <x:c r="E47" s="26" t="s"/>
+      <x:c r="F47" s="27" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B48" s="26" t="s">
+      <x:c r="B48" s="25" t="s">
         <x:v>416</x:v>
       </x:c>
-      <x:c r="C48" s="27" t="s"/>
-      <x:c r="D48" s="27" t="s"/>
-      <x:c r="E48" s="27" t="s"/>
-      <x:c r="F48" s="28" t="n">
+      <x:c r="C48" s="26" t="s"/>
+      <x:c r="D48" s="26" t="s"/>
+      <x:c r="E48" s="26" t="s"/>
+      <x:c r="F48" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B49" s="26" t="s">
+      <x:c r="B49" s="25" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C49" s="27" t="s"/>
-      <x:c r="D49" s="27" t="s"/>
-      <x:c r="E49" s="27" t="s"/>
-      <x:c r="F49" s="28" t="n">
+      <x:c r="C49" s="26" t="s"/>
+      <x:c r="D49" s="26" t="s"/>
+      <x:c r="E49" s="26" t="s"/>
+      <x:c r="F49" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B50" s="26" t="s">
+      <x:c r="B50" s="25" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="C50" s="27" t="s"/>
-      <x:c r="D50" s="27" t="s"/>
-      <x:c r="E50" s="27" t="s"/>
-      <x:c r="F50" s="28" t="n">
+      <x:c r="C50" s="26" t="s"/>
+      <x:c r="D50" s="26" t="s"/>
+      <x:c r="E50" s="26" t="s"/>
+      <x:c r="F50" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B51" s="26" t="s">
+      <x:c r="B51" s="25" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C51" s="27" t="s"/>
-      <x:c r="D51" s="27" t="s"/>
-      <x:c r="E51" s="27" t="s"/>
-      <x:c r="F51" s="28" t="n">
+      <x:c r="C51" s="26" t="s"/>
+      <x:c r="D51" s="26" t="s"/>
+      <x:c r="E51" s="26" t="s"/>
+      <x:c r="F51" s="27" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B52" s="26" t="s">
+      <x:c r="B52" s="25" t="s">
         <x:v>481</x:v>
       </x:c>
-      <x:c r="C52" s="27" t="s"/>
-      <x:c r="D52" s="27" t="s"/>
-      <x:c r="E52" s="27" t="s"/>
-      <x:c r="F52" s="28" t="n">
+      <x:c r="C52" s="26" t="s"/>
+      <x:c r="D52" s="26" t="s"/>
+      <x:c r="E52" s="26" t="s"/>
+      <x:c r="F52" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B53" s="26" t="s">
+      <x:c r="B53" s="25" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C53" s="27" t="s"/>
-      <x:c r="D53" s="27" t="s"/>
-      <x:c r="E53" s="27" t="s"/>
-      <x:c r="F53" s="28" t="n">
+      <x:c r="C53" s="26" t="s"/>
+      <x:c r="D53" s="26" t="s"/>
+      <x:c r="E53" s="26" t="s"/>
+      <x:c r="F53" s="27" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B54" s="26" t="s">
+      <x:c r="B54" s="25" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C54" s="27" t="s"/>
-      <x:c r="D54" s="27" t="s"/>
-      <x:c r="E54" s="27" t="s"/>
-      <x:c r="F54" s="28" t="n">
+      <x:c r="C54" s="26" t="s"/>
+      <x:c r="D54" s="26" t="s"/>
+      <x:c r="E54" s="26" t="s"/>
+      <x:c r="F54" s="27" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B55" s="26" t="s">
+      <x:c r="B55" s="25" t="s">
         <x:v>119</x:v>
       </x:c>
-      <x:c r="C55" s="27" t="s"/>
-      <x:c r="D55" s="27" t="s"/>
-      <x:c r="E55" s="27" t="s"/>
-      <x:c r="F55" s="28" t="n">
+      <x:c r="C55" s="26" t="s"/>
+      <x:c r="D55" s="26" t="s"/>
+      <x:c r="E55" s="26" t="s"/>
+      <x:c r="F55" s="27" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B56" s="29" t="s">
+      <x:c r="B56" s="28" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C56" s="30" t="s"/>
-      <x:c r="D56" s="30" t="s"/>
-      <x:c r="E56" s="30" t="s"/>
-      <x:c r="F56" s="31" t="n">
+      <x:c r="C56" s="29" t="s"/>
+      <x:c r="D56" s="29" t="s"/>
+      <x:c r="E56" s="29" t="s"/>
+      <x:c r="F56" s="30" t="n">
         <x:v>35</x:v>
       </x:c>
     </x:row>
